--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP121" headerRowCount="1">
-  <autoFilter ref="A1:EP121"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP124" headerRowCount="1">
+  <autoFilter ref="A1:EP124"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP121"/>
+  <dimension ref="A1:EP124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE5" t="n">
         <v>0.5</v>
@@ -3702,10 +3702,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -7033,7 +7033,7 @@
         <v>1.5</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -8035,7 +8035,7 @@
         <v>2.67</v>
       </c>
       <c r="DO15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -11777,7 +11777,7 @@
         <v>2</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF23" t="n">
         <v>1</v>
@@ -12262,7 +12262,7 @@
         <v>25</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE24" t="n">
         <v>1.29</v>
@@ -12738,7 +12738,7 @@
         <v>100</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DE25" t="n">
         <v>1.2</v>
@@ -15105,7 +15105,7 @@
         <v>2</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DF30" t="n">
         <v>3</v>
@@ -17995,7 +17995,7 @@
         <v>2.75</v>
       </c>
       <c r="DO36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -20395,7 +20395,7 @@
         <v>0.57</v>
       </c>
       <c r="DO41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -21765,7 +21765,7 @@
         <v>1.14</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF44" t="n">
         <v>0</v>
@@ -22391,170 +22391,170 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
         <v>45920.6875</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
         <v>3</v>
       </c>
       <c r="J46" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
+        <v>7</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
         <v>8</v>
       </c>
-      <c r="M46" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" t="n">
-        <v>7</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>5</v>
-      </c>
       <c r="R46" t="n">
         <v>3</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>26</v>
+      </c>
+      <c r="V46" t="n">
         <v>6</v>
       </c>
-      <c r="U46" t="n">
-        <v>8</v>
-      </c>
-      <c r="V46" t="n">
-        <v>9</v>
-      </c>
       <c r="W46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="X46" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Y46" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="Z46" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Estadio de Mendizorroza</t>
+          <t>Estadio de la Cerámica</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+          <t>Plaza Labrador, Villarreal</t>
         </is>
       </c>
       <c r="AC46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD46" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.33</v>
+        <v>1.55</v>
       </c>
       <c r="AF46" t="n">
-        <v>3.01</v>
+        <v>3.8</v>
       </c>
       <c r="AG46" t="n">
-        <v>3.28</v>
+        <v>5.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.43</v>
+        <v>2.01</v>
       </c>
       <c r="AJ46" t="n">
-        <v>4.85</v>
+        <v>3.05</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AO46" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AP46" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AR46" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AU46" t="n">
         <v>3</v>
       </c>
       <c r="AV46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
         <v>1</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB46" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="BC46" t="n">
         <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
         <v>0</v>
@@ -22572,73 +22572,73 @@
         <v>1</v>
       </c>
       <c r="BJ46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BL46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BN46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ46" t="n">
         <v>1</v>
       </c>
       <c r="BR46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BS46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BT46" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BU46" t="n">
         <v>1</v>
       </c>
       <c r="BV46" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="BW46" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="BX46" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="BY46" t="n">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="BZ46" t="n">
-        <v>1.22</v>
+        <v>2.84</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.08</v>
+        <v>0.75</v>
       </c>
       <c r="CB46" t="n">
-        <v>2.3</v>
+        <v>3.58</v>
       </c>
       <c r="CC46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG46" t="n">
         <v>0</v>
@@ -22656,13 +22656,13 @@
         <v>0</v>
       </c>
       <c r="CL46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM46" t="n">
         <v>0</v>
       </c>
       <c r="CN46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO46" t="n">
         <v>0</v>
@@ -22674,73 +22674,73 @@
         <v>1</v>
       </c>
       <c r="CR46" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="CS46" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="CT46" t="n">
         <v>1</v>
       </c>
       <c r="CU46" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="CV46" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX46" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY46" t="n">
         <v>20</v>
       </c>
-      <c r="CW46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX46" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY46" t="n">
-        <v>4</v>
-      </c>
       <c r="CZ46" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA46" t="n">
         <v>50</v>
-      </c>
-      <c r="DA46" t="n">
-        <v>100</v>
       </c>
       <c r="DB46" t="n">
         <v>50</v>
       </c>
       <c r="DC46" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.5</v>
+        <v>0.14</v>
       </c>
       <c r="DF46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DH46" t="n">
         <v>1.75</v>
       </c>
       <c r="DI46" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DJ46" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK46" t="n">
         <v>50</v>
       </c>
-      <c r="DK46" t="n">
-        <v>0</v>
-      </c>
       <c r="DL46" t="n">
-        <v>1.19</v>
+        <v>2.48</v>
       </c>
       <c r="DM46" t="n">
-        <v>1.32</v>
+        <v>0.71</v>
       </c>
       <c r="DN46" t="n">
-        <v>2.51</v>
+        <v>3.19</v>
       </c>
       <c r="DO46" t="n">
         <v>12</v>
@@ -22767,87 +22767,99 @@
         <v>1</v>
       </c>
       <c r="DW46" t="n">
-        <v>27.45</v>
+        <v>27.48</v>
       </c>
       <c r="DX46" t="n">
-        <v>4.36</v>
+        <v>4.71</v>
       </c>
       <c r="DY46" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ46" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="EA46" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EB46" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EC46" t="inlineStr"/>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EC46" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
       <c r="ED46" t="inlineStr">
         <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EE46" t="inlineStr"/>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EE46" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
       <c r="EF46" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="EG46" t="inlineStr"/>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EG46" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
       <c r="EH46" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="EI46" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="EJ46" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EK46" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EL46" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EM46" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EN46" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EO46" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EP46" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -22867,170 +22879,170 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
         <v>45920.6875</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" t="n">
         <v>3</v>
       </c>
       <c r="J47" t="n">
+        <v>4</v>
+      </c>
+      <c r="K47" t="n">
+        <v>4</v>
+      </c>
+      <c r="L47" t="n">
+        <v>8</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
         <v>7</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>3</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>6</v>
+      </c>
+      <c r="U47" t="n">
+        <v>8</v>
+      </c>
+      <c r="V47" t="n">
+        <v>9</v>
+      </c>
+      <c r="W47" t="n">
+        <v>20</v>
+      </c>
+      <c r="X47" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Estadio de Mendizorroza</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+        </is>
+      </c>
+      <c r="AC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD47" t="n">
         <v>7</v>
       </c>
-      <c r="M47" t="n">
-        <v>2</v>
-      </c>
-      <c r="N47" t="n">
-        <v>2</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>8</v>
-      </c>
-      <c r="R47" t="n">
-        <v>3</v>
-      </c>
-      <c r="S47" t="n">
-        <v>18</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3</v>
-      </c>
-      <c r="U47" t="n">
-        <v>26</v>
-      </c>
-      <c r="V47" t="n">
-        <v>6</v>
-      </c>
-      <c r="W47" t="n">
-        <v>10</v>
-      </c>
-      <c r="X47" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>66</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Estadio de la Cerámica</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>Plaza Labrador, Villarreal</t>
-        </is>
-      </c>
-      <c r="AC47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>3</v>
-      </c>
       <c r="AE47" t="n">
-        <v>1.55</v>
+        <v>2.33</v>
       </c>
       <c r="AF47" t="n">
-        <v>3.8</v>
+        <v>3.01</v>
       </c>
       <c r="AG47" t="n">
-        <v>5.25</v>
+        <v>3.28</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.01</v>
+        <v>2.43</v>
       </c>
       <c r="AJ47" t="n">
-        <v>3.05</v>
+        <v>4.85</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AN47" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AO47" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AP47" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AU47" t="n">
         <v>3</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW47" t="n">
         <v>1</v>
       </c>
       <c r="AX47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB47" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="BC47" t="n">
         <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BE47" t="n">
         <v>0</v>
@@ -23048,175 +23060,175 @@
         <v>1</v>
       </c>
       <c r="BJ47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT47" t="n">
         <v>6</v>
       </c>
-      <c r="BL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN47" t="n">
+      <c r="BU47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV47" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW47" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY47" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CA47" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CB47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR47" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS47" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU47" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV47" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX47" t="n">
         <v>6</v>
       </c>
-      <c r="BO47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP47" t="n">
-        <v>3</v>
-      </c>
-      <c r="BQ47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS47" t="n">
+      <c r="CY47" t="n">
         <v>4</v>
       </c>
-      <c r="BT47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV47" t="n">
-        <v>90</v>
-      </c>
-      <c r="BW47" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX47" t="n">
-        <v>112</v>
-      </c>
-      <c r="BY47" t="n">
-        <v>57</v>
-      </c>
-      <c r="BZ47" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CA47" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB47" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="CC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR47" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS47" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU47" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV47" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX47" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY47" t="n">
-        <v>20</v>
-      </c>
       <c r="CZ47" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DA47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB47" t="n">
         <v>50</v>
       </c>
       <c r="DC47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD47" t="n">
-        <v>2.67</v>
+        <v>1.57</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.14</v>
+        <v>1.5</v>
       </c>
       <c r="DF47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DG47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DH47" t="n">
         <v>1.75</v>
       </c>
       <c r="DI47" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DJ47" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK47" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL47" t="n">
-        <v>2.48</v>
+        <v>1.19</v>
       </c>
       <c r="DM47" t="n">
-        <v>0.71</v>
+        <v>1.32</v>
       </c>
       <c r="DN47" t="n">
-        <v>3.19</v>
+        <v>2.51</v>
       </c>
       <c r="DO47" t="n">
         <v>12</v>
@@ -23243,99 +23255,87 @@
         <v>1</v>
       </c>
       <c r="DW47" t="n">
-        <v>27.48</v>
+        <v>27.45</v>
       </c>
       <c r="DX47" t="n">
-        <v>4.71</v>
+        <v>4.36</v>
       </c>
       <c r="DY47" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="DZ47" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="EA47" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EB47" t="inlineStr">
         <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC47" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
-      </c>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EC47" t="inlineStr"/>
       <c r="ED47" t="inlineStr">
         <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE47" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EE47" t="inlineStr"/>
       <c r="EF47" t="inlineStr">
         <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="EG47" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EG47" t="inlineStr"/>
       <c r="EH47" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="EI47" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EJ47" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="EK47" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EL47" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EM47" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EN47" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="EO47" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EP47" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.16</t>
         </is>
       </c>
     </row>
@@ -23674,10 +23674,10 @@
         <v>25</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DF48" t="n">
         <v>2</v>
@@ -23707,7 +23707,7 @@
         <v>2.96</v>
       </c>
       <c r="DO48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24153,7 +24153,7 @@
         <v>1.2</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DF49" t="n">
         <v>1</v>
@@ -26695,12 +26695,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
@@ -26710,25 +26710,25 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -26740,119 +26740,119 @@
         <v>2</v>
       </c>
       <c r="R55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S55" t="n">
+        <v>9</v>
+      </c>
+      <c r="T55" t="n">
         <v>14</v>
       </c>
-      <c r="T55" t="n">
-        <v>7</v>
-      </c>
       <c r="U55" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V55" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="W55" t="n">
         <v>17</v>
       </c>
       <c r="X55" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Y55" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="Z55" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Estadio Ramón Sánchez Pizjuán</t>
+          <t>Estadio Ciudad de Valencia</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Avenida de Eduardo Dato, Sevilla</t>
+          <t>Calle San Vicente de Paúl 44, Valencia</t>
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE55" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="AF55" t="n">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI55" t="n">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="AJ55" t="n">
-        <v>3.4</v>
+        <v>2.07</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL55" t="n">
         <v>2</v>
       </c>
       <c r="AM55" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN55" t="n">
         <v>1.5</v>
       </c>
-      <c r="AN55" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AO55" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP55" t="n">
         <v>2.38</v>
       </c>
-      <c r="AP55" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AQ55" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.72</v>
+        <v>4.05</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AU55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV55" t="n">
         <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX55" t="n">
         <v>1</v>
       </c>
       <c r="AY55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB55" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="BC55" t="n">
         <v>0</v>
@@ -26873,76 +26873,76 @@
         <v>1</v>
       </c>
       <c r="BI55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL55" t="n">
         <v>2</v>
       </c>
       <c r="BM55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BN55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO55" t="n">
         <v>0</v>
       </c>
       <c r="BP55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU55" t="n">
         <v>1</v>
       </c>
       <c r="BV55" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="BW55" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="BX55" t="n">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="BY55" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="BZ55" t="n">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
       <c r="CA55" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="CB55" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="CC55" t="n">
         <v>0</v>
       </c>
       <c r="CD55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE55" t="n">
         <v>0</v>
       </c>
       <c r="CF55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG55" t="n">
         <v>0</v>
@@ -26966,7 +26966,7 @@
         <v>0</v>
       </c>
       <c r="CN55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO55" t="n">
         <v>0</v>
@@ -26978,73 +26978,73 @@
         <v>1</v>
       </c>
       <c r="CR55" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="CS55" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="CT55" t="n">
         <v>1</v>
       </c>
       <c r="CU55" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="CV55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CW55" t="n">
         <v>1</v>
       </c>
       <c r="CX55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY55" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CZ55" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA55" t="n">
         <v>100</v>
       </c>
       <c r="DB55" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="DC55" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.17</v>
+        <v>0.2</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="DF55" t="n">
         <v>0.5</v>
       </c>
       <c r="DG55" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DH55" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="DI55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ55" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK55" t="n">
         <v>0</v>
       </c>
       <c r="DL55" t="n">
-        <v>1.24</v>
+        <v>0.84</v>
       </c>
       <c r="DM55" t="n">
-        <v>0.93</v>
+        <v>2.34</v>
       </c>
       <c r="DN55" t="n">
-        <v>2.17</v>
+        <v>3.18</v>
       </c>
       <c r="DO55" t="n">
         <v>12</v>
@@ -27059,10 +27059,10 @@
         <v>1</v>
       </c>
       <c r="DS55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU55" t="b">
         <v>0</v>
@@ -27071,99 +27071,87 @@
         <v>1</v>
       </c>
       <c r="DW55" t="n">
-        <v>27.52</v>
+        <v>22.21</v>
       </c>
       <c r="DX55" t="n">
-        <v>3.08</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DY55" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ55" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="EA55" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EB55" t="inlineStr"/>
+      <c r="EC55" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="ED55" t="inlineStr"/>
+      <c r="EE55" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF55" t="inlineStr"/>
+      <c r="EG55" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH55" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI55" t="inlineStr">
+        <is>
+          <t>5.86</t>
+        </is>
+      </c>
+      <c r="EJ55" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="EK55" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL55" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EB55" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EC55" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="ED55" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EE55" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF55" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG55" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EH55" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EI55" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EJ55" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="EK55" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EL55" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
       <c r="EM55" t="inlineStr">
         <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN55" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EO55" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EP55" t="inlineStr">
+        <is>
           <t>1.68</t>
-        </is>
-      </c>
-      <c r="EN55" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EO55" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EP55" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -27183,12 +27171,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -27198,149 +27186,149 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I56" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3</v>
+      </c>
+      <c r="L56" t="n">
+        <v>6</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2</v>
+      </c>
+      <c r="R56" t="n">
         <v>5</v>
       </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
+      <c r="S56" t="n">
+        <v>14</v>
+      </c>
+      <c r="T56" t="n">
         <v>7</v>
       </c>
-      <c r="L56" t="n">
-        <v>8</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>2</v>
-      </c>
-      <c r="R56" t="n">
-        <v>10</v>
-      </c>
-      <c r="S56" t="n">
-        <v>9</v>
-      </c>
-      <c r="T56" t="n">
-        <v>14</v>
-      </c>
       <c r="U56" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V56" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="W56" t="n">
         <v>17</v>
       </c>
       <c r="X56" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y56" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="Z56" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Estadio Ciudad de Valencia</t>
+          <t>Estadio Ramón Sánchez Pizjuán</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Calle San Vicente de Paúl 44, Valencia</t>
+          <t>Avenida de Eduardo Dato, Sevilla</t>
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE56" t="n">
-        <v>8</v>
+        <v>3.15</v>
       </c>
       <c r="AF56" t="n">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI56" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT56" t="n">
         <v>1.4</v>
       </c>
-      <c r="AJ56" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AU56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV56" t="n">
         <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX56" t="n">
         <v>1</v>
       </c>
       <c r="AY56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB56" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="BC56" t="n">
         <v>0</v>
@@ -27361,76 +27349,76 @@
         <v>1</v>
       </c>
       <c r="BI56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT56" t="n">
         <v>5</v>
       </c>
-      <c r="BK56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL56" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM56" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN56" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ56" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR56" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT56" t="n">
-        <v>2</v>
-      </c>
       <c r="BU56" t="n">
         <v>1</v>
       </c>
       <c r="BV56" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="BW56" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="BX56" t="n">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="BY56" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="BZ56" t="n">
-        <v>1.02</v>
+        <v>1.67</v>
       </c>
       <c r="CA56" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="CB56" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="CC56" t="n">
         <v>0</v>
       </c>
       <c r="CD56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE56" t="n">
         <v>0</v>
       </c>
       <c r="CF56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG56" t="n">
         <v>0</v>
@@ -27454,7 +27442,7 @@
         <v>0</v>
       </c>
       <c r="CN56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO56" t="n">
         <v>0</v>
@@ -27466,73 +27454,73 @@
         <v>1</v>
       </c>
       <c r="CR56" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="CS56" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="CT56" t="n">
         <v>1</v>
       </c>
       <c r="CU56" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV56" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW56" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX56" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY56" t="n">
         <v>9</v>
       </c>
-      <c r="CV56" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW56" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX56" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY56" t="n">
-        <v>3</v>
-      </c>
       <c r="CZ56" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA56" t="n">
         <v>100</v>
       </c>
       <c r="DB56" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC56" t="n">
         <v>75</v>
       </c>
-      <c r="DC56" t="n">
-        <v>100</v>
-      </c>
       <c r="DD56" t="n">
-        <v>0.2</v>
+        <v>1.17</v>
       </c>
       <c r="DE56" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="DF56" t="n">
         <v>0.5</v>
       </c>
       <c r="DG56" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DH56" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ56" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK56" t="n">
         <v>0</v>
       </c>
       <c r="DL56" t="n">
-        <v>0.84</v>
+        <v>1.24</v>
       </c>
       <c r="DM56" t="n">
-        <v>2.34</v>
+        <v>0.93</v>
       </c>
       <c r="DN56" t="n">
-        <v>3.18</v>
+        <v>2.17</v>
       </c>
       <c r="DO56" t="n">
         <v>12</v>
@@ -27547,10 +27535,10 @@
         <v>1</v>
       </c>
       <c r="DS56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU56" t="b">
         <v>0</v>
@@ -27559,87 +27547,99 @@
         <v>1</v>
       </c>
       <c r="DW56" t="n">
-        <v>22.21</v>
+        <v>27.52</v>
       </c>
       <c r="DX56" t="n">
-        <v>8.289999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="DY56" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="DZ56" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA56" t="inlineStr">
         <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EB56" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EB56" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
       <c r="EC56" t="inlineStr">
         <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="ED56" t="inlineStr"/>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="ED56" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="EE56" t="inlineStr">
         <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EF56" t="inlineStr"/>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EF56" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
       <c r="EG56" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EH56" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EI56" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EJ56" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EK56" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EL56" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EM56" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EN56" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EO56" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EP56" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -30829,7 +30829,7 @@
         <v>1.6</v>
       </c>
       <c r="DE63" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF63" t="n">
         <v>2</v>
@@ -32233,7 +32233,7 @@
         <v>2.67</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DF66" t="n">
         <v>3</v>
@@ -33157,7 +33157,7 @@
         <v>2</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DF68" t="n">
         <v>2.33</v>
@@ -34566,7 +34566,7 @@
         <v>67</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE71" t="n">
         <v>0.67</v>
@@ -35525,7 +35525,7 @@
         <v>0.67</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -37434,7 +37434,7 @@
         <v>100</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DE77" t="n">
         <v>0.5</v>
@@ -42161,7 +42161,7 @@
         <v>2</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DF87" t="n">
         <v>2.5</v>
@@ -44066,7 +44066,7 @@
         <v>88</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DE91" t="n">
         <v>0.33</v>
@@ -44099,7 +44099,7 @@
         <v>2.36</v>
       </c>
       <c r="DO91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP91" t="b">
         <v>0</v>
@@ -46454,7 +46454,7 @@
         <v>50</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE96" t="n">
         <v>1.67</v>
@@ -46937,7 +46937,7 @@
         <v>1.5</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF97" t="n">
         <v>1.25</v>
@@ -48349,7 +48349,7 @@
         <v>2</v>
       </c>
       <c r="DE100" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DF100" t="n">
         <v>2.5</v>
@@ -50705,7 +50705,7 @@
         <v>1.67</v>
       </c>
       <c r="DE105" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DF105" t="n">
         <v>1.4</v>
@@ -51649,7 +51649,7 @@
         <v>0.2</v>
       </c>
       <c r="DE107" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DF107" t="n">
         <v>0.25</v>
@@ -51679,7 +51679,7 @@
         <v>2.18</v>
       </c>
       <c r="DO107" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -52134,7 +52134,7 @@
         <v>55</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DE108" t="n">
         <v>1</v>
@@ -55457,7 +55457,7 @@
         <v>2.71</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF115" t="n">
         <v>2.67</v>
@@ -57330,7 +57330,7 @@
         <v>80</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE119" t="n">
         <v>1.33</v>
@@ -58311,7 +58311,7 @@
         <v>3.7</v>
       </c>
       <c r="DO121" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -58416,6 +58416,1382 @@
       <c r="EP121" t="inlineStr">
         <is>
           <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>13</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Valencia CF</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>45982.83333333334</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" t="n">
+        <v>7</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>7</v>
+      </c>
+      <c r="M122" t="n">
+        <v>3</v>
+      </c>
+      <c r="N122" t="n">
+        <v>2</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>3</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>11</v>
+      </c>
+      <c r="T122" t="n">
+        <v>7</v>
+      </c>
+      <c r="U122" t="n">
+        <v>14</v>
+      </c>
+      <c r="V122" t="n">
+        <v>7</v>
+      </c>
+      <c r="W122" t="n">
+        <v>16</v>
+      </c>
+      <c r="X122" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>Avenida de Suecia, Valencia</t>
+        </is>
+      </c>
+      <c r="AC122" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>288</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>15</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>63</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>53</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU122" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV122" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX122" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY122" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ122" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA122" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB122" t="n">
+        <v>7</v>
+      </c>
+      <c r="DC122" t="n">
+        <v>68</v>
+      </c>
+      <c r="DD122" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DE122" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF122" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG122" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DH122" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DI122" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DJ122" t="n">
+        <v>62</v>
+      </c>
+      <c r="DK122" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL122" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DM122" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DN122" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DO122" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW122" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="DX122" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="DY122" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="DZ122" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA122" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EB122" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC122" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="ED122" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EE122" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EF122" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EG122" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="EH122" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="EI122" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="EJ122" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EK122" t="inlineStr"/>
+      <c r="EL122" t="inlineStr"/>
+      <c r="EM122" t="inlineStr"/>
+      <c r="EN122" t="inlineStr"/>
+      <c r="EO122" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EP122" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>13</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>45983.54166666666</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" t="n">
+        <v>4</v>
+      </c>
+      <c r="K123" t="n">
+        <v>2</v>
+      </c>
+      <c r="L123" t="n">
+        <v>6</v>
+      </c>
+      <c r="M123" t="n">
+        <v>2</v>
+      </c>
+      <c r="N123" t="n">
+        <v>2</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>2</v>
+      </c>
+      <c r="R123" t="n">
+        <v>4</v>
+      </c>
+      <c r="S123" t="n">
+        <v>3</v>
+      </c>
+      <c r="T123" t="n">
+        <v>3</v>
+      </c>
+      <c r="U123" t="n">
+        <v>5</v>
+      </c>
+      <c r="V123" t="n">
+        <v>7</v>
+      </c>
+      <c r="W123" t="n">
+        <v>21</v>
+      </c>
+      <c r="X123" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>Estadio de Mendizorroza</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+        </is>
+      </c>
+      <c r="AC123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>281</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>92</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>68</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU123" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV123" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX123" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY123" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ123" t="n">
+        <v>64</v>
+      </c>
+      <c r="DA123" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB123" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC123" t="n">
+        <v>74</v>
+      </c>
+      <c r="DD123" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DE123" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DF123" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DG123" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DH123" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DI123" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DJ123" t="n">
+        <v>37</v>
+      </c>
+      <c r="DK123" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL123" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DM123" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DN123" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="DO123" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW123" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="DX123" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DY123" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="DZ123" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="EA123" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EB123" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EC123" t="inlineStr"/>
+      <c r="ED123" t="inlineStr"/>
+      <c r="EE123" t="inlineStr"/>
+      <c r="EF123" t="inlineStr"/>
+      <c r="EG123" t="inlineStr"/>
+      <c r="EH123" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="EI123" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="EJ123" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EK123" t="inlineStr"/>
+      <c r="EL123" t="inlineStr"/>
+      <c r="EM123" t="inlineStr"/>
+      <c r="EN123" t="inlineStr"/>
+      <c r="EO123" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EP123" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>13</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Athletic Club Bilbao</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>45983.63541666666</v>
+      </c>
+      <c r="G124" t="n">
+        <v>4</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>4</v>
+      </c>
+      <c r="J124" t="n">
+        <v>5</v>
+      </c>
+      <c r="K124" t="n">
+        <v>7</v>
+      </c>
+      <c r="L124" t="n">
+        <v>12</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>2</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>7</v>
+      </c>
+      <c r="R124" t="n">
+        <v>2</v>
+      </c>
+      <c r="S124" t="n">
+        <v>12</v>
+      </c>
+      <c r="T124" t="n">
+        <v>11</v>
+      </c>
+      <c r="U124" t="n">
+        <v>19</v>
+      </c>
+      <c r="V124" t="n">
+        <v>13</v>
+      </c>
+      <c r="W124" t="n">
+        <v>9</v>
+      </c>
+      <c r="X124" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA124" t="inlineStr"/>
+      <c r="AB124" t="inlineStr"/>
+      <c r="AC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>83</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU124" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV124" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX124" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY124" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ124" t="n">
+        <v>70</v>
+      </c>
+      <c r="DA124" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB124" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC124" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD124" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE124" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF124" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG124" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DH124" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DI124" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DJ124" t="n">
+        <v>30</v>
+      </c>
+      <c r="DK124" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL124" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DM124" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DN124" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="DO124" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW124" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="DX124" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="DY124" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="DZ124" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="EA124" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EB124" t="inlineStr"/>
+      <c r="EC124" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="ED124" t="inlineStr"/>
+      <c r="EE124" t="inlineStr"/>
+      <c r="EF124" t="inlineStr"/>
+      <c r="EG124" t="inlineStr"/>
+      <c r="EH124" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="EI124" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="EJ124" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EK124" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EL124" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EM124" t="inlineStr"/>
+      <c r="EN124" t="inlineStr"/>
+      <c r="EO124" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EP124" t="inlineStr">
+        <is>
+          <t>1.67</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP124" headerRowCount="1">
-  <autoFilter ref="A1:EP124"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP131" headerRowCount="1">
+  <autoFilter ref="A1:EP131"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP124"/>
+  <dimension ref="A1:EP131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1805,7 +1805,7 @@
         <v>1.14</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2286,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE3" t="n">
         <v>0.67</v>
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3237,7 +3237,7 @@
         <v>1.57</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -4203,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4641,7 +4641,7 @@
         <v>1.86</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5122,10 +5122,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE10" t="n">
         <v>1.33</v>
@@ -5643,7 +5643,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6127,7 +6127,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6554,7 +6554,7 @@
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE12" t="n">
         <v>0.67</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7063,7 +7063,7 @@
         <v>0.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7547,7 +7547,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8470,7 +8470,7 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DE16" t="n">
         <v>0.33</v>
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8971,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9426,10 +9426,10 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DF18" t="n">
         <v>3</v>
@@ -9459,7 +9459,7 @@
         <v>2.89</v>
       </c>
       <c r="DO18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9878,10 +9878,10 @@
         <v>0</v>
       </c>
       <c r="DD19" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="DE19" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9911,7 +9911,7 @@
         <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10353,7 +10353,7 @@
         <v>1.86</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -10383,7 +10383,7 @@
         <v>3.14</v>
       </c>
       <c r="DO20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10867,7 +10867,7 @@
         <v>1.06</v>
       </c>
       <c r="DO21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11335,7 +11335,7 @@
         <v>2.67</v>
       </c>
       <c r="DO22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11774,7 +11774,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE23" t="n">
         <v>1</v>
@@ -11807,7 +11807,7 @@
         <v>1.81</v>
       </c>
       <c r="DO23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12295,7 +12295,7 @@
         <v>2.77</v>
       </c>
       <c r="DO24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12741,7 +12741,7 @@
         <v>1.57</v>
       </c>
       <c r="DE25" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DF25" t="n">
         <v>3</v>
@@ -12771,7 +12771,7 @@
         <v>3.34</v>
       </c>
       <c r="DO25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13222,10 +13222,10 @@
         <v>50</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DF26" t="n">
         <v>0</v>
@@ -13255,7 +13255,7 @@
         <v>2.11</v>
       </c>
       <c r="DO26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13693,7 +13693,7 @@
         <v>1.14</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF27" t="n">
         <v>0</v>
@@ -13723,7 +13723,7 @@
         <v>2.25</v>
       </c>
       <c r="DO27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14181,7 +14181,7 @@
         <v>3</v>
       </c>
       <c r="DE28" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -14211,7 +14211,7 @@
         <v>2.14</v>
       </c>
       <c r="DO28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14671,7 +14671,7 @@
         <v>1.49</v>
       </c>
       <c r="DO29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15102,7 +15102,7 @@
         <v>50</v>
       </c>
       <c r="DD30" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE30" t="n">
         <v>0.67</v>
@@ -15135,7 +15135,7 @@
         <v>1.65</v>
       </c>
       <c r="DO30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15586,7 +15586,7 @@
         <v>50</v>
       </c>
       <c r="DD31" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE31" t="n">
         <v>0.14</v>
@@ -15619,7 +15619,7 @@
         <v>1.56</v>
       </c>
       <c r="DO31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16095,7 +16095,7 @@
         <v>2.84</v>
       </c>
       <c r="DO32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16555,7 +16555,7 @@
         <v>2.15</v>
       </c>
       <c r="DO33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17006,7 +17006,7 @@
         <v>50</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DE34" t="n">
         <v>0.67</v>
@@ -17039,7 +17039,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="DO34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17485,7 +17485,7 @@
         <v>1.67</v>
       </c>
       <c r="DE35" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DF35" t="n">
         <v>1</v>
@@ -17515,7 +17515,7 @@
         <v>4.77</v>
       </c>
       <c r="DO35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18479,7 +18479,7 @@
         <v>2.71</v>
       </c>
       <c r="DO37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18929,7 +18929,7 @@
         <v>0.71</v>
       </c>
       <c r="DE38" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DF38" t="n">
         <v>0.67</v>
@@ -18959,7 +18959,7 @@
         <v>2.12</v>
       </c>
       <c r="DO38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19447,7 +19447,7 @@
         <v>2.04</v>
       </c>
       <c r="DO39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19886,10 +19886,10 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF40" t="n">
         <v>3</v>
@@ -19919,7 +19919,7 @@
         <v>2.95</v>
       </c>
       <c r="DO40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20830,10 +20830,10 @@
         <v>75</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF42" t="n">
         <v>3</v>
@@ -20863,7 +20863,7 @@
         <v>2.33</v>
       </c>
       <c r="DO42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21298,10 +21298,10 @@
         <v>50</v>
       </c>
       <c r="DD43" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE43" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DF43" t="n">
         <v>1.5</v>
@@ -21331,7 +21331,7 @@
         <v>2.96</v>
       </c>
       <c r="DO43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21795,7 +21795,7 @@
         <v>2.35</v>
       </c>
       <c r="DO44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22283,7 +22283,7 @@
         <v>3.56</v>
       </c>
       <c r="DO45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22391,170 +22391,170 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
         <v>45920.6875</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
         <v>3</v>
       </c>
       <c r="J46" t="n">
+        <v>4</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4</v>
+      </c>
+      <c r="L46" t="n">
+        <v>8</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
         <v>7</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>5</v>
+      </c>
+      <c r="R46" t="n">
+        <v>3</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
+        <v>8</v>
+      </c>
+      <c r="V46" t="n">
+        <v>9</v>
+      </c>
+      <c r="W46" t="n">
+        <v>20</v>
+      </c>
+      <c r="X46" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Estadio de Mendizorroza</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+        </is>
+      </c>
+      <c r="AC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="n">
         <v>7</v>
       </c>
-      <c r="M46" t="n">
-        <v>2</v>
-      </c>
-      <c r="N46" t="n">
-        <v>2</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>8</v>
-      </c>
-      <c r="R46" t="n">
-        <v>3</v>
-      </c>
-      <c r="S46" t="n">
-        <v>18</v>
-      </c>
-      <c r="T46" t="n">
-        <v>3</v>
-      </c>
-      <c r="U46" t="n">
-        <v>26</v>
-      </c>
-      <c r="V46" t="n">
-        <v>6</v>
-      </c>
-      <c r="W46" t="n">
-        <v>10</v>
-      </c>
-      <c r="X46" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>66</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>Estadio de la Cerámica</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>Plaza Labrador, Villarreal</t>
-        </is>
-      </c>
-      <c r="AC46" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>3</v>
-      </c>
       <c r="AE46" t="n">
-        <v>1.55</v>
+        <v>2.33</v>
       </c>
       <c r="AF46" t="n">
-        <v>3.8</v>
+        <v>3.01</v>
       </c>
       <c r="AG46" t="n">
-        <v>5.25</v>
+        <v>3.28</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.01</v>
+        <v>2.43</v>
       </c>
       <c r="AJ46" t="n">
-        <v>3.05</v>
+        <v>4.85</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AN46" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AO46" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AP46" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AU46" t="n">
         <v>3</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW46" t="n">
         <v>1</v>
       </c>
       <c r="AX46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB46" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="BC46" t="n">
         <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BE46" t="n">
         <v>0</v>
@@ -22572,178 +22572,178 @@
         <v>1</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK46" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT46" t="n">
         <v>6</v>
       </c>
-      <c r="BL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN46" t="n">
+      <c r="BU46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV46" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CB46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR46" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS46" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU46" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV46" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX46" t="n">
         <v>6</v>
       </c>
-      <c r="BO46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP46" t="n">
-        <v>3</v>
-      </c>
-      <c r="BQ46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS46" t="n">
+      <c r="CY46" t="n">
         <v>4</v>
       </c>
-      <c r="BT46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV46" t="n">
-        <v>90</v>
-      </c>
-      <c r="BW46" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX46" t="n">
-        <v>112</v>
-      </c>
-      <c r="BY46" t="n">
-        <v>57</v>
-      </c>
-      <c r="BZ46" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CA46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB46" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="CC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS46" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU46" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV46" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX46" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY46" t="n">
-        <v>20</v>
-      </c>
       <c r="CZ46" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DA46" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB46" t="n">
         <v>50</v>
       </c>
       <c r="DC46" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>2.67</v>
+        <v>1.57</v>
       </c>
       <c r="DE46" t="n">
-        <v>0.14</v>
+        <v>1.29</v>
       </c>
       <c r="DF46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DG46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DH46" t="n">
         <v>1.75</v>
       </c>
       <c r="DI46" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DJ46" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK46" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL46" t="n">
-        <v>2.48</v>
+        <v>1.19</v>
       </c>
       <c r="DM46" t="n">
-        <v>0.71</v>
+        <v>1.32</v>
       </c>
       <c r="DN46" t="n">
-        <v>3.19</v>
+        <v>2.51</v>
       </c>
       <c r="DO46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22767,99 +22767,87 @@
         <v>1</v>
       </c>
       <c r="DW46" t="n">
-        <v>27.48</v>
+        <v>27.45</v>
       </c>
       <c r="DX46" t="n">
-        <v>4.71</v>
+        <v>4.36</v>
       </c>
       <c r="DY46" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="DZ46" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="EA46" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EB46" t="inlineStr">
         <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC46" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
-      </c>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EC46" t="inlineStr"/>
       <c r="ED46" t="inlineStr">
         <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE46" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EE46" t="inlineStr"/>
       <c r="EF46" t="inlineStr">
         <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="EG46" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EG46" t="inlineStr"/>
       <c r="EH46" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="EI46" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EJ46" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="EK46" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EL46" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EM46" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EN46" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="EO46" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EP46" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.16</t>
         </is>
       </c>
     </row>
@@ -22879,170 +22867,170 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
         <v>45920.6875</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
+        <v>7</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
         <v>8</v>
       </c>
-      <c r="M47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" t="n">
-        <v>7</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>5</v>
-      </c>
       <c r="R47" t="n">
         <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>26</v>
+      </c>
+      <c r="V47" t="n">
         <v>6</v>
       </c>
-      <c r="U47" t="n">
-        <v>8</v>
-      </c>
-      <c r="V47" t="n">
-        <v>9</v>
-      </c>
       <c r="W47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="X47" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Y47" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="Z47" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Estadio de Mendizorroza</t>
+          <t>Estadio de la Cerámica</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+          <t>Plaza Labrador, Villarreal</t>
         </is>
       </c>
       <c r="AC47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD47" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.33</v>
+        <v>1.55</v>
       </c>
       <c r="AF47" t="n">
-        <v>3.01</v>
+        <v>3.8</v>
       </c>
       <c r="AG47" t="n">
-        <v>3.28</v>
+        <v>5.25</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.43</v>
+        <v>2.01</v>
       </c>
       <c r="AJ47" t="n">
-        <v>4.85</v>
+        <v>3.05</v>
       </c>
       <c r="AK47" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AO47" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AP47" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AR47" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AU47" t="n">
         <v>3</v>
       </c>
       <c r="AV47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
         <v>1</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB47" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="BC47" t="n">
         <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
         <v>0</v>
@@ -23060,73 +23048,73 @@
         <v>1</v>
       </c>
       <c r="BJ47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BL47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BN47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ47" t="n">
         <v>1</v>
       </c>
       <c r="BR47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BS47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BT47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BU47" t="n">
         <v>1</v>
       </c>
       <c r="BV47" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="BW47" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="BX47" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="BY47" t="n">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="BZ47" t="n">
-        <v>1.22</v>
+        <v>2.84</v>
       </c>
       <c r="CA47" t="n">
-        <v>1.08</v>
+        <v>0.75</v>
       </c>
       <c r="CB47" t="n">
-        <v>2.3</v>
+        <v>3.58</v>
       </c>
       <c r="CC47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG47" t="n">
         <v>0</v>
@@ -23144,13 +23132,13 @@
         <v>0</v>
       </c>
       <c r="CL47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM47" t="n">
         <v>0</v>
       </c>
       <c r="CN47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO47" t="n">
         <v>0</v>
@@ -23162,76 +23150,76 @@
         <v>1</v>
       </c>
       <c r="CR47" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="CS47" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="CT47" t="n">
         <v>1</v>
       </c>
       <c r="CU47" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="CV47" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX47" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY47" t="n">
         <v>20</v>
       </c>
-      <c r="CW47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX47" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY47" t="n">
-        <v>4</v>
-      </c>
       <c r="CZ47" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA47" t="n">
         <v>50</v>
-      </c>
-      <c r="DA47" t="n">
-        <v>100</v>
       </c>
       <c r="DB47" t="n">
         <v>50</v>
       </c>
       <c r="DC47" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.57</v>
+        <v>2.71</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.5</v>
+        <v>0.14</v>
       </c>
       <c r="DF47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DH47" t="n">
         <v>1.75</v>
       </c>
       <c r="DI47" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DJ47" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK47" t="n">
         <v>50</v>
       </c>
-      <c r="DK47" t="n">
-        <v>0</v>
-      </c>
       <c r="DL47" t="n">
-        <v>1.19</v>
+        <v>2.48</v>
       </c>
       <c r="DM47" t="n">
-        <v>1.32</v>
+        <v>0.71</v>
       </c>
       <c r="DN47" t="n">
-        <v>2.51</v>
+        <v>3.19</v>
       </c>
       <c r="DO47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23255,87 +23243,99 @@
         <v>1</v>
       </c>
       <c r="DW47" t="n">
-        <v>27.45</v>
+        <v>27.48</v>
       </c>
       <c r="DX47" t="n">
-        <v>4.36</v>
+        <v>4.71</v>
       </c>
       <c r="DY47" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ47" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="EA47" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EB47" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EC47" t="inlineStr"/>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EC47" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
       <c r="ED47" t="inlineStr">
         <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EE47" t="inlineStr"/>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EE47" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
       <c r="EF47" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="EG47" t="inlineStr"/>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EG47" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
       <c r="EH47" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="EI47" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="EJ47" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EK47" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EL47" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EM47" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EN47" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EO47" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EP47" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -24183,7 +24183,7 @@
         <v>2.29</v>
       </c>
       <c r="DO49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24633,7 +24633,7 @@
         <v>1.5</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DF50" t="n">
         <v>0.5</v>
@@ -24663,7 +24663,7 @@
         <v>2.63</v>
       </c>
       <c r="DO50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25114,7 +25114,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE51" t="n">
         <v>0.67</v>
@@ -25147,7 +25147,7 @@
         <v>1.99</v>
       </c>
       <c r="DO51" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25615,7 +25615,7 @@
         <v>3.7</v>
       </c>
       <c r="DO52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25723,143 +25723,143 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
         <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L53" t="n">
+        <v>11</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>10</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2</v>
+      </c>
+      <c r="S53" t="n">
+        <v>11</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>21</v>
+      </c>
+      <c r="V53" t="n">
+        <v>5</v>
+      </c>
+      <c r="W53" t="n">
         <v>9</v>
       </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>2</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>5</v>
-      </c>
-      <c r="R53" t="n">
-        <v>3</v>
-      </c>
-      <c r="S53" t="n">
-        <v>12</v>
-      </c>
-      <c r="T53" t="n">
-        <v>3</v>
-      </c>
-      <c r="U53" t="n">
-        <v>17</v>
-      </c>
-      <c r="V53" t="n">
-        <v>6</v>
-      </c>
-      <c r="W53" t="n">
-        <v>19</v>
-      </c>
       <c r="X53" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y53" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="Z53" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>San Mamés Barria</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE53" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ53" t="n">
         <v>1.47</v>
       </c>
-      <c r="AF53" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AR53" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AS53" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AU53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV53" t="n">
         <v>0</v>
@@ -25868,13 +25868,13 @@
         <v>1</v>
       </c>
       <c r="AX53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA53" t="n">
         <v>1</v>
@@ -25886,7 +25886,7 @@
         <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BE53" t="n">
         <v>0</v>
@@ -25901,28 +25901,28 @@
         <v>1</v>
       </c>
       <c r="BI53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BJ53" t="n">
         <v>1</v>
       </c>
       <c r="BK53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BL53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BN53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ53" t="n">
         <v>0</v>
@@ -25931,7 +25931,7 @@
         <v>2</v>
       </c>
       <c r="BS53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT53" t="n">
         <v>2</v>
@@ -25940,143 +25940,143 @@
         <v>1</v>
       </c>
       <c r="BV53" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="BW53" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BX53" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="BY53" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CB53" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR53" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS53" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU53" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV53" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX53" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY53" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ53" t="n">
         <v>59</v>
       </c>
-      <c r="BZ53" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CA53" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB53" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="CC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS53" t="n">
+      <c r="DA53" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB53" t="n">
         <v>17</v>
       </c>
-      <c r="CT53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU53" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV53" t="n">
-        <v>19</v>
-      </c>
-      <c r="CW53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX53" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY53" t="n">
+      <c r="DC53" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD53" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE53" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DF53" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH53" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ53" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK53" t="n">
+        <v>42</v>
+      </c>
+      <c r="DL53" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DM53" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="DN53" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DO53" t="n">
         <v>13</v>
       </c>
-      <c r="CZ53" t="n">
-        <v>42</v>
-      </c>
-      <c r="DA53" t="n">
-        <v>67</v>
-      </c>
-      <c r="DB53" t="n">
-        <v>42</v>
-      </c>
-      <c r="DC53" t="n">
-        <v>67</v>
-      </c>
-      <c r="DD53" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DE53" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DF53" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DH53" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DI53" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DJ53" t="n">
-        <v>59</v>
-      </c>
-      <c r="DK53" t="n">
-        <v>34</v>
-      </c>
-      <c r="DL53" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="DM53" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="DN53" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="DO53" t="n">
-        <v>12</v>
-      </c>
       <c r="DP53" t="b">
         <v>1</v>
       </c>
@@ -26084,10 +26084,10 @@
         <v>1</v>
       </c>
       <c r="DR53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT53" t="b">
         <v>0</v>
@@ -26099,79 +26099,75 @@
         <v>1</v>
       </c>
       <c r="DW53" t="n">
-        <v>17.43</v>
+        <v>20.5</v>
       </c>
       <c r="DX53" t="n">
-        <v>4.72</v>
+        <v>6.93</v>
       </c>
       <c r="DY53" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="DZ53" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA53" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EB53" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC53" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC53" t="inlineStr"/>
       <c r="ED53" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EE53" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF53" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EG53" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EH53" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EI53" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EJ53" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EK53" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EL53" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EM53" t="inlineStr">
@@ -26186,12 +26182,12 @@
       </c>
       <c r="EO53" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP53" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -26211,40 +26207,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>8</v>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -26253,101 +26249,101 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T54" t="n">
         <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W54" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="X54" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y54" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="Z54" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>San Mamés Barria</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="AF54" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="AG54" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AI54" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AJ54" t="n">
-        <v>4.05</v>
+        <v>3.08</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AN54" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AO54" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AR54" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AU54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV54" t="n">
         <v>0</v>
@@ -26356,13 +26352,13 @@
         <v>1</v>
       </c>
       <c r="AX54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA54" t="n">
         <v>1</v>
@@ -26374,7 +26370,7 @@
         <v>0</v>
       </c>
       <c r="BD54" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BE54" t="n">
         <v>0</v>
@@ -26389,28 +26385,28 @@
         <v>1</v>
       </c>
       <c r="BI54" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BJ54" t="n">
         <v>1</v>
       </c>
       <c r="BK54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BN54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ54" t="n">
         <v>0</v>
@@ -26419,7 +26415,7 @@
         <v>2</v>
       </c>
       <c r="BS54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT54" t="n">
         <v>2</v>
@@ -26428,25 +26424,25 @@
         <v>1</v>
       </c>
       <c r="BV54" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="BW54" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BX54" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="BY54" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="BZ54" t="n">
-        <v>2.59</v>
+        <v>1.96</v>
       </c>
       <c r="CA54" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="CB54" t="n">
-        <v>3.26</v>
+        <v>2.71</v>
       </c>
       <c r="CC54" t="n">
         <v>0</v>
@@ -26476,10 +26472,10 @@
         <v>0</v>
       </c>
       <c r="CL54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN54" t="n">
         <v>0</v>
@@ -26494,19 +26490,19 @@
         <v>1</v>
       </c>
       <c r="CR54" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="CS54" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CT54" t="n">
         <v>1</v>
       </c>
       <c r="CU54" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="CV54" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="CW54" t="n">
         <v>1</v>
@@ -26515,55 +26511,55 @@
         <v>3</v>
       </c>
       <c r="CY54" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CZ54" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="DA54" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="DB54" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="DC54" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DD54" t="n">
         <v>1.86</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DF54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DG54" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DH54" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="DI54" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="DJ54" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="DK54" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="DL54" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="DM54" t="n">
-        <v>0.47</v>
+        <v>1.18</v>
       </c>
       <c r="DN54" t="n">
-        <v>1.62</v>
+        <v>2.61</v>
       </c>
       <c r="DO54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26572,10 +26568,10 @@
         <v>1</v>
       </c>
       <c r="DR54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT54" t="b">
         <v>0</v>
@@ -26587,75 +26583,79 @@
         <v>1</v>
       </c>
       <c r="DW54" t="n">
-        <v>20.5</v>
+        <v>17.43</v>
       </c>
       <c r="DX54" t="n">
-        <v>6.93</v>
+        <v>4.72</v>
       </c>
       <c r="DY54" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="DZ54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="EA54" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EB54" t="inlineStr">
         <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC54" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED54" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE54" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="EC54" t="inlineStr"/>
-      <c r="ED54" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EE54" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="EF54" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EG54" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="EH54" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="EI54" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="EJ54" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EK54" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EL54" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EM54" t="inlineStr">
@@ -26670,12 +26670,12 @@
       </c>
       <c r="EO54" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EP54" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -27017,7 +27017,7 @@
         <v>0.2</v>
       </c>
       <c r="DE55" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DF55" t="n">
         <v>0.5</v>
@@ -27047,7 +27047,7 @@
         <v>3.18</v>
       </c>
       <c r="DO55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27523,7 +27523,7 @@
         <v>2.17</v>
       </c>
       <c r="DO56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27978,7 +27978,7 @@
         <v>75</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DE57" t="n">
         <v>0.67</v>
@@ -28011,7 +28011,7 @@
         <v>2.1</v>
       </c>
       <c r="DO57" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28449,7 +28449,7 @@
         <v>2.71</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF58" t="n">
         <v>2</v>
@@ -28479,7 +28479,7 @@
         <v>2.98</v>
       </c>
       <c r="DO58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28937,7 +28937,7 @@
         <v>1.67</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF59" t="n">
         <v>0.5</v>
@@ -28967,7 +28967,7 @@
         <v>3.85</v>
       </c>
       <c r="DO59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29402,7 +29402,7 @@
         <v>100</v>
       </c>
       <c r="DD60" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DE60" t="n">
         <v>0.5</v>
@@ -29435,7 +29435,7 @@
         <v>2.17</v>
       </c>
       <c r="DO60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29870,7 +29870,7 @@
         <v>100</v>
       </c>
       <c r="DD61" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="DE61" t="n">
         <v>1.86</v>
@@ -29903,7 +29903,7 @@
         <v>3.12</v>
       </c>
       <c r="DO61" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30371,7 +30371,7 @@
         <v>2.32</v>
       </c>
       <c r="DO62" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP62" t="b">
         <v>0</v>
@@ -30826,7 +30826,7 @@
         <v>59</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DE63" t="n">
         <v>1</v>
@@ -30859,7 +30859,7 @@
         <v>2.16</v>
       </c>
       <c r="DO63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31289,7 +31289,7 @@
         <v>2.71</v>
       </c>
       <c r="DE64" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DF64" t="n">
         <v>2.33</v>
@@ -31319,7 +31319,7 @@
         <v>4.16</v>
       </c>
       <c r="DO64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31795,7 +31795,7 @@
         <v>2</v>
       </c>
       <c r="DO65" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32230,7 +32230,7 @@
         <v>50</v>
       </c>
       <c r="DD66" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE66" t="n">
         <v>0.67</v>
@@ -32263,7 +32263,7 @@
         <v>4.16</v>
       </c>
       <c r="DO66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32685,7 +32685,7 @@
         <v>1.2</v>
       </c>
       <c r="DE67" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF67" t="n">
         <v>1</v>
@@ -32715,7 +32715,7 @@
         <v>2.84</v>
       </c>
       <c r="DO67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33154,7 +33154,7 @@
         <v>59</v>
       </c>
       <c r="DD68" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE68" t="n">
         <v>1.83</v>
@@ -33187,7 +33187,7 @@
         <v>2.52</v>
       </c>
       <c r="DO68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33621,7 +33621,7 @@
         <v>3</v>
       </c>
       <c r="DE69" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DF69" t="n">
         <v>3</v>
@@ -33651,7 +33651,7 @@
         <v>3.83</v>
       </c>
       <c r="DO69" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34078,7 +34078,7 @@
         <v>50</v>
       </c>
       <c r="DD70" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE70" t="n">
         <v>0.14</v>
@@ -34111,7 +34111,7 @@
         <v>2.27</v>
       </c>
       <c r="DO70" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34599,7 +34599,7 @@
         <v>2.23</v>
       </c>
       <c r="DO71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35046,7 +35046,7 @@
         <v>88</v>
       </c>
       <c r="DD72" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DE72" t="n">
         <v>1.29</v>
@@ -35079,7 +35079,7 @@
         <v>2.29</v>
       </c>
       <c r="DO72" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35522,7 +35522,7 @@
         <v>88</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="DE73" t="n">
         <v>1</v>
@@ -35555,7 +35555,7 @@
         <v>2.02</v>
       </c>
       <c r="DO73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -36043,7 +36043,7 @@
         <v>1.79</v>
       </c>
       <c r="DO74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36501,7 +36501,7 @@
         <v>1.86</v>
       </c>
       <c r="DE75" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF75" t="n">
         <v>1.75</v>
@@ -36531,7 +36531,7 @@
         <v>3.06</v>
       </c>
       <c r="DO75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36999,7 +36999,7 @@
         <v>3.16</v>
       </c>
       <c r="DO76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -37467,7 +37467,7 @@
         <v>2.1</v>
       </c>
       <c r="DO77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -37927,7 +37927,7 @@
         <v>3.75</v>
       </c>
       <c r="DO78" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38043,40 +38043,40 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45935.6875</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K79" t="n">
         <v>5</v>
       </c>
       <c r="L79" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N79" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -38085,104 +38085,104 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
+        <v>3</v>
+      </c>
+      <c r="R79" t="n">
+        <v>2</v>
+      </c>
+      <c r="S79" t="n">
+        <v>7</v>
+      </c>
+      <c r="T79" t="n">
         <v>5</v>
       </c>
-      <c r="R79" t="n">
-        <v>3</v>
-      </c>
-      <c r="S79" t="n">
-        <v>9</v>
-      </c>
-      <c r="T79" t="n">
-        <v>9</v>
-      </c>
       <c r="U79" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V79" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W79" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="X79" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Y79" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z79" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>Estadio Municipal de Anoeta</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
         </is>
       </c>
       <c r="AC79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD79" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="AF79" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AG79" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AJ79" t="n">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AL79" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AM79" t="n">
         <v>1.44</v>
       </c>
       <c r="AN79" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AO79" t="n">
         <v>2.55</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AR79" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AU79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW79" t="n">
         <v>0</v>
@@ -38191,22 +38191,22 @@
         <v>0</v>
       </c>
       <c r="AY79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB79" t="n">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38221,190 +38221,190 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BJ79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BK79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>101</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX79" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY79" t="n">
         <v>10</v>
       </c>
-      <c r="BN79" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR79" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS79" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT79" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV79" t="n">
-        <v>66</v>
-      </c>
-      <c r="BW79" t="n">
-        <v>34</v>
-      </c>
-      <c r="BX79" t="n">
-        <v>107</v>
-      </c>
-      <c r="BY79" t="n">
-        <v>98</v>
-      </c>
-      <c r="BZ79" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CA79" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CB79" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR79" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS79" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU79" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV79" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX79" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY79" t="n">
+      <c r="CZ79" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA79" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>59</v>
+      </c>
+      <c r="DC79" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD79" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF79" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DI79" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DJ79" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK79" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL79" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DM79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DN79" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="DO79" t="n">
         <v>13</v>
       </c>
-      <c r="CZ79" t="n">
-        <v>54</v>
-      </c>
-      <c r="DA79" t="n">
-        <v>88</v>
-      </c>
-      <c r="DB79" t="n">
-        <v>29</v>
-      </c>
-      <c r="DC79" t="n">
-        <v>88</v>
-      </c>
-      <c r="DD79" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DE79" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DF79" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DG79" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH79" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DI79" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DJ79" t="n">
-        <v>46</v>
-      </c>
-      <c r="DK79" t="n">
-        <v>13</v>
-      </c>
-      <c r="DL79" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="DM79" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="DN79" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="DO79" t="n">
-        <v>12</v>
-      </c>
       <c r="DP79" t="b">
         <v>1</v>
       </c>
       <c r="DQ79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS79" t="b">
         <v>0</v>
@@ -38416,102 +38416,94 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW79" t="n">
-        <v>17.75</v>
+        <v>17.19</v>
       </c>
       <c r="DX79" t="n">
-        <v>9.369999999999999</v>
+        <v>3.66</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="ED79" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EE79" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EF79" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EG79" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EH79" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EI79" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EJ79" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EK79" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EL79" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EM79" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EN79" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM79" t="inlineStr"/>
+      <c r="EN79" t="inlineStr"/>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.84</t>
         </is>
       </c>
     </row>
@@ -38531,146 +38523,146 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45935.6875</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K80" t="n">
         <v>5</v>
       </c>
       <c r="L80" t="n">
+        <v>15</v>
+      </c>
+      <c r="M80" t="n">
+        <v>2</v>
+      </c>
+      <c r="N80" t="n">
+        <v>6</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>5</v>
+      </c>
+      <c r="R80" t="n">
+        <v>3</v>
+      </c>
+      <c r="S80" t="n">
+        <v>9</v>
+      </c>
+      <c r="T80" t="n">
+        <v>9</v>
+      </c>
+      <c r="U80" t="n">
+        <v>14</v>
+      </c>
+      <c r="V80" t="n">
         <v>12</v>
       </c>
-      <c r="M80" t="n">
-        <v>1</v>
-      </c>
-      <c r="N80" t="n">
-        <v>2</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>3</v>
-      </c>
-      <c r="R80" t="n">
-        <v>2</v>
-      </c>
-      <c r="S80" t="n">
-        <v>7</v>
-      </c>
-      <c r="T80" t="n">
-        <v>5</v>
-      </c>
-      <c r="U80" t="n">
-        <v>10</v>
-      </c>
-      <c r="V80" t="n">
-        <v>7</v>
-      </c>
       <c r="W80" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X80" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Y80" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z80" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Anoeta</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD80" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="AF80" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AG80" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AI80" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AJ80" t="n">
-        <v>3.85</v>
+        <v>2.96</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AL80" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AM80" t="n">
         <v>1.44</v>
       </c>
       <c r="AN80" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AO80" t="n">
         <v>2.55</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AR80" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AU80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW80" t="n">
         <v>0</v>
@@ -38679,22 +38671,22 @@
         <v>0</v>
       </c>
       <c r="AY80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB80" t="n">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -38709,190 +38701,190 @@
         <v>1</v>
       </c>
       <c r="BI80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BJ80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BK80" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR80" t="n">
         <v>4</v>
       </c>
-      <c r="BL80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM80" t="n">
+      <c r="BS80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV80" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX80" t="n">
         <v>6</v>
       </c>
-      <c r="BN80" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT80" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV80" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW80" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX80" t="n">
-        <v>101</v>
-      </c>
-      <c r="BY80" t="n">
-        <v>90</v>
-      </c>
-      <c r="BZ80" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="CA80" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB80" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CC80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN80" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR80" t="n">
-        <v>14</v>
-      </c>
-      <c r="CS80" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU80" t="n">
-        <v>21</v>
-      </c>
-      <c r="CV80" t="n">
+      <c r="CY80" t="n">
         <v>13</v>
       </c>
-      <c r="CW80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX80" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY80" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ80" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="DA80" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="DB80" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="DC80" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="DF80" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="DG80" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DH80" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="DI80" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="DJ80" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="DK80" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="DL80" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="DM80" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="DN80" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="DO80" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
       </c>
       <c r="DQ80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS80" t="b">
         <v>0</v>
@@ -38904,94 +38896,102 @@
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW80" t="n">
-        <v>17.19</v>
+        <v>17.75</v>
       </c>
       <c r="DX80" t="n">
-        <v>3.66</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EB80" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EC80" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED80" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EE80" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EF80" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EG80" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EH80" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EI80" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EJ80" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EK80" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EL80" t="inlineStr">
+        <is>
           <t>2.02</t>
         </is>
       </c>
-      <c r="EB80" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC80" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="ED80" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE80" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF80" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG80" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="EH80" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="EI80" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="EJ80" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EK80" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EL80" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EM80" t="inlineStr"/>
-      <c r="EN80" t="inlineStr"/>
+      <c r="EM80" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EN80" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
       <c r="EO80" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EP80" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.68</t>
         </is>
       </c>
     </row>
@@ -39325,7 +39325,7 @@
         <v>0.71</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DF81" t="n">
         <v>0.75</v>
@@ -39355,7 +39355,7 @@
         <v>3.36</v>
       </c>
       <c r="DO81" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -39794,7 +39794,7 @@
         <v>84</v>
       </c>
       <c r="DD82" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="DE82" t="n">
         <v>1</v>
@@ -39827,7 +39827,7 @@
         <v>2.32</v>
       </c>
       <c r="DO82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40281,7 +40281,7 @@
         <v>1.17</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF83" t="n">
         <v>1</v>
@@ -40311,7 +40311,7 @@
         <v>2.72</v>
       </c>
       <c r="DO83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -40741,7 +40741,7 @@
         <v>3</v>
       </c>
       <c r="DE84" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DF84" t="n">
         <v>3</v>
@@ -40771,7 +40771,7 @@
         <v>3.49</v>
       </c>
       <c r="DO84" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41198,7 +41198,7 @@
         <v>88</v>
       </c>
       <c r="DD85" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE85" t="n">
         <v>1.33</v>
@@ -41231,7 +41231,7 @@
         <v>3.94</v>
       </c>
       <c r="DO85" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41703,7 +41703,7 @@
         <v>2.53</v>
       </c>
       <c r="DO86" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42158,7 +42158,7 @@
         <v>38</v>
       </c>
       <c r="DD87" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE87" t="n">
         <v>0.67</v>
@@ -42191,7 +42191,7 @@
         <v>3.24</v>
       </c>
       <c r="DO87" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -42621,7 +42621,7 @@
         <v>0.71</v>
       </c>
       <c r="DE88" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DF88" t="n">
         <v>0.8</v>
@@ -42651,7 +42651,7 @@
         <v>3.09</v>
       </c>
       <c r="DO88" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43109,7 +43109,7 @@
         <v>0.2</v>
       </c>
       <c r="DE89" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF89" t="n">
         <v>0.33</v>
@@ -43139,7 +43139,7 @@
         <v>2.17</v>
       </c>
       <c r="DO89" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43578,10 +43578,10 @@
         <v>84</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DE90" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DF90" t="n">
         <v>1.67</v>
@@ -43611,7 +43611,7 @@
         <v>3.13</v>
       </c>
       <c r="DO90" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44529,7 +44529,7 @@
         <v>1.67</v>
       </c>
       <c r="DE92" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF92" t="n">
         <v>1</v>
@@ -44559,7 +44559,7 @@
         <v>2.81</v>
       </c>
       <c r="DO92" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45039,7 +45039,7 @@
         <v>2.1</v>
       </c>
       <c r="DO93" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -45494,7 +45494,7 @@
         <v>78</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE94" t="n">
         <v>0.5</v>
@@ -45527,7 +45527,7 @@
         <v>2.42</v>
       </c>
       <c r="DO94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46011,7 +46011,7 @@
         <v>2.58</v>
       </c>
       <c r="DO95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46487,7 +46487,7 @@
         <v>2.51</v>
       </c>
       <c r="DO96" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -46967,7 +46967,7 @@
         <v>2.31</v>
       </c>
       <c r="DO97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -47414,10 +47414,10 @@
         <v>75</v>
       </c>
       <c r="DD98" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DF98" t="n">
         <v>2.25</v>
@@ -47447,7 +47447,7 @@
         <v>3</v>
       </c>
       <c r="DO98" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -47919,7 +47919,7 @@
         <v>4.52</v>
       </c>
       <c r="DO99" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -48346,7 +48346,7 @@
         <v>84</v>
       </c>
       <c r="DD100" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DE100" t="n">
         <v>1.83</v>
@@ -48379,7 +48379,7 @@
         <v>2.21</v>
       </c>
       <c r="DO100" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -48855,7 +48855,7 @@
         <v>2.88</v>
       </c>
       <c r="DO101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -49290,10 +49290,10 @@
         <v>75</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DE102" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DF102" t="n">
         <v>1.25</v>
@@ -49323,7 +49323,7 @@
         <v>2.07</v>
       </c>
       <c r="DO102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -49758,10 +49758,10 @@
         <v>74</v>
       </c>
       <c r="DD103" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF103" t="n">
         <v>2.6</v>
@@ -49791,7 +49791,7 @@
         <v>3.29</v>
       </c>
       <c r="DO103" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50237,7 +50237,7 @@
         <v>2.71</v>
       </c>
       <c r="DE104" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF104" t="n">
         <v>2.6</v>
@@ -50267,7 +50267,7 @@
         <v>2.79</v>
       </c>
       <c r="DO104" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -50735,7 +50735,7 @@
         <v>2.92</v>
       </c>
       <c r="DO105" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -51211,7 +51211,7 @@
         <v>3.13</v>
       </c>
       <c r="DO106" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -52167,7 +52167,7 @@
         <v>3.06</v>
       </c>
       <c r="DO108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -52635,7 +52635,7 @@
         <v>3.52</v>
       </c>
       <c r="DO109" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -53054,10 +53054,10 @@
         <v>80</v>
       </c>
       <c r="DD110" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE110" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF110" t="n">
         <v>1.8</v>
@@ -53087,7 +53087,7 @@
         <v>2.91</v>
       </c>
       <c r="DO110" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -53542,7 +53542,7 @@
         <v>60</v>
       </c>
       <c r="DD111" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="DE111" t="n">
         <v>0.14</v>
@@ -53575,7 +53575,7 @@
         <v>1.9</v>
       </c>
       <c r="DO111" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP111" t="b">
         <v>0</v>
@@ -54018,10 +54018,10 @@
         <v>70</v>
       </c>
       <c r="DD112" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE112" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DF112" t="n">
         <v>2.2</v>
@@ -54051,7 +54051,7 @@
         <v>3.11</v>
       </c>
       <c r="DO112" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -54535,7 +54535,7 @@
         <v>2.36</v>
       </c>
       <c r="DO113" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -55019,7 +55019,7 @@
         <v>2.35</v>
       </c>
       <c r="DO114" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -55487,7 +55487,7 @@
         <v>3.1</v>
       </c>
       <c r="DO115" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -55914,7 +55914,7 @@
         <v>64</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE116" t="n">
         <v>1.67</v>
@@ -55947,7 +55947,7 @@
         <v>2.69</v>
       </c>
       <c r="DO116" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -56435,7 +56435,7 @@
         <v>2.5</v>
       </c>
       <c r="DO117" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -56873,7 +56873,7 @@
         <v>1.2</v>
       </c>
       <c r="DE118" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DF118" t="n">
         <v>1.25</v>
@@ -56903,7 +56903,7 @@
         <v>3.88</v>
       </c>
       <c r="DO118" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP118" t="b">
         <v>0</v>
@@ -57363,7 +57363,7 @@
         <v>3.06</v>
       </c>
       <c r="DO119" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -57843,7 +57843,7 @@
         <v>2.18</v>
       </c>
       <c r="DO120" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -58465,10 +58465,10 @@
         <v>7</v>
       </c>
       <c r="M122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -58501,10 +58501,10 @@
         <v>15</v>
       </c>
       <c r="Y122" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Z122" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
@@ -58517,10 +58517,10 @@
         </is>
       </c>
       <c r="AC122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE122" t="n">
         <v>1.93</v>
@@ -58637,16 +58637,16 @@
         <v>2</v>
       </c>
       <c r="BQ122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS122" t="n">
         <v>3</v>
       </c>
       <c r="BT122" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU122" t="n">
         <v>1</v>
@@ -59792,6 +59792,3298 @@
       <c r="EP124" t="inlineStr">
         <is>
           <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>13</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>CA Osasuna</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>45983.72916666666</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>3</v>
+      </c>
+      <c r="I125" t="n">
+        <v>4</v>
+      </c>
+      <c r="J125" t="n">
+        <v>3</v>
+      </c>
+      <c r="K125" t="n">
+        <v>3</v>
+      </c>
+      <c r="L125" t="n">
+        <v>6</v>
+      </c>
+      <c r="M125" t="n">
+        <v>3</v>
+      </c>
+      <c r="N125" t="n">
+        <v>2</v>
+      </c>
+      <c r="O125" t="n">
+        <v>2</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>4</v>
+      </c>
+      <c r="R125" t="n">
+        <v>9</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="n">
+        <v>10</v>
+      </c>
+      <c r="U125" t="n">
+        <v>14</v>
+      </c>
+      <c r="V125" t="n">
+        <v>19</v>
+      </c>
+      <c r="W125" t="n">
+        <v>13</v>
+      </c>
+      <c r="X125" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>Carretera El Sadar, Iruñea</t>
+        </is>
+      </c>
+      <c r="AC125" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>290</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>72</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU125" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV125" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX125" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY125" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ125" t="n">
+        <v>37</v>
+      </c>
+      <c r="DA125" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB125" t="n">
+        <v>37</v>
+      </c>
+      <c r="DC125" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD125" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE125" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DF125" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH125" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DI125" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DJ125" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK125" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL125" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DM125" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DN125" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DO125" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW125" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="DX125" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DY125" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="DZ125" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="EA125" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EB125" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EC125" t="inlineStr"/>
+      <c r="ED125" t="inlineStr"/>
+      <c r="EE125" t="inlineStr"/>
+      <c r="EF125" t="inlineStr"/>
+      <c r="EG125" t="inlineStr"/>
+      <c r="EH125" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EI125" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EJ125" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EK125" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EL125" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EM125" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EN125" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EO125" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EP125" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>13</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>RCD Mallorca</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>45983.83333333334</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2</v>
+      </c>
+      <c r="H126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" t="n">
+        <v>3</v>
+      </c>
+      <c r="J126" t="n">
+        <v>3</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1</v>
+      </c>
+      <c r="L126" t="n">
+        <v>4</v>
+      </c>
+      <c r="M126" t="n">
+        <v>2</v>
+      </c>
+      <c r="N126" t="n">
+        <v>2</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>7</v>
+      </c>
+      <c r="R126" t="n">
+        <v>3</v>
+      </c>
+      <c r="S126" t="n">
+        <v>7</v>
+      </c>
+      <c r="T126" t="n">
+        <v>6</v>
+      </c>
+      <c r="U126" t="n">
+        <v>14</v>
+      </c>
+      <c r="V126" t="n">
+        <v>9</v>
+      </c>
+      <c r="W126" t="n">
+        <v>17</v>
+      </c>
+      <c r="X126" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>Estadio de la Cerámica</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>Plaza Labrador, Villarreal</t>
+        </is>
+      </c>
+      <c r="AC126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>76</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>120</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>108</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU126" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV126" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX126" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY126" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ126" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA126" t="n">
+        <v>83</v>
+      </c>
+      <c r="DB126" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC126" t="n">
+        <v>83</v>
+      </c>
+      <c r="DD126" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DE126" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DF126" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DG126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH126" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DI126" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ126" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK126" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL126" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="DM126" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DN126" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="DO126" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW126" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="DX126" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="DY126" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="DZ126" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="EA126" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EB126" t="inlineStr"/>
+      <c r="EC126" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="ED126" t="inlineStr"/>
+      <c r="EE126" t="inlineStr"/>
+      <c r="EF126" t="inlineStr"/>
+      <c r="EG126" t="inlineStr"/>
+      <c r="EH126" t="inlineStr">
+        <is>
+          <t>7.93</t>
+        </is>
+      </c>
+      <c r="EI126" t="inlineStr">
+        <is>
+          <t>5.04</t>
+        </is>
+      </c>
+      <c r="EJ126" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EK126" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL126" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EM126" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EN126" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EO126" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EP126" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>13</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>45984.54166666666</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>5</v>
+      </c>
+      <c r="K127" t="n">
+        <v>6</v>
+      </c>
+      <c r="L127" t="n">
+        <v>11</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1</v>
+      </c>
+      <c r="N127" t="n">
+        <v>2</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1</v>
+      </c>
+      <c r="P127" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>3</v>
+      </c>
+      <c r="R127" t="n">
+        <v>3</v>
+      </c>
+      <c r="S127" t="n">
+        <v>5</v>
+      </c>
+      <c r="T127" t="n">
+        <v>8</v>
+      </c>
+      <c r="U127" t="n">
+        <v>8</v>
+      </c>
+      <c r="V127" t="n">
+        <v>11</v>
+      </c>
+      <c r="W127" t="n">
+        <v>11</v>
+      </c>
+      <c r="X127" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Carlos Tartiere</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>Calle de Ricardo Vázquez Prada, Barrio de la Ería, Oviedo</t>
+        </is>
+      </c>
+      <c r="AC127" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>66</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>89</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU127" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV127" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX127" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY127" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ127" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA127" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB127" t="n">
+        <v>22</v>
+      </c>
+      <c r="DC127" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD127" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DE127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF127" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DG127" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DH127" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DI127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DJ127" t="n">
+        <v>55</v>
+      </c>
+      <c r="DK127" t="n">
+        <v>31</v>
+      </c>
+      <c r="DL127" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="DM127" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DN127" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DO127" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW127" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="DX127" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="DY127" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="DZ127" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA127" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EB127" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EC127" t="inlineStr"/>
+      <c r="ED127" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EE127" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EF127" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EG127" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EH127" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EI127" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EJ127" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="EK127" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EL127" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EM127" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN127" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EO127" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EP127" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>13</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Girona FC</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>45984.63541666666</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" t="n">
+        <v>2</v>
+      </c>
+      <c r="J128" t="n">
+        <v>8</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>8</v>
+      </c>
+      <c r="M128" t="n">
+        <v>3</v>
+      </c>
+      <c r="N128" t="n">
+        <v>4</v>
+      </c>
+      <c r="O128" t="n">
+        <v>1</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>7</v>
+      </c>
+      <c r="R128" t="n">
+        <v>4</v>
+      </c>
+      <c r="S128" t="n">
+        <v>16</v>
+      </c>
+      <c r="T128" t="n">
+        <v>7</v>
+      </c>
+      <c r="U128" t="n">
+        <v>23</v>
+      </c>
+      <c r="V128" t="n">
+        <v>11</v>
+      </c>
+      <c r="W128" t="n">
+        <v>10</v>
+      </c>
+      <c r="X128" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA128" t="inlineStr"/>
+      <c r="AB128" t="inlineStr"/>
+      <c r="AC128" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>62</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>109</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU128" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV128" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX128" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY128" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ128" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA128" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB128" t="n">
+        <v>54</v>
+      </c>
+      <c r="DC128" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD128" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DE128" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF128" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG128" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DH128" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DI128" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DJ128" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK128" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL128" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DM128" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DN128" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="DO128" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW128" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="DX128" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DY128" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="DZ128" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="EA128" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EB128" t="inlineStr"/>
+      <c r="EC128" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="ED128" t="inlineStr"/>
+      <c r="EE128" t="inlineStr"/>
+      <c r="EF128" t="inlineStr"/>
+      <c r="EG128" t="inlineStr"/>
+      <c r="EH128" t="inlineStr">
+        <is>
+          <t>6.32</t>
+        </is>
+      </c>
+      <c r="EI128" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+      <c r="EJ128" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EK128" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EL128" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EM128" t="inlineStr"/>
+      <c r="EN128" t="inlineStr"/>
+      <c r="EO128" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EP128" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>13</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Getafe CF</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>45984.72916666666</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" t="n">
+        <v>6</v>
+      </c>
+      <c r="K129" t="n">
+        <v>7</v>
+      </c>
+      <c r="L129" t="n">
+        <v>13</v>
+      </c>
+      <c r="M129" t="n">
+        <v>2</v>
+      </c>
+      <c r="N129" t="n">
+        <v>3</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>1</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6</v>
+      </c>
+      <c r="S129" t="n">
+        <v>8</v>
+      </c>
+      <c r="T129" t="n">
+        <v>7</v>
+      </c>
+      <c r="U129" t="n">
+        <v>9</v>
+      </c>
+      <c r="V129" t="n">
+        <v>13</v>
+      </c>
+      <c r="W129" t="n">
+        <v>9</v>
+      </c>
+      <c r="X129" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>Coliseum Alfonso Pérez</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>Avenida de Teresa de Calcuta, Getafe</t>
+        </is>
+      </c>
+      <c r="AC129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>117</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>47</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>119</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>3</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU129" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV129" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX129" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY129" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ129" t="n">
+        <v>20</v>
+      </c>
+      <c r="DA129" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB129" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC129" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD129" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE129" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF129" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DG129" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DH129" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DI129" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DJ129" t="n">
+        <v>80</v>
+      </c>
+      <c r="DK129" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL129" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DM129" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DN129" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DO129" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW129" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="DX129" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="DY129" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="DZ129" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="EA129" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EB129" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EC129" t="inlineStr"/>
+      <c r="ED129" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EE129" t="inlineStr"/>
+      <c r="EF129" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EG129" t="inlineStr"/>
+      <c r="EH129" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EI129" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EJ129" t="inlineStr">
+        <is>
+          <t>4.94</t>
+        </is>
+      </c>
+      <c r="EK129" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EL129" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EM129" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EN129" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EO129" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EP129" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>13</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Elche CF</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>45984.83333333334</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2</v>
+      </c>
+      <c r="H130" t="n">
+        <v>2</v>
+      </c>
+      <c r="I130" t="n">
+        <v>4</v>
+      </c>
+      <c r="J130" t="n">
+        <v>2</v>
+      </c>
+      <c r="K130" t="n">
+        <v>8</v>
+      </c>
+      <c r="L130" t="n">
+        <v>10</v>
+      </c>
+      <c r="M130" t="n">
+        <v>3</v>
+      </c>
+      <c r="N130" t="n">
+        <v>1</v>
+      </c>
+      <c r="O130" t="n">
+        <v>1</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>6</v>
+      </c>
+      <c r="R130" t="n">
+        <v>7</v>
+      </c>
+      <c r="S130" t="n">
+        <v>9</v>
+      </c>
+      <c r="T130" t="n">
+        <v>13</v>
+      </c>
+      <c r="U130" t="n">
+        <v>15</v>
+      </c>
+      <c r="V130" t="n">
+        <v>20</v>
+      </c>
+      <c r="W130" t="n">
+        <v>10</v>
+      </c>
+      <c r="X130" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Martínez Valero</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>Avenida Manuel Martínez Valero 3, Elche</t>
+        </is>
+      </c>
+      <c r="AC130" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>70</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>84</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>112</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU130" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV130" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX130" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY130" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ130" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA130" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB130" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC130" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD130" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DE130" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF130" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG130" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DH130" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DI130" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DJ130" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK130" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL130" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DM130" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DN130" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="DO130" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW130" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="DX130" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="DY130" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="DZ130" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="EA130" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EB130" t="inlineStr"/>
+      <c r="EC130" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="ED130" t="inlineStr"/>
+      <c r="EE130" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EF130" t="inlineStr"/>
+      <c r="EG130" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EH130" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EI130" t="inlineStr">
+        <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="EJ130" t="inlineStr">
+        <is>
+          <t>6.99</t>
+        </is>
+      </c>
+      <c r="EK130" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EL130" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EM130" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EN130" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EO130" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EP130" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>13</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>RCD Espanyol</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Sevilla FC</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>45985.83333333334</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" t="n">
+        <v>3</v>
+      </c>
+      <c r="J131" t="n">
+        <v>4</v>
+      </c>
+      <c r="K131" t="n">
+        <v>13</v>
+      </c>
+      <c r="L131" t="n">
+        <v>17</v>
+      </c>
+      <c r="M131" t="n">
+        <v>4</v>
+      </c>
+      <c r="N131" t="n">
+        <v>1</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>5</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6</v>
+      </c>
+      <c r="S131" t="n">
+        <v>3</v>
+      </c>
+      <c r="T131" t="n">
+        <v>16</v>
+      </c>
+      <c r="U131" t="n">
+        <v>8</v>
+      </c>
+      <c r="V131" t="n">
+        <v>22</v>
+      </c>
+      <c r="W131" t="n">
+        <v>18</v>
+      </c>
+      <c r="X131" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>RCDE Stadium</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+        </is>
+      </c>
+      <c r="AC131" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>280</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>77</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>97</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU131" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV131" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX131" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY131" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ131" t="n">
+        <v>62</v>
+      </c>
+      <c r="DA131" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB131" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC131" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD131" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE131" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DF131" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DG131" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH131" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI131" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DJ131" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK131" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL131" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DM131" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN131" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DO131" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW131" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="DX131" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="DY131" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="DZ131" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="EA131" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EB131" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EC131" t="inlineStr"/>
+      <c r="ED131" t="inlineStr"/>
+      <c r="EE131" t="inlineStr"/>
+      <c r="EF131" t="inlineStr"/>
+      <c r="EG131" t="inlineStr"/>
+      <c r="EH131" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="EI131" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="EJ131" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EK131" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EL131" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EM131" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EN131" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EO131" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EP131" t="inlineStr">
+        <is>
+          <t>1.92</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -60792,7 +60792,7 @@
         <v>3</v>
       </c>
       <c r="R127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -60804,7 +60804,7 @@
         <v>8</v>
       </c>
       <c r="V127" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W127" t="n">
         <v>11</v>
@@ -60979,10 +60979,10 @@
         <v>1.03</v>
       </c>
       <c r="CA127" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="CB127" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="CC127" t="n">
         <v>0</v>
@@ -61042,7 +61042,7 @@
         <v>13</v>
       </c>
       <c r="CV127" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CW127" t="n">
         <v>1</v>
@@ -62921,7 +62921,7 @@
         <v>29</v>
       </c>
       <c r="CS131" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CT131" t="n">
         <v>1</v>
@@ -62936,7 +62936,7 @@
         <v>1</v>
       </c>
       <c r="CX131" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CY131" t="n">
         <v>3</v>
@@ -63028,32 +63028,36 @@
       </c>
       <c r="EA131" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EB131" t="inlineStr">
         <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EC131" t="inlineStr"/>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC131" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
       <c r="ED131" t="inlineStr"/>
       <c r="EE131" t="inlineStr"/>
       <c r="EF131" t="inlineStr"/>
       <c r="EG131" t="inlineStr"/>
       <c r="EH131" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="EI131" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="EJ131" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EK131" t="inlineStr">
@@ -63078,12 +63082,12 @@
       </c>
       <c r="EO131" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EP131" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.81</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP131" headerRowCount="1">
-  <autoFilter ref="A1:EP131"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP132" headerRowCount="1">
+  <autoFilter ref="A1:EP132"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP131"/>
+  <dimension ref="A1:EP132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7517,7 +7517,7 @@
         <v>2.71</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -16525,7 +16525,7 @@
         <v>1.17</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
         <v>50</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE34" t="n">
         <v>0.67</v>
@@ -22391,170 +22391,170 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
         <v>45920.6875</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
         <v>3</v>
       </c>
       <c r="J46" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
+        <v>7</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
         <v>8</v>
       </c>
-      <c r="M46" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" t="n">
-        <v>7</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>5</v>
-      </c>
       <c r="R46" t="n">
         <v>3</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>26</v>
+      </c>
+      <c r="V46" t="n">
         <v>6</v>
       </c>
-      <c r="U46" t="n">
-        <v>8</v>
-      </c>
-      <c r="V46" t="n">
-        <v>9</v>
-      </c>
       <c r="W46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="X46" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Y46" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="Z46" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Estadio de Mendizorroza</t>
+          <t>Estadio de la Cerámica</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+          <t>Plaza Labrador, Villarreal</t>
         </is>
       </c>
       <c r="AC46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD46" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.33</v>
+        <v>1.55</v>
       </c>
       <c r="AF46" t="n">
-        <v>3.01</v>
+        <v>3.8</v>
       </c>
       <c r="AG46" t="n">
-        <v>3.28</v>
+        <v>5.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.43</v>
+        <v>2.01</v>
       </c>
       <c r="AJ46" t="n">
-        <v>4.85</v>
+        <v>3.05</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AO46" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AP46" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AR46" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AU46" t="n">
         <v>3</v>
       </c>
       <c r="AV46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
         <v>1</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB46" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="BC46" t="n">
         <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
         <v>0</v>
@@ -22572,73 +22572,73 @@
         <v>1</v>
       </c>
       <c r="BJ46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BL46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BN46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ46" t="n">
         <v>1</v>
       </c>
       <c r="BR46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BS46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BT46" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BU46" t="n">
         <v>1</v>
       </c>
       <c r="BV46" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="BW46" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="BX46" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="BY46" t="n">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="BZ46" t="n">
-        <v>1.22</v>
+        <v>2.84</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.08</v>
+        <v>0.75</v>
       </c>
       <c r="CB46" t="n">
-        <v>2.3</v>
+        <v>3.58</v>
       </c>
       <c r="CC46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG46" t="n">
         <v>0</v>
@@ -22656,13 +22656,13 @@
         <v>0</v>
       </c>
       <c r="CL46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM46" t="n">
         <v>0</v>
       </c>
       <c r="CN46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO46" t="n">
         <v>0</v>
@@ -22674,73 +22674,73 @@
         <v>1</v>
       </c>
       <c r="CR46" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="CS46" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="CT46" t="n">
         <v>1</v>
       </c>
       <c r="CU46" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="CV46" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX46" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY46" t="n">
         <v>20</v>
       </c>
-      <c r="CW46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX46" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY46" t="n">
-        <v>4</v>
-      </c>
       <c r="CZ46" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA46" t="n">
         <v>50</v>
-      </c>
-      <c r="DA46" t="n">
-        <v>100</v>
       </c>
       <c r="DB46" t="n">
         <v>50</v>
       </c>
       <c r="DC46" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.57</v>
+        <v>2.71</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.29</v>
+        <v>0.14</v>
       </c>
       <c r="DF46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DH46" t="n">
         <v>1.75</v>
       </c>
       <c r="DI46" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DJ46" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK46" t="n">
         <v>50</v>
       </c>
-      <c r="DK46" t="n">
-        <v>0</v>
-      </c>
       <c r="DL46" t="n">
-        <v>1.19</v>
+        <v>2.48</v>
       </c>
       <c r="DM46" t="n">
-        <v>1.32</v>
+        <v>0.71</v>
       </c>
       <c r="DN46" t="n">
-        <v>2.51</v>
+        <v>3.19</v>
       </c>
       <c r="DO46" t="n">
         <v>13</v>
@@ -22767,87 +22767,99 @@
         <v>1</v>
       </c>
       <c r="DW46" t="n">
-        <v>27.45</v>
+        <v>27.48</v>
       </c>
       <c r="DX46" t="n">
-        <v>4.36</v>
+        <v>4.71</v>
       </c>
       <c r="DY46" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ46" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="EA46" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EB46" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EC46" t="inlineStr"/>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EC46" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
       <c r="ED46" t="inlineStr">
         <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EE46" t="inlineStr"/>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EE46" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
       <c r="EF46" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="EG46" t="inlineStr"/>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EG46" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
       <c r="EH46" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="EI46" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="EJ46" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EK46" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EL46" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EM46" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EN46" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EO46" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EP46" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -22867,170 +22879,170 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
         <v>45920.6875</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" t="n">
         <v>3</v>
       </c>
       <c r="J47" t="n">
+        <v>4</v>
+      </c>
+      <c r="K47" t="n">
+        <v>4</v>
+      </c>
+      <c r="L47" t="n">
+        <v>8</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
         <v>7</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>3</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>6</v>
+      </c>
+      <c r="U47" t="n">
+        <v>8</v>
+      </c>
+      <c r="V47" t="n">
+        <v>9</v>
+      </c>
+      <c r="W47" t="n">
+        <v>20</v>
+      </c>
+      <c r="X47" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Estadio de Mendizorroza</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+        </is>
+      </c>
+      <c r="AC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD47" t="n">
         <v>7</v>
       </c>
-      <c r="M47" t="n">
-        <v>2</v>
-      </c>
-      <c r="N47" t="n">
-        <v>2</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>8</v>
-      </c>
-      <c r="R47" t="n">
-        <v>3</v>
-      </c>
-      <c r="S47" t="n">
-        <v>18</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3</v>
-      </c>
-      <c r="U47" t="n">
-        <v>26</v>
-      </c>
-      <c r="V47" t="n">
-        <v>6</v>
-      </c>
-      <c r="W47" t="n">
-        <v>10</v>
-      </c>
-      <c r="X47" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>66</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Estadio de la Cerámica</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>Plaza Labrador, Villarreal</t>
-        </is>
-      </c>
-      <c r="AC47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>3</v>
-      </c>
       <c r="AE47" t="n">
-        <v>1.55</v>
+        <v>2.33</v>
       </c>
       <c r="AF47" t="n">
-        <v>3.8</v>
+        <v>3.01</v>
       </c>
       <c r="AG47" t="n">
-        <v>5.25</v>
+        <v>3.28</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.01</v>
+        <v>2.43</v>
       </c>
       <c r="AJ47" t="n">
-        <v>3.05</v>
+        <v>4.85</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AN47" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AO47" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AP47" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AU47" t="n">
         <v>3</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW47" t="n">
         <v>1</v>
       </c>
       <c r="AX47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB47" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="BC47" t="n">
         <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BE47" t="n">
         <v>0</v>
@@ -23048,175 +23060,175 @@
         <v>1</v>
       </c>
       <c r="BJ47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT47" t="n">
         <v>6</v>
       </c>
-      <c r="BL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN47" t="n">
+      <c r="BU47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV47" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW47" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY47" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CA47" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CB47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR47" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS47" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU47" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV47" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX47" t="n">
         <v>6</v>
       </c>
-      <c r="BO47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP47" t="n">
-        <v>3</v>
-      </c>
-      <c r="BQ47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS47" t="n">
+      <c r="CY47" t="n">
         <v>4</v>
       </c>
-      <c r="BT47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV47" t="n">
-        <v>90</v>
-      </c>
-      <c r="BW47" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX47" t="n">
-        <v>112</v>
-      </c>
-      <c r="BY47" t="n">
-        <v>57</v>
-      </c>
-      <c r="BZ47" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CA47" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB47" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="CC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR47" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS47" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU47" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV47" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX47" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY47" t="n">
-        <v>20</v>
-      </c>
       <c r="CZ47" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DA47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB47" t="n">
         <v>50</v>
       </c>
       <c r="DC47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD47" t="n">
-        <v>2.71</v>
+        <v>1.57</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.14</v>
+        <v>1.29</v>
       </c>
       <c r="DF47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DG47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DH47" t="n">
         <v>1.75</v>
       </c>
       <c r="DI47" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DJ47" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK47" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL47" t="n">
-        <v>2.48</v>
+        <v>1.19</v>
       </c>
       <c r="DM47" t="n">
-        <v>0.71</v>
+        <v>1.32</v>
       </c>
       <c r="DN47" t="n">
-        <v>3.19</v>
+        <v>2.51</v>
       </c>
       <c r="DO47" t="n">
         <v>13</v>
@@ -23243,99 +23255,87 @@
         <v>1</v>
       </c>
       <c r="DW47" t="n">
-        <v>27.48</v>
+        <v>27.45</v>
       </c>
       <c r="DX47" t="n">
-        <v>4.71</v>
+        <v>4.36</v>
       </c>
       <c r="DY47" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="DZ47" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="EA47" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EB47" t="inlineStr">
         <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC47" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
-      </c>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EC47" t="inlineStr"/>
       <c r="ED47" t="inlineStr">
         <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE47" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EE47" t="inlineStr"/>
       <c r="EF47" t="inlineStr">
         <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="EG47" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EG47" t="inlineStr"/>
       <c r="EH47" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="EI47" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EJ47" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="EK47" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EL47" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EM47" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EN47" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="EO47" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EP47" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.16</t>
         </is>
       </c>
     </row>
@@ -26695,12 +26695,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
@@ -26710,149 +26710,149 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="n">
+        <v>6</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2</v>
+      </c>
+      <c r="R55" t="n">
         <v>5</v>
       </c>
-      <c r="J55" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" t="n">
+      <c r="S55" t="n">
+        <v>14</v>
+      </c>
+      <c r="T55" t="n">
         <v>7</v>
       </c>
-      <c r="L55" t="n">
-        <v>8</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>2</v>
-      </c>
-      <c r="R55" t="n">
-        <v>10</v>
-      </c>
-      <c r="S55" t="n">
-        <v>9</v>
-      </c>
-      <c r="T55" t="n">
-        <v>14</v>
-      </c>
       <c r="U55" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V55" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="W55" t="n">
         <v>17</v>
       </c>
       <c r="X55" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y55" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="Z55" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Estadio Ciudad de Valencia</t>
+          <t>Estadio Ramón Sánchez Pizjuán</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Calle San Vicente de Paúl 44, Valencia</t>
+          <t>Avenida de Eduardo Dato, Sevilla</t>
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE55" t="n">
-        <v>8</v>
+        <v>3.15</v>
       </c>
       <c r="AF55" t="n">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI55" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT55" t="n">
         <v>1.4</v>
       </c>
-      <c r="AJ55" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AU55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV55" t="n">
         <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX55" t="n">
         <v>1</v>
       </c>
       <c r="AY55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB55" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="BC55" t="n">
         <v>0</v>
@@ -26873,76 +26873,76 @@
         <v>1</v>
       </c>
       <c r="BI55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT55" t="n">
         <v>5</v>
       </c>
-      <c r="BK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL55" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM55" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN55" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ55" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR55" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT55" t="n">
-        <v>2</v>
-      </c>
       <c r="BU55" t="n">
         <v>1</v>
       </c>
       <c r="BV55" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="BW55" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="BX55" t="n">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="BY55" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="BZ55" t="n">
-        <v>1.02</v>
+        <v>1.67</v>
       </c>
       <c r="CA55" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="CB55" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="CC55" t="n">
         <v>0</v>
       </c>
       <c r="CD55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE55" t="n">
         <v>0</v>
       </c>
       <c r="CF55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG55" t="n">
         <v>0</v>
@@ -26966,7 +26966,7 @@
         <v>0</v>
       </c>
       <c r="CN55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO55" t="n">
         <v>0</v>
@@ -26978,73 +26978,73 @@
         <v>1</v>
       </c>
       <c r="CR55" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="CS55" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="CT55" t="n">
         <v>1</v>
       </c>
       <c r="CU55" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV55" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX55" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY55" t="n">
         <v>9</v>
       </c>
-      <c r="CV55" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW55" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX55" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY55" t="n">
-        <v>3</v>
-      </c>
       <c r="CZ55" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA55" t="n">
         <v>100</v>
       </c>
       <c r="DB55" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC55" t="n">
         <v>75</v>
       </c>
-      <c r="DC55" t="n">
-        <v>100</v>
-      </c>
       <c r="DD55" t="n">
-        <v>0.2</v>
+        <v>1.17</v>
       </c>
       <c r="DE55" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DF55" t="n">
         <v>0.5</v>
       </c>
       <c r="DG55" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DH55" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ55" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK55" t="n">
         <v>0</v>
       </c>
       <c r="DL55" t="n">
-        <v>0.84</v>
+        <v>1.24</v>
       </c>
       <c r="DM55" t="n">
-        <v>2.34</v>
+        <v>0.93</v>
       </c>
       <c r="DN55" t="n">
-        <v>3.18</v>
+        <v>2.17</v>
       </c>
       <c r="DO55" t="n">
         <v>13</v>
@@ -27059,10 +27059,10 @@
         <v>1</v>
       </c>
       <c r="DS55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU55" t="b">
         <v>0</v>
@@ -27071,87 +27071,99 @@
         <v>1</v>
       </c>
       <c r="DW55" t="n">
-        <v>22.21</v>
+        <v>27.52</v>
       </c>
       <c r="DX55" t="n">
-        <v>8.289999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="DY55" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="DZ55" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA55" t="inlineStr">
         <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EB55" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EB55" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
       <c r="EC55" t="inlineStr">
         <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="ED55" t="inlineStr"/>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="ED55" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="EE55" t="inlineStr">
         <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EF55" t="inlineStr"/>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EF55" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
       <c r="EG55" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EH55" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EI55" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EJ55" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EK55" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EL55" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EM55" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EN55" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EO55" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EP55" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -27171,12 +27183,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -27186,25 +27198,25 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -27216,119 +27228,119 @@
         <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S56" t="n">
+        <v>9</v>
+      </c>
+      <c r="T56" t="n">
         <v>14</v>
       </c>
-      <c r="T56" t="n">
-        <v>7</v>
-      </c>
       <c r="U56" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V56" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="W56" t="n">
         <v>17</v>
       </c>
       <c r="X56" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Y56" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="Z56" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Estadio Ramón Sánchez Pizjuán</t>
+          <t>Estadio Ciudad de Valencia</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Avenida de Eduardo Dato, Sevilla</t>
+          <t>Calle San Vicente de Paúl 44, Valencia</t>
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE56" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="AF56" t="n">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="AG56" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI56" t="n">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="AJ56" t="n">
-        <v>3.4</v>
+        <v>2.07</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL56" t="n">
         <v>2</v>
       </c>
       <c r="AM56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN56" t="n">
         <v>1.5</v>
       </c>
-      <c r="AN56" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AO56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP56" t="n">
         <v>2.38</v>
       </c>
-      <c r="AP56" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AQ56" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AR56" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.72</v>
+        <v>4.05</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AU56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV56" t="n">
         <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX56" t="n">
         <v>1</v>
       </c>
       <c r="AY56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB56" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="BC56" t="n">
         <v>0</v>
@@ -27349,76 +27361,76 @@
         <v>1</v>
       </c>
       <c r="BI56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL56" t="n">
         <v>2</v>
       </c>
       <c r="BM56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BN56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO56" t="n">
         <v>0</v>
       </c>
       <c r="BP56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU56" t="n">
         <v>1</v>
       </c>
       <c r="BV56" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="BW56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="BX56" t="n">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="BY56" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="BZ56" t="n">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
       <c r="CA56" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="CB56" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="CC56" t="n">
         <v>0</v>
       </c>
       <c r="CD56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE56" t="n">
         <v>0</v>
       </c>
       <c r="CF56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG56" t="n">
         <v>0</v>
@@ -27442,7 +27454,7 @@
         <v>0</v>
       </c>
       <c r="CN56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO56" t="n">
         <v>0</v>
@@ -27454,73 +27466,73 @@
         <v>1</v>
       </c>
       <c r="CR56" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="CS56" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="CT56" t="n">
         <v>1</v>
       </c>
       <c r="CU56" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="CV56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CW56" t="n">
         <v>1</v>
       </c>
       <c r="CX56" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY56" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CZ56" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA56" t="n">
         <v>100</v>
       </c>
       <c r="DB56" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="DC56" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.17</v>
+        <v>0.2</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="DF56" t="n">
         <v>0.5</v>
       </c>
       <c r="DG56" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DH56" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="DI56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ56" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK56" t="n">
         <v>0</v>
       </c>
       <c r="DL56" t="n">
-        <v>1.24</v>
+        <v>0.84</v>
       </c>
       <c r="DM56" t="n">
-        <v>0.93</v>
+        <v>2.34</v>
       </c>
       <c r="DN56" t="n">
-        <v>2.17</v>
+        <v>3.18</v>
       </c>
       <c r="DO56" t="n">
         <v>13</v>
@@ -27535,10 +27547,10 @@
         <v>1</v>
       </c>
       <c r="DS56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU56" t="b">
         <v>0</v>
@@ -27547,99 +27559,87 @@
         <v>1</v>
       </c>
       <c r="DW56" t="n">
-        <v>27.52</v>
+        <v>22.21</v>
       </c>
       <c r="DX56" t="n">
-        <v>3.08</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DY56" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ56" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="EA56" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EB56" t="inlineStr"/>
+      <c r="EC56" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="ED56" t="inlineStr"/>
+      <c r="EE56" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF56" t="inlineStr"/>
+      <c r="EG56" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH56" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI56" t="inlineStr">
+        <is>
+          <t>5.86</t>
+        </is>
+      </c>
+      <c r="EJ56" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="EK56" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL56" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EB56" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EC56" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="ED56" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EE56" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF56" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG56" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EH56" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EI56" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EJ56" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="EK56" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EL56" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
       <c r="EM56" t="inlineStr">
         <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN56" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EO56" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EP56" t="inlineStr">
+        <is>
           <t>1.68</t>
-        </is>
-      </c>
-      <c r="EN56" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EO56" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EP56" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -27978,7 +27978,7 @@
         <v>75</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE57" t="n">
         <v>0.67</v>
@@ -28127,40 +28127,40 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>45924.8125</v>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L58" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -28169,128 +28169,128 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R58" t="n">
         <v>3</v>
       </c>
       <c r="S58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U58" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="V58" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W58" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="X58" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y58" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Z58" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Estadio Wanda Metropolitano</t>
+          <t>Estadio Municipal de Anoeta</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Rosas, Madrid</t>
+          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
         </is>
       </c>
       <c r="AC58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF58" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AG58" t="n">
-        <v>6.5</v>
+        <v>5.13</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AJ58" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AL58" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AM58" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AN58" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AO58" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AP58" t="n">
         <v>1.99</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AR58" t="n">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="AS58" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AU58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB58" t="n">
-        <v>117</v>
+        <v>290</v>
       </c>
       <c r="BC58" t="n">
         <v>0</v>
       </c>
       <c r="BD58" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="BE58" t="n">
         <v>0</v>
@@ -28305,10 +28305,10 @@
         <v>1</v>
       </c>
       <c r="BI58" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BJ58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BK58" t="n">
         <v>4</v>
@@ -28317,52 +28317,52 @@
         <v>2</v>
       </c>
       <c r="BM58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BN58" t="n">
         <v>6</v>
       </c>
       <c r="BO58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BS58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT58" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BU58" t="n">
         <v>1</v>
       </c>
       <c r="BV58" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="BW58" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="BX58" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="BY58" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="BZ58" t="n">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="CA58" t="n">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="CB58" t="n">
-        <v>3.33</v>
+        <v>2.69</v>
       </c>
       <c r="CC58" t="n">
         <v>0</v>
@@ -28395,7 +28395,7 @@
         <v>0</v>
       </c>
       <c r="CM58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN58" t="n">
         <v>0</v>
@@ -28413,70 +28413,70 @@
         <v>22</v>
       </c>
       <c r="CS58" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CT58" t="n">
         <v>1</v>
       </c>
       <c r="CU58" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CV58" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="CW58" t="n">
         <v>1</v>
       </c>
       <c r="CX58" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="CY58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CZ58" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="DA58" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DB58" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="DC58" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>2.71</v>
+        <v>1.67</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.25</v>
+        <v>0.43</v>
       </c>
       <c r="DF58" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="DG58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH58" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="DI58" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="DJ58" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="DK58" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL58" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="DM58" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="DN58" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="DO58" t="n">
         <v>13</v>
@@ -28485,117 +28485,97 @@
         <v>1</v>
       </c>
       <c r="DQ58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU58" t="b">
         <v>0</v>
       </c>
       <c r="DV58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW58" t="n">
-        <v>18.88</v>
+        <v>13.25</v>
       </c>
       <c r="DX58" t="n">
-        <v>6.34</v>
+        <v>3.2</v>
       </c>
       <c r="DY58" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="DZ58" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EA58" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EB58" t="inlineStr">
         <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EC58" t="inlineStr">
-        <is>
-          <t>3.42</t>
-        </is>
-      </c>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EC58" t="inlineStr"/>
       <c r="ED58" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EE58" t="inlineStr">
+        <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="EE58" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
       <c r="EF58" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EG58" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EH58" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="EI58" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="EJ58" t="inlineStr">
         <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EK58" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="EL58" t="inlineStr">
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EK58" t="inlineStr"/>
+      <c r="EL58" t="inlineStr"/>
+      <c r="EM58" t="inlineStr"/>
+      <c r="EN58" t="inlineStr"/>
+      <c r="EO58" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EP58" t="inlineStr">
         <is>
           <t>2.06</t>
-        </is>
-      </c>
-      <c r="EM58" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EN58" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="EO58" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EP58" t="inlineStr">
-        <is>
-          <t>2.18</t>
         </is>
       </c>
     </row>
@@ -28615,40 +28595,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
         <v>45924.8125</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L59" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -28657,128 +28637,128 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R59" t="n">
         <v>3</v>
       </c>
       <c r="S59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U59" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="V59" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W59" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="X59" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y59" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="Z59" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Anoeta</t>
+          <t>Estadio Wanda Metropolitano</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
+          <t>Rosas, Madrid</t>
         </is>
       </c>
       <c r="AC59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF59" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG59" t="n">
-        <v>5.13</v>
+        <v>6.5</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AI59" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AJ59" t="n">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AL59" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AM59" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AN59" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AO59" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AP59" t="n">
         <v>1.99</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AR59" t="n">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="AS59" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AT59" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AU59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB59" t="n">
-        <v>290</v>
+        <v>117</v>
       </c>
       <c r="BC59" t="n">
         <v>0</v>
       </c>
       <c r="BD59" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="BE59" t="n">
         <v>0</v>
@@ -28793,10 +28773,10 @@
         <v>1</v>
       </c>
       <c r="BI59" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BJ59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK59" t="n">
         <v>4</v>
@@ -28805,52 +28785,52 @@
         <v>2</v>
       </c>
       <c r="BM59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BN59" t="n">
         <v>6</v>
       </c>
       <c r="BO59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BS59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT59" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BU59" t="n">
         <v>1</v>
       </c>
       <c r="BV59" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="BW59" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="BX59" t="n">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="BY59" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="BZ59" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="CA59" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="CB59" t="n">
-        <v>2.69</v>
+        <v>3.33</v>
       </c>
       <c r="CC59" t="n">
         <v>0</v>
@@ -28883,7 +28863,7 @@
         <v>0</v>
       </c>
       <c r="CM59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN59" t="n">
         <v>0</v>
@@ -28901,70 +28881,70 @@
         <v>22</v>
       </c>
       <c r="CS59" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CT59" t="n">
         <v>1</v>
       </c>
       <c r="CU59" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CV59" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="CW59" t="n">
         <v>1</v>
       </c>
       <c r="CX59" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CZ59" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="DA59" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="DB59" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="DC59" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.43</v>
+        <v>1.25</v>
       </c>
       <c r="DF59" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DG59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DH59" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="DI59" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="DJ59" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="DK59" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DL59" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="DM59" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="DN59" t="n">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="DO59" t="n">
         <v>13</v>
@@ -28973,97 +28953,117 @@
         <v>1</v>
       </c>
       <c r="DQ59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU59" t="b">
         <v>0</v>
       </c>
       <c r="DV59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW59" t="n">
-        <v>13.25</v>
+        <v>18.88</v>
       </c>
       <c r="DX59" t="n">
-        <v>3.2</v>
+        <v>6.34</v>
       </c>
       <c r="DY59" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="DZ59" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="EA59" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB59" t="inlineStr">
         <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EC59" t="inlineStr"/>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC59" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
       <c r="ED59" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EE59" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EF59" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EG59" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EH59" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="EI59" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="EJ59" t="inlineStr">
         <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EK59" t="inlineStr"/>
-      <c r="EL59" t="inlineStr"/>
-      <c r="EM59" t="inlineStr"/>
-      <c r="EN59" t="inlineStr"/>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EK59" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EL59" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EM59" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EN59" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
       <c r="EO59" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EP59" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.18</t>
         </is>
       </c>
     </row>
@@ -29405,7 +29405,7 @@
         <v>1.67</v>
       </c>
       <c r="DE60" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF60" t="n">
         <v>3</v>
@@ -30826,7 +30826,7 @@
         <v>59</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE63" t="n">
         <v>1</v>
@@ -37437,7 +37437,7 @@
         <v>1.57</v>
       </c>
       <c r="DE77" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF77" t="n">
         <v>1.33</v>
@@ -38043,146 +38043,146 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45935.6875</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K79" t="n">
         <v>5</v>
       </c>
       <c r="L79" t="n">
+        <v>15</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2</v>
+      </c>
+      <c r="N79" t="n">
+        <v>6</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>5</v>
+      </c>
+      <c r="R79" t="n">
+        <v>3</v>
+      </c>
+      <c r="S79" t="n">
+        <v>9</v>
+      </c>
+      <c r="T79" t="n">
+        <v>9</v>
+      </c>
+      <c r="U79" t="n">
+        <v>14</v>
+      </c>
+      <c r="V79" t="n">
         <v>12</v>
       </c>
-      <c r="M79" t="n">
-        <v>1</v>
-      </c>
-      <c r="N79" t="n">
-        <v>2</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>3</v>
-      </c>
-      <c r="R79" t="n">
-        <v>2</v>
-      </c>
-      <c r="S79" t="n">
-        <v>7</v>
-      </c>
-      <c r="T79" t="n">
-        <v>5</v>
-      </c>
-      <c r="U79" t="n">
-        <v>10</v>
-      </c>
-      <c r="V79" t="n">
-        <v>7</v>
-      </c>
       <c r="W79" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X79" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Y79" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z79" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Anoeta</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="AF79" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AG79" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AI79" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AJ79" t="n">
-        <v>3.85</v>
+        <v>2.96</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AM79" t="n">
         <v>1.44</v>
       </c>
       <c r="AN79" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AO79" t="n">
         <v>2.55</v>
       </c>
       <c r="AP79" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AR79" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AU79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW79" t="n">
         <v>0</v>
@@ -38191,22 +38191,22 @@
         <v>0</v>
       </c>
       <c r="AY79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38221,178 +38221,178 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BJ79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BK79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR79" t="n">
         <v>4</v>
       </c>
-      <c r="BL79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM79" t="n">
+      <c r="BS79" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX79" t="n">
         <v>6</v>
       </c>
-      <c r="BN79" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT79" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV79" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW79" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX79" t="n">
-        <v>101</v>
-      </c>
-      <c r="BY79" t="n">
-        <v>90</v>
-      </c>
-      <c r="BZ79" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="CA79" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB79" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN79" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR79" t="n">
-        <v>14</v>
-      </c>
-      <c r="CS79" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU79" t="n">
-        <v>21</v>
-      </c>
-      <c r="CV79" t="n">
+      <c r="CY79" t="n">
         <v>13</v>
       </c>
-      <c r="CW79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX79" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY79" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ79" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="DA79" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="DB79" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="DC79" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="DF79" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="DG79" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DH79" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="DI79" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="DJ79" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="DK79" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="DN79" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="DO79" t="n">
         <v>13</v>
@@ -38401,10 +38401,10 @@
         <v>1</v>
       </c>
       <c r="DQ79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS79" t="b">
         <v>0</v>
@@ -38416,94 +38416,102 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW79" t="n">
-        <v>17.19</v>
+        <v>17.75</v>
       </c>
       <c r="DX79" t="n">
-        <v>3.66</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EB79" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EC79" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED79" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EE79" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EG79" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EJ79" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EK79" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EL79" t="inlineStr">
+        <is>
           <t>2.02</t>
         </is>
       </c>
-      <c r="EB79" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC79" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="ED79" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE79" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF79" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG79" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="EH79" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="EI79" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="EJ79" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EK79" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EL79" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EM79" t="inlineStr"/>
-      <c r="EN79" t="inlineStr"/>
+      <c r="EM79" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EN79" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.68</t>
         </is>
       </c>
     </row>
@@ -38523,40 +38531,40 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45935.6875</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K80" t="n">
         <v>5</v>
       </c>
       <c r="L80" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -38565,104 +38573,104 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
+        <v>3</v>
+      </c>
+      <c r="R80" t="n">
+        <v>2</v>
+      </c>
+      <c r="S80" t="n">
+        <v>7</v>
+      </c>
+      <c r="T80" t="n">
         <v>5</v>
       </c>
-      <c r="R80" t="n">
-        <v>3</v>
-      </c>
-      <c r="S80" t="n">
-        <v>9</v>
-      </c>
-      <c r="T80" t="n">
-        <v>9</v>
-      </c>
       <c r="U80" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V80" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W80" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="X80" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Y80" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z80" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>Estadio Municipal de Anoeta</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
         </is>
       </c>
       <c r="AC80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="AF80" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AJ80" t="n">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AL80" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AM80" t="n">
         <v>1.44</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AO80" t="n">
         <v>2.55</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AR80" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AU80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW80" t="n">
         <v>0</v>
@@ -38671,22 +38679,22 @@
         <v>0</v>
       </c>
       <c r="AY80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB80" t="n">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -38701,178 +38709,178 @@
         <v>1</v>
       </c>
       <c r="BI80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BJ80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BK80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM80" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>101</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV80" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX80" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY80" t="n">
         <v>10</v>
       </c>
-      <c r="BN80" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR80" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS80" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT80" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV80" t="n">
-        <v>66</v>
-      </c>
-      <c r="BW80" t="n">
-        <v>34</v>
-      </c>
-      <c r="BX80" t="n">
-        <v>107</v>
-      </c>
-      <c r="BY80" t="n">
-        <v>98</v>
-      </c>
-      <c r="BZ80" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CA80" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CB80" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CC80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR80" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS80" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU80" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV80" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX80" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY80" t="n">
-        <v>13</v>
-      </c>
       <c r="CZ80" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="DA80" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="DB80" t="n">
+        <v>59</v>
+      </c>
+      <c r="DC80" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD80" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE80" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF80" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DI80" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DJ80" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK80" t="n">
         <v>29</v>
       </c>
-      <c r="DC80" t="n">
-        <v>88</v>
-      </c>
-      <c r="DD80" t="n">
-        <v>2</v>
-      </c>
-      <c r="DE80" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DF80" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DG80" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH80" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DI80" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DJ80" t="n">
-        <v>46</v>
-      </c>
-      <c r="DK80" t="n">
-        <v>13</v>
-      </c>
       <c r="DL80" t="n">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="DM80" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="DN80" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="DO80" t="n">
         <v>13</v>
@@ -38881,10 +38889,10 @@
         <v>1</v>
       </c>
       <c r="DQ80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS80" t="b">
         <v>0</v>
@@ -38896,102 +38904,94 @@
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW80" t="n">
-        <v>17.75</v>
+        <v>17.19</v>
       </c>
       <c r="DX80" t="n">
-        <v>9.369999999999999</v>
+        <v>3.66</v>
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EB80" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EC80" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="ED80" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EE80" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EF80" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EG80" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EH80" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EI80" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EJ80" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EK80" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EL80" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EM80" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EN80" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM80" t="inlineStr"/>
+      <c r="EN80" t="inlineStr"/>
       <c r="EO80" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EP80" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.84</t>
         </is>
       </c>
     </row>
@@ -43578,7 +43578,7 @@
         <v>84</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE90" t="n">
         <v>2</v>
@@ -45497,7 +45497,7 @@
         <v>2</v>
       </c>
       <c r="DE94" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF94" t="n">
         <v>2</v>
@@ -49290,7 +49290,7 @@
         <v>75</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE102" t="n">
         <v>0.5</v>
@@ -52605,7 +52605,7 @@
         <v>3</v>
       </c>
       <c r="DE109" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF109" t="n">
         <v>3</v>
@@ -57011,12 +57011,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F119" s="2" t="n">
@@ -57026,25 +57026,25 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K119" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L119" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -57056,125 +57056,117 @@
         <v>4</v>
       </c>
       <c r="R119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S119" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T119" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U119" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="V119" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W119" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X119" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y119" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Z119" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>Estadio de Mestalla</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>Avenida de Suecia, Valencia</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE119" t="n">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="AF119" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="AG119" t="n">
-        <v>2.15</v>
+        <v>2.98</v>
       </c>
       <c r="AH119" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AI119" t="n">
-        <v>1.91</v>
+        <v>3.04</v>
       </c>
       <c r="AJ119" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="AK119" t="n">
-        <v>1.72</v>
+        <v>2.43</v>
       </c>
       <c r="AL119" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AM119" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="AN119" t="n">
-        <v>1.84</v>
+        <v>2.87</v>
       </c>
       <c r="AO119" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="AR119" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="AS119" t="n">
-        <v>2.89</v>
+        <v>2.05</v>
       </c>
       <c r="AT119" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AU119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW119" t="n">
         <v>0</v>
       </c>
       <c r="AX119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB119" t="n">
-        <v>-1</v>
+        <v>298</v>
       </c>
       <c r="BC119" t="n">
         <v>0</v>
       </c>
       <c r="BD119" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="BE119" t="n">
         <v>0</v>
@@ -57189,64 +57181,64 @@
         <v>1</v>
       </c>
       <c r="BI119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ119" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BK119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL119" t="n">
         <v>6</v>
       </c>
-      <c r="BL119" t="n">
-        <v>1</v>
-      </c>
       <c r="BM119" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BN119" t="n">
         <v>7</v>
       </c>
       <c r="BO119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT119" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BU119" t="n">
         <v>1</v>
       </c>
       <c r="BV119" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="BW119" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="BX119" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="BY119" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="BZ119" t="n">
-        <v>1.74</v>
+        <v>0.96</v>
       </c>
       <c r="CA119" t="n">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="CB119" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="CC119" t="n">
         <v>0</v>
@@ -57279,10 +57271,10 @@
         <v>0</v>
       </c>
       <c r="CM119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO119" t="n">
         <v>0</v>
@@ -57294,19 +57286,19 @@
         <v>1</v>
       </c>
       <c r="CR119" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="CS119" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="CT119" t="n">
         <v>1</v>
       </c>
       <c r="CU119" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CV119" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CW119" t="n">
         <v>1</v>
@@ -57315,52 +57307,52 @@
         <v>6</v>
       </c>
       <c r="CY119" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CZ119" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="DA119" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="DB119" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="DC119" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE119" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="DF119" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG119" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="DH119" t="n">
         <v>0.82</v>
       </c>
       <c r="DI119" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="DJ119" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="DK119" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="DL119" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="DM119" t="n">
-        <v>1.6</v>
+        <v>0.97</v>
       </c>
       <c r="DN119" t="n">
-        <v>3.06</v>
+        <v>2.18</v>
       </c>
       <c r="DO119" t="n">
         <v>13</v>
@@ -57369,7 +57361,7 @@
         <v>1</v>
       </c>
       <c r="DQ119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR119" t="b">
         <v>0</v>
@@ -57384,102 +57376,90 @@
         <v>0</v>
       </c>
       <c r="DV119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW119" t="n">
-        <v>17.01</v>
+        <v>17.48</v>
       </c>
       <c r="DX119" t="n">
-        <v>5.56</v>
+        <v>5.64</v>
       </c>
       <c r="DY119" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="DZ119" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="EA119" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="EB119" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC119" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr"/>
       <c r="ED119" t="inlineStr">
         <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EE119" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EE119" t="inlineStr"/>
       <c r="EF119" t="inlineStr">
         <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="EG119" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EG119" t="inlineStr"/>
       <c r="EH119" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EI119" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EJ119" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EK119" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="EL119" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EM119" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EN119" t="inlineStr">
+        <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="EM119" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EN119" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
       <c r="EO119" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EP119" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.43</t>
         </is>
       </c>
     </row>
@@ -57499,12 +57479,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F120" s="2" t="n">
@@ -57514,25 +57494,25 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K120" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L120" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -57544,117 +57524,125 @@
         <v>4</v>
       </c>
       <c r="R120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S120" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T120" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U120" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="V120" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W120" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="X120" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y120" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Z120" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA120" t="inlineStr"/>
-      <c r="AB120" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>Avenida de Suecia, Valencia</t>
+        </is>
+      </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE120" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="AF120" t="n">
-        <v>2.58</v>
+        <v>3.45</v>
       </c>
       <c r="AG120" t="n">
-        <v>2.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH120" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AI120" t="n">
-        <v>3.04</v>
+        <v>1.91</v>
       </c>
       <c r="AJ120" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="AK120" t="n">
-        <v>2.43</v>
+        <v>1.72</v>
       </c>
       <c r="AL120" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AM120" t="n">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="AN120" t="n">
-        <v>2.87</v>
+        <v>1.84</v>
       </c>
       <c r="AO120" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.77</v>
+        <v>1.37</v>
       </c>
       <c r="AR120" t="n">
-        <v>4.45</v>
+        <v>2.85</v>
       </c>
       <c r="AS120" t="n">
-        <v>2.05</v>
+        <v>2.89</v>
       </c>
       <c r="AT120" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AU120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW120" t="n">
         <v>0</v>
       </c>
       <c r="AX120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB120" t="n">
-        <v>298</v>
+        <v>-1</v>
       </c>
       <c r="BC120" t="n">
         <v>0</v>
       </c>
       <c r="BD120" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="BE120" t="n">
         <v>0</v>
@@ -57669,64 +57657,64 @@
         <v>1</v>
       </c>
       <c r="BI120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ120" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BK120" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BL120" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BM120" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BN120" t="n">
         <v>7</v>
       </c>
       <c r="BO120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT120" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BU120" t="n">
         <v>1</v>
       </c>
       <c r="BV120" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="BW120" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="BX120" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="BY120" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="BZ120" t="n">
-        <v>0.96</v>
+        <v>1.74</v>
       </c>
       <c r="CA120" t="n">
-        <v>1.63</v>
+        <v>1.09</v>
       </c>
       <c r="CB120" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="CC120" t="n">
         <v>0</v>
@@ -57759,10 +57747,10 @@
         <v>0</v>
       </c>
       <c r="CM120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO120" t="n">
         <v>0</v>
@@ -57774,19 +57762,19 @@
         <v>1</v>
       </c>
       <c r="CR120" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="CS120" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="CT120" t="n">
         <v>1</v>
       </c>
       <c r="CU120" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CV120" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CW120" t="n">
         <v>1</v>
@@ -57795,52 +57783,52 @@
         <v>6</v>
       </c>
       <c r="CY120" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CZ120" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="DA120" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="DB120" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="DC120" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="DF120" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG120" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DH120" t="n">
         <v>0.82</v>
       </c>
       <c r="DI120" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="DJ120" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="DK120" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="DL120" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="DM120" t="n">
-        <v>0.97</v>
+        <v>1.6</v>
       </c>
       <c r="DN120" t="n">
-        <v>2.18</v>
+        <v>3.06</v>
       </c>
       <c r="DO120" t="n">
         <v>13</v>
@@ -57849,7 +57837,7 @@
         <v>1</v>
       </c>
       <c r="DQ120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR120" t="b">
         <v>0</v>
@@ -57864,90 +57852,102 @@
         <v>0</v>
       </c>
       <c r="DV120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW120" t="n">
-        <v>17.48</v>
+        <v>17.01</v>
       </c>
       <c r="DX120" t="n">
-        <v>5.64</v>
+        <v>5.56</v>
       </c>
       <c r="DY120" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="DZ120" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="EA120" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB120" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EC120" t="inlineStr"/>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC120" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
       <c r="ED120" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EE120" t="inlineStr"/>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE120" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
       <c r="EF120" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="EG120" t="inlineStr"/>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EG120" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EH120" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EI120" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EJ120" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EK120" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EL120" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EM120" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EN120" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EO120" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EP120" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -62002,7 +62002,7 @@
         <v>60</v>
       </c>
       <c r="DD129" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE129" t="n">
         <v>1.5</v>
@@ -63088,6 +63088,482 @@
       <c r="EP131" t="inlineStr">
         <is>
           <t>1.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>14</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Getafe CF</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Elche CF</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>45989.83333333334</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>3</v>
+      </c>
+      <c r="K132" t="n">
+        <v>5</v>
+      </c>
+      <c r="L132" t="n">
+        <v>8</v>
+      </c>
+      <c r="M132" t="n">
+        <v>2</v>
+      </c>
+      <c r="N132" t="n">
+        <v>2</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>6</v>
+      </c>
+      <c r="R132" t="n">
+        <v>4</v>
+      </c>
+      <c r="S132" t="n">
+        <v>9</v>
+      </c>
+      <c r="T132" t="n">
+        <v>5</v>
+      </c>
+      <c r="U132" t="n">
+        <v>15</v>
+      </c>
+      <c r="V132" t="n">
+        <v>9</v>
+      </c>
+      <c r="W132" t="n">
+        <v>18</v>
+      </c>
+      <c r="X132" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>66</v>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>Coliseum Alfonso Pérez</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>Avenida de Teresa de Calcuta, Getafe</t>
+        </is>
+      </c>
+      <c r="AC132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>293</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU132" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV132" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX132" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY132" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ132" t="n">
+        <v>34</v>
+      </c>
+      <c r="DA132" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB132" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC132" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD132" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DE132" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DF132" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG132" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH132" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DI132" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DJ132" t="n">
+        <v>67</v>
+      </c>
+      <c r="DK132" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL132" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DM132" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="DN132" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DO132" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW132" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="DX132" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DY132" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="DZ132" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="EA132" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EB132" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EC132" t="inlineStr"/>
+      <c r="ED132" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EE132" t="inlineStr"/>
+      <c r="EF132" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EG132" t="inlineStr"/>
+      <c r="EH132" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="EI132" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="EJ132" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EK132" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EL132" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EM132" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EN132" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EO132" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EP132" t="inlineStr">
+        <is>
+          <t>2.27</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP132" headerRowCount="1">
-  <autoFilter ref="A1:EP132"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP134" headerRowCount="1">
+  <autoFilter ref="A1:EP134"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP132"/>
+  <dimension ref="A1:EP134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DE4" t="n">
         <v>1.86</v>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -6097,7 +6097,7 @@
         <v>3</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6557,7 +6557,7 @@
         <v>1.86</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -7030,7 +7030,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DE13" t="n">
         <v>1.83</v>
@@ -15589,7 +15589,7 @@
         <v>2</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -17965,7 +17965,7 @@
         <v>1.86</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DF36" t="n">
         <v>3</v>
@@ -22713,7 +22713,7 @@
         <v>2.71</v>
       </c>
       <c r="DE46" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DF46" t="n">
         <v>3</v>
@@ -24630,7 +24630,7 @@
         <v>100</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DE50" t="n">
         <v>1.5</v>
@@ -25615,7 +25615,7 @@
         <v>3.7</v>
       </c>
       <c r="DO52" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25723,40 +25723,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -25765,101 +25765,101 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T53" t="n">
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W53" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="X53" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y53" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="Z53" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>San Mamés Barria</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="AF53" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="AG53" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AJ53" t="n">
-        <v>4.05</v>
+        <v>3.08</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AO53" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AR53" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AU53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV53" t="n">
         <v>0</v>
@@ -25868,13 +25868,13 @@
         <v>1</v>
       </c>
       <c r="AX53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA53" t="n">
         <v>1</v>
@@ -25886,7 +25886,7 @@
         <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BE53" t="n">
         <v>0</v>
@@ -25901,28 +25901,28 @@
         <v>1</v>
       </c>
       <c r="BI53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BJ53" t="n">
         <v>1</v>
       </c>
       <c r="BK53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BN53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ53" t="n">
         <v>0</v>
@@ -25931,7 +25931,7 @@
         <v>2</v>
       </c>
       <c r="BS53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT53" t="n">
         <v>2</v>
@@ -25940,25 +25940,25 @@
         <v>1</v>
       </c>
       <c r="BV53" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="BW53" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BX53" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="BY53" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="BZ53" t="n">
-        <v>2.59</v>
+        <v>1.96</v>
       </c>
       <c r="CA53" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="CB53" t="n">
-        <v>3.26</v>
+        <v>2.71</v>
       </c>
       <c r="CC53" t="n">
         <v>0</v>
@@ -25988,10 +25988,10 @@
         <v>0</v>
       </c>
       <c r="CL53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN53" t="n">
         <v>0</v>
@@ -26006,19 +26006,19 @@
         <v>1</v>
       </c>
       <c r="CR53" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="CS53" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CT53" t="n">
         <v>1</v>
       </c>
       <c r="CU53" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="CV53" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="CW53" t="n">
         <v>1</v>
@@ -26027,52 +26027,52 @@
         <v>3</v>
       </c>
       <c r="CY53" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CZ53" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA53" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB53" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC53" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD53" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DE53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF53" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DI53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DJ53" t="n">
         <v>59</v>
       </c>
-      <c r="DA53" t="n">
-        <v>59</v>
-      </c>
-      <c r="DB53" t="n">
-        <v>17</v>
-      </c>
-      <c r="DC53" t="n">
-        <v>84</v>
-      </c>
-      <c r="DD53" t="n">
-        <v>2</v>
-      </c>
-      <c r="DE53" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DF53" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH53" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI53" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DJ53" t="n">
-        <v>42</v>
-      </c>
       <c r="DK53" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="DL53" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="DM53" t="n">
-        <v>0.47</v>
+        <v>1.18</v>
       </c>
       <c r="DN53" t="n">
-        <v>1.62</v>
+        <v>2.61</v>
       </c>
       <c r="DO53" t="n">
         <v>13</v>
@@ -26084,10 +26084,10 @@
         <v>1</v>
       </c>
       <c r="DR53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT53" t="b">
         <v>0</v>
@@ -26099,75 +26099,79 @@
         <v>1</v>
       </c>
       <c r="DW53" t="n">
-        <v>20.5</v>
+        <v>17.43</v>
       </c>
       <c r="DX53" t="n">
-        <v>6.93</v>
+        <v>4.72</v>
       </c>
       <c r="DY53" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="DZ53" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="EA53" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EB53" t="inlineStr">
         <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC53" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED53" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE53" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="EC53" t="inlineStr"/>
-      <c r="ED53" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EE53" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="EF53" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EG53" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="EH53" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="EI53" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="EJ53" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EK53" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EL53" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EM53" t="inlineStr">
@@ -26182,12 +26186,12 @@
       </c>
       <c r="EO53" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EP53" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -26207,143 +26211,143 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
         <v>8</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L54" t="n">
+        <v>11</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>4</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>10</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2</v>
+      </c>
+      <c r="S54" t="n">
+        <v>11</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>21</v>
+      </c>
+      <c r="V54" t="n">
+        <v>5</v>
+      </c>
+      <c r="W54" t="n">
         <v>9</v>
       </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>2</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>5</v>
-      </c>
-      <c r="R54" t="n">
-        <v>3</v>
-      </c>
-      <c r="S54" t="n">
-        <v>12</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3</v>
-      </c>
-      <c r="U54" t="n">
-        <v>17</v>
-      </c>
-      <c r="V54" t="n">
-        <v>6</v>
-      </c>
-      <c r="W54" t="n">
-        <v>19</v>
-      </c>
       <c r="X54" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y54" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="Z54" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>San Mamés Barria</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE54" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ54" t="n">
         <v>1.47</v>
       </c>
-      <c r="AF54" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AR54" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AS54" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AU54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV54" t="n">
         <v>0</v>
@@ -26352,13 +26356,13 @@
         <v>1</v>
       </c>
       <c r="AX54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA54" t="n">
         <v>1</v>
@@ -26370,7 +26374,7 @@
         <v>0</v>
       </c>
       <c r="BD54" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BE54" t="n">
         <v>0</v>
@@ -26385,28 +26389,28 @@
         <v>1</v>
       </c>
       <c r="BI54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BJ54" t="n">
         <v>1</v>
       </c>
       <c r="BK54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BL54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BN54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ54" t="n">
         <v>0</v>
@@ -26415,7 +26419,7 @@
         <v>2</v>
       </c>
       <c r="BS54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT54" t="n">
         <v>2</v>
@@ -26424,139 +26428,139 @@
         <v>1</v>
       </c>
       <c r="BV54" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="BW54" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BX54" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="BY54" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ54" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CA54" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CB54" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR54" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS54" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU54" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV54" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX54" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY54" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ54" t="n">
         <v>59</v>
       </c>
-      <c r="BZ54" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CA54" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB54" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="CC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR54" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS54" t="n">
+      <c r="DA54" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB54" t="n">
         <v>17</v>
       </c>
-      <c r="CT54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU54" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV54" t="n">
-        <v>19</v>
-      </c>
-      <c r="CW54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX54" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY54" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ54" t="n">
+      <c r="DC54" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD54" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE54" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DF54" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH54" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ54" t="n">
         <v>42</v>
       </c>
-      <c r="DA54" t="n">
-        <v>67</v>
-      </c>
-      <c r="DB54" t="n">
+      <c r="DK54" t="n">
         <v>42</v>
       </c>
-      <c r="DC54" t="n">
-        <v>67</v>
-      </c>
-      <c r="DD54" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DE54" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DF54" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG54" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DH54" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DI54" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DJ54" t="n">
-        <v>59</v>
-      </c>
-      <c r="DK54" t="n">
-        <v>34</v>
-      </c>
       <c r="DL54" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="DM54" t="n">
-        <v>1.18</v>
+        <v>0.47</v>
       </c>
       <c r="DN54" t="n">
-        <v>2.61</v>
+        <v>1.62</v>
       </c>
       <c r="DO54" t="n">
         <v>13</v>
@@ -26568,10 +26572,10 @@
         <v>1</v>
       </c>
       <c r="DR54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT54" t="b">
         <v>0</v>
@@ -26583,79 +26587,75 @@
         <v>1</v>
       </c>
       <c r="DW54" t="n">
-        <v>17.43</v>
+        <v>20.5</v>
       </c>
       <c r="DX54" t="n">
-        <v>4.72</v>
+        <v>6.93</v>
       </c>
       <c r="DY54" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="DZ54" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA54" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EB54" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC54" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC54" t="inlineStr"/>
       <c r="ED54" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EE54" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF54" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EG54" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EH54" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EI54" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EJ54" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EK54" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EL54" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EM54" t="inlineStr">
@@ -26670,12 +26670,12 @@
       </c>
       <c r="EO54" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP54" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -26695,12 +26695,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
@@ -26710,25 +26710,25 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -26740,119 +26740,119 @@
         <v>2</v>
       </c>
       <c r="R55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S55" t="n">
+        <v>9</v>
+      </c>
+      <c r="T55" t="n">
         <v>14</v>
       </c>
-      <c r="T55" t="n">
-        <v>7</v>
-      </c>
       <c r="U55" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V55" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="W55" t="n">
         <v>17</v>
       </c>
       <c r="X55" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Y55" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="Z55" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Estadio Ramón Sánchez Pizjuán</t>
+          <t>Estadio Ciudad de Valencia</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Avenida de Eduardo Dato, Sevilla</t>
+          <t>Calle San Vicente de Paúl 44, Valencia</t>
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE55" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="AF55" t="n">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI55" t="n">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="AJ55" t="n">
-        <v>3.4</v>
+        <v>2.07</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL55" t="n">
         <v>2</v>
       </c>
       <c r="AM55" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN55" t="n">
         <v>1.5</v>
       </c>
-      <c r="AN55" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AO55" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP55" t="n">
         <v>2.38</v>
       </c>
-      <c r="AP55" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AQ55" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.72</v>
+        <v>4.05</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AU55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV55" t="n">
         <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX55" t="n">
         <v>1</v>
       </c>
       <c r="AY55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB55" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="BC55" t="n">
         <v>0</v>
@@ -26873,76 +26873,76 @@
         <v>1</v>
       </c>
       <c r="BI55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL55" t="n">
         <v>2</v>
       </c>
       <c r="BM55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BN55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO55" t="n">
         <v>0</v>
       </c>
       <c r="BP55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU55" t="n">
         <v>1</v>
       </c>
       <c r="BV55" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="BW55" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="BX55" t="n">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="BY55" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="BZ55" t="n">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
       <c r="CA55" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="CB55" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="CC55" t="n">
         <v>0</v>
       </c>
       <c r="CD55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE55" t="n">
         <v>0</v>
       </c>
       <c r="CF55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG55" t="n">
         <v>0</v>
@@ -26966,7 +26966,7 @@
         <v>0</v>
       </c>
       <c r="CN55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO55" t="n">
         <v>0</v>
@@ -26978,73 +26978,73 @@
         <v>1</v>
       </c>
       <c r="CR55" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="CS55" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="CT55" t="n">
         <v>1</v>
       </c>
       <c r="CU55" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="CV55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CW55" t="n">
         <v>1</v>
       </c>
       <c r="CX55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY55" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CZ55" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA55" t="n">
         <v>100</v>
       </c>
       <c r="DB55" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="DC55" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.17</v>
+        <v>0.2</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="DF55" t="n">
         <v>0.5</v>
       </c>
       <c r="DG55" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DH55" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="DI55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ55" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK55" t="n">
         <v>0</v>
       </c>
       <c r="DL55" t="n">
-        <v>1.24</v>
+        <v>0.84</v>
       </c>
       <c r="DM55" t="n">
-        <v>0.93</v>
+        <v>2.34</v>
       </c>
       <c r="DN55" t="n">
-        <v>2.17</v>
+        <v>3.18</v>
       </c>
       <c r="DO55" t="n">
         <v>13</v>
@@ -27059,10 +27059,10 @@
         <v>1</v>
       </c>
       <c r="DS55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU55" t="b">
         <v>0</v>
@@ -27071,99 +27071,87 @@
         <v>1</v>
       </c>
       <c r="DW55" t="n">
-        <v>27.52</v>
+        <v>22.21</v>
       </c>
       <c r="DX55" t="n">
-        <v>3.08</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DY55" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ55" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="EA55" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EB55" t="inlineStr"/>
+      <c r="EC55" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="ED55" t="inlineStr"/>
+      <c r="EE55" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF55" t="inlineStr"/>
+      <c r="EG55" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH55" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI55" t="inlineStr">
+        <is>
+          <t>5.86</t>
+        </is>
+      </c>
+      <c r="EJ55" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="EK55" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL55" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EB55" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EC55" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="ED55" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EE55" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF55" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG55" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EH55" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EI55" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EJ55" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="EK55" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EL55" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
       <c r="EM55" t="inlineStr">
         <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN55" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EO55" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EP55" t="inlineStr">
+        <is>
           <t>1.68</t>
-        </is>
-      </c>
-      <c r="EN55" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EO55" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EP55" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -27183,12 +27171,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -27198,149 +27186,149 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I56" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3</v>
+      </c>
+      <c r="L56" t="n">
+        <v>6</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2</v>
+      </c>
+      <c r="R56" t="n">
         <v>5</v>
       </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
+      <c r="S56" t="n">
+        <v>14</v>
+      </c>
+      <c r="T56" t="n">
         <v>7</v>
       </c>
-      <c r="L56" t="n">
-        <v>8</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>2</v>
-      </c>
-      <c r="R56" t="n">
-        <v>10</v>
-      </c>
-      <c r="S56" t="n">
-        <v>9</v>
-      </c>
-      <c r="T56" t="n">
-        <v>14</v>
-      </c>
       <c r="U56" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V56" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="W56" t="n">
         <v>17</v>
       </c>
       <c r="X56" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y56" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="Z56" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Estadio Ciudad de Valencia</t>
+          <t>Estadio Ramón Sánchez Pizjuán</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Calle San Vicente de Paúl 44, Valencia</t>
+          <t>Avenida de Eduardo Dato, Sevilla</t>
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE56" t="n">
-        <v>8</v>
+        <v>3.15</v>
       </c>
       <c r="AF56" t="n">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI56" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT56" t="n">
         <v>1.4</v>
       </c>
-      <c r="AJ56" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AU56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV56" t="n">
         <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX56" t="n">
         <v>1</v>
       </c>
       <c r="AY56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB56" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="BC56" t="n">
         <v>0</v>
@@ -27361,76 +27349,76 @@
         <v>1</v>
       </c>
       <c r="BI56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT56" t="n">
         <v>5</v>
       </c>
-      <c r="BK56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL56" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM56" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN56" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ56" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR56" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT56" t="n">
-        <v>2</v>
-      </c>
       <c r="BU56" t="n">
         <v>1</v>
       </c>
       <c r="BV56" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="BW56" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="BX56" t="n">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="BY56" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="BZ56" t="n">
-        <v>1.02</v>
+        <v>1.67</v>
       </c>
       <c r="CA56" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="CB56" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="CC56" t="n">
         <v>0</v>
       </c>
       <c r="CD56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE56" t="n">
         <v>0</v>
       </c>
       <c r="CF56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG56" t="n">
         <v>0</v>
@@ -27454,7 +27442,7 @@
         <v>0</v>
       </c>
       <c r="CN56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO56" t="n">
         <v>0</v>
@@ -27466,73 +27454,73 @@
         <v>1</v>
       </c>
       <c r="CR56" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="CS56" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="CT56" t="n">
         <v>1</v>
       </c>
       <c r="CU56" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV56" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW56" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX56" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY56" t="n">
         <v>9</v>
       </c>
-      <c r="CV56" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW56" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX56" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY56" t="n">
-        <v>3</v>
-      </c>
       <c r="CZ56" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA56" t="n">
         <v>100</v>
       </c>
       <c r="DB56" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC56" t="n">
         <v>75</v>
       </c>
-      <c r="DC56" t="n">
-        <v>100</v>
-      </c>
       <c r="DD56" t="n">
-        <v>0.2</v>
+        <v>1.17</v>
       </c>
       <c r="DE56" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DF56" t="n">
         <v>0.5</v>
       </c>
       <c r="DG56" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DH56" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ56" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK56" t="n">
         <v>0</v>
       </c>
       <c r="DL56" t="n">
-        <v>0.84</v>
+        <v>1.24</v>
       </c>
       <c r="DM56" t="n">
-        <v>2.34</v>
+        <v>0.93</v>
       </c>
       <c r="DN56" t="n">
-        <v>3.18</v>
+        <v>2.17</v>
       </c>
       <c r="DO56" t="n">
         <v>13</v>
@@ -27547,10 +27535,10 @@
         <v>1</v>
       </c>
       <c r="DS56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU56" t="b">
         <v>0</v>
@@ -27559,87 +27547,99 @@
         <v>1</v>
       </c>
       <c r="DW56" t="n">
-        <v>22.21</v>
+        <v>27.52</v>
       </c>
       <c r="DX56" t="n">
-        <v>8.289999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="DY56" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="DZ56" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA56" t="inlineStr">
         <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EB56" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EB56" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
       <c r="EC56" t="inlineStr">
         <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="ED56" t="inlineStr"/>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="ED56" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="EE56" t="inlineStr">
         <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EF56" t="inlineStr"/>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EF56" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
       <c r="EG56" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EH56" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EI56" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EJ56" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EK56" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EL56" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EM56" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EN56" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EO56" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EP56" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -27981,7 +27981,7 @@
         <v>1.57</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DF57" t="n">
         <v>3</v>
@@ -28011,7 +28011,7 @@
         <v>2.1</v>
       </c>
       <c r="DO57" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28127,40 +28127,40 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>45924.8125</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L58" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -28169,128 +28169,128 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R58" t="n">
         <v>3</v>
       </c>
       <c r="S58" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T58" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U58" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="V58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W58" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="X58" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y58" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="Z58" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Anoeta</t>
+          <t>Estadio Wanda Metropolitano</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
+          <t>Rosas, Madrid</t>
         </is>
       </c>
       <c r="AC58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF58" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG58" t="n">
-        <v>5.13</v>
+        <v>6.5</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AI58" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AJ58" t="n">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AL58" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AM58" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AN58" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AO58" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AP58" t="n">
         <v>1.99</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AR58" t="n">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="AS58" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AU58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB58" t="n">
-        <v>290</v>
+        <v>117</v>
       </c>
       <c r="BC58" t="n">
         <v>0</v>
       </c>
       <c r="BD58" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="BE58" t="n">
         <v>0</v>
@@ -28305,10 +28305,10 @@
         <v>1</v>
       </c>
       <c r="BI58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BJ58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK58" t="n">
         <v>4</v>
@@ -28317,52 +28317,52 @@
         <v>2</v>
       </c>
       <c r="BM58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BN58" t="n">
         <v>6</v>
       </c>
       <c r="BO58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BS58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT58" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BU58" t="n">
         <v>1</v>
       </c>
       <c r="BV58" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="BW58" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="BX58" t="n">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="BY58" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="BZ58" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="CA58" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="CB58" t="n">
-        <v>2.69</v>
+        <v>3.33</v>
       </c>
       <c r="CC58" t="n">
         <v>0</v>
@@ -28395,7 +28395,7 @@
         <v>0</v>
       </c>
       <c r="CM58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN58" t="n">
         <v>0</v>
@@ -28413,70 +28413,70 @@
         <v>22</v>
       </c>
       <c r="CS58" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CT58" t="n">
         <v>1</v>
       </c>
       <c r="CU58" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CV58" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="CW58" t="n">
         <v>1</v>
       </c>
       <c r="CX58" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CZ58" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="DA58" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="DB58" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="DC58" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.43</v>
+        <v>1.25</v>
       </c>
       <c r="DF58" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DG58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DH58" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="DI58" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="DJ58" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="DK58" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DL58" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="DM58" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="DN58" t="n">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="DO58" t="n">
         <v>13</v>
@@ -28485,97 +28485,117 @@
         <v>1</v>
       </c>
       <c r="DQ58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU58" t="b">
         <v>0</v>
       </c>
       <c r="DV58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW58" t="n">
-        <v>13.25</v>
+        <v>18.88</v>
       </c>
       <c r="DX58" t="n">
-        <v>3.2</v>
+        <v>6.34</v>
       </c>
       <c r="DY58" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="DZ58" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="EA58" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB58" t="inlineStr">
         <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EC58" t="inlineStr"/>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC58" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
       <c r="ED58" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EE58" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EF58" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EG58" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EH58" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="EI58" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="EJ58" t="inlineStr">
         <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EK58" t="inlineStr"/>
-      <c r="EL58" t="inlineStr"/>
-      <c r="EM58" t="inlineStr"/>
-      <c r="EN58" t="inlineStr"/>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EK58" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EL58" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EM58" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EN58" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
       <c r="EO58" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EP58" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.18</t>
         </is>
       </c>
     </row>
@@ -28595,40 +28615,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
         <v>45924.8125</v>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K59" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L59" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -28637,128 +28657,128 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R59" t="n">
         <v>3</v>
       </c>
       <c r="S59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U59" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="V59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W59" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="X59" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y59" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Z59" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Estadio Wanda Metropolitano</t>
+          <t>Estadio Municipal de Anoeta</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Rosas, Madrid</t>
+          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
         </is>
       </c>
       <c r="AC59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF59" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AG59" t="n">
-        <v>6.5</v>
+        <v>5.13</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AJ59" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AL59" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AM59" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AN59" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AO59" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AP59" t="n">
         <v>1.99</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AR59" t="n">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="AS59" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AT59" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AU59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB59" t="n">
-        <v>117</v>
+        <v>290</v>
       </c>
       <c r="BC59" t="n">
         <v>0</v>
       </c>
       <c r="BD59" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="BE59" t="n">
         <v>0</v>
@@ -28773,10 +28793,10 @@
         <v>1</v>
       </c>
       <c r="BI59" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BJ59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BK59" t="n">
         <v>4</v>
@@ -28785,52 +28805,52 @@
         <v>2</v>
       </c>
       <c r="BM59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BN59" t="n">
         <v>6</v>
       </c>
       <c r="BO59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BS59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT59" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BU59" t="n">
         <v>1</v>
       </c>
       <c r="BV59" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="BW59" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="BX59" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="BY59" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="BZ59" t="n">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="CA59" t="n">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="CB59" t="n">
-        <v>3.33</v>
+        <v>2.69</v>
       </c>
       <c r="CC59" t="n">
         <v>0</v>
@@ -28863,7 +28883,7 @@
         <v>0</v>
       </c>
       <c r="CM59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN59" t="n">
         <v>0</v>
@@ -28881,70 +28901,70 @@
         <v>22</v>
       </c>
       <c r="CS59" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CT59" t="n">
         <v>1</v>
       </c>
       <c r="CU59" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CV59" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="CW59" t="n">
         <v>1</v>
       </c>
       <c r="CX59" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="CY59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CZ59" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="DA59" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DB59" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="DC59" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DD59" t="n">
-        <v>2.71</v>
+        <v>1.67</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.25</v>
+        <v>0.43</v>
       </c>
       <c r="DF59" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="DG59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH59" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="DI59" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="DJ59" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="DK59" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL59" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="DM59" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="DN59" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="DO59" t="n">
         <v>13</v>
@@ -28953,117 +28973,97 @@
         <v>1</v>
       </c>
       <c r="DQ59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU59" t="b">
         <v>0</v>
       </c>
       <c r="DV59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW59" t="n">
-        <v>18.88</v>
+        <v>13.25</v>
       </c>
       <c r="DX59" t="n">
-        <v>6.34</v>
+        <v>3.2</v>
       </c>
       <c r="DY59" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="DZ59" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EA59" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EB59" t="inlineStr">
         <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EC59" t="inlineStr">
-        <is>
-          <t>3.42</t>
-        </is>
-      </c>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EC59" t="inlineStr"/>
       <c r="ED59" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EE59" t="inlineStr">
+        <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="EE59" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
       <c r="EF59" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EG59" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EH59" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="EI59" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="EJ59" t="inlineStr">
         <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EK59" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="EL59" t="inlineStr">
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EK59" t="inlineStr"/>
+      <c r="EL59" t="inlineStr"/>
+      <c r="EM59" t="inlineStr"/>
+      <c r="EN59" t="inlineStr"/>
+      <c r="EO59" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EP59" t="inlineStr">
         <is>
           <t>2.06</t>
-        </is>
-      </c>
-      <c r="EM59" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EN59" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="EO59" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EP59" t="inlineStr">
-        <is>
-          <t>2.18</t>
         </is>
       </c>
     </row>
@@ -29435,7 +29435,7 @@
         <v>2.17</v>
       </c>
       <c r="DO60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -31762,10 +31762,10 @@
         <v>50</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DE65" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DF65" t="n">
         <v>0.67</v>
@@ -31795,7 +31795,7 @@
         <v>2</v>
       </c>
       <c r="DO65" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -34081,7 +34081,7 @@
         <v>1.86</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DF70" t="n">
         <v>2</v>
@@ -35079,7 +35079,7 @@
         <v>2.29</v>
       </c>
       <c r="DO72" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -37467,7 +37467,7 @@
         <v>2.1</v>
       </c>
       <c r="DO77" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -41673,7 +41673,7 @@
         <v>2.71</v>
       </c>
       <c r="DE86" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DF86" t="n">
         <v>2.5</v>
@@ -46934,7 +46934,7 @@
         <v>78</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DE97" t="n">
         <v>1</v>
@@ -48825,7 +48825,7 @@
         <v>1.2</v>
       </c>
       <c r="DE101" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DF101" t="n">
         <v>0.67</v>
@@ -52635,7 +52635,7 @@
         <v>3.52</v>
       </c>
       <c r="DO109" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -53545,7 +53545,7 @@
         <v>0.71</v>
       </c>
       <c r="DE111" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DF111" t="n">
         <v>0.6</v>
@@ -54505,7 +54505,7 @@
         <v>1.14</v>
       </c>
       <c r="DE113" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DF113" t="n">
         <v>0.83</v>
@@ -54989,7 +54989,7 @@
         <v>1.17</v>
       </c>
       <c r="DE114" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DF114" t="n">
         <v>0.8</v>
@@ -57322,7 +57322,7 @@
         <v>74</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DE119" t="n">
         <v>1.29</v>
@@ -57355,7 +57355,7 @@
         <v>2.18</v>
       </c>
       <c r="DO119" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -63564,6 +63564,934 @@
       <c r="EP132" t="inlineStr">
         <is>
           <t>2.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>14</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>RCD Mallorca</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>CA Osasuna</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>45990.54166666666</v>
+      </c>
+      <c r="G133" t="n">
+        <v>2</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2</v>
+      </c>
+      <c r="I133" t="n">
+        <v>4</v>
+      </c>
+      <c r="J133" t="n">
+        <v>2</v>
+      </c>
+      <c r="K133" t="n">
+        <v>8</v>
+      </c>
+      <c r="L133" t="n">
+        <v>10</v>
+      </c>
+      <c r="M133" t="n">
+        <v>3</v>
+      </c>
+      <c r="N133" t="n">
+        <v>4</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>4</v>
+      </c>
+      <c r="R133" t="n">
+        <v>2</v>
+      </c>
+      <c r="S133" t="n">
+        <v>3</v>
+      </c>
+      <c r="T133" t="n">
+        <v>12</v>
+      </c>
+      <c r="U133" t="n">
+        <v>7</v>
+      </c>
+      <c r="V133" t="n">
+        <v>14</v>
+      </c>
+      <c r="W133" t="n">
+        <v>10</v>
+      </c>
+      <c r="X133" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA133" t="inlineStr"/>
+      <c r="AB133" t="inlineStr"/>
+      <c r="AC133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU133" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV133" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX133" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY133" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ133" t="n">
+        <v>16</v>
+      </c>
+      <c r="DA133" t="n">
+        <v>48</v>
+      </c>
+      <c r="DB133" t="n">
+        <v>16</v>
+      </c>
+      <c r="DC133" t="n">
+        <v>56</v>
+      </c>
+      <c r="DD133" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DE133" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DF133" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG133" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DH133" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DI133" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DJ133" t="n">
+        <v>85</v>
+      </c>
+      <c r="DK133" t="n">
+        <v>52</v>
+      </c>
+      <c r="DL133" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DM133" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="DN133" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DO133" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW133" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="DX133" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="DY133" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="DZ133" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="EA133" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EB133" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EC133" t="inlineStr"/>
+      <c r="ED133" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EE133" t="inlineStr"/>
+      <c r="EF133" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="EG133" t="inlineStr"/>
+      <c r="EH133" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EI133" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EJ133" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EK133" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EL133" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EM133" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EN133" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EO133" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EP133" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>14</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>45990.63541666666</v>
+      </c>
+      <c r="G134" t="n">
+        <v>3</v>
+      </c>
+      <c r="H134" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" t="n">
+        <v>4</v>
+      </c>
+      <c r="J134" t="n">
+        <v>5</v>
+      </c>
+      <c r="K134" t="n">
+        <v>4</v>
+      </c>
+      <c r="L134" t="n">
+        <v>9</v>
+      </c>
+      <c r="M134" t="n">
+        <v>2</v>
+      </c>
+      <c r="N134" t="n">
+        <v>3</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>6</v>
+      </c>
+      <c r="R134" t="n">
+        <v>3</v>
+      </c>
+      <c r="S134" t="n">
+        <v>12</v>
+      </c>
+      <c r="T134" t="n">
+        <v>6</v>
+      </c>
+      <c r="U134" t="n">
+        <v>18</v>
+      </c>
+      <c r="V134" t="n">
+        <v>9</v>
+      </c>
+      <c r="W134" t="n">
+        <v>10</v>
+      </c>
+      <c r="X134" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>69</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="inlineStr"/>
+      <c r="AC134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>83</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>63</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>157</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>69</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU134" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV134" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX134" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY134" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ134" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA134" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB134" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC134" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD134" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE134" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DF134" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG134" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH134" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DI134" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DJ134" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK134" t="n">
+        <v>42</v>
+      </c>
+      <c r="DL134" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DM134" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DN134" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="DO134" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW134" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="DX134" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="DY134" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="DZ134" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="EA134" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EB134" t="inlineStr"/>
+      <c r="EC134" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="ED134" t="inlineStr"/>
+      <c r="EE134" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EF134" t="inlineStr"/>
+      <c r="EG134" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EH134" t="inlineStr">
+        <is>
+          <t>13.31</t>
+        </is>
+      </c>
+      <c r="EI134" t="inlineStr">
+        <is>
+          <t>7.36</t>
+        </is>
+      </c>
+      <c r="EJ134" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="EK134" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EL134" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EM134" t="inlineStr"/>
+      <c r="EN134" t="inlineStr"/>
+      <c r="EO134" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EP134" t="inlineStr">
+        <is>
+          <t>1.93</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP134" headerRowCount="1">
-  <autoFilter ref="A1:EP134"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP140" headerRowCount="1">
+  <autoFilter ref="A1:EP140"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP134"/>
+  <dimension ref="A1:EP140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE2" t="n">
         <v>1.25</v>
@@ -2289,7 +2289,7 @@
         <v>2.71</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -3735,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE7" t="n">
         <v>1.29</v>
@@ -4203,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5613,7 +5613,7 @@
         <v>1.86</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5643,7 +5643,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6127,7 +6127,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7063,7 +7063,7 @@
         <v>0.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7514,7 +7514,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE14" t="n">
         <v>0.43</v>
@@ -7547,7 +7547,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8002,7 +8002,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DE15" t="n">
         <v>1.86</v>
@@ -8035,7 +8035,7 @@
         <v>2.67</v>
       </c>
       <c r="DO15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8938,10 +8938,10 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE17" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8971,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9459,7 +9459,7 @@
         <v>2.89</v>
       </c>
       <c r="DO18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9881,7 +9881,7 @@
         <v>0.71</v>
       </c>
       <c r="DE19" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9911,7 +9911,7 @@
         <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10834,7 +10834,7 @@
         <v>0</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DE21" t="n">
         <v>1.29</v>
@@ -10867,7 +10867,7 @@
         <v>1.06</v>
       </c>
       <c r="DO21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11302,10 +11302,10 @@
         <v>50</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11335,7 +11335,7 @@
         <v>2.67</v>
       </c>
       <c r="DO22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11807,7 +11807,7 @@
         <v>1.81</v>
       </c>
       <c r="DO23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12771,7 +12771,7 @@
         <v>3.34</v>
       </c>
       <c r="DO25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13255,7 +13255,7 @@
         <v>2.11</v>
       </c>
       <c r="DO26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13690,7 +13690,7 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE27" t="n">
         <v>1.29</v>
@@ -13723,7 +13723,7 @@
         <v>2.25</v>
       </c>
       <c r="DO27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14211,7 +14211,7 @@
         <v>2.14</v>
       </c>
       <c r="DO28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14638,10 +14638,10 @@
         <v>25</v>
       </c>
       <c r="DD29" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF29" t="n">
         <v>0.5</v>
@@ -14671,7 +14671,7 @@
         <v>1.49</v>
       </c>
       <c r="DO29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15105,7 +15105,7 @@
         <v>1.86</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="DF30" t="n">
         <v>3</v>
@@ -15135,7 +15135,7 @@
         <v>1.65</v>
       </c>
       <c r="DO30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15619,7 +15619,7 @@
         <v>1.56</v>
       </c>
       <c r="DO31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16522,7 +16522,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DE33" t="n">
         <v>0.43</v>
@@ -16555,7 +16555,7 @@
         <v>2.15</v>
       </c>
       <c r="DO33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17009,7 +17009,7 @@
         <v>1.57</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DF34" t="n">
         <v>0</v>
@@ -17039,7 +17039,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="DO34" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17482,10 +17482,10 @@
         <v>100</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE35" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DF35" t="n">
         <v>1</v>
@@ -17515,7 +17515,7 @@
         <v>4.77</v>
       </c>
       <c r="DO35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17995,7 +17995,7 @@
         <v>2.75</v>
       </c>
       <c r="DO36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18446,10 +18446,10 @@
         <v>50</v>
       </c>
       <c r="DD37" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF37" t="n">
         <v>1</v>
@@ -18479,7 +18479,7 @@
         <v>2.71</v>
       </c>
       <c r="DO37" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18926,7 +18926,7 @@
         <v>67</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE38" t="n">
         <v>0.5</v>
@@ -18959,7 +18959,7 @@
         <v>2.12</v>
       </c>
       <c r="DO38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19414,10 +19414,10 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF39" t="n">
         <v>0</v>
@@ -19447,7 +19447,7 @@
         <v>2.04</v>
       </c>
       <c r="DO39" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20863,7 +20863,7 @@
         <v>2.33</v>
       </c>
       <c r="DO42" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21331,7 +21331,7 @@
         <v>2.96</v>
       </c>
       <c r="DO43" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21762,7 +21762,7 @@
         <v>75</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE44" t="n">
         <v>1</v>
@@ -21795,7 +21795,7 @@
         <v>2.35</v>
       </c>
       <c r="DO44" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22253,7 +22253,7 @@
         <v>3</v>
       </c>
       <c r="DE45" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DF45" t="n">
         <v>3</v>
@@ -22283,7 +22283,7 @@
         <v>3.56</v>
       </c>
       <c r="DO45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22743,7 +22743,7 @@
         <v>3.19</v>
       </c>
       <c r="DO46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23231,7 +23231,7 @@
         <v>2.51</v>
       </c>
       <c r="DO47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23677,7 +23677,7 @@
         <v>1.57</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="DF48" t="n">
         <v>2</v>
@@ -24663,7 +24663,7 @@
         <v>2.63</v>
       </c>
       <c r="DO50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25117,7 +25117,7 @@
         <v>1.86</v>
       </c>
       <c r="DE51" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DF51" t="n">
         <v>2</v>
@@ -25147,7 +25147,7 @@
         <v>1.99</v>
       </c>
       <c r="DO51" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25723,143 +25723,143 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
         <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L53" t="n">
+        <v>11</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>10</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2</v>
+      </c>
+      <c r="S53" t="n">
+        <v>11</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>21</v>
+      </c>
+      <c r="V53" t="n">
+        <v>5</v>
+      </c>
+      <c r="W53" t="n">
         <v>9</v>
       </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>2</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>5</v>
-      </c>
-      <c r="R53" t="n">
-        <v>3</v>
-      </c>
-      <c r="S53" t="n">
-        <v>12</v>
-      </c>
-      <c r="T53" t="n">
-        <v>3</v>
-      </c>
-      <c r="U53" t="n">
-        <v>17</v>
-      </c>
-      <c r="V53" t="n">
-        <v>6</v>
-      </c>
-      <c r="W53" t="n">
-        <v>19</v>
-      </c>
       <c r="X53" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y53" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="Z53" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>San Mamés Barria</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE53" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ53" t="n">
         <v>1.47</v>
       </c>
-      <c r="AF53" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AR53" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AS53" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AU53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV53" t="n">
         <v>0</v>
@@ -25868,13 +25868,13 @@
         <v>1</v>
       </c>
       <c r="AX53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA53" t="n">
         <v>1</v>
@@ -25886,7 +25886,7 @@
         <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BE53" t="n">
         <v>0</v>
@@ -25901,28 +25901,28 @@
         <v>1</v>
       </c>
       <c r="BI53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BJ53" t="n">
         <v>1</v>
       </c>
       <c r="BK53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BL53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BN53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ53" t="n">
         <v>0</v>
@@ -25931,7 +25931,7 @@
         <v>2</v>
       </c>
       <c r="BS53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT53" t="n">
         <v>2</v>
@@ -25940,139 +25940,139 @@
         <v>1</v>
       </c>
       <c r="BV53" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="BW53" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BX53" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="BY53" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CB53" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR53" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS53" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU53" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV53" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX53" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY53" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ53" t="n">
         <v>59</v>
       </c>
-      <c r="BZ53" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CA53" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB53" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="CC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS53" t="n">
+      <c r="DA53" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB53" t="n">
         <v>17</v>
       </c>
-      <c r="CT53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU53" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV53" t="n">
-        <v>19</v>
-      </c>
-      <c r="CW53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX53" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY53" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ53" t="n">
+      <c r="DC53" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD53" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE53" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DF53" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH53" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ53" t="n">
         <v>42</v>
       </c>
-      <c r="DA53" t="n">
-        <v>67</v>
-      </c>
-      <c r="DB53" t="n">
+      <c r="DK53" t="n">
         <v>42</v>
       </c>
-      <c r="DC53" t="n">
-        <v>67</v>
-      </c>
-      <c r="DD53" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DE53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DF53" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DH53" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DI53" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DJ53" t="n">
-        <v>59</v>
-      </c>
-      <c r="DK53" t="n">
-        <v>34</v>
-      </c>
       <c r="DL53" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="DM53" t="n">
-        <v>1.18</v>
+        <v>0.47</v>
       </c>
       <c r="DN53" t="n">
-        <v>2.61</v>
+        <v>1.62</v>
       </c>
       <c r="DO53" t="n">
         <v>13</v>
@@ -26084,10 +26084,10 @@
         <v>1</v>
       </c>
       <c r="DR53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT53" t="b">
         <v>0</v>
@@ -26099,79 +26099,75 @@
         <v>1</v>
       </c>
       <c r="DW53" t="n">
-        <v>17.43</v>
+        <v>20.5</v>
       </c>
       <c r="DX53" t="n">
-        <v>4.72</v>
+        <v>6.93</v>
       </c>
       <c r="DY53" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="DZ53" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA53" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EB53" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC53" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC53" t="inlineStr"/>
       <c r="ED53" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EE53" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF53" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EG53" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EH53" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EI53" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EJ53" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EK53" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EL53" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EM53" t="inlineStr">
@@ -26186,12 +26182,12 @@
       </c>
       <c r="EO53" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP53" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -26211,40 +26207,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>8</v>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -26253,101 +26249,101 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T54" t="n">
         <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W54" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="X54" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y54" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="Z54" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>San Mamés Barria</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="AF54" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="AG54" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AI54" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AJ54" t="n">
-        <v>4.05</v>
+        <v>3.08</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AN54" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AO54" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AR54" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AU54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV54" t="n">
         <v>0</v>
@@ -26356,13 +26352,13 @@
         <v>1</v>
       </c>
       <c r="AX54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA54" t="n">
         <v>1</v>
@@ -26374,7 +26370,7 @@
         <v>0</v>
       </c>
       <c r="BD54" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BE54" t="n">
         <v>0</v>
@@ -26389,28 +26385,28 @@
         <v>1</v>
       </c>
       <c r="BI54" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BJ54" t="n">
         <v>1</v>
       </c>
       <c r="BK54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BN54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ54" t="n">
         <v>0</v>
@@ -26419,7 +26415,7 @@
         <v>2</v>
       </c>
       <c r="BS54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT54" t="n">
         <v>2</v>
@@ -26428,25 +26424,25 @@
         <v>1</v>
       </c>
       <c r="BV54" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="BW54" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BX54" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="BY54" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="BZ54" t="n">
-        <v>2.59</v>
+        <v>1.96</v>
       </c>
       <c r="CA54" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="CB54" t="n">
-        <v>3.26</v>
+        <v>2.71</v>
       </c>
       <c r="CC54" t="n">
         <v>0</v>
@@ -26476,10 +26472,10 @@
         <v>0</v>
       </c>
       <c r="CL54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN54" t="n">
         <v>0</v>
@@ -26494,77 +26490,77 @@
         <v>1</v>
       </c>
       <c r="CR54" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="CS54" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU54" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV54" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX54" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY54" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ54" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA54" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB54" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC54" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD54" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DE54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF54" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DI54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DJ54" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK54" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL54" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM54" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DN54" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="DO54" t="n">
         <v>14</v>
       </c>
-      <c r="CT54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU54" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV54" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX54" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY54" t="n">
-        <v>9</v>
-      </c>
-      <c r="CZ54" t="n">
-        <v>59</v>
-      </c>
-      <c r="DA54" t="n">
-        <v>59</v>
-      </c>
-      <c r="DB54" t="n">
-        <v>17</v>
-      </c>
-      <c r="DC54" t="n">
-        <v>84</v>
-      </c>
-      <c r="DD54" t="n">
-        <v>2</v>
-      </c>
-      <c r="DE54" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DF54" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH54" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI54" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DJ54" t="n">
-        <v>42</v>
-      </c>
-      <c r="DK54" t="n">
-        <v>42</v>
-      </c>
-      <c r="DL54" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="DM54" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="DN54" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="DO54" t="n">
-        <v>13</v>
-      </c>
       <c r="DP54" t="b">
         <v>1</v>
       </c>
@@ -26572,10 +26568,10 @@
         <v>1</v>
       </c>
       <c r="DR54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT54" t="b">
         <v>0</v>
@@ -26587,75 +26583,79 @@
         <v>1</v>
       </c>
       <c r="DW54" t="n">
-        <v>20.5</v>
+        <v>17.43</v>
       </c>
       <c r="DX54" t="n">
-        <v>6.93</v>
+        <v>4.72</v>
       </c>
       <c r="DY54" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="DZ54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="EA54" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EB54" t="inlineStr">
         <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC54" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED54" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE54" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="EC54" t="inlineStr"/>
-      <c r="ED54" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EE54" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="EF54" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EG54" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="EH54" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="EI54" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="EJ54" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EK54" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EL54" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EM54" t="inlineStr">
@@ -26670,12 +26670,12 @@
       </c>
       <c r="EO54" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EP54" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -26695,12 +26695,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
@@ -26710,149 +26710,149 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="n">
+        <v>6</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2</v>
+      </c>
+      <c r="R55" t="n">
         <v>5</v>
       </c>
-      <c r="J55" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" t="n">
+      <c r="S55" t="n">
+        <v>14</v>
+      </c>
+      <c r="T55" t="n">
         <v>7</v>
       </c>
-      <c r="L55" t="n">
-        <v>8</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>2</v>
-      </c>
-      <c r="R55" t="n">
-        <v>10</v>
-      </c>
-      <c r="S55" t="n">
-        <v>9</v>
-      </c>
-      <c r="T55" t="n">
-        <v>14</v>
-      </c>
       <c r="U55" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V55" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="W55" t="n">
         <v>17</v>
       </c>
       <c r="X55" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y55" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="Z55" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Estadio Ciudad de Valencia</t>
+          <t>Estadio Ramón Sánchez Pizjuán</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Calle San Vicente de Paúl 44, Valencia</t>
+          <t>Avenida de Eduardo Dato, Sevilla</t>
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE55" t="n">
-        <v>8</v>
+        <v>3.15</v>
       </c>
       <c r="AF55" t="n">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI55" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT55" t="n">
         <v>1.4</v>
       </c>
-      <c r="AJ55" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AU55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV55" t="n">
         <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX55" t="n">
         <v>1</v>
       </c>
       <c r="AY55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB55" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="BC55" t="n">
         <v>0</v>
@@ -26873,76 +26873,76 @@
         <v>1</v>
       </c>
       <c r="BI55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT55" t="n">
         <v>5</v>
       </c>
-      <c r="BK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL55" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM55" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN55" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ55" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR55" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT55" t="n">
-        <v>2</v>
-      </c>
       <c r="BU55" t="n">
         <v>1</v>
       </c>
       <c r="BV55" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="BW55" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="BX55" t="n">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="BY55" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="BZ55" t="n">
-        <v>1.02</v>
+        <v>1.67</v>
       </c>
       <c r="CA55" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="CB55" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="CC55" t="n">
         <v>0</v>
       </c>
       <c r="CD55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE55" t="n">
         <v>0</v>
       </c>
       <c r="CF55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG55" t="n">
         <v>0</v>
@@ -26966,7 +26966,7 @@
         <v>0</v>
       </c>
       <c r="CN55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO55" t="n">
         <v>0</v>
@@ -26978,76 +26978,76 @@
         <v>1</v>
       </c>
       <c r="CR55" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="CS55" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="CT55" t="n">
         <v>1</v>
       </c>
       <c r="CU55" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV55" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX55" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY55" t="n">
         <v>9</v>
       </c>
-      <c r="CV55" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW55" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX55" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY55" t="n">
-        <v>3</v>
-      </c>
       <c r="CZ55" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA55" t="n">
         <v>100</v>
       </c>
       <c r="DB55" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC55" t="n">
         <v>75</v>
       </c>
-      <c r="DC55" t="n">
-        <v>100</v>
-      </c>
       <c r="DD55" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="DE55" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF55" t="n">
         <v>0.5</v>
       </c>
       <c r="DG55" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DH55" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ55" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK55" t="n">
         <v>0</v>
       </c>
       <c r="DL55" t="n">
-        <v>0.84</v>
+        <v>1.24</v>
       </c>
       <c r="DM55" t="n">
-        <v>2.34</v>
+        <v>0.93</v>
       </c>
       <c r="DN55" t="n">
-        <v>3.18</v>
+        <v>2.17</v>
       </c>
       <c r="DO55" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27059,10 +27059,10 @@
         <v>1</v>
       </c>
       <c r="DS55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU55" t="b">
         <v>0</v>
@@ -27071,87 +27071,99 @@
         <v>1</v>
       </c>
       <c r="DW55" t="n">
-        <v>22.21</v>
+        <v>27.52</v>
       </c>
       <c r="DX55" t="n">
-        <v>8.289999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="DY55" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="DZ55" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA55" t="inlineStr">
         <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EB55" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EB55" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
       <c r="EC55" t="inlineStr">
         <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="ED55" t="inlineStr"/>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="ED55" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="EE55" t="inlineStr">
         <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EF55" t="inlineStr"/>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EF55" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
       <c r="EG55" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EH55" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EI55" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EJ55" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EK55" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EL55" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EM55" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EN55" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EO55" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EP55" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -27171,12 +27183,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -27186,25 +27198,25 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -27216,119 +27228,119 @@
         <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S56" t="n">
+        <v>9</v>
+      </c>
+      <c r="T56" t="n">
         <v>14</v>
       </c>
-      <c r="T56" t="n">
-        <v>7</v>
-      </c>
       <c r="U56" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V56" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="W56" t="n">
         <v>17</v>
       </c>
       <c r="X56" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Y56" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="Z56" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Estadio Ramón Sánchez Pizjuán</t>
+          <t>Estadio Ciudad de Valencia</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Avenida de Eduardo Dato, Sevilla</t>
+          <t>Calle San Vicente de Paúl 44, Valencia</t>
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE56" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="AF56" t="n">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="AG56" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI56" t="n">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="AJ56" t="n">
-        <v>3.4</v>
+        <v>2.07</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL56" t="n">
         <v>2</v>
       </c>
       <c r="AM56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN56" t="n">
         <v>1.5</v>
       </c>
-      <c r="AN56" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AO56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP56" t="n">
         <v>2.38</v>
       </c>
-      <c r="AP56" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AQ56" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AR56" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.72</v>
+        <v>4.05</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AU56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV56" t="n">
         <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX56" t="n">
         <v>1</v>
       </c>
       <c r="AY56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB56" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="BC56" t="n">
         <v>0</v>
@@ -27349,76 +27361,76 @@
         <v>1</v>
       </c>
       <c r="BI56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL56" t="n">
         <v>2</v>
       </c>
       <c r="BM56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BN56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO56" t="n">
         <v>0</v>
       </c>
       <c r="BP56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU56" t="n">
         <v>1</v>
       </c>
       <c r="BV56" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="BW56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="BX56" t="n">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="BY56" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="BZ56" t="n">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
       <c r="CA56" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="CB56" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="CC56" t="n">
         <v>0</v>
       </c>
       <c r="CD56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE56" t="n">
         <v>0</v>
       </c>
       <c r="CF56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG56" t="n">
         <v>0</v>
@@ -27442,7 +27454,7 @@
         <v>0</v>
       </c>
       <c r="CN56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO56" t="n">
         <v>0</v>
@@ -27454,76 +27466,76 @@
         <v>1</v>
       </c>
       <c r="CR56" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="CS56" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="CT56" t="n">
         <v>1</v>
       </c>
       <c r="CU56" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="CV56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CW56" t="n">
         <v>1</v>
       </c>
       <c r="CX56" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY56" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CZ56" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA56" t="n">
         <v>100</v>
       </c>
       <c r="DB56" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="DC56" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.17</v>
+        <v>0.17</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="DF56" t="n">
         <v>0.5</v>
       </c>
       <c r="DG56" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DH56" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="DI56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ56" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK56" t="n">
         <v>0</v>
       </c>
       <c r="DL56" t="n">
-        <v>1.24</v>
+        <v>0.84</v>
       </c>
       <c r="DM56" t="n">
-        <v>0.93</v>
+        <v>2.34</v>
       </c>
       <c r="DN56" t="n">
-        <v>2.17</v>
+        <v>3.18</v>
       </c>
       <c r="DO56" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27535,10 +27547,10 @@
         <v>1</v>
       </c>
       <c r="DS56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU56" t="b">
         <v>0</v>
@@ -27547,99 +27559,87 @@
         <v>1</v>
       </c>
       <c r="DW56" t="n">
-        <v>27.52</v>
+        <v>22.21</v>
       </c>
       <c r="DX56" t="n">
-        <v>3.08</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DY56" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ56" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="EA56" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EB56" t="inlineStr"/>
+      <c r="EC56" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="ED56" t="inlineStr"/>
+      <c r="EE56" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF56" t="inlineStr"/>
+      <c r="EG56" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH56" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI56" t="inlineStr">
+        <is>
+          <t>5.86</t>
+        </is>
+      </c>
+      <c r="EJ56" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="EK56" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL56" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EB56" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EC56" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="ED56" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EE56" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF56" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG56" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EH56" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EI56" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EJ56" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="EK56" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EL56" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
       <c r="EM56" t="inlineStr">
         <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN56" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EO56" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EP56" t="inlineStr">
+        <is>
           <t>1.68</t>
-        </is>
-      </c>
-      <c r="EN56" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EO56" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EP56" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -28446,7 +28446,7 @@
         <v>84</v>
       </c>
       <c r="DD58" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE58" t="n">
         <v>1.25</v>
@@ -28934,7 +28934,7 @@
         <v>100</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE59" t="n">
         <v>0.43</v>
@@ -28967,7 +28967,7 @@
         <v>3.85</v>
       </c>
       <c r="DO59" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29903,7 +29903,7 @@
         <v>3.12</v>
       </c>
       <c r="DO61" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30338,10 +30338,10 @@
         <v>100</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE62" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DF62" t="n">
         <v>0</v>
@@ -30371,7 +30371,7 @@
         <v>2.32</v>
       </c>
       <c r="DO62" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP62" t="b">
         <v>0</v>
@@ -30859,7 +30859,7 @@
         <v>2.16</v>
       </c>
       <c r="DO63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31286,10 +31286,10 @@
         <v>100</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE64" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DF64" t="n">
         <v>2.33</v>
@@ -31319,7 +31319,7 @@
         <v>4.16</v>
       </c>
       <c r="DO64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -32233,7 +32233,7 @@
         <v>2.71</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="DF66" t="n">
         <v>3</v>
@@ -32263,7 +32263,7 @@
         <v>4.16</v>
       </c>
       <c r="DO66" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -33187,7 +33187,7 @@
         <v>2.52</v>
       </c>
       <c r="DO68" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33651,7 +33651,7 @@
         <v>3.83</v>
       </c>
       <c r="DO69" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34111,7 +34111,7 @@
         <v>2.27</v>
       </c>
       <c r="DO70" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34569,7 +34569,7 @@
         <v>1.57</v>
       </c>
       <c r="DE71" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DF71" t="n">
         <v>2.33</v>
@@ -35555,7 +35555,7 @@
         <v>2.02</v>
       </c>
       <c r="DO73" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -36010,7 +36010,7 @@
         <v>88</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE74" t="n">
         <v>0.33</v>
@@ -36531,7 +36531,7 @@
         <v>3.06</v>
       </c>
       <c r="DO75" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36969,7 +36969,7 @@
         <v>3</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF76" t="n">
         <v>3</v>
@@ -36999,7 +36999,7 @@
         <v>3.16</v>
       </c>
       <c r="DO76" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -37894,7 +37894,7 @@
         <v>100</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DE78" t="n">
         <v>1.86</v>
@@ -37927,7 +37927,7 @@
         <v>3.75</v>
       </c>
       <c r="DO78" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38365,7 +38365,7 @@
         <v>2</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF79" t="n">
         <v>2.5</v>
@@ -38395,7 +38395,7 @@
         <v>3.25</v>
       </c>
       <c r="DO79" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -38850,7 +38850,7 @@
         <v>71</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE80" t="n">
         <v>1.25</v>
@@ -39322,7 +39322,7 @@
         <v>59</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE81" t="n">
         <v>1.5</v>
@@ -39355,7 +39355,7 @@
         <v>3.36</v>
       </c>
       <c r="DO81" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -39797,7 +39797,7 @@
         <v>0.71</v>
       </c>
       <c r="DE82" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DF82" t="n">
         <v>0.75</v>
@@ -39827,7 +39827,7 @@
         <v>2.32</v>
       </c>
       <c r="DO82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40278,7 +40278,7 @@
         <v>88</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DE83" t="n">
         <v>0.43</v>
@@ -40311,7 +40311,7 @@
         <v>2.72</v>
       </c>
       <c r="DO83" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -40771,7 +40771,7 @@
         <v>3.49</v>
       </c>
       <c r="DO84" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41201,7 +41201,7 @@
         <v>2.71</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF85" t="n">
         <v>3</v>
@@ -41231,7 +41231,7 @@
         <v>3.94</v>
       </c>
       <c r="DO85" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41670,7 +41670,7 @@
         <v>75</v>
       </c>
       <c r="DD86" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE86" t="n">
         <v>0.25</v>
@@ -41703,7 +41703,7 @@
         <v>2.53</v>
       </c>
       <c r="DO86" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42161,7 +42161,7 @@
         <v>1.86</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="DF87" t="n">
         <v>2.5</v>
@@ -42191,7 +42191,7 @@
         <v>3.24</v>
       </c>
       <c r="DO87" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -42618,7 +42618,7 @@
         <v>68</v>
       </c>
       <c r="DD88" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE88" t="n">
         <v>0.86</v>
@@ -42651,7 +42651,7 @@
         <v>3.09</v>
       </c>
       <c r="DO88" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43106,7 +43106,7 @@
         <v>80</v>
       </c>
       <c r="DD89" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DE89" t="n">
         <v>1.25</v>
@@ -43581,7 +43581,7 @@
         <v>1.57</v>
       </c>
       <c r="DE90" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DF90" t="n">
         <v>1.67</v>
@@ -43611,7 +43611,7 @@
         <v>3.13</v>
       </c>
       <c r="DO90" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44526,7 +44526,7 @@
         <v>63</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE92" t="n">
         <v>1.29</v>
@@ -44559,7 +44559,7 @@
         <v>2.81</v>
       </c>
       <c r="DO92" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45006,10 +45006,10 @@
         <v>90</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DF93" t="n">
         <v>0.8</v>
@@ -45039,7 +45039,7 @@
         <v>2.1</v>
       </c>
       <c r="DO93" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -45527,7 +45527,7 @@
         <v>2.42</v>
       </c>
       <c r="DO94" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46011,7 +46011,7 @@
         <v>2.58</v>
       </c>
       <c r="DO95" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46457,7 +46457,7 @@
         <v>1.57</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF96" t="n">
         <v>1.75</v>
@@ -46967,7 +46967,7 @@
         <v>2.31</v>
       </c>
       <c r="DO97" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -47447,7 +47447,7 @@
         <v>3</v>
       </c>
       <c r="DO98" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -47919,7 +47919,7 @@
         <v>4.52</v>
       </c>
       <c r="DO99" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -48379,7 +48379,7 @@
         <v>2.21</v>
       </c>
       <c r="DO100" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -49323,7 +49323,7 @@
         <v>2.07</v>
       </c>
       <c r="DO102" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -50234,7 +50234,7 @@
         <v>80</v>
       </c>
       <c r="DD104" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE104" t="n">
         <v>1.29</v>
@@ -50267,7 +50267,7 @@
         <v>2.79</v>
       </c>
       <c r="DO104" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -50702,10 +50702,10 @@
         <v>30</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE105" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="DF105" t="n">
         <v>1.4</v>
@@ -50735,7 +50735,7 @@
         <v>2.92</v>
       </c>
       <c r="DO105" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -51646,7 +51646,7 @@
         <v>88</v>
       </c>
       <c r="DD107" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DE107" t="n">
         <v>1.83</v>
@@ -51679,7 +51679,7 @@
         <v>2.18</v>
       </c>
       <c r="DO107" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -52137,7 +52137,7 @@
         <v>1.57</v>
       </c>
       <c r="DE108" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DF108" t="n">
         <v>1.6</v>
@@ -52167,7 +52167,7 @@
         <v>3.06</v>
       </c>
       <c r="DO108" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -53087,7 +53087,7 @@
         <v>2.91</v>
       </c>
       <c r="DO110" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -53575,7 +53575,7 @@
         <v>1.9</v>
       </c>
       <c r="DO111" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP111" t="b">
         <v>0</v>
@@ -54051,7 +54051,7 @@
         <v>3.11</v>
       </c>
       <c r="DO112" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -54502,7 +54502,7 @@
         <v>62</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE113" t="n">
         <v>0.57</v>
@@ -54535,7 +54535,7 @@
         <v>2.36</v>
       </c>
       <c r="DO113" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -54986,7 +54986,7 @@
         <v>67</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DE114" t="n">
         <v>0.25</v>
@@ -55019,7 +55019,7 @@
         <v>2.35</v>
       </c>
       <c r="DO114" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -55454,7 +55454,7 @@
         <v>75</v>
       </c>
       <c r="DD115" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE115" t="n">
         <v>1</v>
@@ -55487,7 +55487,7 @@
         <v>3.1</v>
       </c>
       <c r="DO115" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -55917,7 +55917,7 @@
         <v>2</v>
       </c>
       <c r="DE116" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF116" t="n">
         <v>2.17</v>
@@ -55947,7 +55947,7 @@
         <v>2.69</v>
       </c>
       <c r="DO116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -56405,7 +56405,7 @@
         <v>1.86</v>
       </c>
       <c r="DE117" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DF117" t="n">
         <v>1.67</v>
@@ -56435,7 +56435,7 @@
         <v>2.5</v>
       </c>
       <c r="DO117" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -56873,7 +56873,7 @@
         <v>1.2</v>
       </c>
       <c r="DE118" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DF118" t="n">
         <v>1.25</v>
@@ -57801,7 +57801,7 @@
         <v>1.57</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF120" t="n">
         <v>1.4</v>
@@ -58278,7 +58278,7 @@
         <v>84</v>
       </c>
       <c r="DD121" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE121" t="n">
         <v>1.86</v>
@@ -58311,7 +58311,7 @@
         <v>3.7</v>
       </c>
       <c r="DO121" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -59259,7 +59259,7 @@
         <v>2.7</v>
       </c>
       <c r="DO123" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -59673,7 +59673,7 @@
         <v>3</v>
       </c>
       <c r="DE124" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="DF124" t="n">
         <v>3</v>
@@ -59703,7 +59703,7 @@
         <v>3.71</v>
       </c>
       <c r="DO124" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -60163,7 +60163,7 @@
         <v>2.9</v>
       </c>
       <c r="DO125" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -60631,7 +60631,7 @@
         <v>3.29</v>
       </c>
       <c r="DO126" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -61575,7 +61575,7 @@
         <v>2.72</v>
       </c>
       <c r="DO128" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -62035,7 +62035,7 @@
         <v>2.46</v>
       </c>
       <c r="DO129" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -62481,7 +62481,7 @@
         <v>1.86</v>
       </c>
       <c r="DE130" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DF130" t="n">
         <v>2</v>
@@ -62511,7 +62511,7 @@
         <v>3.72</v>
       </c>
       <c r="DO130" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -62987,7 +62987,7 @@
         <v>2.6</v>
       </c>
       <c r="DO131" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -63649,10 +63649,10 @@
         <v>15</v>
       </c>
       <c r="Y133" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Z133" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AA133" t="inlineStr"/>
       <c r="AB133" t="inlineStr"/>
@@ -63968,40 +63968,40 @@
       </c>
       <c r="EA133" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="EB133" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EC133" t="inlineStr"/>
       <c r="ED133" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EE133" t="inlineStr"/>
       <c r="EF133" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EG133" t="inlineStr"/>
       <c r="EH133" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="EI133" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EJ133" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EK133" t="inlineStr">
@@ -64026,12 +64026,12 @@
       </c>
       <c r="EO133" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EP133" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -64096,13 +64096,13 @@
         <v>6</v>
       </c>
       <c r="R134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S134" t="n">
         <v>12</v>
       </c>
       <c r="T134" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U134" t="n">
         <v>18</v>
@@ -64275,10 +64275,10 @@
         <v>2.02</v>
       </c>
       <c r="CA134" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="CB134" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="CC134" t="n">
         <v>0</v>
@@ -64436,62 +64436,2910 @@
       </c>
       <c r="EA134" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EB134" t="inlineStr"/>
       <c r="EC134" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="ED134" t="inlineStr"/>
       <c r="EE134" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF134" t="inlineStr"/>
       <c r="EG134" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EH134" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="EI134" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="EJ134" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EK134" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EL134" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EM134" t="inlineStr"/>
       <c r="EN134" t="inlineStr"/>
       <c r="EO134" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EP134" t="inlineStr">
         <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>14</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Athletic Club Bilbao</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>45990.72916666666</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>2</v>
+      </c>
+      <c r="I135" t="n">
+        <v>2</v>
+      </c>
+      <c r="J135" t="n">
+        <v>4</v>
+      </c>
+      <c r="K135" t="n">
+        <v>2</v>
+      </c>
+      <c r="L135" t="n">
+        <v>6</v>
+      </c>
+      <c r="M135" t="n">
+        <v>3</v>
+      </c>
+      <c r="N135" t="n">
+        <v>2</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>4</v>
+      </c>
+      <c r="R135" t="n">
+        <v>4</v>
+      </c>
+      <c r="S135" t="n">
+        <v>7</v>
+      </c>
+      <c r="T135" t="n">
+        <v>10</v>
+      </c>
+      <c r="U135" t="n">
+        <v>11</v>
+      </c>
+      <c r="V135" t="n">
+        <v>14</v>
+      </c>
+      <c r="W135" t="n">
+        <v>11</v>
+      </c>
+      <c r="X135" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>Estadio Ciudad de Valencia</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>Calle San Vicente de Paúl 44, Valencia</t>
+        </is>
+      </c>
+      <c r="AC135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>285</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>95</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>118</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU135" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV135" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX135" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY135" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ135" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA135" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB135" t="n">
+        <v>57</v>
+      </c>
+      <c r="DC135" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD135" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DE135" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DG135" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH135" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="DI135" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DJ135" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK135" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL135" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DM135" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DN135" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="DO135" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW135" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="DX135" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="DY135" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="DZ135" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="EA135" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EB135" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EC135" t="inlineStr"/>
+      <c r="ED135" t="inlineStr"/>
+      <c r="EE135" t="inlineStr"/>
+      <c r="EF135" t="inlineStr"/>
+      <c r="EG135" t="inlineStr"/>
+      <c r="EH135" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EI135" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="EJ135" t="inlineStr">
+        <is>
+          <t>3.96</t>
+        </is>
+      </c>
+      <c r="EK135" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EL135" t="inlineStr">
+        <is>
           <t>1.93</t>
+        </is>
+      </c>
+      <c r="EM135" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EN135" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EO135" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EP135" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>14</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>45990.83333333334</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>2</v>
+      </c>
+      <c r="J136" t="n">
+        <v>7</v>
+      </c>
+      <c r="K136" t="n">
+        <v>2</v>
+      </c>
+      <c r="L136" t="n">
+        <v>9</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>1</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>8</v>
+      </c>
+      <c r="R136" t="n">
+        <v>1</v>
+      </c>
+      <c r="S136" t="n">
+        <v>6</v>
+      </c>
+      <c r="T136" t="n">
+        <v>11</v>
+      </c>
+      <c r="U136" t="n">
+        <v>14</v>
+      </c>
+      <c r="V136" t="n">
+        <v>12</v>
+      </c>
+      <c r="W136" t="n">
+        <v>5</v>
+      </c>
+      <c r="X136" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>Estadio Wanda Metropolitano</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>Rosas, Madrid</t>
+        </is>
+      </c>
+      <c r="AC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>117</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>45</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>54</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>103</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>96</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU136" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV136" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX136" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY136" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ136" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA136" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB136" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC136" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD136" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DE136" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DF136" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DG136" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH136" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DI136" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="DJ136" t="n">
+        <v>55</v>
+      </c>
+      <c r="DK136" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL136" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DM136" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DN136" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="DO136" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW136" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="DX136" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="DY136" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="DZ136" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA136" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EB136" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EC136" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="ED136" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EE136" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EF136" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EG136" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EH136" t="inlineStr">
+        <is>
+          <t>12.97</t>
+        </is>
+      </c>
+      <c r="EI136" t="inlineStr">
+        <is>
+          <t>6.23</t>
+        </is>
+      </c>
+      <c r="EJ136" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EK136" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EL136" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EM136" t="inlineStr"/>
+      <c r="EN136" t="inlineStr"/>
+      <c r="EO136" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EP136" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>14</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>45991.54166666666</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2</v>
+      </c>
+      <c r="H137" t="n">
+        <v>3</v>
+      </c>
+      <c r="I137" t="n">
+        <v>5</v>
+      </c>
+      <c r="J137" t="n">
+        <v>8</v>
+      </c>
+      <c r="K137" t="n">
+        <v>2</v>
+      </c>
+      <c r="L137" t="n">
+        <v>10</v>
+      </c>
+      <c r="M137" t="n">
+        <v>3</v>
+      </c>
+      <c r="N137" t="n">
+        <v>7</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>7</v>
+      </c>
+      <c r="R137" t="n">
+        <v>5</v>
+      </c>
+      <c r="S137" t="n">
+        <v>11</v>
+      </c>
+      <c r="T137" t="n">
+        <v>5</v>
+      </c>
+      <c r="U137" t="n">
+        <v>18</v>
+      </c>
+      <c r="V137" t="n">
+        <v>10</v>
+      </c>
+      <c r="W137" t="n">
+        <v>15</v>
+      </c>
+      <c r="X137" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Anoeta</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
+        </is>
+      </c>
+      <c r="AC137" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>76</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>142</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU137" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV137" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX137" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY137" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ137" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA137" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB137" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC137" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD137" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DE137" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DF137" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG137" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DH137" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DI137" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DJ137" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK137" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL137" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DM137" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DN137" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DO137" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW137" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="DX137" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="DY137" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="DZ137" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="EA137" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EB137" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EC137" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="ED137" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EE137" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EF137" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EG137" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EH137" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EI137" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EJ137" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="EK137" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EL137" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EM137" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EN137" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EO137" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EP137" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>14</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Sevilla FC</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>45991.63541666666</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>2</v>
+      </c>
+      <c r="I138" t="n">
+        <v>2</v>
+      </c>
+      <c r="J138" t="n">
+        <v>6</v>
+      </c>
+      <c r="K138" t="n">
+        <v>4</v>
+      </c>
+      <c r="L138" t="n">
+        <v>10</v>
+      </c>
+      <c r="M138" t="n">
+        <v>2</v>
+      </c>
+      <c r="N138" t="n">
+        <v>3</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>3</v>
+      </c>
+      <c r="R138" t="n">
+        <v>4</v>
+      </c>
+      <c r="S138" t="n">
+        <v>6</v>
+      </c>
+      <c r="T138" t="n">
+        <v>5</v>
+      </c>
+      <c r="U138" t="n">
+        <v>9</v>
+      </c>
+      <c r="V138" t="n">
+        <v>9</v>
+      </c>
+      <c r="W138" t="n">
+        <v>14</v>
+      </c>
+      <c r="X138" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>Estadio Ramón Sánchez Pizjuán</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>Avenida de Eduardo Dato, Sevilla</t>
+        </is>
+      </c>
+      <c r="AC138" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>284</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>92</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>121</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>57</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU138" t="n">
+        <v>22</v>
+      </c>
+      <c r="CV138" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX138" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY138" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ138" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA138" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB138" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC138" t="n">
+        <v>83</v>
+      </c>
+      <c r="DD138" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE138" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DF138" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DG138" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH138" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DI138" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DJ138" t="n">
+        <v>34</v>
+      </c>
+      <c r="DK138" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL138" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DM138" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DN138" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="DO138" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP138" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ138" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW138" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="DX138" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="DY138" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="DZ138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA138" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EB138" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EC138" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="ED138" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EE138" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EF138" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="EG138" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EH138" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="EI138" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EJ138" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="EK138" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EL138" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EM138" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EN138" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EO138" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EP138" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>14</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>RCD Espanyol</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>45991.72916666666</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" t="n">
+        <v>4</v>
+      </c>
+      <c r="K139" t="n">
+        <v>3</v>
+      </c>
+      <c r="L139" t="n">
+        <v>7</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1</v>
+      </c>
+      <c r="N139" t="n">
+        <v>2</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>4</v>
+      </c>
+      <c r="R139" t="n">
+        <v>2</v>
+      </c>
+      <c r="S139" t="n">
+        <v>7</v>
+      </c>
+      <c r="T139" t="n">
+        <v>7</v>
+      </c>
+      <c r="U139" t="n">
+        <v>11</v>
+      </c>
+      <c r="V139" t="n">
+        <v>9</v>
+      </c>
+      <c r="W139" t="n">
+        <v>12</v>
+      </c>
+      <c r="X139" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA139" t="inlineStr"/>
+      <c r="AB139" t="inlineStr"/>
+      <c r="AC139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>280</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>122</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>89</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU139" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV139" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX139" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY139" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ139" t="n">
+        <v>27</v>
+      </c>
+      <c r="DA139" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB139" t="n">
+        <v>27</v>
+      </c>
+      <c r="DC139" t="n">
+        <v>66</v>
+      </c>
+      <c r="DD139" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DE139" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF139" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DG139" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH139" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DI139" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DJ139" t="n">
+        <v>73</v>
+      </c>
+      <c r="DK139" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL139" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DM139" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DN139" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="DO139" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW139" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="DX139" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="DY139" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="DZ139" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="EA139" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EB139" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC139" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="ED139" t="inlineStr"/>
+      <c r="EE139" t="inlineStr"/>
+      <c r="EF139" t="inlineStr"/>
+      <c r="EG139" t="inlineStr"/>
+      <c r="EH139" t="inlineStr">
+        <is>
+          <t>4.43</t>
+        </is>
+      </c>
+      <c r="EI139" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="EJ139" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EK139" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EL139" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EM139" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EN139" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EO139" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EP139" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>14</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Girona FC</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>45991.83333333334</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" t="n">
+        <v>2</v>
+      </c>
+      <c r="J140" t="n">
+        <v>2</v>
+      </c>
+      <c r="K140" t="n">
+        <v>5</v>
+      </c>
+      <c r="L140" t="n">
+        <v>7</v>
+      </c>
+      <c r="M140" t="n">
+        <v>3</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>4</v>
+      </c>
+      <c r="R140" t="n">
+        <v>4</v>
+      </c>
+      <c r="S140" t="n">
+        <v>6</v>
+      </c>
+      <c r="T140" t="n">
+        <v>21</v>
+      </c>
+      <c r="U140" t="n">
+        <v>10</v>
+      </c>
+      <c r="V140" t="n">
+        <v>25</v>
+      </c>
+      <c r="W140" t="n">
+        <v>9</v>
+      </c>
+      <c r="X140" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>Estadi Municipal de Montilivi</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>Avenida Montlivi 141, Girona</t>
+        </is>
+      </c>
+      <c r="AC140" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>106</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU140" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV140" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX140" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY140" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ140" t="n">
+        <v>64</v>
+      </c>
+      <c r="DA140" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB140" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC140" t="n">
+        <v>72</v>
+      </c>
+      <c r="DD140" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DE140" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DF140" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DG140" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH140" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DI140" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DJ140" t="n">
+        <v>36</v>
+      </c>
+      <c r="DK140" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL140" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DM140" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DN140" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="DO140" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW140" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="DX140" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="DY140" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="DZ140" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA140" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EB140" t="inlineStr"/>
+      <c r="EC140" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="ED140" t="inlineStr"/>
+      <c r="EE140" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EF140" t="inlineStr"/>
+      <c r="EG140" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH140" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EI140" t="inlineStr">
+        <is>
+          <t>5.69</t>
+        </is>
+      </c>
+      <c r="EJ140" t="inlineStr">
+        <is>
+          <t>6.99</t>
+        </is>
+      </c>
+      <c r="EK140" t="inlineStr"/>
+      <c r="EL140" t="inlineStr"/>
+      <c r="EM140" t="inlineStr"/>
+      <c r="EN140" t="inlineStr"/>
+      <c r="EO140" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EP140" t="inlineStr">
+        <is>
+          <t>1.60</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP140" headerRowCount="1">
-  <autoFilter ref="A1:EP140"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP143" headerRowCount="1">
+  <autoFilter ref="A1:EP143"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP140"/>
+  <dimension ref="A1:EP143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -3267,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -4638,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DE8" t="n">
         <v>1.29</v>
@@ -5125,7 +5125,7 @@
         <v>2</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -8473,7 +8473,7 @@
         <v>1.67</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9881,7 +9881,7 @@
         <v>0.71</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -10350,7 +10350,7 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DE20" t="n">
         <v>1.25</v>
@@ -10383,7 +10383,7 @@
         <v>3.14</v>
       </c>
       <c r="DO20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -12295,7 +12295,7 @@
         <v>2.77</v>
       </c>
       <c r="DO24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12741,7 +12741,7 @@
         <v>1.57</v>
       </c>
       <c r="DE25" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF25" t="n">
         <v>3</v>
@@ -16062,7 +16062,7 @@
         <v>50</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="DE32" t="n">
         <v>1.86</v>
@@ -16095,7 +16095,7 @@
         <v>2.84</v>
       </c>
       <c r="DO32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -17485,7 +17485,7 @@
         <v>1.43</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DF35" t="n">
         <v>1</v>
@@ -17962,7 +17962,7 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DE36" t="n">
         <v>0.57</v>
@@ -19919,7 +19919,7 @@
         <v>2.95</v>
       </c>
       <c r="DO40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20365,7 +20365,7 @@
         <v>3</v>
       </c>
       <c r="DE41" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="DF41" t="n">
         <v>0</v>
@@ -20395,7 +20395,7 @@
         <v>0.57</v>
       </c>
       <c r="DO41" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -22391,170 +22391,170 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
         <v>45920.6875</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
         <v>3</v>
       </c>
       <c r="J46" t="n">
+        <v>4</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4</v>
+      </c>
+      <c r="L46" t="n">
+        <v>8</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
         <v>7</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>5</v>
+      </c>
+      <c r="R46" t="n">
+        <v>3</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
+        <v>8</v>
+      </c>
+      <c r="V46" t="n">
+        <v>9</v>
+      </c>
+      <c r="W46" t="n">
+        <v>20</v>
+      </c>
+      <c r="X46" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Estadio de Mendizorroza</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+        </is>
+      </c>
+      <c r="AC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="n">
         <v>7</v>
       </c>
-      <c r="M46" t="n">
-        <v>2</v>
-      </c>
-      <c r="N46" t="n">
-        <v>2</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>8</v>
-      </c>
-      <c r="R46" t="n">
-        <v>3</v>
-      </c>
-      <c r="S46" t="n">
-        <v>18</v>
-      </c>
-      <c r="T46" t="n">
-        <v>3</v>
-      </c>
-      <c r="U46" t="n">
-        <v>26</v>
-      </c>
-      <c r="V46" t="n">
-        <v>6</v>
-      </c>
-      <c r="W46" t="n">
-        <v>10</v>
-      </c>
-      <c r="X46" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>66</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>Estadio de la Cerámica</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>Plaza Labrador, Villarreal</t>
-        </is>
-      </c>
-      <c r="AC46" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>3</v>
-      </c>
       <c r="AE46" t="n">
-        <v>1.55</v>
+        <v>2.33</v>
       </c>
       <c r="AF46" t="n">
-        <v>3.8</v>
+        <v>3.01</v>
       </c>
       <c r="AG46" t="n">
-        <v>5.25</v>
+        <v>3.28</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.01</v>
+        <v>2.43</v>
       </c>
       <c r="AJ46" t="n">
-        <v>3.05</v>
+        <v>4.85</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AN46" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AO46" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AP46" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AU46" t="n">
         <v>3</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW46" t="n">
         <v>1</v>
       </c>
       <c r="AX46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB46" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="BC46" t="n">
         <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BE46" t="n">
         <v>0</v>
@@ -22572,175 +22572,175 @@
         <v>1</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK46" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT46" t="n">
         <v>6</v>
       </c>
-      <c r="BL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN46" t="n">
+      <c r="BU46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV46" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CB46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR46" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS46" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU46" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV46" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX46" t="n">
         <v>6</v>
       </c>
-      <c r="BO46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP46" t="n">
-        <v>3</v>
-      </c>
-      <c r="BQ46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS46" t="n">
+      <c r="CY46" t="n">
         <v>4</v>
       </c>
-      <c r="BT46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV46" t="n">
-        <v>90</v>
-      </c>
-      <c r="BW46" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX46" t="n">
-        <v>112</v>
-      </c>
-      <c r="BY46" t="n">
-        <v>57</v>
-      </c>
-      <c r="BZ46" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CA46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB46" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="CC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS46" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU46" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV46" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX46" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY46" t="n">
-        <v>20</v>
-      </c>
       <c r="CZ46" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DA46" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB46" t="n">
         <v>50</v>
       </c>
       <c r="DC46" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>2.71</v>
+        <v>1.57</v>
       </c>
       <c r="DE46" t="n">
-        <v>0.25</v>
+        <v>1.29</v>
       </c>
       <c r="DF46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DG46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DH46" t="n">
         <v>1.75</v>
       </c>
       <c r="DI46" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DJ46" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK46" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL46" t="n">
-        <v>2.48</v>
+        <v>1.19</v>
       </c>
       <c r="DM46" t="n">
-        <v>0.71</v>
+        <v>1.32</v>
       </c>
       <c r="DN46" t="n">
-        <v>3.19</v>
+        <v>2.51</v>
       </c>
       <c r="DO46" t="n">
         <v>14</v>
@@ -22767,99 +22767,87 @@
         <v>1</v>
       </c>
       <c r="DW46" t="n">
-        <v>27.48</v>
+        <v>27.45</v>
       </c>
       <c r="DX46" t="n">
-        <v>4.71</v>
+        <v>4.36</v>
       </c>
       <c r="DY46" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="DZ46" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="EA46" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EB46" t="inlineStr">
         <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC46" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
-      </c>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EC46" t="inlineStr"/>
       <c r="ED46" t="inlineStr">
         <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE46" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EE46" t="inlineStr"/>
       <c r="EF46" t="inlineStr">
         <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="EG46" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EG46" t="inlineStr"/>
       <c r="EH46" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="EI46" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EJ46" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="EK46" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EL46" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EM46" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EN46" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="EO46" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EP46" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.16</t>
         </is>
       </c>
     </row>
@@ -22879,170 +22867,170 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
         <v>45920.6875</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
+        <v>7</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
         <v>8</v>
       </c>
-      <c r="M47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" t="n">
-        <v>7</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>5</v>
-      </c>
       <c r="R47" t="n">
         <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>26</v>
+      </c>
+      <c r="V47" t="n">
         <v>6</v>
       </c>
-      <c r="U47" t="n">
-        <v>8</v>
-      </c>
-      <c r="V47" t="n">
-        <v>9</v>
-      </c>
       <c r="W47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="X47" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Y47" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="Z47" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Estadio de Mendizorroza</t>
+          <t>Estadio de la Cerámica</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+          <t>Plaza Labrador, Villarreal</t>
         </is>
       </c>
       <c r="AC47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD47" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.33</v>
+        <v>1.55</v>
       </c>
       <c r="AF47" t="n">
-        <v>3.01</v>
+        <v>3.8</v>
       </c>
       <c r="AG47" t="n">
-        <v>3.28</v>
+        <v>5.25</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.43</v>
+        <v>2.01</v>
       </c>
       <c r="AJ47" t="n">
-        <v>4.85</v>
+        <v>3.05</v>
       </c>
       <c r="AK47" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AO47" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AP47" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AR47" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AU47" t="n">
         <v>3</v>
       </c>
       <c r="AV47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
         <v>1</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB47" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="BC47" t="n">
         <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
         <v>0</v>
@@ -23060,73 +23048,73 @@
         <v>1</v>
       </c>
       <c r="BJ47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BL47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BN47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ47" t="n">
         <v>1</v>
       </c>
       <c r="BR47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BS47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BT47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BU47" t="n">
         <v>1</v>
       </c>
       <c r="BV47" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="BW47" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="BX47" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="BY47" t="n">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="BZ47" t="n">
-        <v>1.22</v>
+        <v>2.84</v>
       </c>
       <c r="CA47" t="n">
-        <v>1.08</v>
+        <v>0.75</v>
       </c>
       <c r="CB47" t="n">
-        <v>2.3</v>
+        <v>3.58</v>
       </c>
       <c r="CC47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG47" t="n">
         <v>0</v>
@@ -23144,13 +23132,13 @@
         <v>0</v>
       </c>
       <c r="CL47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM47" t="n">
         <v>0</v>
       </c>
       <c r="CN47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO47" t="n">
         <v>0</v>
@@ -23162,73 +23150,73 @@
         <v>1</v>
       </c>
       <c r="CR47" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="CS47" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="CT47" t="n">
         <v>1</v>
       </c>
       <c r="CU47" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="CV47" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX47" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY47" t="n">
         <v>20</v>
       </c>
-      <c r="CW47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX47" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY47" t="n">
-        <v>4</v>
-      </c>
       <c r="CZ47" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA47" t="n">
         <v>50</v>
-      </c>
-      <c r="DA47" t="n">
-        <v>100</v>
       </c>
       <c r="DB47" t="n">
         <v>50</v>
       </c>
       <c r="DC47" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.57</v>
+        <v>2.71</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DH47" t="n">
         <v>1.75</v>
       </c>
       <c r="DI47" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DJ47" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK47" t="n">
         <v>50</v>
       </c>
-      <c r="DK47" t="n">
-        <v>0</v>
-      </c>
       <c r="DL47" t="n">
-        <v>1.19</v>
+        <v>2.48</v>
       </c>
       <c r="DM47" t="n">
-        <v>1.32</v>
+        <v>0.71</v>
       </c>
       <c r="DN47" t="n">
-        <v>2.51</v>
+        <v>3.19</v>
       </c>
       <c r="DO47" t="n">
         <v>14</v>
@@ -23255,87 +23243,99 @@
         <v>1</v>
       </c>
       <c r="DW47" t="n">
-        <v>27.45</v>
+        <v>27.48</v>
       </c>
       <c r="DX47" t="n">
-        <v>4.36</v>
+        <v>4.71</v>
       </c>
       <c r="DY47" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ47" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="EA47" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EB47" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EC47" t="inlineStr"/>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EC47" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
       <c r="ED47" t="inlineStr">
         <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EE47" t="inlineStr"/>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EE47" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
       <c r="EF47" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="EG47" t="inlineStr"/>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EG47" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
       <c r="EH47" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="EI47" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="EJ47" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EK47" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EL47" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EM47" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EN47" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EO47" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EP47" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -23707,7 +23707,7 @@
         <v>2.96</v>
       </c>
       <c r="DO48" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24150,7 +24150,7 @@
         <v>100</v>
       </c>
       <c r="DD49" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="DE49" t="n">
         <v>1.83</v>
@@ -24183,7 +24183,7 @@
         <v>2.29</v>
       </c>
       <c r="DO49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24633,7 +24633,7 @@
         <v>1.43</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF50" t="n">
         <v>0.5</v>
@@ -25723,40 +25723,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -25765,101 +25765,101 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T53" t="n">
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W53" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="X53" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y53" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="Z53" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>San Mamés Barria</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="AF53" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="AG53" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AJ53" t="n">
-        <v>4.05</v>
+        <v>3.08</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AO53" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AR53" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AU53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV53" t="n">
         <v>0</v>
@@ -25868,13 +25868,13 @@
         <v>1</v>
       </c>
       <c r="AX53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA53" t="n">
         <v>1</v>
@@ -25886,7 +25886,7 @@
         <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BE53" t="n">
         <v>0</v>
@@ -25901,28 +25901,28 @@
         <v>1</v>
       </c>
       <c r="BI53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BJ53" t="n">
         <v>1</v>
       </c>
       <c r="BK53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BN53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ53" t="n">
         <v>0</v>
@@ -25931,7 +25931,7 @@
         <v>2</v>
       </c>
       <c r="BS53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT53" t="n">
         <v>2</v>
@@ -25940,25 +25940,25 @@
         <v>1</v>
       </c>
       <c r="BV53" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="BW53" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BX53" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="BY53" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="BZ53" t="n">
-        <v>2.59</v>
+        <v>1.96</v>
       </c>
       <c r="CA53" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="CB53" t="n">
-        <v>3.26</v>
+        <v>2.71</v>
       </c>
       <c r="CC53" t="n">
         <v>0</v>
@@ -25988,10 +25988,10 @@
         <v>0</v>
       </c>
       <c r="CL53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN53" t="n">
         <v>0</v>
@@ -26006,77 +26006,77 @@
         <v>1</v>
       </c>
       <c r="CR53" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="CS53" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU53" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV53" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX53" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY53" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ53" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA53" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB53" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC53" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD53" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DE53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF53" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DI53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DJ53" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK53" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL53" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM53" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DN53" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="DO53" t="n">
         <v>14</v>
       </c>
-      <c r="CT53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU53" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV53" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX53" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY53" t="n">
-        <v>9</v>
-      </c>
-      <c r="CZ53" t="n">
-        <v>59</v>
-      </c>
-      <c r="DA53" t="n">
-        <v>59</v>
-      </c>
-      <c r="DB53" t="n">
-        <v>17</v>
-      </c>
-      <c r="DC53" t="n">
-        <v>84</v>
-      </c>
-      <c r="DD53" t="n">
-        <v>2</v>
-      </c>
-      <c r="DE53" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DF53" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH53" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI53" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DJ53" t="n">
-        <v>42</v>
-      </c>
-      <c r="DK53" t="n">
-        <v>42</v>
-      </c>
-      <c r="DL53" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="DM53" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="DN53" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="DO53" t="n">
-        <v>13</v>
-      </c>
       <c r="DP53" t="b">
         <v>1</v>
       </c>
@@ -26084,10 +26084,10 @@
         <v>1</v>
       </c>
       <c r="DR53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT53" t="b">
         <v>0</v>
@@ -26099,75 +26099,79 @@
         <v>1</v>
       </c>
       <c r="DW53" t="n">
-        <v>20.5</v>
+        <v>17.43</v>
       </c>
       <c r="DX53" t="n">
-        <v>6.93</v>
+        <v>4.72</v>
       </c>
       <c r="DY53" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="DZ53" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="EA53" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EB53" t="inlineStr">
         <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC53" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED53" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE53" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="EC53" t="inlineStr"/>
-      <c r="ED53" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EE53" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="EF53" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EG53" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="EH53" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="EI53" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="EJ53" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EK53" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EL53" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EM53" t="inlineStr">
@@ -26182,12 +26186,12 @@
       </c>
       <c r="EO53" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EP53" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -26207,143 +26211,143 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
         <v>8</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L54" t="n">
+        <v>11</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>4</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>10</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2</v>
+      </c>
+      <c r="S54" t="n">
+        <v>11</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>21</v>
+      </c>
+      <c r="V54" t="n">
+        <v>5</v>
+      </c>
+      <c r="W54" t="n">
         <v>9</v>
       </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>2</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>5</v>
-      </c>
-      <c r="R54" t="n">
-        <v>3</v>
-      </c>
-      <c r="S54" t="n">
-        <v>12</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3</v>
-      </c>
-      <c r="U54" t="n">
-        <v>17</v>
-      </c>
-      <c r="V54" t="n">
-        <v>6</v>
-      </c>
-      <c r="W54" t="n">
-        <v>19</v>
-      </c>
       <c r="X54" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y54" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="Z54" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>San Mamés Barria</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE54" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ54" t="n">
         <v>1.47</v>
       </c>
-      <c r="AF54" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AR54" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AS54" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AU54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV54" t="n">
         <v>0</v>
@@ -26352,13 +26356,13 @@
         <v>1</v>
       </c>
       <c r="AX54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA54" t="n">
         <v>1</v>
@@ -26370,7 +26374,7 @@
         <v>0</v>
       </c>
       <c r="BD54" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BE54" t="n">
         <v>0</v>
@@ -26385,28 +26389,28 @@
         <v>1</v>
       </c>
       <c r="BI54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BJ54" t="n">
         <v>1</v>
       </c>
       <c r="BK54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BL54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BN54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ54" t="n">
         <v>0</v>
@@ -26415,7 +26419,7 @@
         <v>2</v>
       </c>
       <c r="BS54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT54" t="n">
         <v>2</v>
@@ -26424,139 +26428,139 @@
         <v>1</v>
       </c>
       <c r="BV54" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="BW54" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BX54" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="BY54" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ54" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CA54" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CB54" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR54" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS54" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU54" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV54" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX54" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY54" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ54" t="n">
         <v>59</v>
       </c>
-      <c r="BZ54" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CA54" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB54" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="CC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR54" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS54" t="n">
+      <c r="DA54" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB54" t="n">
         <v>17</v>
       </c>
-      <c r="CT54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU54" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV54" t="n">
-        <v>19</v>
-      </c>
-      <c r="CW54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX54" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY54" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ54" t="n">
+      <c r="DC54" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD54" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE54" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DF54" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH54" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ54" t="n">
         <v>42</v>
       </c>
-      <c r="DA54" t="n">
-        <v>67</v>
-      </c>
-      <c r="DB54" t="n">
+      <c r="DK54" t="n">
         <v>42</v>
       </c>
-      <c r="DC54" t="n">
-        <v>67</v>
-      </c>
-      <c r="DD54" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DE54" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DF54" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG54" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DH54" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DI54" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DJ54" t="n">
-        <v>59</v>
-      </c>
-      <c r="DK54" t="n">
-        <v>34</v>
-      </c>
       <c r="DL54" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="DM54" t="n">
-        <v>1.18</v>
+        <v>0.47</v>
       </c>
       <c r="DN54" t="n">
-        <v>2.61</v>
+        <v>1.62</v>
       </c>
       <c r="DO54" t="n">
         <v>14</v>
@@ -26568,10 +26572,10 @@
         <v>1</v>
       </c>
       <c r="DR54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT54" t="b">
         <v>0</v>
@@ -26583,79 +26587,75 @@
         <v>1</v>
       </c>
       <c r="DW54" t="n">
-        <v>17.43</v>
+        <v>20.5</v>
       </c>
       <c r="DX54" t="n">
-        <v>4.72</v>
+        <v>6.93</v>
       </c>
       <c r="DY54" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="DZ54" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA54" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EB54" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC54" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC54" t="inlineStr"/>
       <c r="ED54" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EE54" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF54" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EG54" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EH54" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EI54" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EJ54" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EK54" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EL54" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EM54" t="inlineStr">
@@ -26670,12 +26670,12 @@
       </c>
       <c r="EO54" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP54" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -26695,12 +26695,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
@@ -26710,25 +26710,25 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -26740,119 +26740,119 @@
         <v>2</v>
       </c>
       <c r="R55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S55" t="n">
+        <v>9</v>
+      </c>
+      <c r="T55" t="n">
         <v>14</v>
       </c>
-      <c r="T55" t="n">
-        <v>7</v>
-      </c>
       <c r="U55" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V55" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="W55" t="n">
         <v>17</v>
       </c>
       <c r="X55" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Y55" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="Z55" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Estadio Ramón Sánchez Pizjuán</t>
+          <t>Estadio Ciudad de Valencia</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Avenida de Eduardo Dato, Sevilla</t>
+          <t>Calle San Vicente de Paúl 44, Valencia</t>
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE55" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="AF55" t="n">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI55" t="n">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="AJ55" t="n">
-        <v>3.4</v>
+        <v>2.07</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL55" t="n">
         <v>2</v>
       </c>
       <c r="AM55" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN55" t="n">
         <v>1.5</v>
       </c>
-      <c r="AN55" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AO55" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP55" t="n">
         <v>2.38</v>
       </c>
-      <c r="AP55" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AQ55" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.72</v>
+        <v>4.05</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AU55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV55" t="n">
         <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX55" t="n">
         <v>1</v>
       </c>
       <c r="AY55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB55" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="BC55" t="n">
         <v>0</v>
@@ -26873,76 +26873,76 @@
         <v>1</v>
       </c>
       <c r="BI55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL55" t="n">
         <v>2</v>
       </c>
       <c r="BM55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BN55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO55" t="n">
         <v>0</v>
       </c>
       <c r="BP55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU55" t="n">
         <v>1</v>
       </c>
       <c r="BV55" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="BW55" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="BX55" t="n">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="BY55" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="BZ55" t="n">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
       <c r="CA55" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="CB55" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="CC55" t="n">
         <v>0</v>
       </c>
       <c r="CD55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE55" t="n">
         <v>0</v>
       </c>
       <c r="CF55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG55" t="n">
         <v>0</v>
@@ -26966,7 +26966,7 @@
         <v>0</v>
       </c>
       <c r="CN55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO55" t="n">
         <v>0</v>
@@ -26978,73 +26978,73 @@
         <v>1</v>
       </c>
       <c r="CR55" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="CS55" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="CT55" t="n">
         <v>1</v>
       </c>
       <c r="CU55" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="CV55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CW55" t="n">
         <v>1</v>
       </c>
       <c r="CX55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY55" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CZ55" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA55" t="n">
         <v>100</v>
       </c>
       <c r="DB55" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="DC55" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1</v>
+        <v>0.17</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF55" t="n">
         <v>0.5</v>
       </c>
       <c r="DG55" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DH55" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="DI55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ55" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK55" t="n">
         <v>0</v>
       </c>
       <c r="DL55" t="n">
-        <v>1.24</v>
+        <v>0.84</v>
       </c>
       <c r="DM55" t="n">
-        <v>0.93</v>
+        <v>2.34</v>
       </c>
       <c r="DN55" t="n">
-        <v>2.17</v>
+        <v>3.18</v>
       </c>
       <c r="DO55" t="n">
         <v>14</v>
@@ -27059,10 +27059,10 @@
         <v>1</v>
       </c>
       <c r="DS55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU55" t="b">
         <v>0</v>
@@ -27071,99 +27071,87 @@
         <v>1</v>
       </c>
       <c r="DW55" t="n">
-        <v>27.52</v>
+        <v>22.21</v>
       </c>
       <c r="DX55" t="n">
-        <v>3.08</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DY55" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ55" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="EA55" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EB55" t="inlineStr"/>
+      <c r="EC55" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="ED55" t="inlineStr"/>
+      <c r="EE55" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF55" t="inlineStr"/>
+      <c r="EG55" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH55" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI55" t="inlineStr">
+        <is>
+          <t>5.86</t>
+        </is>
+      </c>
+      <c r="EJ55" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="EK55" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL55" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EB55" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EC55" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="ED55" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EE55" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF55" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG55" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EH55" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EI55" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EJ55" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="EK55" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EL55" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
       <c r="EM55" t="inlineStr">
         <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN55" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EO55" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EP55" t="inlineStr">
+        <is>
           <t>1.68</t>
-        </is>
-      </c>
-      <c r="EN55" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EO55" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EP55" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -27183,12 +27171,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -27198,149 +27186,149 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I56" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3</v>
+      </c>
+      <c r="L56" t="n">
+        <v>6</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2</v>
+      </c>
+      <c r="R56" t="n">
         <v>5</v>
       </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
+      <c r="S56" t="n">
+        <v>14</v>
+      </c>
+      <c r="T56" t="n">
         <v>7</v>
       </c>
-      <c r="L56" t="n">
-        <v>8</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>2</v>
-      </c>
-      <c r="R56" t="n">
-        <v>10</v>
-      </c>
-      <c r="S56" t="n">
-        <v>9</v>
-      </c>
-      <c r="T56" t="n">
-        <v>14</v>
-      </c>
       <c r="U56" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V56" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="W56" t="n">
         <v>17</v>
       </c>
       <c r="X56" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y56" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="Z56" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Estadio Ciudad de Valencia</t>
+          <t>Estadio Ramón Sánchez Pizjuán</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Calle San Vicente de Paúl 44, Valencia</t>
+          <t>Avenida de Eduardo Dato, Sevilla</t>
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE56" t="n">
-        <v>8</v>
+        <v>3.15</v>
       </c>
       <c r="AF56" t="n">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI56" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT56" t="n">
         <v>1.4</v>
       </c>
-      <c r="AJ56" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AU56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV56" t="n">
         <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX56" t="n">
         <v>1</v>
       </c>
       <c r="AY56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB56" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="BC56" t="n">
         <v>0</v>
@@ -27361,76 +27349,76 @@
         <v>1</v>
       </c>
       <c r="BI56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT56" t="n">
         <v>5</v>
       </c>
-      <c r="BK56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL56" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM56" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN56" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ56" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR56" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT56" t="n">
-        <v>2</v>
-      </c>
       <c r="BU56" t="n">
         <v>1</v>
       </c>
       <c r="BV56" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="BW56" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="BX56" t="n">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="BY56" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="BZ56" t="n">
-        <v>1.02</v>
+        <v>1.67</v>
       </c>
       <c r="CA56" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="CB56" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="CC56" t="n">
         <v>0</v>
       </c>
       <c r="CD56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE56" t="n">
         <v>0</v>
       </c>
       <c r="CF56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG56" t="n">
         <v>0</v>
@@ -27454,7 +27442,7 @@
         <v>0</v>
       </c>
       <c r="CN56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO56" t="n">
         <v>0</v>
@@ -27466,73 +27454,73 @@
         <v>1</v>
       </c>
       <c r="CR56" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="CS56" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="CT56" t="n">
         <v>1</v>
       </c>
       <c r="CU56" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV56" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW56" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX56" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY56" t="n">
         <v>9</v>
       </c>
-      <c r="CV56" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW56" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX56" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY56" t="n">
-        <v>3</v>
-      </c>
       <c r="CZ56" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA56" t="n">
         <v>100</v>
       </c>
       <c r="DB56" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC56" t="n">
         <v>75</v>
       </c>
-      <c r="DC56" t="n">
-        <v>100</v>
-      </c>
       <c r="DD56" t="n">
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="DF56" t="n">
         <v>0.5</v>
       </c>
       <c r="DG56" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DH56" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ56" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK56" t="n">
         <v>0</v>
       </c>
       <c r="DL56" t="n">
-        <v>0.84</v>
+        <v>1.24</v>
       </c>
       <c r="DM56" t="n">
-        <v>2.34</v>
+        <v>0.93</v>
       </c>
       <c r="DN56" t="n">
-        <v>3.18</v>
+        <v>2.17</v>
       </c>
       <c r="DO56" t="n">
         <v>14</v>
@@ -27547,10 +27535,10 @@
         <v>1</v>
       </c>
       <c r="DS56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU56" t="b">
         <v>0</v>
@@ -27559,87 +27547,99 @@
         <v>1</v>
       </c>
       <c r="DW56" t="n">
-        <v>22.21</v>
+        <v>27.52</v>
       </c>
       <c r="DX56" t="n">
-        <v>8.289999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="DY56" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="DZ56" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA56" t="inlineStr">
         <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EB56" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EB56" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
       <c r="EC56" t="inlineStr">
         <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="ED56" t="inlineStr"/>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="ED56" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="EE56" t="inlineStr">
         <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EF56" t="inlineStr"/>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EF56" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
       <c r="EG56" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EH56" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EI56" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EJ56" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EK56" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EL56" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EM56" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EN56" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EO56" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EP56" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -28479,7 +28479,7 @@
         <v>2.98</v>
       </c>
       <c r="DO58" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -31289,7 +31289,7 @@
         <v>2.75</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DF64" t="n">
         <v>2.33</v>
@@ -31319,7 +31319,7 @@
         <v>4.16</v>
       </c>
       <c r="DO64" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -32682,7 +32682,7 @@
         <v>75</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="DE67" t="n">
         <v>1.29</v>
@@ -32715,7 +32715,7 @@
         <v>2.84</v>
       </c>
       <c r="DO67" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -34599,7 +34599,7 @@
         <v>2.23</v>
       </c>
       <c r="DO71" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -36013,7 +36013,7 @@
         <v>1.13</v>
       </c>
       <c r="DE74" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="DF74" t="n">
         <v>0.25</v>
@@ -36043,7 +36043,7 @@
         <v>1.79</v>
       </c>
       <c r="DO74" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36498,7 +36498,7 @@
         <v>59</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DE75" t="n">
         <v>0.43</v>
@@ -38883,7 +38883,7 @@
         <v>3.36</v>
       </c>
       <c r="DO80" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39325,7 +39325,7 @@
         <v>0.63</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF81" t="n">
         <v>0.75</v>
@@ -43139,7 +43139,7 @@
         <v>2.17</v>
       </c>
       <c r="DO89" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43581,7 +43581,7 @@
         <v>1.57</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DF90" t="n">
         <v>1.67</v>
@@ -44069,7 +44069,7 @@
         <v>1.57</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="DF91" t="n">
         <v>1.75</v>
@@ -44099,7 +44099,7 @@
         <v>2.36</v>
       </c>
       <c r="DO91" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP91" t="b">
         <v>0</v>
@@ -45978,7 +45978,7 @@
         <v>70</v>
       </c>
       <c r="DD95" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DE95" t="n">
         <v>1.29</v>
@@ -46487,7 +46487,7 @@
         <v>2.51</v>
       </c>
       <c r="DO96" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -47417,7 +47417,7 @@
         <v>1.86</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF98" t="n">
         <v>2.25</v>
@@ -47919,7 +47919,7 @@
         <v>4.52</v>
       </c>
       <c r="DO99" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -48822,7 +48822,7 @@
         <v>42</v>
       </c>
       <c r="DD101" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="DE101" t="n">
         <v>0.57</v>
@@ -48855,7 +48855,7 @@
         <v>2.88</v>
       </c>
       <c r="DO101" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -49791,7 +49791,7 @@
         <v>3.29</v>
       </c>
       <c r="DO103" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -51181,7 +51181,7 @@
         <v>3</v>
       </c>
       <c r="DE106" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="DF106" t="n">
         <v>3</v>
@@ -51211,7 +51211,7 @@
         <v>3.13</v>
       </c>
       <c r="DO106" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -56402,7 +56402,7 @@
         <v>75</v>
       </c>
       <c r="DD117" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DE117" t="n">
         <v>0.57</v>
@@ -56870,10 +56870,10 @@
         <v>53</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="DE118" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DF118" t="n">
         <v>1.25</v>
@@ -56903,7 +56903,7 @@
         <v>3.88</v>
       </c>
       <c r="DO118" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP118" t="b">
         <v>0</v>
@@ -57011,12 +57011,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F119" s="2" t="n">
@@ -57026,25 +57026,25 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K119" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L119" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -57056,117 +57056,125 @@
         <v>4</v>
       </c>
       <c r="R119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S119" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T119" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U119" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="V119" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W119" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="X119" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y119" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Z119" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA119" t="inlineStr"/>
-      <c r="AB119" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>Avenida de Suecia, Valencia</t>
+        </is>
+      </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE119" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="AF119" t="n">
-        <v>2.58</v>
+        <v>3.45</v>
       </c>
       <c r="AG119" t="n">
-        <v>2.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH119" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AI119" t="n">
-        <v>3.04</v>
+        <v>1.91</v>
       </c>
       <c r="AJ119" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="AK119" t="n">
-        <v>2.43</v>
+        <v>1.72</v>
       </c>
       <c r="AL119" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AM119" t="n">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="AN119" t="n">
-        <v>2.87</v>
+        <v>1.84</v>
       </c>
       <c r="AO119" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.77</v>
+        <v>1.37</v>
       </c>
       <c r="AR119" t="n">
-        <v>4.45</v>
+        <v>2.85</v>
       </c>
       <c r="AS119" t="n">
-        <v>2.05</v>
+        <v>2.89</v>
       </c>
       <c r="AT119" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AU119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW119" t="n">
         <v>0</v>
       </c>
       <c r="AX119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB119" t="n">
-        <v>298</v>
+        <v>-1</v>
       </c>
       <c r="BC119" t="n">
         <v>0</v>
       </c>
       <c r="BD119" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="BE119" t="n">
         <v>0</v>
@@ -57181,64 +57189,64 @@
         <v>1</v>
       </c>
       <c r="BI119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ119" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BK119" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BL119" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BM119" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BN119" t="n">
         <v>7</v>
       </c>
       <c r="BO119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT119" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BU119" t="n">
         <v>1</v>
       </c>
       <c r="BV119" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="BW119" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="BX119" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="BY119" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="BZ119" t="n">
-        <v>0.96</v>
+        <v>1.74</v>
       </c>
       <c r="CA119" t="n">
-        <v>1.63</v>
+        <v>1.09</v>
       </c>
       <c r="CB119" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="CC119" t="n">
         <v>0</v>
@@ -57271,10 +57279,10 @@
         <v>0</v>
       </c>
       <c r="CM119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO119" t="n">
         <v>0</v>
@@ -57286,19 +57294,19 @@
         <v>1</v>
       </c>
       <c r="CR119" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="CS119" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="CT119" t="n">
         <v>1</v>
       </c>
       <c r="CU119" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CV119" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CW119" t="n">
         <v>1</v>
@@ -57307,52 +57315,52 @@
         <v>6</v>
       </c>
       <c r="CY119" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CZ119" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="DA119" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="DB119" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="DC119" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="DE119" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="DF119" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG119" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DH119" t="n">
         <v>0.82</v>
       </c>
       <c r="DI119" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="DJ119" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="DK119" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="DL119" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="DM119" t="n">
-        <v>0.97</v>
+        <v>1.6</v>
       </c>
       <c r="DN119" t="n">
-        <v>2.18</v>
+        <v>3.06</v>
       </c>
       <c r="DO119" t="n">
         <v>14</v>
@@ -57361,7 +57369,7 @@
         <v>1</v>
       </c>
       <c r="DQ119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR119" t="b">
         <v>0</v>
@@ -57376,90 +57384,102 @@
         <v>0</v>
       </c>
       <c r="DV119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW119" t="n">
-        <v>17.48</v>
+        <v>17.01</v>
       </c>
       <c r="DX119" t="n">
-        <v>5.64</v>
+        <v>5.56</v>
       </c>
       <c r="DY119" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="DZ119" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="EA119" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB119" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EC119" t="inlineStr"/>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
       <c r="ED119" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EE119" t="inlineStr"/>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE119" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
       <c r="EF119" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="EG119" t="inlineStr"/>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EG119" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EH119" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EI119" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EJ119" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EK119" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EL119" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EM119" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EN119" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EO119" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EP119" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -57479,12 +57499,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F120" s="2" t="n">
@@ -57494,25 +57514,25 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K120" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L120" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -57524,125 +57544,117 @@
         <v>4</v>
       </c>
       <c r="R120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S120" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T120" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U120" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="V120" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W120" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X120" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y120" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Z120" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>Estadio de Mestalla</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>Avenida de Suecia, Valencia</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AA120" t="inlineStr"/>
+      <c r="AB120" t="inlineStr"/>
       <c r="AC120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE120" t="n">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="AF120" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="AG120" t="n">
-        <v>2.15</v>
+        <v>2.98</v>
       </c>
       <c r="AH120" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AI120" t="n">
-        <v>1.91</v>
+        <v>3.04</v>
       </c>
       <c r="AJ120" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="AK120" t="n">
-        <v>1.72</v>
+        <v>2.43</v>
       </c>
       <c r="AL120" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AM120" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="AN120" t="n">
-        <v>1.84</v>
+        <v>2.87</v>
       </c>
       <c r="AO120" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="AR120" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="AS120" t="n">
-        <v>2.89</v>
+        <v>2.05</v>
       </c>
       <c r="AT120" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AU120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW120" t="n">
         <v>0</v>
       </c>
       <c r="AX120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB120" t="n">
-        <v>-1</v>
+        <v>298</v>
       </c>
       <c r="BC120" t="n">
         <v>0</v>
       </c>
       <c r="BD120" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="BE120" t="n">
         <v>0</v>
@@ -57657,64 +57669,64 @@
         <v>1</v>
       </c>
       <c r="BI120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ120" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BK120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL120" t="n">
         <v>6</v>
       </c>
-      <c r="BL120" t="n">
-        <v>1</v>
-      </c>
       <c r="BM120" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BN120" t="n">
         <v>7</v>
       </c>
       <c r="BO120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT120" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BU120" t="n">
         <v>1</v>
       </c>
       <c r="BV120" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="BW120" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="BX120" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="BY120" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="BZ120" t="n">
-        <v>1.74</v>
+        <v>0.96</v>
       </c>
       <c r="CA120" t="n">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="CB120" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="CC120" t="n">
         <v>0</v>
@@ -57747,10 +57759,10 @@
         <v>0</v>
       </c>
       <c r="CM120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO120" t="n">
         <v>0</v>
@@ -57762,19 +57774,19 @@
         <v>1</v>
       </c>
       <c r="CR120" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="CS120" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="CT120" t="n">
         <v>1</v>
       </c>
       <c r="CU120" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CV120" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CW120" t="n">
         <v>1</v>
@@ -57783,61 +57795,61 @@
         <v>6</v>
       </c>
       <c r="CY120" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CZ120" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="DA120" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="DB120" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="DC120" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="DF120" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG120" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="DH120" t="n">
         <v>0.82</v>
       </c>
       <c r="DI120" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="DJ120" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="DK120" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="DL120" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="DM120" t="n">
-        <v>1.6</v>
+        <v>0.97</v>
       </c>
       <c r="DN120" t="n">
-        <v>3.06</v>
+        <v>2.18</v>
       </c>
       <c r="DO120" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
       </c>
       <c r="DQ120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR120" t="b">
         <v>0</v>
@@ -57852,102 +57864,90 @@
         <v>0</v>
       </c>
       <c r="DV120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW120" t="n">
-        <v>17.01</v>
+        <v>17.48</v>
       </c>
       <c r="DX120" t="n">
-        <v>5.56</v>
+        <v>5.64</v>
       </c>
       <c r="DY120" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="DZ120" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="EA120" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="EB120" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC120" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EC120" t="inlineStr"/>
       <c r="ED120" t="inlineStr">
         <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EE120" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EE120" t="inlineStr"/>
       <c r="EF120" t="inlineStr">
         <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="EG120" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EG120" t="inlineStr"/>
       <c r="EH120" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EI120" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EJ120" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EK120" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="EL120" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EM120" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EN120" t="inlineStr">
+        <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="EM120" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EN120" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
       <c r="EO120" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EP120" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.43</t>
         </is>
       </c>
     </row>
@@ -58787,7 +58787,7 @@
         <v>2.75</v>
       </c>
       <c r="DO122" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -59703,7 +59703,7 @@
         <v>3.71</v>
       </c>
       <c r="DO124" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -61099,7 +61099,7 @@
         <v>2.27</v>
       </c>
       <c r="DO127" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP127" t="b">
         <v>0</v>
@@ -62005,7 +62005,7 @@
         <v>1.57</v>
       </c>
       <c r="DE129" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF129" t="n">
         <v>1.6</v>
@@ -62481,7 +62481,7 @@
         <v>1.86</v>
       </c>
       <c r="DE130" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DF130" t="n">
         <v>2</v>
@@ -66501,10 +66501,10 @@
         <v>15</v>
       </c>
       <c r="Y139" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z139" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA139" t="inlineStr"/>
       <c r="AB139" t="inlineStr"/>
@@ -67221,7 +67221,7 @@
         <v>1.13</v>
       </c>
       <c r="DE140" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DF140" t="n">
         <v>1.14</v>
@@ -67340,6 +67340,1374 @@
       <c r="EP140" t="inlineStr">
         <is>
           <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>14</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Valencia CF</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>45992.83333333334</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" t="n">
+        <v>2</v>
+      </c>
+      <c r="J141" t="n">
+        <v>10</v>
+      </c>
+      <c r="K141" t="n">
+        <v>5</v>
+      </c>
+      <c r="L141" t="n">
+        <v>15</v>
+      </c>
+      <c r="M141" t="n">
+        <v>1</v>
+      </c>
+      <c r="N141" t="n">
+        <v>1</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>7</v>
+      </c>
+      <c r="R141" t="n">
+        <v>2</v>
+      </c>
+      <c r="S141" t="n">
+        <v>12</v>
+      </c>
+      <c r="T141" t="n">
+        <v>8</v>
+      </c>
+      <c r="U141" t="n">
+        <v>19</v>
+      </c>
+      <c r="V141" t="n">
+        <v>10</v>
+      </c>
+      <c r="W141" t="n">
+        <v>11</v>
+      </c>
+      <c r="X141" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA141" t="inlineStr"/>
+      <c r="AB141" t="inlineStr"/>
+      <c r="AC141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>37</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>54</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>93</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU141" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV141" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX141" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY141" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ141" t="n">
+        <v>34</v>
+      </c>
+      <c r="DA141" t="n">
+        <v>54</v>
+      </c>
+      <c r="DB141" t="n">
+        <v>9</v>
+      </c>
+      <c r="DC141" t="n">
+        <v>52</v>
+      </c>
+      <c r="DD141" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DE141" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DF141" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG141" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DH141" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DI141" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ141" t="n">
+        <v>67</v>
+      </c>
+      <c r="DK141" t="n">
+        <v>47</v>
+      </c>
+      <c r="DL141" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="DM141" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DN141" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DO141" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW141" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="DX141" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="DY141" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="DZ141" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="EA141" t="inlineStr"/>
+      <c r="EB141" t="inlineStr"/>
+      <c r="EC141" t="inlineStr"/>
+      <c r="ED141" t="inlineStr"/>
+      <c r="EE141" t="inlineStr"/>
+      <c r="EF141" t="inlineStr"/>
+      <c r="EG141" t="inlineStr"/>
+      <c r="EH141" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="EI141" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EJ141" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EK141" t="inlineStr"/>
+      <c r="EL141" t="inlineStr"/>
+      <c r="EM141" t="inlineStr"/>
+      <c r="EN141" t="inlineStr"/>
+      <c r="EO141" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EP141" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>19</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>45993.83333333334</v>
+      </c>
+      <c r="G142" t="n">
+        <v>3</v>
+      </c>
+      <c r="H142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" t="n">
+        <v>4</v>
+      </c>
+      <c r="J142" t="n">
+        <v>5</v>
+      </c>
+      <c r="K142" t="n">
+        <v>4</v>
+      </c>
+      <c r="L142" t="n">
+        <v>9</v>
+      </c>
+      <c r="M142" t="n">
+        <v>1</v>
+      </c>
+      <c r="N142" t="n">
+        <v>1</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>6</v>
+      </c>
+      <c r="R142" t="n">
+        <v>2</v>
+      </c>
+      <c r="S142" t="n">
+        <v>13</v>
+      </c>
+      <c r="T142" t="n">
+        <v>5</v>
+      </c>
+      <c r="U142" t="n">
+        <v>19</v>
+      </c>
+      <c r="V142" t="n">
+        <v>7</v>
+      </c>
+      <c r="W142" t="n">
+        <v>12</v>
+      </c>
+      <c r="X142" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>Camp Nou</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>Carrer d'Arístides Maillol, Barcelona</t>
+        </is>
+      </c>
+      <c r="AC142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>83</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>95</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU142" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV142" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX142" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY142" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ142" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA142" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB142" t="n">
+        <v>60</v>
+      </c>
+      <c r="DC142" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD142" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE142" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DF142" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG142" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH142" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DI142" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DJ142" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK142" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL142" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DM142" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DN142" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="DO142" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW142" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="DX142" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="DY142" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="DZ142" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA142" t="inlineStr"/>
+      <c r="EB142" t="inlineStr"/>
+      <c r="EC142" t="inlineStr"/>
+      <c r="ED142" t="inlineStr"/>
+      <c r="EE142" t="inlineStr"/>
+      <c r="EF142" t="inlineStr"/>
+      <c r="EG142" t="inlineStr"/>
+      <c r="EH142" t="inlineStr">
+        <is>
+          <t>4.47</t>
+        </is>
+      </c>
+      <c r="EI142" t="inlineStr">
+        <is>
+          <t>4.46</t>
+        </is>
+      </c>
+      <c r="EJ142" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EK142" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EL142" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EM142" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EN142" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EO142" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EP142" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>19</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Athletic Club Bilbao</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>45994.75</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>3</v>
+      </c>
+      <c r="I143" t="n">
+        <v>3</v>
+      </c>
+      <c r="J143" t="n">
+        <v>5</v>
+      </c>
+      <c r="K143" t="n">
+        <v>7</v>
+      </c>
+      <c r="L143" t="n">
+        <v>12</v>
+      </c>
+      <c r="M143" t="n">
+        <v>2</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>4</v>
+      </c>
+      <c r="R143" t="n">
+        <v>8</v>
+      </c>
+      <c r="S143" t="n">
+        <v>5</v>
+      </c>
+      <c r="T143" t="n">
+        <v>5</v>
+      </c>
+      <c r="U143" t="n">
+        <v>9</v>
+      </c>
+      <c r="V143" t="n">
+        <v>13</v>
+      </c>
+      <c r="W143" t="n">
+        <v>15</v>
+      </c>
+      <c r="X143" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>San Mamés Barria</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
+        </is>
+      </c>
+      <c r="AC143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>84</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>53</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>63</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>118</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>95</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU143" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV143" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX143" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY143" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ143" t="n">
+        <v>46</v>
+      </c>
+      <c r="DA143" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB143" t="n">
+        <v>26</v>
+      </c>
+      <c r="DC143" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD143" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DE143" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF143" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DG143" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DH143" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DI143" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="DJ143" t="n">
+        <v>55</v>
+      </c>
+      <c r="DK143" t="n">
+        <v>41</v>
+      </c>
+      <c r="DL143" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DM143" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DN143" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="DO143" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW143" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="DX143" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="DY143" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="DZ143" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="EA143" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EB143" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EC143" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="ED143" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EE143" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EF143" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EG143" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="EH143" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EI143" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="EJ143" t="inlineStr">
+        <is>
+          <t>4.43</t>
+        </is>
+      </c>
+      <c r="EK143" t="inlineStr"/>
+      <c r="EL143" t="inlineStr"/>
+      <c r="EM143" t="inlineStr"/>
+      <c r="EN143" t="inlineStr"/>
+      <c r="EO143" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EP143" t="inlineStr">
+        <is>
+          <t>1.81</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP143" headerRowCount="1">
-  <autoFilter ref="A1:EP143"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP144" headerRowCount="1">
+  <autoFilter ref="A1:EP144"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP143"/>
+  <dimension ref="A1:EP144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -9878,7 +9878,7 @@
         <v>0</v>
       </c>
       <c r="DD19" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DE19" t="n">
         <v>2</v>
@@ -9911,7 +9911,7 @@
         <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -13222,7 +13222,7 @@
         <v>50</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DE26" t="n">
         <v>0.86</v>
@@ -14181,7 +14181,7 @@
         <v>3</v>
       </c>
       <c r="DE28" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -14211,7 +14211,7 @@
         <v>2.14</v>
       </c>
       <c r="DO28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -20833,7 +20833,7 @@
         <v>2</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DF42" t="n">
         <v>3</v>
@@ -24663,7 +24663,7 @@
         <v>2.63</v>
       </c>
       <c r="DO50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -26695,12 +26695,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
@@ -26710,149 +26710,149 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="n">
+        <v>6</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2</v>
+      </c>
+      <c r="R55" t="n">
         <v>5</v>
       </c>
-      <c r="J55" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" t="n">
+      <c r="S55" t="n">
+        <v>14</v>
+      </c>
+      <c r="T55" t="n">
         <v>7</v>
       </c>
-      <c r="L55" t="n">
-        <v>8</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>2</v>
-      </c>
-      <c r="R55" t="n">
-        <v>10</v>
-      </c>
-      <c r="S55" t="n">
-        <v>9</v>
-      </c>
-      <c r="T55" t="n">
-        <v>14</v>
-      </c>
       <c r="U55" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V55" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="W55" t="n">
         <v>17</v>
       </c>
       <c r="X55" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y55" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="Z55" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Estadio Ciudad de Valencia</t>
+          <t>Estadio Ramón Sánchez Pizjuán</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Calle San Vicente de Paúl 44, Valencia</t>
+          <t>Avenida de Eduardo Dato, Sevilla</t>
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE55" t="n">
-        <v>8</v>
+        <v>3.15</v>
       </c>
       <c r="AF55" t="n">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI55" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT55" t="n">
         <v>1.4</v>
       </c>
-      <c r="AJ55" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AU55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV55" t="n">
         <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX55" t="n">
         <v>1</v>
       </c>
       <c r="AY55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB55" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="BC55" t="n">
         <v>0</v>
@@ -26873,76 +26873,76 @@
         <v>1</v>
       </c>
       <c r="BI55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT55" t="n">
         <v>5</v>
       </c>
-      <c r="BK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL55" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM55" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN55" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ55" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR55" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT55" t="n">
-        <v>2</v>
-      </c>
       <c r="BU55" t="n">
         <v>1</v>
       </c>
       <c r="BV55" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="BW55" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="BX55" t="n">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="BY55" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="BZ55" t="n">
-        <v>1.02</v>
+        <v>1.67</v>
       </c>
       <c r="CA55" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="CB55" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="CC55" t="n">
         <v>0</v>
       </c>
       <c r="CD55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE55" t="n">
         <v>0</v>
       </c>
       <c r="CF55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG55" t="n">
         <v>0</v>
@@ -26966,7 +26966,7 @@
         <v>0</v>
       </c>
       <c r="CN55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO55" t="n">
         <v>0</v>
@@ -26978,73 +26978,73 @@
         <v>1</v>
       </c>
       <c r="CR55" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="CS55" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="CT55" t="n">
         <v>1</v>
       </c>
       <c r="CU55" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV55" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX55" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY55" t="n">
         <v>9</v>
       </c>
-      <c r="CV55" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW55" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX55" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY55" t="n">
-        <v>3</v>
-      </c>
       <c r="CZ55" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA55" t="n">
         <v>100</v>
       </c>
       <c r="DB55" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC55" t="n">
         <v>75</v>
       </c>
-      <c r="DC55" t="n">
-        <v>100</v>
-      </c>
       <c r="DD55" t="n">
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="DE55" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF55" t="n">
         <v>0.5</v>
       </c>
       <c r="DG55" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DH55" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ55" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK55" t="n">
         <v>0</v>
       </c>
       <c r="DL55" t="n">
-        <v>0.84</v>
+        <v>1.24</v>
       </c>
       <c r="DM55" t="n">
-        <v>2.34</v>
+        <v>0.93</v>
       </c>
       <c r="DN55" t="n">
-        <v>3.18</v>
+        <v>2.17</v>
       </c>
       <c r="DO55" t="n">
         <v>14</v>
@@ -27059,10 +27059,10 @@
         <v>1</v>
       </c>
       <c r="DS55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU55" t="b">
         <v>0</v>
@@ -27071,87 +27071,99 @@
         <v>1</v>
       </c>
       <c r="DW55" t="n">
-        <v>22.21</v>
+        <v>27.52</v>
       </c>
       <c r="DX55" t="n">
-        <v>8.289999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="DY55" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="DZ55" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA55" t="inlineStr">
         <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EB55" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EB55" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
       <c r="EC55" t="inlineStr">
         <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="ED55" t="inlineStr"/>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="ED55" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="EE55" t="inlineStr">
         <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EF55" t="inlineStr"/>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EF55" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
       <c r="EG55" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EH55" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EI55" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EJ55" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EK55" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EL55" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EM55" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EN55" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EO55" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EP55" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -27171,12 +27183,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -27186,25 +27198,25 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -27216,119 +27228,119 @@
         <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S56" t="n">
+        <v>9</v>
+      </c>
+      <c r="T56" t="n">
         <v>14</v>
       </c>
-      <c r="T56" t="n">
-        <v>7</v>
-      </c>
       <c r="U56" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V56" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="W56" t="n">
         <v>17</v>
       </c>
       <c r="X56" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Y56" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="Z56" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Estadio Ramón Sánchez Pizjuán</t>
+          <t>Estadio Ciudad de Valencia</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Avenida de Eduardo Dato, Sevilla</t>
+          <t>Calle San Vicente de Paúl 44, Valencia</t>
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE56" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="AF56" t="n">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="AG56" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI56" t="n">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="AJ56" t="n">
-        <v>3.4</v>
+        <v>2.07</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL56" t="n">
         <v>2</v>
       </c>
       <c r="AM56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN56" t="n">
         <v>1.5</v>
       </c>
-      <c r="AN56" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AO56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP56" t="n">
         <v>2.38</v>
       </c>
-      <c r="AP56" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AQ56" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AR56" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.72</v>
+        <v>4.05</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AU56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV56" t="n">
         <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX56" t="n">
         <v>1</v>
       </c>
       <c r="AY56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB56" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="BC56" t="n">
         <v>0</v>
@@ -27349,76 +27361,76 @@
         <v>1</v>
       </c>
       <c r="BI56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL56" t="n">
         <v>2</v>
       </c>
       <c r="BM56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BN56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO56" t="n">
         <v>0</v>
       </c>
       <c r="BP56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU56" t="n">
         <v>1</v>
       </c>
       <c r="BV56" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="BW56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="BX56" t="n">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="BY56" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="BZ56" t="n">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
       <c r="CA56" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="CB56" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="CC56" t="n">
         <v>0</v>
       </c>
       <c r="CD56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE56" t="n">
         <v>0</v>
       </c>
       <c r="CF56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG56" t="n">
         <v>0</v>
@@ -27442,7 +27454,7 @@
         <v>0</v>
       </c>
       <c r="CN56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO56" t="n">
         <v>0</v>
@@ -27454,73 +27466,73 @@
         <v>1</v>
       </c>
       <c r="CR56" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="CS56" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="CT56" t="n">
         <v>1</v>
       </c>
       <c r="CU56" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="CV56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CW56" t="n">
         <v>1</v>
       </c>
       <c r="CX56" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY56" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CZ56" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA56" t="n">
         <v>100</v>
       </c>
       <c r="DB56" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="DC56" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD56" t="n">
-        <v>1</v>
+        <v>0.17</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF56" t="n">
         <v>0.5</v>
       </c>
       <c r="DG56" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DH56" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="DI56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ56" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK56" t="n">
         <v>0</v>
       </c>
       <c r="DL56" t="n">
-        <v>1.24</v>
+        <v>0.84</v>
       </c>
       <c r="DM56" t="n">
-        <v>0.93</v>
+        <v>2.34</v>
       </c>
       <c r="DN56" t="n">
-        <v>2.17</v>
+        <v>3.18</v>
       </c>
       <c r="DO56" t="n">
         <v>14</v>
@@ -27535,10 +27547,10 @@
         <v>1</v>
       </c>
       <c r="DS56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU56" t="b">
         <v>0</v>
@@ -27547,99 +27559,87 @@
         <v>1</v>
       </c>
       <c r="DW56" t="n">
-        <v>27.52</v>
+        <v>22.21</v>
       </c>
       <c r="DX56" t="n">
-        <v>3.08</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DY56" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ56" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="EA56" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EB56" t="inlineStr"/>
+      <c r="EC56" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="ED56" t="inlineStr"/>
+      <c r="EE56" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF56" t="inlineStr"/>
+      <c r="EG56" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH56" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI56" t="inlineStr">
+        <is>
+          <t>5.86</t>
+        </is>
+      </c>
+      <c r="EJ56" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="EK56" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL56" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EB56" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EC56" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="ED56" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EE56" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF56" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG56" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EH56" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EI56" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EJ56" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="EK56" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EL56" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
       <c r="EM56" t="inlineStr">
         <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN56" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EO56" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EP56" t="inlineStr">
+        <is>
           <t>1.68</t>
-        </is>
-      </c>
-      <c r="EN56" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EO56" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EP56" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -28937,7 +28937,7 @@
         <v>1.43</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DF59" t="n">
         <v>0.5</v>
@@ -29870,7 +29870,7 @@
         <v>100</v>
       </c>
       <c r="DD61" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DE61" t="n">
         <v>1.86</v>
@@ -29903,7 +29903,7 @@
         <v>3.12</v>
       </c>
       <c r="DO61" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -35522,7 +35522,7 @@
         <v>88</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DE73" t="n">
         <v>1</v>
@@ -36501,7 +36501,7 @@
         <v>1.63</v>
       </c>
       <c r="DE75" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DF75" t="n">
         <v>1.75</v>
@@ -36531,7 +36531,7 @@
         <v>3.06</v>
       </c>
       <c r="DO75" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -39794,7 +39794,7 @@
         <v>84</v>
       </c>
       <c r="DD82" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DE82" t="n">
         <v>1.33</v>
@@ -40281,7 +40281,7 @@
         <v>1</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DF83" t="n">
         <v>1</v>
@@ -53057,7 +53057,7 @@
         <v>1.86</v>
       </c>
       <c r="DE110" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DF110" t="n">
         <v>1.8</v>
@@ -53542,7 +53542,7 @@
         <v>60</v>
       </c>
       <c r="DD111" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DE111" t="n">
         <v>0.25</v>
@@ -56435,7 +56435,7 @@
         <v>2.5</v>
       </c>
       <c r="DO117" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -57011,12 +57011,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F119" s="2" t="n">
@@ -57026,25 +57026,25 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K119" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L119" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -57056,125 +57056,117 @@
         <v>4</v>
       </c>
       <c r="R119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S119" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T119" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U119" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="V119" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W119" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X119" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y119" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Z119" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>Estadio de Mestalla</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>Avenida de Suecia, Valencia</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE119" t="n">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="AF119" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="AG119" t="n">
-        <v>2.15</v>
+        <v>2.98</v>
       </c>
       <c r="AH119" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AI119" t="n">
-        <v>1.91</v>
+        <v>3.04</v>
       </c>
       <c r="AJ119" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="AK119" t="n">
-        <v>1.72</v>
+        <v>2.43</v>
       </c>
       <c r="AL119" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AM119" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="AN119" t="n">
-        <v>1.84</v>
+        <v>2.87</v>
       </c>
       <c r="AO119" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="AR119" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="AS119" t="n">
-        <v>2.89</v>
+        <v>2.05</v>
       </c>
       <c r="AT119" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AU119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW119" t="n">
         <v>0</v>
       </c>
       <c r="AX119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB119" t="n">
-        <v>-1</v>
+        <v>298</v>
       </c>
       <c r="BC119" t="n">
         <v>0</v>
       </c>
       <c r="BD119" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="BE119" t="n">
         <v>0</v>
@@ -57189,64 +57181,64 @@
         <v>1</v>
       </c>
       <c r="BI119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ119" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BK119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL119" t="n">
         <v>6</v>
       </c>
-      <c r="BL119" t="n">
-        <v>1</v>
-      </c>
       <c r="BM119" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BN119" t="n">
         <v>7</v>
       </c>
       <c r="BO119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT119" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BU119" t="n">
         <v>1</v>
       </c>
       <c r="BV119" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="BW119" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="BX119" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="BY119" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="BZ119" t="n">
-        <v>1.74</v>
+        <v>0.96</v>
       </c>
       <c r="CA119" t="n">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="CB119" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="CC119" t="n">
         <v>0</v>
@@ -57279,10 +57271,10 @@
         <v>0</v>
       </c>
       <c r="CM119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO119" t="n">
         <v>0</v>
@@ -57294,19 +57286,19 @@
         <v>1</v>
       </c>
       <c r="CR119" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="CS119" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="CT119" t="n">
         <v>1</v>
       </c>
       <c r="CU119" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CV119" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CW119" t="n">
         <v>1</v>
@@ -57315,52 +57307,52 @@
         <v>6</v>
       </c>
       <c r="CY119" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CZ119" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="DA119" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="DB119" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="DC119" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="DE119" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="DF119" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG119" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="DH119" t="n">
         <v>0.82</v>
       </c>
       <c r="DI119" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="DJ119" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="DK119" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="DL119" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="DM119" t="n">
-        <v>1.6</v>
+        <v>0.97</v>
       </c>
       <c r="DN119" t="n">
-        <v>3.06</v>
+        <v>2.18</v>
       </c>
       <c r="DO119" t="n">
         <v>14</v>
@@ -57369,7 +57361,7 @@
         <v>1</v>
       </c>
       <c r="DQ119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR119" t="b">
         <v>0</v>
@@ -57384,102 +57376,90 @@
         <v>0</v>
       </c>
       <c r="DV119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW119" t="n">
-        <v>17.01</v>
+        <v>17.48</v>
       </c>
       <c r="DX119" t="n">
-        <v>5.56</v>
+        <v>5.64</v>
       </c>
       <c r="DY119" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="DZ119" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="EA119" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="EB119" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC119" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr"/>
       <c r="ED119" t="inlineStr">
         <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EE119" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EE119" t="inlineStr"/>
       <c r="EF119" t="inlineStr">
         <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="EG119" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EG119" t="inlineStr"/>
       <c r="EH119" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EI119" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EJ119" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EK119" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="EL119" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EM119" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EN119" t="inlineStr">
+        <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="EM119" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EN119" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
       <c r="EO119" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EP119" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.43</t>
         </is>
       </c>
     </row>
@@ -57499,12 +57479,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F120" s="2" t="n">
@@ -57514,25 +57494,25 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K120" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L120" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -57544,117 +57524,125 @@
         <v>4</v>
       </c>
       <c r="R120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S120" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T120" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U120" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="V120" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W120" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="X120" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y120" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Z120" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA120" t="inlineStr"/>
-      <c r="AB120" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>Avenida de Suecia, Valencia</t>
+        </is>
+      </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE120" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="AF120" t="n">
-        <v>2.58</v>
+        <v>3.45</v>
       </c>
       <c r="AG120" t="n">
-        <v>2.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH120" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AI120" t="n">
-        <v>3.04</v>
+        <v>1.91</v>
       </c>
       <c r="AJ120" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="AK120" t="n">
-        <v>2.43</v>
+        <v>1.72</v>
       </c>
       <c r="AL120" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AM120" t="n">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="AN120" t="n">
-        <v>2.87</v>
+        <v>1.84</v>
       </c>
       <c r="AO120" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.77</v>
+        <v>1.37</v>
       </c>
       <c r="AR120" t="n">
-        <v>4.45</v>
+        <v>2.85</v>
       </c>
       <c r="AS120" t="n">
-        <v>2.05</v>
+        <v>2.89</v>
       </c>
       <c r="AT120" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AU120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW120" t="n">
         <v>0</v>
       </c>
       <c r="AX120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB120" t="n">
-        <v>298</v>
+        <v>-1</v>
       </c>
       <c r="BC120" t="n">
         <v>0</v>
       </c>
       <c r="BD120" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="BE120" t="n">
         <v>0</v>
@@ -57669,64 +57657,64 @@
         <v>1</v>
       </c>
       <c r="BI120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ120" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BK120" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BL120" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BM120" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BN120" t="n">
         <v>7</v>
       </c>
       <c r="BO120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT120" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BU120" t="n">
         <v>1</v>
       </c>
       <c r="BV120" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="BW120" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="BX120" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="BY120" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="BZ120" t="n">
-        <v>0.96</v>
+        <v>1.74</v>
       </c>
       <c r="CA120" t="n">
-        <v>1.63</v>
+        <v>1.09</v>
       </c>
       <c r="CB120" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="CC120" t="n">
         <v>0</v>
@@ -57759,10 +57747,10 @@
         <v>0</v>
       </c>
       <c r="CM120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO120" t="n">
         <v>0</v>
@@ -57774,19 +57762,19 @@
         <v>1</v>
       </c>
       <c r="CR120" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="CS120" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="CT120" t="n">
         <v>1</v>
       </c>
       <c r="CU120" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CV120" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CW120" t="n">
         <v>1</v>
@@ -57795,52 +57783,52 @@
         <v>6</v>
       </c>
       <c r="CY120" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CZ120" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="DA120" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="DB120" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="DC120" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="DF120" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG120" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DH120" t="n">
         <v>0.82</v>
       </c>
       <c r="DI120" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="DJ120" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="DK120" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="DL120" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="DM120" t="n">
-        <v>0.97</v>
+        <v>1.6</v>
       </c>
       <c r="DN120" t="n">
-        <v>2.18</v>
+        <v>3.06</v>
       </c>
       <c r="DO120" t="n">
         <v>14</v>
@@ -57849,7 +57837,7 @@
         <v>1</v>
       </c>
       <c r="DQ120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR120" t="b">
         <v>0</v>
@@ -57864,90 +57852,102 @@
         <v>0</v>
       </c>
       <c r="DV120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW120" t="n">
-        <v>17.48</v>
+        <v>17.01</v>
       </c>
       <c r="DX120" t="n">
-        <v>5.64</v>
+        <v>5.56</v>
       </c>
       <c r="DY120" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="DZ120" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="EA120" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB120" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EC120" t="inlineStr"/>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC120" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
       <c r="ED120" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EE120" t="inlineStr"/>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE120" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
       <c r="EF120" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="EG120" t="inlineStr"/>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EG120" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EH120" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EI120" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EJ120" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EK120" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EL120" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EM120" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EN120" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EO120" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EP120" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -60601,7 +60601,7 @@
         <v>2.71</v>
       </c>
       <c r="DE126" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DF126" t="n">
         <v>2.67</v>
@@ -61066,7 +61066,7 @@
         <v>69</v>
       </c>
       <c r="DD127" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DE127" t="n">
         <v>1.25</v>
@@ -65331,7 +65331,7 @@
         <v>2.87</v>
       </c>
       <c r="DO136" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -68711,6 +68711,482 @@
         </is>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>15</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>RCD Mallorca</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>45996.83333333334</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>8</v>
+      </c>
+      <c r="K144" t="n">
+        <v>5</v>
+      </c>
+      <c r="L144" t="n">
+        <v>13</v>
+      </c>
+      <c r="M144" t="n">
+        <v>2</v>
+      </c>
+      <c r="N144" t="n">
+        <v>1</v>
+      </c>
+      <c r="O144" t="n">
+        <v>2</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>3</v>
+      </c>
+      <c r="R144" t="n">
+        <v>5</v>
+      </c>
+      <c r="S144" t="n">
+        <v>12</v>
+      </c>
+      <c r="T144" t="n">
+        <v>8</v>
+      </c>
+      <c r="U144" t="n">
+        <v>15</v>
+      </c>
+      <c r="V144" t="n">
+        <v>13</v>
+      </c>
+      <c r="W144" t="n">
+        <v>14</v>
+      </c>
+      <c r="X144" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Carlos Tartiere</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>Calle de Ricardo Vázquez Prada, Barrio de la Ería, Oviedo</t>
+        </is>
+      </c>
+      <c r="AC144" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI144" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK144" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL144" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM144" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN144" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ144" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT144" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV144" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW144" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX144" t="n">
+        <v>84</v>
+      </c>
+      <c r="BY144" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ144" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CA144" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CB144" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR144" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS144" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU144" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV144" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX144" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY144" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ144" t="n">
+        <v>58</v>
+      </c>
+      <c r="DA144" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB144" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC144" t="n">
+        <v>72</v>
+      </c>
+      <c r="DD144" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DE144" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF144" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DG144" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DH144" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DI144" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DJ144" t="n">
+        <v>43</v>
+      </c>
+      <c r="DK144" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL144" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="DM144" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DN144" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DO144" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW144" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="DX144" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="DY144" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="DZ144" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA144" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EB144" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EC144" t="inlineStr"/>
+      <c r="ED144" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EE144" t="inlineStr"/>
+      <c r="EF144" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EG144" t="inlineStr"/>
+      <c r="EH144" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EI144" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="EJ144" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EK144" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EL144" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EM144" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EN144" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EO144" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EP144" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP152" headerRowCount="1">
-  <autoFilter ref="A1:EP152"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP153" headerRowCount="1">
+  <autoFilter ref="A1:EP153"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP152"/>
+  <dimension ref="A1:EP153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3705,7 +3705,7 @@
         <v>1.75</v>
       </c>
       <c r="DE6" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -6127,7 +6127,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -8035,7 +8035,7 @@
         <v>2.67</v>
       </c>
       <c r="DO15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8470,7 +8470,7 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE16" t="n">
         <v>0.43</v>
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -11777,7 +11777,7 @@
         <v>2</v>
       </c>
       <c r="DE23" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF23" t="n">
         <v>1</v>
@@ -11807,7 +11807,7 @@
         <v>1.81</v>
       </c>
       <c r="DO23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -15619,7 +15619,7 @@
         <v>1.56</v>
       </c>
       <c r="DO31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -19447,7 +19447,7 @@
         <v>2.04</v>
       </c>
       <c r="DO39" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19886,7 +19886,7 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE40" t="n">
         <v>1.11</v>
@@ -19919,7 +19919,7 @@
         <v>2.95</v>
       </c>
       <c r="DO40" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -21765,7 +21765,7 @@
         <v>1.13</v>
       </c>
       <c r="DE44" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF44" t="n">
         <v>0</v>
@@ -21795,7 +21795,7 @@
         <v>2.35</v>
       </c>
       <c r="DO44" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -23219,7 +23219,7 @@
         <v>3.19</v>
       </c>
       <c r="DO47" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -27535,7 +27535,7 @@
         <v>3.18</v>
       </c>
       <c r="DO56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -29402,7 +29402,7 @@
         <v>100</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE60" t="n">
         <v>0.43</v>
@@ -29435,7 +29435,7 @@
         <v>2.17</v>
       </c>
       <c r="DO60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30829,7 +30829,7 @@
         <v>1.57</v>
       </c>
       <c r="DE63" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF63" t="n">
         <v>2</v>
@@ -30859,7 +30859,7 @@
         <v>2.16</v>
       </c>
       <c r="DO63" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -34111,7 +34111,7 @@
         <v>2.27</v>
       </c>
       <c r="DO70" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -35046,7 +35046,7 @@
         <v>88</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE72" t="n">
         <v>1.13</v>
@@ -35079,7 +35079,7 @@
         <v>2.29</v>
       </c>
       <c r="DO72" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35525,7 +35525,7 @@
         <v>0.75</v>
       </c>
       <c r="DE73" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -35555,7 +35555,7 @@
         <v>2.02</v>
       </c>
       <c r="DO73" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -41703,7 +41703,7 @@
         <v>2.53</v>
       </c>
       <c r="DO86" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -43139,7 +43139,7 @@
         <v>2.17</v>
       </c>
       <c r="DO89" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -46937,7 +46937,7 @@
         <v>1.43</v>
       </c>
       <c r="DE97" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF97" t="n">
         <v>1.25</v>
@@ -46967,7 +46967,7 @@
         <v>2.31</v>
       </c>
       <c r="DO97" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -48346,7 +48346,7 @@
         <v>84</v>
       </c>
       <c r="DD100" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE100" t="n">
         <v>2</v>
@@ -48379,7 +48379,7 @@
         <v>2.21</v>
       </c>
       <c r="DO100" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -51679,7 +51679,7 @@
         <v>2.18</v>
       </c>
       <c r="DO107" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -53575,7 +53575,7 @@
         <v>1.9</v>
       </c>
       <c r="DO111" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP111" t="b">
         <v>0</v>
@@ -55019,7 +55019,7 @@
         <v>2.35</v>
       </c>
       <c r="DO114" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -55457,7 +55457,7 @@
         <v>2.75</v>
       </c>
       <c r="DE115" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF115" t="n">
         <v>2.67</v>
@@ -55487,7 +55487,7 @@
         <v>3.1</v>
       </c>
       <c r="DO115" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -57011,12 +57011,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F119" s="2" t="n">
@@ -57026,25 +57026,25 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K119" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L119" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -57056,125 +57056,117 @@
         <v>4</v>
       </c>
       <c r="R119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S119" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T119" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U119" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="V119" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W119" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X119" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y119" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Z119" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>Estadio de Mestalla</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>Avenida de Suecia, Valencia</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE119" t="n">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="AF119" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="AG119" t="n">
-        <v>2.15</v>
+        <v>2.98</v>
       </c>
       <c r="AH119" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AI119" t="n">
-        <v>1.91</v>
+        <v>3.04</v>
       </c>
       <c r="AJ119" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="AK119" t="n">
-        <v>1.72</v>
+        <v>2.43</v>
       </c>
       <c r="AL119" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AM119" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="AN119" t="n">
-        <v>1.84</v>
+        <v>2.87</v>
       </c>
       <c r="AO119" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="AR119" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="AS119" t="n">
-        <v>2.89</v>
+        <v>2.05</v>
       </c>
       <c r="AT119" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AU119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW119" t="n">
         <v>0</v>
       </c>
       <c r="AX119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB119" t="n">
-        <v>-1</v>
+        <v>298</v>
       </c>
       <c r="BC119" t="n">
         <v>0</v>
       </c>
       <c r="BD119" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="BE119" t="n">
         <v>0</v>
@@ -57189,64 +57181,64 @@
         <v>1</v>
       </c>
       <c r="BI119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ119" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BK119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL119" t="n">
         <v>6</v>
       </c>
-      <c r="BL119" t="n">
-        <v>1</v>
-      </c>
       <c r="BM119" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BN119" t="n">
         <v>7</v>
       </c>
       <c r="BO119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT119" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BU119" t="n">
         <v>1</v>
       </c>
       <c r="BV119" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="BW119" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="BX119" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="BY119" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="BZ119" t="n">
-        <v>1.74</v>
+        <v>0.96</v>
       </c>
       <c r="CA119" t="n">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="CB119" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="CC119" t="n">
         <v>0</v>
@@ -57279,10 +57271,10 @@
         <v>0</v>
       </c>
       <c r="CM119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO119" t="n">
         <v>0</v>
@@ -57294,19 +57286,19 @@
         <v>1</v>
       </c>
       <c r="CR119" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="CS119" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="CT119" t="n">
         <v>1</v>
       </c>
       <c r="CU119" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CV119" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CW119" t="n">
         <v>1</v>
@@ -57315,52 +57307,52 @@
         <v>6</v>
       </c>
       <c r="CY119" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CZ119" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="DA119" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="DB119" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="DC119" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="DD119" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DE119" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DF119" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG119" t="n">
         <v>1.5</v>
-      </c>
-      <c r="DE119" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DF119" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DG119" t="n">
-        <v>1.4</v>
       </c>
       <c r="DH119" t="n">
         <v>0.82</v>
       </c>
       <c r="DI119" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="DJ119" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="DK119" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="DL119" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="DM119" t="n">
-        <v>1.6</v>
+        <v>0.97</v>
       </c>
       <c r="DN119" t="n">
-        <v>3.06</v>
+        <v>2.18</v>
       </c>
       <c r="DO119" t="n">
         <v>15</v>
@@ -57369,7 +57361,7 @@
         <v>1</v>
       </c>
       <c r="DQ119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR119" t="b">
         <v>0</v>
@@ -57384,102 +57376,90 @@
         <v>0</v>
       </c>
       <c r="DV119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW119" t="n">
-        <v>17.01</v>
+        <v>17.48</v>
       </c>
       <c r="DX119" t="n">
-        <v>5.56</v>
+        <v>5.64</v>
       </c>
       <c r="DY119" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="DZ119" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="EA119" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="EB119" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC119" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr"/>
       <c r="ED119" t="inlineStr">
         <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EE119" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EE119" t="inlineStr"/>
       <c r="EF119" t="inlineStr">
         <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="EG119" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EG119" t="inlineStr"/>
       <c r="EH119" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EI119" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EJ119" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EK119" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="EL119" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EM119" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EN119" t="inlineStr">
+        <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="EM119" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EN119" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
       <c r="EO119" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EP119" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.43</t>
         </is>
       </c>
     </row>
@@ -57499,12 +57479,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F120" s="2" t="n">
@@ -57514,25 +57494,25 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K120" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L120" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -57544,117 +57524,125 @@
         <v>4</v>
       </c>
       <c r="R120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S120" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T120" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U120" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="V120" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W120" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="X120" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y120" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Z120" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA120" t="inlineStr"/>
-      <c r="AB120" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>Avenida de Suecia, Valencia</t>
+        </is>
+      </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE120" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="AF120" t="n">
-        <v>2.58</v>
+        <v>3.45</v>
       </c>
       <c r="AG120" t="n">
-        <v>2.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH120" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AI120" t="n">
-        <v>3.04</v>
+        <v>1.91</v>
       </c>
       <c r="AJ120" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="AK120" t="n">
-        <v>2.43</v>
+        <v>1.72</v>
       </c>
       <c r="AL120" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AM120" t="n">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="AN120" t="n">
-        <v>2.87</v>
+        <v>1.84</v>
       </c>
       <c r="AO120" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.77</v>
+        <v>1.37</v>
       </c>
       <c r="AR120" t="n">
-        <v>4.45</v>
+        <v>2.85</v>
       </c>
       <c r="AS120" t="n">
-        <v>2.05</v>
+        <v>2.89</v>
       </c>
       <c r="AT120" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AU120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW120" t="n">
         <v>0</v>
       </c>
       <c r="AX120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB120" t="n">
-        <v>298</v>
+        <v>-1</v>
       </c>
       <c r="BC120" t="n">
         <v>0</v>
       </c>
       <c r="BD120" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="BE120" t="n">
         <v>0</v>
@@ -57669,64 +57657,64 @@
         <v>1</v>
       </c>
       <c r="BI120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ120" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BK120" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BL120" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BM120" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BN120" t="n">
         <v>7</v>
       </c>
       <c r="BO120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT120" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BU120" t="n">
         <v>1</v>
       </c>
       <c r="BV120" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="BW120" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="BX120" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="BY120" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="BZ120" t="n">
-        <v>0.96</v>
+        <v>1.74</v>
       </c>
       <c r="CA120" t="n">
-        <v>1.63</v>
+        <v>1.09</v>
       </c>
       <c r="CB120" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="CC120" t="n">
         <v>0</v>
@@ -57759,10 +57747,10 @@
         <v>0</v>
       </c>
       <c r="CM120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO120" t="n">
         <v>0</v>
@@ -57774,19 +57762,19 @@
         <v>1</v>
       </c>
       <c r="CR120" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="CS120" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="CT120" t="n">
         <v>1</v>
       </c>
       <c r="CU120" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CV120" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CW120" t="n">
         <v>1</v>
@@ -57795,52 +57783,52 @@
         <v>6</v>
       </c>
       <c r="CY120" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CZ120" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="DA120" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="DB120" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="DC120" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="DF120" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG120" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DH120" t="n">
         <v>0.82</v>
       </c>
       <c r="DI120" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="DJ120" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="DK120" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="DL120" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="DM120" t="n">
-        <v>0.97</v>
+        <v>1.6</v>
       </c>
       <c r="DN120" t="n">
-        <v>2.18</v>
+        <v>3.06</v>
       </c>
       <c r="DO120" t="n">
         <v>15</v>
@@ -57849,7 +57837,7 @@
         <v>1</v>
       </c>
       <c r="DQ120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR120" t="b">
         <v>0</v>
@@ -57864,90 +57852,102 @@
         <v>0</v>
       </c>
       <c r="DV120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW120" t="n">
-        <v>17.48</v>
+        <v>17.01</v>
       </c>
       <c r="DX120" t="n">
-        <v>5.64</v>
+        <v>5.56</v>
       </c>
       <c r="DY120" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="DZ120" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="EA120" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB120" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EC120" t="inlineStr"/>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC120" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
       <c r="ED120" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EE120" t="inlineStr"/>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE120" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
       <c r="EF120" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="EG120" t="inlineStr"/>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EG120" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EH120" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EI120" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EJ120" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EK120" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EL120" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EM120" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EN120" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EO120" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EP120" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -58757,7 +58757,7 @@
         <v>1.5</v>
       </c>
       <c r="DE122" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF122" t="n">
         <v>1.33</v>
@@ -58787,7 +58787,7 @@
         <v>2.75</v>
       </c>
       <c r="DO122" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -60130,7 +60130,7 @@
         <v>84</v>
       </c>
       <c r="DD125" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE125" t="n">
         <v>0.75</v>
@@ -60163,7 +60163,7 @@
         <v>2.9</v>
       </c>
       <c r="DO125" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -63927,7 +63927,7 @@
         <v>2.14</v>
       </c>
       <c r="DO133" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -64863,7 +64863,7 @@
         <v>2.45</v>
       </c>
       <c r="DO135" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -71605,7 +71605,7 @@
         <v>4</v>
       </c>
       <c r="M150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N150" t="n">
         <v>6</v>
@@ -71657,7 +71657,7 @@
         </is>
       </c>
       <c r="AC150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD150" t="n">
         <v>6</v>
@@ -71777,7 +71777,7 @@
         <v>1</v>
       </c>
       <c r="BQ150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR150" t="n">
         <v>5</v>
@@ -71786,7 +71786,7 @@
         <v>1</v>
       </c>
       <c r="BT150" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BU150" t="n">
         <v>1</v>
@@ -72129,10 +72129,10 @@
         <v>22</v>
       </c>
       <c r="Y151" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z151" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
@@ -72575,7 +72575,7 @@
         <v>1</v>
       </c>
       <c r="O152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P152" t="n">
         <v>0</v>
@@ -72621,7 +72621,7 @@
         </is>
       </c>
       <c r="AC152" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD152" t="n">
         <v>1</v>
@@ -72741,7 +72741,7 @@
         <v>0</v>
       </c>
       <c r="BQ152" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BR152" t="n">
         <v>1</v>
@@ -72750,7 +72750,7 @@
         <v>0</v>
       </c>
       <c r="BT152" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BU152" t="n">
         <v>1</v>
@@ -72980,6 +72980,494 @@
       <c r="EP152" t="inlineStr">
         <is>
           <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>15</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CA Osasuna</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>45999.83333333334</v>
+      </c>
+      <c r="G153" t="n">
+        <v>2</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>2</v>
+      </c>
+      <c r="J153" t="n">
+        <v>3</v>
+      </c>
+      <c r="K153" t="n">
+        <v>3</v>
+      </c>
+      <c r="L153" t="n">
+        <v>6</v>
+      </c>
+      <c r="M153" t="n">
+        <v>2</v>
+      </c>
+      <c r="N153" t="n">
+        <v>2</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>6</v>
+      </c>
+      <c r="R153" t="n">
+        <v>5</v>
+      </c>
+      <c r="S153" t="n">
+        <v>8</v>
+      </c>
+      <c r="T153" t="n">
+        <v>6</v>
+      </c>
+      <c r="U153" t="n">
+        <v>14</v>
+      </c>
+      <c r="V153" t="n">
+        <v>11</v>
+      </c>
+      <c r="W153" t="n">
+        <v>15</v>
+      </c>
+      <c r="X153" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>Carretera El Sadar, Iruñea</t>
+        </is>
+      </c>
+      <c r="AC153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>287</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD153" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM153" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV153" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW153" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX153" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY153" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ153" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CA153" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CB153" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="CC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR153" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS153" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU153" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV153" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX153" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY153" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ153" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA153" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB153" t="n">
+        <v>23</v>
+      </c>
+      <c r="DC153" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD153" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DE153" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DF153" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG153" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH153" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DI153" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DJ153" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK153" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL153" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DM153" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DN153" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DO153" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP153" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ153" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW153" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="DX153" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="DY153" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="DZ153" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="EA153" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EB153" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EC153" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="ED153" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EE153" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EF153" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EG153" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="EH153" t="inlineStr">
+        <is>
+          <t>5.10</t>
+        </is>
+      </c>
+      <c r="EI153" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="EJ153" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EK153" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EL153" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EM153" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EN153" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EO153" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EP153" t="inlineStr">
+        <is>
+          <t>1.83</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP153" headerRowCount="1">
-  <autoFilter ref="A1:EP153"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP154" headerRowCount="1">
+  <autoFilter ref="A1:EP154"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP153"/>
+  <dimension ref="A1:EP154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8938,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE17" t="n">
         <v>1.33</v>
@@ -9429,7 +9429,7 @@
         <v>2.75</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="DF18" t="n">
         <v>3</v>
@@ -17482,7 +17482,7 @@
         <v>100</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE35" t="n">
         <v>2</v>
@@ -17515,7 +17515,7 @@
         <v>4.77</v>
       </c>
       <c r="DO35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18929,7 +18929,7 @@
         <v>0.63</v>
       </c>
       <c r="DE38" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="DF38" t="n">
         <v>0.67</v>
@@ -22391,170 +22391,170 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
         <v>45920.6875</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
         <v>3</v>
       </c>
       <c r="J46" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
+        <v>7</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
         <v>8</v>
       </c>
-      <c r="M46" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" t="n">
-        <v>7</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>5</v>
-      </c>
       <c r="R46" t="n">
         <v>3</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>26</v>
+      </c>
+      <c r="V46" t="n">
         <v>6</v>
       </c>
-      <c r="U46" t="n">
-        <v>8</v>
-      </c>
-      <c r="V46" t="n">
-        <v>9</v>
-      </c>
       <c r="W46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="X46" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Y46" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="Z46" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Estadio de Mendizorroza</t>
+          <t>Estadio de la Cerámica</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+          <t>Plaza Labrador, Villarreal</t>
         </is>
       </c>
       <c r="AC46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD46" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.33</v>
+        <v>1.55</v>
       </c>
       <c r="AF46" t="n">
-        <v>3.01</v>
+        <v>3.8</v>
       </c>
       <c r="AG46" t="n">
-        <v>3.28</v>
+        <v>5.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.43</v>
+        <v>2.01</v>
       </c>
       <c r="AJ46" t="n">
-        <v>4.85</v>
+        <v>3.05</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AO46" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AP46" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AR46" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AU46" t="n">
         <v>3</v>
       </c>
       <c r="AV46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
         <v>1</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB46" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="BC46" t="n">
         <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
         <v>0</v>
@@ -22572,73 +22572,73 @@
         <v>1</v>
       </c>
       <c r="BJ46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BL46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BN46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ46" t="n">
         <v>1</v>
       </c>
       <c r="BR46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BS46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BT46" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BU46" t="n">
         <v>1</v>
       </c>
       <c r="BV46" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="BW46" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="BX46" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="BY46" t="n">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="BZ46" t="n">
-        <v>1.22</v>
+        <v>2.84</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.08</v>
+        <v>0.75</v>
       </c>
       <c r="CB46" t="n">
-        <v>2.3</v>
+        <v>3.58</v>
       </c>
       <c r="CC46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG46" t="n">
         <v>0</v>
@@ -22656,13 +22656,13 @@
         <v>0</v>
       </c>
       <c r="CL46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM46" t="n">
         <v>0</v>
       </c>
       <c r="CN46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO46" t="n">
         <v>0</v>
@@ -22674,73 +22674,73 @@
         <v>1</v>
       </c>
       <c r="CR46" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="CS46" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="CT46" t="n">
         <v>1</v>
       </c>
       <c r="CU46" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="CV46" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX46" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY46" t="n">
         <v>20</v>
       </c>
-      <c r="CW46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX46" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY46" t="n">
-        <v>4</v>
-      </c>
       <c r="CZ46" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA46" t="n">
         <v>50</v>
-      </c>
-      <c r="DA46" t="n">
-        <v>100</v>
       </c>
       <c r="DB46" t="n">
         <v>50</v>
       </c>
       <c r="DC46" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="DF46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DH46" t="n">
         <v>1.75</v>
       </c>
       <c r="DI46" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DJ46" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK46" t="n">
         <v>50</v>
       </c>
-      <c r="DK46" t="n">
-        <v>0</v>
-      </c>
       <c r="DL46" t="n">
-        <v>1.19</v>
+        <v>2.48</v>
       </c>
       <c r="DM46" t="n">
-        <v>1.32</v>
+        <v>0.71</v>
       </c>
       <c r="DN46" t="n">
-        <v>2.51</v>
+        <v>3.19</v>
       </c>
       <c r="DO46" t="n">
         <v>15</v>
@@ -22767,87 +22767,99 @@
         <v>1</v>
       </c>
       <c r="DW46" t="n">
-        <v>27.45</v>
+        <v>27.48</v>
       </c>
       <c r="DX46" t="n">
-        <v>4.36</v>
+        <v>4.71</v>
       </c>
       <c r="DY46" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ46" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="EA46" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EB46" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EC46" t="inlineStr"/>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EC46" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
       <c r="ED46" t="inlineStr">
         <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EE46" t="inlineStr"/>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EE46" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
       <c r="EF46" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="EG46" t="inlineStr"/>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EG46" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
       <c r="EH46" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="EI46" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="EJ46" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EK46" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EL46" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EM46" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EN46" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EO46" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EP46" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -22867,170 +22879,170 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
         <v>45920.6875</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" t="n">
         <v>3</v>
       </c>
       <c r="J47" t="n">
+        <v>4</v>
+      </c>
+      <c r="K47" t="n">
+        <v>4</v>
+      </c>
+      <c r="L47" t="n">
+        <v>8</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
         <v>7</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>3</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>6</v>
+      </c>
+      <c r="U47" t="n">
+        <v>8</v>
+      </c>
+      <c r="V47" t="n">
+        <v>9</v>
+      </c>
+      <c r="W47" t="n">
+        <v>20</v>
+      </c>
+      <c r="X47" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Estadio de Mendizorroza</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+        </is>
+      </c>
+      <c r="AC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD47" t="n">
         <v>7</v>
       </c>
-      <c r="M47" t="n">
-        <v>2</v>
-      </c>
-      <c r="N47" t="n">
-        <v>2</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>8</v>
-      </c>
-      <c r="R47" t="n">
-        <v>3</v>
-      </c>
-      <c r="S47" t="n">
-        <v>18</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3</v>
-      </c>
-      <c r="U47" t="n">
-        <v>26</v>
-      </c>
-      <c r="V47" t="n">
-        <v>6</v>
-      </c>
-      <c r="W47" t="n">
-        <v>10</v>
-      </c>
-      <c r="X47" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>66</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Estadio de la Cerámica</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>Plaza Labrador, Villarreal</t>
-        </is>
-      </c>
-      <c r="AC47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>3</v>
-      </c>
       <c r="AE47" t="n">
-        <v>1.55</v>
+        <v>2.33</v>
       </c>
       <c r="AF47" t="n">
-        <v>3.8</v>
+        <v>3.01</v>
       </c>
       <c r="AG47" t="n">
-        <v>5.25</v>
+        <v>3.28</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.01</v>
+        <v>2.43</v>
       </c>
       <c r="AJ47" t="n">
-        <v>3.05</v>
+        <v>4.85</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AN47" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AO47" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AP47" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AU47" t="n">
         <v>3</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW47" t="n">
         <v>1</v>
       </c>
       <c r="AX47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB47" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="BC47" t="n">
         <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BE47" t="n">
         <v>0</v>
@@ -23048,175 +23060,175 @@
         <v>1</v>
       </c>
       <c r="BJ47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT47" t="n">
         <v>6</v>
       </c>
-      <c r="BL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN47" t="n">
+      <c r="BU47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV47" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW47" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY47" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CA47" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CB47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR47" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS47" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU47" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV47" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX47" t="n">
         <v>6</v>
       </c>
-      <c r="BO47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP47" t="n">
-        <v>3</v>
-      </c>
-      <c r="BQ47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS47" t="n">
+      <c r="CY47" t="n">
         <v>4</v>
       </c>
-      <c r="BT47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV47" t="n">
-        <v>90</v>
-      </c>
-      <c r="BW47" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX47" t="n">
-        <v>112</v>
-      </c>
-      <c r="BY47" t="n">
-        <v>57</v>
-      </c>
-      <c r="BZ47" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CA47" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB47" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="CC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR47" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS47" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU47" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV47" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX47" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY47" t="n">
-        <v>20</v>
-      </c>
       <c r="CZ47" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DA47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB47" t="n">
         <v>50</v>
       </c>
       <c r="DC47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD47" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="DF47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DG47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DH47" t="n">
         <v>1.75</v>
       </c>
       <c r="DI47" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DJ47" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK47" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL47" t="n">
-        <v>2.48</v>
+        <v>1.19</v>
       </c>
       <c r="DM47" t="n">
-        <v>0.71</v>
+        <v>1.32</v>
       </c>
       <c r="DN47" t="n">
-        <v>3.19</v>
+        <v>2.51</v>
       </c>
       <c r="DO47" t="n">
         <v>15</v>
@@ -23243,99 +23255,87 @@
         <v>1</v>
       </c>
       <c r="DW47" t="n">
-        <v>27.48</v>
+        <v>27.45</v>
       </c>
       <c r="DX47" t="n">
-        <v>4.71</v>
+        <v>4.36</v>
       </c>
       <c r="DY47" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="DZ47" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="EA47" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EB47" t="inlineStr">
         <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC47" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
-      </c>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EC47" t="inlineStr"/>
       <c r="ED47" t="inlineStr">
         <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE47" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EE47" t="inlineStr"/>
       <c r="EF47" t="inlineStr">
         <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="EG47" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EG47" t="inlineStr"/>
       <c r="EH47" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="EI47" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EJ47" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="EK47" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EL47" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EM47" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EN47" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="EO47" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EP47" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.16</t>
         </is>
       </c>
     </row>
@@ -25723,40 +25723,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -25765,101 +25765,101 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T53" t="n">
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W53" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="X53" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y53" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="Z53" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>San Mamés Barria</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="AF53" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="AG53" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AJ53" t="n">
-        <v>4.05</v>
+        <v>3.08</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AO53" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AR53" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AU53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV53" t="n">
         <v>0</v>
@@ -25868,13 +25868,13 @@
         <v>1</v>
       </c>
       <c r="AX53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA53" t="n">
         <v>1</v>
@@ -25886,7 +25886,7 @@
         <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BE53" t="n">
         <v>0</v>
@@ -25901,28 +25901,28 @@
         <v>1</v>
       </c>
       <c r="BI53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BJ53" t="n">
         <v>1</v>
       </c>
       <c r="BK53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BN53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ53" t="n">
         <v>0</v>
@@ -25931,7 +25931,7 @@
         <v>2</v>
       </c>
       <c r="BS53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT53" t="n">
         <v>2</v>
@@ -25940,25 +25940,25 @@
         <v>1</v>
       </c>
       <c r="BV53" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="BW53" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BX53" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="BY53" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="BZ53" t="n">
-        <v>2.59</v>
+        <v>1.96</v>
       </c>
       <c r="CA53" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="CB53" t="n">
-        <v>3.26</v>
+        <v>2.71</v>
       </c>
       <c r="CC53" t="n">
         <v>0</v>
@@ -25988,10 +25988,10 @@
         <v>0</v>
       </c>
       <c r="CL53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN53" t="n">
         <v>0</v>
@@ -26006,19 +26006,19 @@
         <v>1</v>
       </c>
       <c r="CR53" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="CS53" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CT53" t="n">
         <v>1</v>
       </c>
       <c r="CU53" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="CV53" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="CW53" t="n">
         <v>1</v>
@@ -26027,55 +26027,55 @@
         <v>3</v>
       </c>
       <c r="CY53" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CZ53" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA53" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB53" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC53" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD53" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DE53" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF53" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DI53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DJ53" t="n">
         <v>59</v>
       </c>
-      <c r="DA53" t="n">
-        <v>59</v>
-      </c>
-      <c r="DB53" t="n">
-        <v>17</v>
-      </c>
-      <c r="DC53" t="n">
-        <v>84</v>
-      </c>
-      <c r="DD53" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DE53" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="DF53" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH53" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI53" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DJ53" t="n">
-        <v>42</v>
-      </c>
       <c r="DK53" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="DL53" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="DM53" t="n">
-        <v>0.47</v>
+        <v>1.18</v>
       </c>
       <c r="DN53" t="n">
-        <v>1.62</v>
+        <v>2.61</v>
       </c>
       <c r="DO53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26084,10 +26084,10 @@
         <v>1</v>
       </c>
       <c r="DR53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT53" t="b">
         <v>0</v>
@@ -26099,75 +26099,79 @@
         <v>1</v>
       </c>
       <c r="DW53" t="n">
-        <v>20.5</v>
+        <v>17.43</v>
       </c>
       <c r="DX53" t="n">
-        <v>6.93</v>
+        <v>4.72</v>
       </c>
       <c r="DY53" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="DZ53" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="EA53" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EB53" t="inlineStr">
         <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC53" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED53" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE53" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="EC53" t="inlineStr"/>
-      <c r="ED53" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EE53" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="EF53" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EG53" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="EH53" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="EI53" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="EJ53" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EK53" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EL53" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EM53" t="inlineStr">
@@ -26182,12 +26186,12 @@
       </c>
       <c r="EO53" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EP53" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -26207,143 +26211,143 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
         <v>8</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L54" t="n">
+        <v>11</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>4</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>10</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2</v>
+      </c>
+      <c r="S54" t="n">
+        <v>11</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>21</v>
+      </c>
+      <c r="V54" t="n">
+        <v>5</v>
+      </c>
+      <c r="W54" t="n">
         <v>9</v>
       </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>2</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>5</v>
-      </c>
-      <c r="R54" t="n">
-        <v>3</v>
-      </c>
-      <c r="S54" t="n">
-        <v>12</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3</v>
-      </c>
-      <c r="U54" t="n">
-        <v>17</v>
-      </c>
-      <c r="V54" t="n">
-        <v>6</v>
-      </c>
-      <c r="W54" t="n">
-        <v>19</v>
-      </c>
       <c r="X54" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y54" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="Z54" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>San Mamés Barria</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE54" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ54" t="n">
         <v>1.47</v>
       </c>
-      <c r="AF54" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AR54" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AS54" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AU54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV54" t="n">
         <v>0</v>
@@ -26352,13 +26356,13 @@
         <v>1</v>
       </c>
       <c r="AX54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA54" t="n">
         <v>1</v>
@@ -26370,7 +26374,7 @@
         <v>0</v>
       </c>
       <c r="BD54" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BE54" t="n">
         <v>0</v>
@@ -26385,28 +26389,28 @@
         <v>1</v>
       </c>
       <c r="BI54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BJ54" t="n">
         <v>1</v>
       </c>
       <c r="BK54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BL54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BN54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ54" t="n">
         <v>0</v>
@@ -26415,7 +26419,7 @@
         <v>2</v>
       </c>
       <c r="BS54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT54" t="n">
         <v>2</v>
@@ -26424,139 +26428,139 @@
         <v>1</v>
       </c>
       <c r="BV54" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="BW54" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BX54" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="BY54" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ54" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CA54" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CB54" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR54" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS54" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU54" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV54" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX54" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY54" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ54" t="n">
         <v>59</v>
       </c>
-      <c r="BZ54" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CA54" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB54" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="CC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR54" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS54" t="n">
+      <c r="DA54" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB54" t="n">
         <v>17</v>
       </c>
-      <c r="CT54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU54" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV54" t="n">
-        <v>19</v>
-      </c>
-      <c r="CW54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX54" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY54" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ54" t="n">
-        <v>42</v>
-      </c>
-      <c r="DA54" t="n">
-        <v>67</v>
-      </c>
-      <c r="DB54" t="n">
-        <v>42</v>
-      </c>
       <c r="DC54" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.78</v>
+        <v>2.11</v>
       </c>
       <c r="DE54" t="n">
         <v>0.43</v>
       </c>
       <c r="DF54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="DH54" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="DI54" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="DJ54" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="DK54" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="DL54" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="DM54" t="n">
-        <v>1.18</v>
+        <v>0.47</v>
       </c>
       <c r="DN54" t="n">
-        <v>2.61</v>
+        <v>1.62</v>
       </c>
       <c r="DO54" t="n">
         <v>15</v>
@@ -26568,10 +26572,10 @@
         <v>1</v>
       </c>
       <c r="DR54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT54" t="b">
         <v>0</v>
@@ -26583,79 +26587,75 @@
         <v>1</v>
       </c>
       <c r="DW54" t="n">
-        <v>17.43</v>
+        <v>20.5</v>
       </c>
       <c r="DX54" t="n">
-        <v>4.72</v>
+        <v>6.93</v>
       </c>
       <c r="DY54" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="DZ54" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA54" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EB54" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC54" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC54" t="inlineStr"/>
       <c r="ED54" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EE54" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF54" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EG54" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EH54" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EI54" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EJ54" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EK54" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EL54" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EM54" t="inlineStr">
@@ -26670,12 +26670,12 @@
       </c>
       <c r="EO54" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP54" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -26695,12 +26695,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
@@ -26710,25 +26710,25 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -26740,119 +26740,119 @@
         <v>2</v>
       </c>
       <c r="R55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S55" t="n">
+        <v>9</v>
+      </c>
+      <c r="T55" t="n">
         <v>14</v>
       </c>
-      <c r="T55" t="n">
-        <v>7</v>
-      </c>
       <c r="U55" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V55" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="W55" t="n">
         <v>17</v>
       </c>
       <c r="X55" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Y55" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="Z55" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Estadio Ramón Sánchez Pizjuán</t>
+          <t>Estadio Ciudad de Valencia</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Avenida de Eduardo Dato, Sevilla</t>
+          <t>Calle San Vicente de Paúl 44, Valencia</t>
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE55" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="AF55" t="n">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI55" t="n">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="AJ55" t="n">
-        <v>3.4</v>
+        <v>2.07</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL55" t="n">
         <v>2</v>
       </c>
       <c r="AM55" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN55" t="n">
         <v>1.5</v>
       </c>
-      <c r="AN55" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AO55" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP55" t="n">
         <v>2.38</v>
       </c>
-      <c r="AP55" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AQ55" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.72</v>
+        <v>4.05</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AU55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV55" t="n">
         <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX55" t="n">
         <v>1</v>
       </c>
       <c r="AY55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB55" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="BC55" t="n">
         <v>0</v>
@@ -26873,76 +26873,76 @@
         <v>1</v>
       </c>
       <c r="BI55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL55" t="n">
         <v>2</v>
       </c>
       <c r="BM55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BN55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO55" t="n">
         <v>0</v>
       </c>
       <c r="BP55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU55" t="n">
         <v>1</v>
       </c>
       <c r="BV55" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="BW55" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="BX55" t="n">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="BY55" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="BZ55" t="n">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
       <c r="CA55" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="CB55" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="CC55" t="n">
         <v>0</v>
       </c>
       <c r="CD55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE55" t="n">
         <v>0</v>
       </c>
       <c r="CF55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG55" t="n">
         <v>0</v>
@@ -26966,7 +26966,7 @@
         <v>0</v>
       </c>
       <c r="CN55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO55" t="n">
         <v>0</v>
@@ -26978,73 +26978,73 @@
         <v>1</v>
       </c>
       <c r="CR55" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="CS55" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="CT55" t="n">
         <v>1</v>
       </c>
       <c r="CU55" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="CV55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CW55" t="n">
         <v>1</v>
       </c>
       <c r="CX55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY55" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CZ55" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA55" t="n">
         <v>100</v>
       </c>
       <c r="DB55" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="DC55" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1</v>
+        <v>0.17</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF55" t="n">
         <v>0.5</v>
       </c>
       <c r="DG55" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DH55" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="DI55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ55" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK55" t="n">
         <v>0</v>
       </c>
       <c r="DL55" t="n">
-        <v>1.24</v>
+        <v>0.84</v>
       </c>
       <c r="DM55" t="n">
-        <v>0.93</v>
+        <v>2.34</v>
       </c>
       <c r="DN55" t="n">
-        <v>2.17</v>
+        <v>3.18</v>
       </c>
       <c r="DO55" t="n">
         <v>15</v>
@@ -27059,10 +27059,10 @@
         <v>1</v>
       </c>
       <c r="DS55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU55" t="b">
         <v>0</v>
@@ -27071,99 +27071,87 @@
         <v>1</v>
       </c>
       <c r="DW55" t="n">
-        <v>27.52</v>
+        <v>22.21</v>
       </c>
       <c r="DX55" t="n">
-        <v>3.08</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DY55" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ55" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="EA55" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EB55" t="inlineStr"/>
+      <c r="EC55" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="ED55" t="inlineStr"/>
+      <c r="EE55" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF55" t="inlineStr"/>
+      <c r="EG55" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH55" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI55" t="inlineStr">
+        <is>
+          <t>5.86</t>
+        </is>
+      </c>
+      <c r="EJ55" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="EK55" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL55" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EB55" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EC55" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="ED55" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EE55" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF55" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG55" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EH55" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EI55" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EJ55" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="EK55" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EL55" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
       <c r="EM55" t="inlineStr">
         <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN55" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EO55" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EP55" t="inlineStr">
+        <is>
           <t>1.68</t>
-        </is>
-      </c>
-      <c r="EN55" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EO55" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EP55" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -27183,12 +27171,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -27198,149 +27186,149 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I56" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3</v>
+      </c>
+      <c r="L56" t="n">
+        <v>6</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2</v>
+      </c>
+      <c r="R56" t="n">
         <v>5</v>
       </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
+      <c r="S56" t="n">
+        <v>14</v>
+      </c>
+      <c r="T56" t="n">
         <v>7</v>
       </c>
-      <c r="L56" t="n">
-        <v>8</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>2</v>
-      </c>
-      <c r="R56" t="n">
-        <v>10</v>
-      </c>
-      <c r="S56" t="n">
-        <v>9</v>
-      </c>
-      <c r="T56" t="n">
-        <v>14</v>
-      </c>
       <c r="U56" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V56" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="W56" t="n">
         <v>17</v>
       </c>
       <c r="X56" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y56" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="Z56" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Estadio Ciudad de Valencia</t>
+          <t>Estadio Ramón Sánchez Pizjuán</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Calle San Vicente de Paúl 44, Valencia</t>
+          <t>Avenida de Eduardo Dato, Sevilla</t>
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE56" t="n">
-        <v>8</v>
+        <v>3.15</v>
       </c>
       <c r="AF56" t="n">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI56" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT56" t="n">
         <v>1.4</v>
       </c>
-      <c r="AJ56" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AU56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV56" t="n">
         <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX56" t="n">
         <v>1</v>
       </c>
       <c r="AY56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB56" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="BC56" t="n">
         <v>0</v>
@@ -27361,76 +27349,76 @@
         <v>1</v>
       </c>
       <c r="BI56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT56" t="n">
         <v>5</v>
       </c>
-      <c r="BK56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL56" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM56" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN56" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ56" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR56" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT56" t="n">
-        <v>2</v>
-      </c>
       <c r="BU56" t="n">
         <v>1</v>
       </c>
       <c r="BV56" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="BW56" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="BX56" t="n">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="BY56" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="BZ56" t="n">
-        <v>1.02</v>
+        <v>1.67</v>
       </c>
       <c r="CA56" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="CB56" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="CC56" t="n">
         <v>0</v>
       </c>
       <c r="CD56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE56" t="n">
         <v>0</v>
       </c>
       <c r="CF56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG56" t="n">
         <v>0</v>
@@ -27454,7 +27442,7 @@
         <v>0</v>
       </c>
       <c r="CN56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO56" t="n">
         <v>0</v>
@@ -27466,73 +27454,73 @@
         <v>1</v>
       </c>
       <c r="CR56" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="CS56" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="CT56" t="n">
         <v>1</v>
       </c>
       <c r="CU56" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV56" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW56" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX56" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY56" t="n">
         <v>9</v>
       </c>
-      <c r="CV56" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW56" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX56" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY56" t="n">
-        <v>3</v>
-      </c>
       <c r="CZ56" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA56" t="n">
         <v>100</v>
       </c>
       <c r="DB56" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC56" t="n">
         <v>75</v>
       </c>
-      <c r="DC56" t="n">
-        <v>100</v>
-      </c>
       <c r="DD56" t="n">
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="DE56" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF56" t="n">
         <v>0.5</v>
       </c>
       <c r="DG56" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DH56" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ56" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK56" t="n">
         <v>0</v>
       </c>
       <c r="DL56" t="n">
-        <v>0.84</v>
+        <v>1.24</v>
       </c>
       <c r="DM56" t="n">
-        <v>2.34</v>
+        <v>0.93</v>
       </c>
       <c r="DN56" t="n">
-        <v>3.18</v>
+        <v>2.17</v>
       </c>
       <c r="DO56" t="n">
         <v>15</v>
@@ -27547,10 +27535,10 @@
         <v>1</v>
       </c>
       <c r="DS56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU56" t="b">
         <v>0</v>
@@ -27559,87 +27547,99 @@
         <v>1</v>
       </c>
       <c r="DW56" t="n">
-        <v>22.21</v>
+        <v>27.52</v>
       </c>
       <c r="DX56" t="n">
-        <v>8.289999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="DY56" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="DZ56" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA56" t="inlineStr">
         <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EB56" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EB56" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
       <c r="EC56" t="inlineStr">
         <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="ED56" t="inlineStr"/>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="ED56" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="EE56" t="inlineStr">
         <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EF56" t="inlineStr"/>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EF56" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
       <c r="EG56" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EH56" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EI56" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EJ56" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EK56" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EL56" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EM56" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EN56" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EO56" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EP56" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -28127,40 +28127,40 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>45924.8125</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L58" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -28169,128 +28169,128 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R58" t="n">
         <v>3</v>
       </c>
       <c r="S58" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T58" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U58" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="V58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W58" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="X58" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y58" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="Z58" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Anoeta</t>
+          <t>Estadio Wanda Metropolitano</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
+          <t>Rosas, Madrid</t>
         </is>
       </c>
       <c r="AC58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF58" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG58" t="n">
-        <v>5.13</v>
+        <v>6.5</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AI58" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AJ58" t="n">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AL58" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AM58" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AN58" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AO58" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AP58" t="n">
         <v>1.99</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AR58" t="n">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="AS58" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AU58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB58" t="n">
-        <v>290</v>
+        <v>117</v>
       </c>
       <c r="BC58" t="n">
         <v>0</v>
       </c>
       <c r="BD58" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="BE58" t="n">
         <v>0</v>
@@ -28305,10 +28305,10 @@
         <v>1</v>
       </c>
       <c r="BI58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BJ58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK58" t="n">
         <v>4</v>
@@ -28317,52 +28317,52 @@
         <v>2</v>
       </c>
       <c r="BM58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BN58" t="n">
         <v>6</v>
       </c>
       <c r="BO58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BS58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT58" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BU58" t="n">
         <v>1</v>
       </c>
       <c r="BV58" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="BW58" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="BX58" t="n">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="BY58" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="BZ58" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="CA58" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="CB58" t="n">
-        <v>2.69</v>
+        <v>3.33</v>
       </c>
       <c r="CC58" t="n">
         <v>0</v>
@@ -28395,7 +28395,7 @@
         <v>0</v>
       </c>
       <c r="CM58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN58" t="n">
         <v>0</v>
@@ -28413,70 +28413,70 @@
         <v>22</v>
       </c>
       <c r="CS58" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CT58" t="n">
         <v>1</v>
       </c>
       <c r="CU58" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CV58" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="CW58" t="n">
         <v>1</v>
       </c>
       <c r="CX58" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CZ58" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="DA58" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="DB58" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="DC58" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.43</v>
+        <v>2.75</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.5</v>
+        <v>1.11</v>
       </c>
       <c r="DF58" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DG58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DH58" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="DI58" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="DJ58" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="DK58" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DL58" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="DM58" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="DN58" t="n">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="DO58" t="n">
         <v>15</v>
@@ -28485,97 +28485,117 @@
         <v>1</v>
       </c>
       <c r="DQ58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU58" t="b">
         <v>0</v>
       </c>
       <c r="DV58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW58" t="n">
-        <v>13.25</v>
+        <v>18.88</v>
       </c>
       <c r="DX58" t="n">
-        <v>3.2</v>
+        <v>6.34</v>
       </c>
       <c r="DY58" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="DZ58" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="EA58" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB58" t="inlineStr">
         <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EC58" t="inlineStr"/>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC58" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
       <c r="ED58" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EE58" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EF58" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EG58" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EH58" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="EI58" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="EJ58" t="inlineStr">
         <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EK58" t="inlineStr"/>
-      <c r="EL58" t="inlineStr"/>
-      <c r="EM58" t="inlineStr"/>
-      <c r="EN58" t="inlineStr"/>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EK58" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EL58" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EM58" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EN58" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
       <c r="EO58" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EP58" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.18</t>
         </is>
       </c>
     </row>
@@ -28595,40 +28615,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
         <v>45924.8125</v>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K59" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L59" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -28637,128 +28657,128 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R59" t="n">
         <v>3</v>
       </c>
       <c r="S59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U59" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="V59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W59" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="X59" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y59" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Z59" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Estadio Wanda Metropolitano</t>
+          <t>Estadio Municipal de Anoeta</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Rosas, Madrid</t>
+          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
         </is>
       </c>
       <c r="AC59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF59" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AG59" t="n">
-        <v>6.5</v>
+        <v>5.13</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AJ59" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AL59" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AM59" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AN59" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AO59" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AP59" t="n">
         <v>1.99</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AR59" t="n">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="AS59" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AT59" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AU59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB59" t="n">
-        <v>117</v>
+        <v>290</v>
       </c>
       <c r="BC59" t="n">
         <v>0</v>
       </c>
       <c r="BD59" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="BE59" t="n">
         <v>0</v>
@@ -28773,10 +28793,10 @@
         <v>1</v>
       </c>
       <c r="BI59" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BJ59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BK59" t="n">
         <v>4</v>
@@ -28785,52 +28805,52 @@
         <v>2</v>
       </c>
       <c r="BM59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BN59" t="n">
         <v>6</v>
       </c>
       <c r="BO59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BS59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT59" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BU59" t="n">
         <v>1</v>
       </c>
       <c r="BV59" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="BW59" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="BX59" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="BY59" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="BZ59" t="n">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="CA59" t="n">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="CB59" t="n">
-        <v>3.33</v>
+        <v>2.69</v>
       </c>
       <c r="CC59" t="n">
         <v>0</v>
@@ -28863,7 +28883,7 @@
         <v>0</v>
       </c>
       <c r="CM59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN59" t="n">
         <v>0</v>
@@ -28881,70 +28901,70 @@
         <v>22</v>
       </c>
       <c r="CS59" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CT59" t="n">
         <v>1</v>
       </c>
       <c r="CU59" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CV59" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="CW59" t="n">
         <v>1</v>
       </c>
       <c r="CX59" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="CY59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CZ59" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="DA59" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DB59" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="DC59" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DD59" t="n">
-        <v>2.75</v>
+        <v>1.25</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.11</v>
+        <v>0.5</v>
       </c>
       <c r="DF59" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="DG59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH59" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="DI59" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="DJ59" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="DK59" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL59" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="DM59" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="DN59" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="DO59" t="n">
         <v>15</v>
@@ -28953,117 +28973,97 @@
         <v>1</v>
       </c>
       <c r="DQ59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU59" t="b">
         <v>0</v>
       </c>
       <c r="DV59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW59" t="n">
-        <v>18.88</v>
+        <v>13.25</v>
       </c>
       <c r="DX59" t="n">
-        <v>6.34</v>
+        <v>3.2</v>
       </c>
       <c r="DY59" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="DZ59" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EA59" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EB59" t="inlineStr">
         <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EC59" t="inlineStr">
-        <is>
-          <t>3.42</t>
-        </is>
-      </c>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EC59" t="inlineStr"/>
       <c r="ED59" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EE59" t="inlineStr">
+        <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="EE59" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
       <c r="EF59" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EG59" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EH59" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="EI59" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="EJ59" t="inlineStr">
         <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EK59" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="EL59" t="inlineStr">
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EK59" t="inlineStr"/>
+      <c r="EL59" t="inlineStr"/>
+      <c r="EM59" t="inlineStr"/>
+      <c r="EN59" t="inlineStr"/>
+      <c r="EO59" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EP59" t="inlineStr">
         <is>
           <t>2.06</t>
-        </is>
-      </c>
-      <c r="EM59" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EN59" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="EO59" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EP59" t="inlineStr">
-        <is>
-          <t>2.18</t>
         </is>
       </c>
     </row>
@@ -33651,7 +33651,7 @@
         <v>3.83</v>
       </c>
       <c r="DO69" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -38043,146 +38043,146 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45935.6875</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K79" t="n">
         <v>5</v>
       </c>
       <c r="L79" t="n">
+        <v>15</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2</v>
+      </c>
+      <c r="N79" t="n">
+        <v>6</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>5</v>
+      </c>
+      <c r="R79" t="n">
+        <v>3</v>
+      </c>
+      <c r="S79" t="n">
+        <v>9</v>
+      </c>
+      <c r="T79" t="n">
+        <v>9</v>
+      </c>
+      <c r="U79" t="n">
+        <v>14</v>
+      </c>
+      <c r="V79" t="n">
         <v>12</v>
       </c>
-      <c r="M79" t="n">
-        <v>1</v>
-      </c>
-      <c r="N79" t="n">
-        <v>2</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>3</v>
-      </c>
-      <c r="R79" t="n">
-        <v>2</v>
-      </c>
-      <c r="S79" t="n">
-        <v>7</v>
-      </c>
-      <c r="T79" t="n">
-        <v>5</v>
-      </c>
-      <c r="U79" t="n">
-        <v>10</v>
-      </c>
-      <c r="V79" t="n">
-        <v>7</v>
-      </c>
       <c r="W79" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X79" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Y79" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z79" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Anoeta</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="AF79" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AG79" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AI79" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AJ79" t="n">
-        <v>3.85</v>
+        <v>2.96</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AM79" t="n">
         <v>1.44</v>
       </c>
       <c r="AN79" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AO79" t="n">
         <v>2.55</v>
       </c>
       <c r="AP79" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AR79" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AU79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW79" t="n">
         <v>0</v>
@@ -38191,22 +38191,22 @@
         <v>0</v>
       </c>
       <c r="AY79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38221,178 +38221,178 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BJ79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BK79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR79" t="n">
         <v>4</v>
       </c>
-      <c r="BL79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM79" t="n">
+      <c r="BS79" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX79" t="n">
         <v>6</v>
       </c>
-      <c r="BN79" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT79" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV79" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW79" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX79" t="n">
-        <v>101</v>
-      </c>
-      <c r="BY79" t="n">
-        <v>90</v>
-      </c>
-      <c r="BZ79" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="CA79" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB79" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN79" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR79" t="n">
-        <v>14</v>
-      </c>
-      <c r="CS79" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU79" t="n">
-        <v>21</v>
-      </c>
-      <c r="CV79" t="n">
+      <c r="CY79" t="n">
         <v>13</v>
       </c>
-      <c r="CW79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX79" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY79" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ79" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="DA79" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="DB79" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="DC79" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.43</v>
+        <v>2.11</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="DF79" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="DG79" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DH79" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="DI79" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="DJ79" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="DK79" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="DN79" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="DO79" t="n">
         <v>15</v>
@@ -38401,10 +38401,10 @@
         <v>1</v>
       </c>
       <c r="DQ79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS79" t="b">
         <v>0</v>
@@ -38416,94 +38416,102 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW79" t="n">
-        <v>17.19</v>
+        <v>17.75</v>
       </c>
       <c r="DX79" t="n">
-        <v>3.66</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EB79" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EC79" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED79" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EE79" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EG79" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EJ79" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EK79" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EL79" t="inlineStr">
+        <is>
           <t>2.02</t>
         </is>
       </c>
-      <c r="EB79" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC79" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="ED79" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE79" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF79" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG79" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="EH79" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="EI79" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="EJ79" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EK79" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EL79" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EM79" t="inlineStr"/>
-      <c r="EN79" t="inlineStr"/>
+      <c r="EM79" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EN79" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.68</t>
         </is>
       </c>
     </row>
@@ -38523,40 +38531,40 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45935.6875</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K80" t="n">
         <v>5</v>
       </c>
       <c r="L80" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -38565,104 +38573,104 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
+        <v>3</v>
+      </c>
+      <c r="R80" t="n">
+        <v>2</v>
+      </c>
+      <c r="S80" t="n">
+        <v>7</v>
+      </c>
+      <c r="T80" t="n">
         <v>5</v>
       </c>
-      <c r="R80" t="n">
-        <v>3</v>
-      </c>
-      <c r="S80" t="n">
-        <v>9</v>
-      </c>
-      <c r="T80" t="n">
-        <v>9</v>
-      </c>
       <c r="U80" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V80" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W80" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="X80" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Y80" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z80" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>Estadio Municipal de Anoeta</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
         </is>
       </c>
       <c r="AC80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="AF80" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AJ80" t="n">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AL80" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AM80" t="n">
         <v>1.44</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AO80" t="n">
         <v>2.55</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AR80" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AU80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW80" t="n">
         <v>0</v>
@@ -38671,22 +38679,22 @@
         <v>0</v>
       </c>
       <c r="AY80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB80" t="n">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -38701,178 +38709,178 @@
         <v>1</v>
       </c>
       <c r="BI80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BJ80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BK80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM80" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>101</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV80" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX80" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY80" t="n">
         <v>10</v>
       </c>
-      <c r="BN80" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR80" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS80" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT80" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV80" t="n">
-        <v>66</v>
-      </c>
-      <c r="BW80" t="n">
-        <v>34</v>
-      </c>
-      <c r="BX80" t="n">
-        <v>107</v>
-      </c>
-      <c r="BY80" t="n">
-        <v>98</v>
-      </c>
-      <c r="BZ80" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CA80" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CB80" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CC80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR80" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS80" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU80" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV80" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX80" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY80" t="n">
-        <v>13</v>
-      </c>
       <c r="CZ80" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="DA80" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="DB80" t="n">
+        <v>59</v>
+      </c>
+      <c r="DC80" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD80" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE80" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DF80" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DI80" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DJ80" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK80" t="n">
         <v>29</v>
       </c>
-      <c r="DC80" t="n">
-        <v>88</v>
-      </c>
-      <c r="DD80" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DE80" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DF80" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DG80" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH80" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DI80" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DJ80" t="n">
-        <v>46</v>
-      </c>
-      <c r="DK80" t="n">
-        <v>13</v>
-      </c>
       <c r="DL80" t="n">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="DM80" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="DN80" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="DO80" t="n">
         <v>15</v>
@@ -38881,10 +38889,10 @@
         <v>1</v>
       </c>
       <c r="DQ80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS80" t="b">
         <v>0</v>
@@ -38896,102 +38904,94 @@
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW80" t="n">
-        <v>17.75</v>
+        <v>17.19</v>
       </c>
       <c r="DX80" t="n">
-        <v>9.369999999999999</v>
+        <v>3.66</v>
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EB80" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EC80" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="ED80" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EE80" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EF80" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EG80" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EH80" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EI80" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EJ80" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EK80" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EL80" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EM80" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EN80" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM80" t="inlineStr"/>
+      <c r="EN80" t="inlineStr"/>
       <c r="EO80" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EP80" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.84</t>
         </is>
       </c>
     </row>
@@ -40741,7 +40741,7 @@
         <v>3</v>
       </c>
       <c r="DE84" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="DF84" t="n">
         <v>3</v>
@@ -40771,7 +40771,7 @@
         <v>3.49</v>
       </c>
       <c r="DO84" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -44526,7 +44526,7 @@
         <v>63</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE92" t="n">
         <v>1.25</v>
@@ -49293,7 +49293,7 @@
         <v>1.57</v>
       </c>
       <c r="DE102" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="DF102" t="n">
         <v>1.25</v>
@@ -50702,7 +50702,7 @@
         <v>30</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE105" t="n">
         <v>1</v>
@@ -50735,7 +50735,7 @@
         <v>2.92</v>
       </c>
       <c r="DO105" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -61545,7 +61545,7 @@
         <v>1.63</v>
       </c>
       <c r="DE128" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="DF128" t="n">
         <v>2</v>
@@ -65778,7 +65778,7 @@
         <v>67</v>
       </c>
       <c r="DD137" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE137" t="n">
         <v>1.86</v>
@@ -67251,7 +67251,7 @@
         <v>3.35</v>
       </c>
       <c r="DO140" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -71437,7 +71437,7 @@
         <v>2</v>
       </c>
       <c r="DE149" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="DF149" t="n">
         <v>1.86</v>
@@ -73471,6 +73471,494 @@
         </is>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>16</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Girona FC</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>46003.83333333334</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="n">
+        <v>2</v>
+      </c>
+      <c r="I154" t="n">
+        <v>3</v>
+      </c>
+      <c r="J154" t="n">
+        <v>4</v>
+      </c>
+      <c r="K154" t="n">
+        <v>3</v>
+      </c>
+      <c r="L154" t="n">
+        <v>7</v>
+      </c>
+      <c r="M154" t="n">
+        <v>1</v>
+      </c>
+      <c r="N154" t="n">
+        <v>2</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>4</v>
+      </c>
+      <c r="R154" t="n">
+        <v>3</v>
+      </c>
+      <c r="S154" t="n">
+        <v>5</v>
+      </c>
+      <c r="T154" t="n">
+        <v>11</v>
+      </c>
+      <c r="U154" t="n">
+        <v>9</v>
+      </c>
+      <c r="V154" t="n">
+        <v>14</v>
+      </c>
+      <c r="W154" t="n">
+        <v>20</v>
+      </c>
+      <c r="X154" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Anoeta</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
+        </is>
+      </c>
+      <c r="AC154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>312</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>71</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI154" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM154" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT154" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV154" t="n">
+        <v>87</v>
+      </c>
+      <c r="BW154" t="n">
+        <v>79</v>
+      </c>
+      <c r="BX154" t="n">
+        <v>177</v>
+      </c>
+      <c r="BY154" t="n">
+        <v>173</v>
+      </c>
+      <c r="BZ154" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CA154" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CB154" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="CC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR154" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS154" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU154" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV154" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX154" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY154" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ154" t="n">
+        <v>64</v>
+      </c>
+      <c r="DA154" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB154" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC154" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD154" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE154" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF154" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG154" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DH154" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DI154" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DJ154" t="n">
+        <v>36</v>
+      </c>
+      <c r="DK154" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL154" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DM154" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DN154" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DO154" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW154" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="DX154" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="DY154" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="DZ154" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA154" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EB154" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC154" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="ED154" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EE154" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EF154" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EG154" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EH154" t="inlineStr">
+        <is>
+          <t>5.09</t>
+        </is>
+      </c>
+      <c r="EI154" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EJ154" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EK154" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EL154" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EM154" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EN154" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EO154" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EP154" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP154" headerRowCount="1">
-  <autoFilter ref="A1:EP154"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP161" headerRowCount="1">
+  <autoFilter ref="A1:EP161"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP154"/>
+  <dimension ref="A1:EP161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2289,7 +2289,7 @@
         <v>2.75</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE4" t="n">
         <v>2</v>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3267,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE6" t="n">
         <v>0.89</v>
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DE7" t="n">
         <v>1.13</v>
@@ -4203,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -6097,7 +6097,7 @@
         <v>2.57</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6127,7 +6127,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -7030,7 +7030,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE13" t="n">
         <v>2</v>
@@ -7063,7 +7063,7 @@
         <v>0.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7514,10 +7514,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7547,7 +7547,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8473,7 +8473,7 @@
         <v>1.86</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8619,37 +8619,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
         <v>45893.72916666666</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>2</v>
@@ -8664,119 +8664,119 @@
         <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
+        <v>12</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>19</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5</v>
+      </c>
+      <c r="W17" t="n">
         <v>8</v>
       </c>
-      <c r="T17" t="n">
-        <v>11</v>
-      </c>
-      <c r="U17" t="n">
-        <v>15</v>
-      </c>
-      <c r="V17" t="n">
-        <v>14</v>
-      </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
       <c r="X17" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Y17" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="Z17" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Anoeta</t>
+          <t>Estadio de la Cerámica</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
+          <t>Plaza Labrador, Villarreal</t>
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD17" t="n">
         <v>2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.4</v>
+        <v>4.35</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.19</v>
+        <v>1.72</v>
       </c>
       <c r="AJ17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV17" t="n">
         <v>4</v>
       </c>
-      <c r="AK17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU17" t="n">
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA17" t="n">
         <v>4</v>
       </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>2</v>
-      </c>
       <c r="BB17" t="n">
-        <v>-1</v>
+        <v>76</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
@@ -8797,10 +8797,10 @@
         <v>1</v>
       </c>
       <c r="BI17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK17" t="n">
         <v>4</v>
@@ -8809,7 +8809,7 @@
         <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BN17" t="n">
         <v>4</v>
@@ -8818,16 +8818,16 @@
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT17" t="n">
         <v>3</v>
@@ -8836,37 +8836,37 @@
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="BW17" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="BX17" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="BY17" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.38</v>
+        <v>0.72</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.15</v>
+        <v>2.79</v>
       </c>
       <c r="CC17" t="n">
         <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE17" t="n">
         <v>0</v>
       </c>
       <c r="CF17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG17" t="n">
         <v>0</v>
@@ -8881,13 +8881,13 @@
         <v>1</v>
       </c>
       <c r="CK17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN17" t="n">
         <v>0</v>
@@ -8902,25 +8902,25 @@
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="CS17" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="CT17" t="n">
         <v>1</v>
       </c>
       <c r="CU17" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="CV17" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="CW17" t="n">
         <v>1</v>
       </c>
       <c r="CX17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CY17" t="n">
         <v>10</v>
@@ -8929,46 +8929,46 @@
         <v>0</v>
       </c>
       <c r="DA17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.25</v>
+        <v>2.75</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="DF17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG17" t="n">
         <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DI17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="DM17" t="n">
         <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="DO17" t="n">
         <v>15</v>
@@ -8986,108 +8986,72 @@
         <v>1</v>
       </c>
       <c r="DT17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU17" t="b">
         <v>0</v>
       </c>
       <c r="DV17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW17" t="n">
-        <v>28.66</v>
+        <v>30.77</v>
       </c>
       <c r="DX17" t="n">
-        <v>3.5</v>
+        <v>4.54</v>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="DZ17" t="inlineStr">
         <is>
-          <t>43%</t>
-        </is>
-      </c>
-      <c r="EA17" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="EB17" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EC17" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="ED17" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="EA17" t="inlineStr"/>
+      <c r="EB17" t="inlineStr"/>
+      <c r="EC17" t="inlineStr"/>
+      <c r="ED17" t="inlineStr"/>
       <c r="EE17" t="inlineStr">
         <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EF17" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
-      </c>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EF17" t="inlineStr"/>
       <c r="EG17" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EH17" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="EI17" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="EJ17" t="inlineStr">
         <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EK17" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="EL17" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EM17" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EN17" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EK17" t="inlineStr"/>
+      <c r="EL17" t="inlineStr"/>
+      <c r="EM17" t="inlineStr"/>
+      <c r="EN17" t="inlineStr"/>
       <c r="EO17" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EP17" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.85</t>
         </is>
       </c>
     </row>
@@ -9107,37 +9071,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
         <v>45893.72916666666</v>
       </c>
       <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
         <v>5</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>8</v>
-      </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
         <v>2</v>
@@ -9152,119 +9116,119 @@
         <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="U18" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="W18" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X18" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="Z18" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Estadio de la Cerámica</t>
+          <t>Estadio Municipal de Anoeta</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Plaza Labrador, Villarreal</t>
+          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
         <v>2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>4.35</v>
+        <v>3.4</v>
       </c>
       <c r="AG18" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.72</v>
+        <v>2.19</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AN18" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AO18" t="n">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AU18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB18" t="n">
-        <v>76</v>
+        <v>-1</v>
       </c>
       <c r="BC18" t="n">
         <v>0</v>
@@ -9285,10 +9249,10 @@
         <v>1</v>
       </c>
       <c r="BI18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK18" t="n">
         <v>4</v>
@@ -9297,7 +9261,7 @@
         <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN18" t="n">
         <v>4</v>
@@ -9306,16 +9270,16 @@
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT18" t="n">
         <v>3</v>
@@ -9324,37 +9288,37 @@
         <v>1</v>
       </c>
       <c r="BV18" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="BW18" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="BX18" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="BY18" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.72</v>
+        <v>1.38</v>
       </c>
       <c r="CB18" t="n">
-        <v>2.79</v>
+        <v>3.15</v>
       </c>
       <c r="CC18" t="n">
         <v>0</v>
       </c>
       <c r="CD18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE18" t="n">
         <v>0</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG18" t="n">
         <v>0</v>
@@ -9369,13 +9333,13 @@
         <v>1</v>
       </c>
       <c r="CK18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN18" t="n">
         <v>0</v>
@@ -9390,25 +9354,25 @@
         <v>1</v>
       </c>
       <c r="CR18" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV18" t="n">
         <v>15</v>
       </c>
-      <c r="CS18" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU18" t="n">
+      <c r="CW18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX18" t="n">
         <v>9</v>
-      </c>
-      <c r="CV18" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX18" t="n">
-        <v>6</v>
       </c>
       <c r="CY18" t="n">
         <v>10</v>
@@ -9417,49 +9381,49 @@
         <v>0</v>
       </c>
       <c r="DA18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DB18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.75</v>
+        <v>1.25</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.75</v>
+        <v>1.57</v>
       </c>
       <c r="DF18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DG18" t="n">
         <v>0</v>
       </c>
       <c r="DH18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DI18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DJ18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
       </c>
       <c r="DL18" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="DM18" t="n">
         <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9474,72 +9438,108 @@
         <v>1</v>
       </c>
       <c r="DT18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU18" t="b">
         <v>0</v>
       </c>
       <c r="DV18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW18" t="n">
-        <v>30.77</v>
+        <v>28.66</v>
       </c>
       <c r="DX18" t="n">
-        <v>4.54</v>
+        <v>3.5</v>
       </c>
       <c r="DY18" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="DZ18" t="inlineStr">
         <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="EA18" t="inlineStr"/>
-      <c r="EB18" t="inlineStr"/>
-      <c r="EC18" t="inlineStr"/>
-      <c r="ED18" t="inlineStr"/>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="EA18" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EB18" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EC18" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="ED18" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
       <c r="EE18" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EF18" t="inlineStr"/>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EF18" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
       <c r="EG18" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EH18" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="EI18" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="EJ18" t="inlineStr">
         <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EK18" t="inlineStr"/>
-      <c r="EL18" t="inlineStr"/>
-      <c r="EM18" t="inlineStr"/>
-      <c r="EN18" t="inlineStr"/>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EK18" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EL18" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EM18" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EN18" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
       <c r="EO18" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EP18" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9881,7 @@
         <v>0.75</v>
       </c>
       <c r="DE19" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9911,7 +9911,7 @@
         <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10834,7 +10834,7 @@
         <v>0</v>
       </c>
       <c r="DD21" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE21" t="n">
         <v>1.13</v>
@@ -10867,7 +10867,7 @@
         <v>1.06</v>
       </c>
       <c r="DO21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11302,7 +11302,7 @@
         <v>50</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DE22" t="n">
         <v>1.57</v>
@@ -12295,7 +12295,7 @@
         <v>2.77</v>
       </c>
       <c r="DO24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12738,7 +12738,7 @@
         <v>100</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE25" t="n">
         <v>1.13</v>
@@ -12771,7 +12771,7 @@
         <v>3.34</v>
       </c>
       <c r="DO25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13255,7 +13255,7 @@
         <v>2.11</v>
       </c>
       <c r="DO26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13723,7 +13723,7 @@
         <v>2.25</v>
       </c>
       <c r="DO27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14211,7 +14211,7 @@
         <v>2.14</v>
       </c>
       <c r="DO28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14638,7 +14638,7 @@
         <v>25</v>
       </c>
       <c r="DD29" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DE29" t="n">
         <v>1.86</v>
@@ -15105,7 +15105,7 @@
         <v>1.63</v>
       </c>
       <c r="DE30" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF30" t="n">
         <v>3</v>
@@ -15589,7 +15589,7 @@
         <v>2.11</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15619,7 +15619,7 @@
         <v>1.56</v>
       </c>
       <c r="DO31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16522,10 +16522,10 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -16555,7 +16555,7 @@
         <v>2.15</v>
       </c>
       <c r="DO33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17006,10 +17006,10 @@
         <v>50</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF34" t="n">
         <v>0</v>
@@ -17039,7 +17039,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="DO34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17485,7 +17485,7 @@
         <v>1.25</v>
       </c>
       <c r="DE35" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF35" t="n">
         <v>1</v>
@@ -17995,7 +17995,7 @@
         <v>2.75</v>
       </c>
       <c r="DO36" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18446,7 +18446,7 @@
         <v>50</v>
       </c>
       <c r="DD37" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE37" t="n">
         <v>1.86</v>
@@ -18926,7 +18926,7 @@
         <v>67</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DE38" t="n">
         <v>0.75</v>
@@ -18959,7 +18959,7 @@
         <v>2.12</v>
       </c>
       <c r="DO38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -20365,7 +20365,7 @@
         <v>3</v>
       </c>
       <c r="DE41" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF41" t="n">
         <v>0</v>
@@ -20395,7 +20395,7 @@
         <v>0.57</v>
       </c>
       <c r="DO41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20863,7 +20863,7 @@
         <v>2.33</v>
       </c>
       <c r="DO42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -22253,7 +22253,7 @@
         <v>2.57</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF45" t="n">
         <v>3</v>
@@ -22283,7 +22283,7 @@
         <v>3.56</v>
       </c>
       <c r="DO45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22713,7 +22713,7 @@
         <v>2.75</v>
       </c>
       <c r="DE46" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF46" t="n">
         <v>3</v>
@@ -23198,7 +23198,7 @@
         <v>100</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE47" t="n">
         <v>1.25</v>
@@ -23231,7 +23231,7 @@
         <v>2.51</v>
       </c>
       <c r="DO47" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23677,7 +23677,7 @@
         <v>1.5</v>
       </c>
       <c r="DE48" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF48" t="n">
         <v>2</v>
@@ -23707,7 +23707,7 @@
         <v>2.96</v>
       </c>
       <c r="DO48" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24630,7 +24630,7 @@
         <v>100</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE50" t="n">
         <v>1.13</v>
@@ -24663,7 +24663,7 @@
         <v>2.63</v>
       </c>
       <c r="DO50" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25117,7 +25117,7 @@
         <v>2</v>
       </c>
       <c r="DE51" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF51" t="n">
         <v>2</v>
@@ -25147,7 +25147,7 @@
         <v>1.99</v>
       </c>
       <c r="DO51" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25615,7 +25615,7 @@
         <v>3.7</v>
       </c>
       <c r="DO52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26533,7 +26533,7 @@
         <v>2.11</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF54" t="n">
         <v>3</v>
@@ -26563,7 +26563,7 @@
         <v>1.62</v>
       </c>
       <c r="DO54" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26695,12 +26695,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
@@ -26710,149 +26710,149 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="n">
+        <v>6</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2</v>
+      </c>
+      <c r="R55" t="n">
         <v>5</v>
       </c>
-      <c r="J55" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" t="n">
+      <c r="S55" t="n">
+        <v>14</v>
+      </c>
+      <c r="T55" t="n">
         <v>7</v>
       </c>
-      <c r="L55" t="n">
-        <v>8</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>2</v>
-      </c>
-      <c r="R55" t="n">
-        <v>10</v>
-      </c>
-      <c r="S55" t="n">
-        <v>9</v>
-      </c>
-      <c r="T55" t="n">
-        <v>14</v>
-      </c>
       <c r="U55" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V55" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="W55" t="n">
         <v>17</v>
       </c>
       <c r="X55" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y55" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="Z55" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Estadio Ciudad de Valencia</t>
+          <t>Estadio Ramón Sánchez Pizjuán</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Calle San Vicente de Paúl 44, Valencia</t>
+          <t>Avenida de Eduardo Dato, Sevilla</t>
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE55" t="n">
-        <v>8</v>
+        <v>3.15</v>
       </c>
       <c r="AF55" t="n">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI55" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT55" t="n">
         <v>1.4</v>
       </c>
-      <c r="AJ55" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AU55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV55" t="n">
         <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX55" t="n">
         <v>1</v>
       </c>
       <c r="AY55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB55" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="BC55" t="n">
         <v>0</v>
@@ -26873,76 +26873,76 @@
         <v>1</v>
       </c>
       <c r="BI55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT55" t="n">
         <v>5</v>
       </c>
-      <c r="BK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL55" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM55" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN55" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ55" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR55" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT55" t="n">
-        <v>2</v>
-      </c>
       <c r="BU55" t="n">
         <v>1</v>
       </c>
       <c r="BV55" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="BW55" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="BX55" t="n">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="BY55" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="BZ55" t="n">
-        <v>1.02</v>
+        <v>1.67</v>
       </c>
       <c r="CA55" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="CB55" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="CC55" t="n">
         <v>0</v>
       </c>
       <c r="CD55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE55" t="n">
         <v>0</v>
       </c>
       <c r="CF55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG55" t="n">
         <v>0</v>
@@ -26966,7 +26966,7 @@
         <v>0</v>
       </c>
       <c r="CN55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO55" t="n">
         <v>0</v>
@@ -26978,73 +26978,73 @@
         <v>1</v>
       </c>
       <c r="CR55" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="CS55" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="CT55" t="n">
         <v>1</v>
       </c>
       <c r="CU55" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV55" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX55" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY55" t="n">
         <v>9</v>
       </c>
-      <c r="CV55" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW55" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX55" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY55" t="n">
-        <v>3</v>
-      </c>
       <c r="CZ55" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA55" t="n">
         <v>100</v>
       </c>
       <c r="DB55" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC55" t="n">
         <v>75</v>
       </c>
-      <c r="DC55" t="n">
-        <v>100</v>
-      </c>
       <c r="DD55" t="n">
-        <v>0.17</v>
+        <v>1.25</v>
       </c>
       <c r="DE55" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DF55" t="n">
         <v>0.5</v>
       </c>
       <c r="DG55" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DH55" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ55" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK55" t="n">
         <v>0</v>
       </c>
       <c r="DL55" t="n">
-        <v>0.84</v>
+        <v>1.24</v>
       </c>
       <c r="DM55" t="n">
-        <v>2.34</v>
+        <v>0.93</v>
       </c>
       <c r="DN55" t="n">
-        <v>3.18</v>
+        <v>2.17</v>
       </c>
       <c r="DO55" t="n">
         <v>15</v>
@@ -27059,10 +27059,10 @@
         <v>1</v>
       </c>
       <c r="DS55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU55" t="b">
         <v>0</v>
@@ -27071,87 +27071,99 @@
         <v>1</v>
       </c>
       <c r="DW55" t="n">
-        <v>22.21</v>
+        <v>27.52</v>
       </c>
       <c r="DX55" t="n">
-        <v>8.289999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="DY55" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="DZ55" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA55" t="inlineStr">
         <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EB55" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EB55" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
       <c r="EC55" t="inlineStr">
         <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="ED55" t="inlineStr"/>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="ED55" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="EE55" t="inlineStr">
         <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EF55" t="inlineStr"/>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EF55" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
       <c r="EG55" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EH55" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EI55" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EJ55" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EK55" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EL55" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EM55" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EN55" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EO55" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EP55" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -27171,12 +27183,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -27186,25 +27198,25 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -27216,119 +27228,119 @@
         <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S56" t="n">
+        <v>9</v>
+      </c>
+      <c r="T56" t="n">
         <v>14</v>
       </c>
-      <c r="T56" t="n">
-        <v>7</v>
-      </c>
       <c r="U56" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V56" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="W56" t="n">
         <v>17</v>
       </c>
       <c r="X56" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Y56" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="Z56" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Estadio Ramón Sánchez Pizjuán</t>
+          <t>Estadio Ciudad de Valencia</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Avenida de Eduardo Dato, Sevilla</t>
+          <t>Calle San Vicente de Paúl 44, Valencia</t>
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE56" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="AF56" t="n">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="AG56" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI56" t="n">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="AJ56" t="n">
-        <v>3.4</v>
+        <v>2.07</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL56" t="n">
         <v>2</v>
       </c>
       <c r="AM56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN56" t="n">
         <v>1.5</v>
       </c>
-      <c r="AN56" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AO56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP56" t="n">
         <v>2.38</v>
       </c>
-      <c r="AP56" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AQ56" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AR56" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.72</v>
+        <v>4.05</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AU56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV56" t="n">
         <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX56" t="n">
         <v>1</v>
       </c>
       <c r="AY56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB56" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="BC56" t="n">
         <v>0</v>
@@ -27349,76 +27361,76 @@
         <v>1</v>
       </c>
       <c r="BI56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL56" t="n">
         <v>2</v>
       </c>
       <c r="BM56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BN56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO56" t="n">
         <v>0</v>
       </c>
       <c r="BP56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU56" t="n">
         <v>1</v>
       </c>
       <c r="BV56" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="BW56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="BX56" t="n">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="BY56" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="BZ56" t="n">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
       <c r="CA56" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="CB56" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="CC56" t="n">
         <v>0</v>
       </c>
       <c r="CD56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE56" t="n">
         <v>0</v>
       </c>
       <c r="CF56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG56" t="n">
         <v>0</v>
@@ -27442,7 +27454,7 @@
         <v>0</v>
       </c>
       <c r="CN56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO56" t="n">
         <v>0</v>
@@ -27454,73 +27466,73 @@
         <v>1</v>
       </c>
       <c r="CR56" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="CS56" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="CT56" t="n">
         <v>1</v>
       </c>
       <c r="CU56" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="CV56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CW56" t="n">
         <v>1</v>
       </c>
       <c r="CX56" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY56" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CZ56" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA56" t="n">
         <v>100</v>
       </c>
       <c r="DB56" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="DC56" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD56" t="n">
-        <v>1</v>
+        <v>0.17</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="DF56" t="n">
         <v>0.5</v>
       </c>
       <c r="DG56" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DH56" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="DI56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ56" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK56" t="n">
         <v>0</v>
       </c>
       <c r="DL56" t="n">
-        <v>1.24</v>
+        <v>0.84</v>
       </c>
       <c r="DM56" t="n">
-        <v>0.93</v>
+        <v>2.34</v>
       </c>
       <c r="DN56" t="n">
-        <v>2.17</v>
+        <v>3.18</v>
       </c>
       <c r="DO56" t="n">
         <v>15</v>
@@ -27535,10 +27547,10 @@
         <v>1</v>
       </c>
       <c r="DS56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU56" t="b">
         <v>0</v>
@@ -27547,99 +27559,87 @@
         <v>1</v>
       </c>
       <c r="DW56" t="n">
-        <v>27.52</v>
+        <v>22.21</v>
       </c>
       <c r="DX56" t="n">
-        <v>3.08</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DY56" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ56" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="EA56" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EB56" t="inlineStr"/>
+      <c r="EC56" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="ED56" t="inlineStr"/>
+      <c r="EE56" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF56" t="inlineStr"/>
+      <c r="EG56" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH56" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI56" t="inlineStr">
+        <is>
+          <t>5.86</t>
+        </is>
+      </c>
+      <c r="EJ56" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="EK56" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL56" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EB56" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EC56" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="ED56" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EE56" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF56" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG56" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EH56" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EI56" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EJ56" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="EK56" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EL56" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
       <c r="EM56" t="inlineStr">
         <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN56" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EO56" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EP56" t="inlineStr">
+        <is>
           <t>1.68</t>
-        </is>
-      </c>
-      <c r="EN56" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EO56" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EP56" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -27978,7 +27978,7 @@
         <v>75</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE57" t="n">
         <v>0.57</v>
@@ -28011,7 +28011,7 @@
         <v>2.1</v>
       </c>
       <c r="DO57" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28446,7 +28446,7 @@
         <v>84</v>
       </c>
       <c r="DD58" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE58" t="n">
         <v>1.11</v>
@@ -28967,7 +28967,7 @@
         <v>3.85</v>
       </c>
       <c r="DO59" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29405,7 +29405,7 @@
         <v>1.86</v>
       </c>
       <c r="DE60" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF60" t="n">
         <v>3</v>
@@ -29435,7 +29435,7 @@
         <v>2.17</v>
       </c>
       <c r="DO60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29903,7 +29903,7 @@
         <v>3.12</v>
       </c>
       <c r="DO61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30341,7 +30341,7 @@
         <v>1.13</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF62" t="n">
         <v>0</v>
@@ -30371,7 +30371,7 @@
         <v>2.32</v>
       </c>
       <c r="DO62" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP62" t="b">
         <v>0</v>
@@ -30826,7 +30826,7 @@
         <v>59</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE63" t="n">
         <v>0.89</v>
@@ -31286,10 +31286,10 @@
         <v>100</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE64" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF64" t="n">
         <v>2.33</v>
@@ -31319,7 +31319,7 @@
         <v>4.16</v>
       </c>
       <c r="DO64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31762,7 +31762,7 @@
         <v>50</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE65" t="n">
         <v>0.57</v>
@@ -31795,7 +31795,7 @@
         <v>2</v>
       </c>
       <c r="DO65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32233,7 +32233,7 @@
         <v>2.75</v>
       </c>
       <c r="DE66" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF66" t="n">
         <v>3</v>
@@ -33187,7 +33187,7 @@
         <v>2.52</v>
       </c>
       <c r="DO68" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -34081,7 +34081,7 @@
         <v>1.63</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF70" t="n">
         <v>2</v>
@@ -34569,7 +34569,7 @@
         <v>1.5</v>
       </c>
       <c r="DE71" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF71" t="n">
         <v>2.33</v>
@@ -34599,7 +34599,7 @@
         <v>2.23</v>
       </c>
       <c r="DO71" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35079,7 +35079,7 @@
         <v>2.29</v>
       </c>
       <c r="DO72" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -36013,7 +36013,7 @@
         <v>1.13</v>
       </c>
       <c r="DE74" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF74" t="n">
         <v>0.25</v>
@@ -36043,7 +36043,7 @@
         <v>1.79</v>
       </c>
       <c r="DO74" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36531,7 +36531,7 @@
         <v>3.06</v>
       </c>
       <c r="DO75" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37434,10 +37434,10 @@
         <v>100</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE77" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF77" t="n">
         <v>1.33</v>
@@ -37467,7 +37467,7 @@
         <v>2.1</v>
       </c>
       <c r="DO77" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -37894,7 +37894,7 @@
         <v>100</v>
       </c>
       <c r="DD78" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE78" t="n">
         <v>2</v>
@@ -37927,7 +37927,7 @@
         <v>3.75</v>
       </c>
       <c r="DO78" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38043,40 +38043,40 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45935.6875</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K79" t="n">
         <v>5</v>
       </c>
       <c r="L79" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N79" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -38085,104 +38085,104 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
+        <v>3</v>
+      </c>
+      <c r="R79" t="n">
+        <v>2</v>
+      </c>
+      <c r="S79" t="n">
+        <v>7</v>
+      </c>
+      <c r="T79" t="n">
         <v>5</v>
       </c>
-      <c r="R79" t="n">
-        <v>3</v>
-      </c>
-      <c r="S79" t="n">
-        <v>9</v>
-      </c>
-      <c r="T79" t="n">
-        <v>9</v>
-      </c>
       <c r="U79" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V79" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W79" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="X79" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Y79" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z79" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>Estadio Municipal de Anoeta</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
         </is>
       </c>
       <c r="AC79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD79" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="AF79" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AG79" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AJ79" t="n">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AL79" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AM79" t="n">
         <v>1.44</v>
       </c>
       <c r="AN79" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AO79" t="n">
         <v>2.55</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AR79" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AU79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW79" t="n">
         <v>0</v>
@@ -38191,22 +38191,22 @@
         <v>0</v>
       </c>
       <c r="AY79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB79" t="n">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38221,178 +38221,178 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BJ79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BK79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>101</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX79" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY79" t="n">
         <v>10</v>
       </c>
-      <c r="BN79" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR79" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS79" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT79" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV79" t="n">
-        <v>66</v>
-      </c>
-      <c r="BW79" t="n">
-        <v>34</v>
-      </c>
-      <c r="BX79" t="n">
-        <v>107</v>
-      </c>
-      <c r="BY79" t="n">
-        <v>98</v>
-      </c>
-      <c r="BZ79" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CA79" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CB79" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR79" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS79" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU79" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV79" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX79" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY79" t="n">
-        <v>13</v>
-      </c>
       <c r="CZ79" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="DA79" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="DB79" t="n">
+        <v>59</v>
+      </c>
+      <c r="DC79" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE79" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DF79" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DI79" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DJ79" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK79" t="n">
         <v>29</v>
       </c>
-      <c r="DC79" t="n">
-        <v>88</v>
-      </c>
-      <c r="DD79" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DE79" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DF79" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DG79" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH79" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DI79" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DJ79" t="n">
-        <v>46</v>
-      </c>
-      <c r="DK79" t="n">
-        <v>13</v>
-      </c>
       <c r="DL79" t="n">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="DN79" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="DO79" t="n">
         <v>15</v>
@@ -38401,10 +38401,10 @@
         <v>1</v>
       </c>
       <c r="DQ79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS79" t="b">
         <v>0</v>
@@ -38416,102 +38416,94 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW79" t="n">
-        <v>17.75</v>
+        <v>17.19</v>
       </c>
       <c r="DX79" t="n">
-        <v>9.369999999999999</v>
+        <v>3.66</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="ED79" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EE79" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EF79" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EG79" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EH79" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EI79" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EJ79" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EK79" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EL79" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EM79" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EN79" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM79" t="inlineStr"/>
+      <c r="EN79" t="inlineStr"/>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.84</t>
         </is>
       </c>
     </row>
@@ -38531,146 +38523,146 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45935.6875</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K80" t="n">
         <v>5</v>
       </c>
       <c r="L80" t="n">
+        <v>15</v>
+      </c>
+      <c r="M80" t="n">
+        <v>2</v>
+      </c>
+      <c r="N80" t="n">
+        <v>6</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>5</v>
+      </c>
+      <c r="R80" t="n">
+        <v>3</v>
+      </c>
+      <c r="S80" t="n">
+        <v>9</v>
+      </c>
+      <c r="T80" t="n">
+        <v>9</v>
+      </c>
+      <c r="U80" t="n">
+        <v>14</v>
+      </c>
+      <c r="V80" t="n">
         <v>12</v>
       </c>
-      <c r="M80" t="n">
-        <v>1</v>
-      </c>
-      <c r="N80" t="n">
-        <v>2</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>3</v>
-      </c>
-      <c r="R80" t="n">
-        <v>2</v>
-      </c>
-      <c r="S80" t="n">
-        <v>7</v>
-      </c>
-      <c r="T80" t="n">
-        <v>5</v>
-      </c>
-      <c r="U80" t="n">
-        <v>10</v>
-      </c>
-      <c r="V80" t="n">
-        <v>7</v>
-      </c>
       <c r="W80" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X80" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Y80" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z80" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Anoeta</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD80" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="AF80" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AG80" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AI80" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AJ80" t="n">
-        <v>3.85</v>
+        <v>2.96</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AL80" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AM80" t="n">
         <v>1.44</v>
       </c>
       <c r="AN80" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AO80" t="n">
         <v>2.55</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AR80" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AU80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW80" t="n">
         <v>0</v>
@@ -38679,22 +38671,22 @@
         <v>0</v>
       </c>
       <c r="AY80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB80" t="n">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -38709,178 +38701,178 @@
         <v>1</v>
       </c>
       <c r="BI80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BJ80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BK80" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR80" t="n">
         <v>4</v>
       </c>
-      <c r="BL80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM80" t="n">
+      <c r="BS80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV80" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX80" t="n">
         <v>6</v>
       </c>
-      <c r="BN80" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT80" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV80" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW80" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX80" t="n">
-        <v>101</v>
-      </c>
-      <c r="BY80" t="n">
-        <v>90</v>
-      </c>
-      <c r="BZ80" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="CA80" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB80" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CC80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN80" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR80" t="n">
-        <v>14</v>
-      </c>
-      <c r="CS80" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU80" t="n">
-        <v>21</v>
-      </c>
-      <c r="CV80" t="n">
+      <c r="CY80" t="n">
         <v>13</v>
       </c>
-      <c r="CW80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX80" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY80" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ80" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="DA80" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="DB80" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="DC80" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.25</v>
+        <v>2.11</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="DF80" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="DG80" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DH80" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="DI80" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="DJ80" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="DK80" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="DL80" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="DM80" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="DN80" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="DO80" t="n">
         <v>15</v>
@@ -38889,10 +38881,10 @@
         <v>1</v>
       </c>
       <c r="DQ80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS80" t="b">
         <v>0</v>
@@ -38904,94 +38896,102 @@
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW80" t="n">
-        <v>17.19</v>
+        <v>17.75</v>
       </c>
       <c r="DX80" t="n">
-        <v>3.66</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EB80" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EC80" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED80" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EE80" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EF80" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EG80" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EH80" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EI80" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EJ80" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EK80" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EL80" t="inlineStr">
+        <is>
           <t>2.02</t>
         </is>
       </c>
-      <c r="EB80" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC80" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="ED80" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE80" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF80" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG80" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="EH80" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="EI80" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="EJ80" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EK80" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EL80" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EM80" t="inlineStr"/>
-      <c r="EN80" t="inlineStr"/>
+      <c r="EM80" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EN80" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
       <c r="EO80" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EP80" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.68</t>
         </is>
       </c>
     </row>
@@ -39322,7 +39322,7 @@
         <v>59</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DE81" t="n">
         <v>1.13</v>
@@ -39355,7 +39355,7 @@
         <v>3.36</v>
       </c>
       <c r="DO81" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -39797,7 +39797,7 @@
         <v>0.75</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF82" t="n">
         <v>0.75</v>
@@ -39827,7 +39827,7 @@
         <v>2.32</v>
       </c>
       <c r="DO82" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40278,7 +40278,7 @@
         <v>88</v>
       </c>
       <c r="DD83" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE83" t="n">
         <v>0.5</v>
@@ -40311,7 +40311,7 @@
         <v>2.72</v>
       </c>
       <c r="DO83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -41670,10 +41670,10 @@
         <v>75</v>
       </c>
       <c r="DD86" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE86" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF86" t="n">
         <v>2.5</v>
@@ -41703,7 +41703,7 @@
         <v>2.53</v>
       </c>
       <c r="DO86" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42161,7 +42161,7 @@
         <v>2</v>
       </c>
       <c r="DE87" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF87" t="n">
         <v>2.5</v>
@@ -42191,7 +42191,7 @@
         <v>3.24</v>
       </c>
       <c r="DO87" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -42618,7 +42618,7 @@
         <v>68</v>
       </c>
       <c r="DD88" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DE88" t="n">
         <v>0.75</v>
@@ -42651,7 +42651,7 @@
         <v>3.09</v>
       </c>
       <c r="DO88" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43578,10 +43578,10 @@
         <v>84</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE90" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF90" t="n">
         <v>1.67</v>
@@ -43611,7 +43611,7 @@
         <v>3.13</v>
       </c>
       <c r="DO90" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44066,10 +44066,10 @@
         <v>88</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF91" t="n">
         <v>1.75</v>
@@ -44099,7 +44099,7 @@
         <v>2.36</v>
       </c>
       <c r="DO91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP91" t="b">
         <v>0</v>
@@ -44559,7 +44559,7 @@
         <v>2.81</v>
       </c>
       <c r="DO92" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45009,7 +45009,7 @@
         <v>1.13</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF93" t="n">
         <v>0.8</v>
@@ -45039,7 +45039,7 @@
         <v>2.1</v>
       </c>
       <c r="DO93" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -45497,7 +45497,7 @@
         <v>2.11</v>
       </c>
       <c r="DE94" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF94" t="n">
         <v>2</v>
@@ -45527,7 +45527,7 @@
         <v>2.42</v>
       </c>
       <c r="DO94" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46011,7 +46011,7 @@
         <v>2.58</v>
       </c>
       <c r="DO95" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46934,7 +46934,7 @@
         <v>78</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE97" t="n">
         <v>0.89</v>
@@ -47919,7 +47919,7 @@
         <v>4.52</v>
       </c>
       <c r="DO99" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -48379,7 +48379,7 @@
         <v>2.21</v>
       </c>
       <c r="DO100" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -49290,7 +49290,7 @@
         <v>75</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE102" t="n">
         <v>0.75</v>
@@ -49323,7 +49323,7 @@
         <v>2.07</v>
       </c>
       <c r="DO102" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -50234,7 +50234,7 @@
         <v>80</v>
       </c>
       <c r="DD104" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE104" t="n">
         <v>1.25</v>
@@ -50267,7 +50267,7 @@
         <v>2.79</v>
       </c>
       <c r="DO104" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -50705,7 +50705,7 @@
         <v>1.25</v>
       </c>
       <c r="DE105" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF105" t="n">
         <v>1.4</v>
@@ -51181,7 +51181,7 @@
         <v>2.57</v>
       </c>
       <c r="DE106" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF106" t="n">
         <v>3</v>
@@ -51211,7 +51211,7 @@
         <v>3.13</v>
       </c>
       <c r="DO106" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -52134,10 +52134,10 @@
         <v>55</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE108" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF108" t="n">
         <v>1.6</v>
@@ -52167,7 +52167,7 @@
         <v>3.06</v>
       </c>
       <c r="DO108" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -52605,7 +52605,7 @@
         <v>3</v>
       </c>
       <c r="DE109" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF109" t="n">
         <v>3</v>
@@ -52635,7 +52635,7 @@
         <v>3.52</v>
       </c>
       <c r="DO109" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -53545,7 +53545,7 @@
         <v>0.75</v>
       </c>
       <c r="DE111" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF111" t="n">
         <v>0.6</v>
@@ -53575,7 +53575,7 @@
         <v>1.9</v>
       </c>
       <c r="DO111" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP111" t="b">
         <v>0</v>
@@ -54051,7 +54051,7 @@
         <v>3.11</v>
       </c>
       <c r="DO112" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -54535,7 +54535,7 @@
         <v>2.36</v>
       </c>
       <c r="DO113" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -54986,10 +54986,10 @@
         <v>67</v>
       </c>
       <c r="DD114" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE114" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF114" t="n">
         <v>0.8</v>
@@ -55019,7 +55019,7 @@
         <v>2.35</v>
       </c>
       <c r="DO114" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -55454,7 +55454,7 @@
         <v>75</v>
       </c>
       <c r="DD115" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE115" t="n">
         <v>0.89</v>
@@ -56405,7 +56405,7 @@
         <v>1.78</v>
       </c>
       <c r="DE117" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF117" t="n">
         <v>1.67</v>
@@ -56435,7 +56435,7 @@
         <v>2.5</v>
       </c>
       <c r="DO117" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -56873,7 +56873,7 @@
         <v>1.17</v>
       </c>
       <c r="DE118" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF118" t="n">
         <v>1.25</v>
@@ -57011,12 +57011,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F119" s="2" t="n">
@@ -57026,25 +57026,25 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K119" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L119" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -57056,117 +57056,125 @@
         <v>4</v>
       </c>
       <c r="R119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S119" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T119" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U119" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="V119" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W119" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="X119" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y119" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Z119" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA119" t="inlineStr"/>
-      <c r="AB119" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>Avenida de Suecia, Valencia</t>
+        </is>
+      </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE119" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="AF119" t="n">
-        <v>2.58</v>
+        <v>3.45</v>
       </c>
       <c r="AG119" t="n">
-        <v>2.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH119" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AI119" t="n">
-        <v>3.04</v>
+        <v>1.91</v>
       </c>
       <c r="AJ119" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="AK119" t="n">
-        <v>2.43</v>
+        <v>1.72</v>
       </c>
       <c r="AL119" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AM119" t="n">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="AN119" t="n">
-        <v>2.87</v>
+        <v>1.84</v>
       </c>
       <c r="AO119" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.77</v>
+        <v>1.37</v>
       </c>
       <c r="AR119" t="n">
-        <v>4.45</v>
+        <v>2.85</v>
       </c>
       <c r="AS119" t="n">
-        <v>2.05</v>
+        <v>2.89</v>
       </c>
       <c r="AT119" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AU119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW119" t="n">
         <v>0</v>
       </c>
       <c r="AX119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB119" t="n">
-        <v>298</v>
+        <v>-1</v>
       </c>
       <c r="BC119" t="n">
         <v>0</v>
       </c>
       <c r="BD119" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="BE119" t="n">
         <v>0</v>
@@ -57181,64 +57189,64 @@
         <v>1</v>
       </c>
       <c r="BI119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ119" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BK119" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BL119" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BM119" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BN119" t="n">
         <v>7</v>
       </c>
       <c r="BO119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT119" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BU119" t="n">
         <v>1</v>
       </c>
       <c r="BV119" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="BW119" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="BX119" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="BY119" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="BZ119" t="n">
-        <v>0.96</v>
+        <v>1.74</v>
       </c>
       <c r="CA119" t="n">
-        <v>1.63</v>
+        <v>1.09</v>
       </c>
       <c r="CB119" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="CC119" t="n">
         <v>0</v>
@@ -57271,10 +57279,10 @@
         <v>0</v>
       </c>
       <c r="CM119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO119" t="n">
         <v>0</v>
@@ -57286,19 +57294,19 @@
         <v>1</v>
       </c>
       <c r="CR119" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="CS119" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="CT119" t="n">
         <v>1</v>
       </c>
       <c r="CU119" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CV119" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CW119" t="n">
         <v>1</v>
@@ -57307,52 +57315,52 @@
         <v>6</v>
       </c>
       <c r="CY119" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CZ119" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="DA119" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="DB119" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="DC119" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DE119" t="n">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="DF119" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG119" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DH119" t="n">
         <v>0.82</v>
       </c>
       <c r="DI119" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="DJ119" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="DK119" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="DL119" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="DM119" t="n">
-        <v>0.97</v>
+        <v>1.6</v>
       </c>
       <c r="DN119" t="n">
-        <v>2.18</v>
+        <v>3.06</v>
       </c>
       <c r="DO119" t="n">
         <v>15</v>
@@ -57361,7 +57369,7 @@
         <v>1</v>
       </c>
       <c r="DQ119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR119" t="b">
         <v>0</v>
@@ -57376,90 +57384,102 @@
         <v>0</v>
       </c>
       <c r="DV119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW119" t="n">
-        <v>17.48</v>
+        <v>17.01</v>
       </c>
       <c r="DX119" t="n">
-        <v>5.64</v>
+        <v>5.56</v>
       </c>
       <c r="DY119" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="DZ119" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="EA119" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB119" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EC119" t="inlineStr"/>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
       <c r="ED119" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EE119" t="inlineStr"/>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE119" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
       <c r="EF119" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="EG119" t="inlineStr"/>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EG119" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EH119" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EI119" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EJ119" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EK119" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EL119" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EM119" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EN119" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EO119" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EP119" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -57479,12 +57499,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F120" s="2" t="n">
@@ -57494,25 +57514,25 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K120" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L120" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -57524,125 +57544,117 @@
         <v>4</v>
       </c>
       <c r="R120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S120" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T120" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U120" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="V120" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W120" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X120" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y120" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Z120" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>Estadio de Mestalla</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>Avenida de Suecia, Valencia</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AA120" t="inlineStr"/>
+      <c r="AB120" t="inlineStr"/>
       <c r="AC120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE120" t="n">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="AF120" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="AG120" t="n">
-        <v>2.15</v>
+        <v>2.98</v>
       </c>
       <c r="AH120" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AI120" t="n">
-        <v>1.91</v>
+        <v>3.04</v>
       </c>
       <c r="AJ120" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="AK120" t="n">
-        <v>1.72</v>
+        <v>2.43</v>
       </c>
       <c r="AL120" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AM120" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="AN120" t="n">
-        <v>1.84</v>
+        <v>2.87</v>
       </c>
       <c r="AO120" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="AR120" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="AS120" t="n">
-        <v>2.89</v>
+        <v>2.05</v>
       </c>
       <c r="AT120" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AU120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW120" t="n">
         <v>0</v>
       </c>
       <c r="AX120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB120" t="n">
-        <v>-1</v>
+        <v>298</v>
       </c>
       <c r="BC120" t="n">
         <v>0</v>
       </c>
       <c r="BD120" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="BE120" t="n">
         <v>0</v>
@@ -57657,64 +57669,64 @@
         <v>1</v>
       </c>
       <c r="BI120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ120" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BK120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL120" t="n">
         <v>6</v>
       </c>
-      <c r="BL120" t="n">
-        <v>1</v>
-      </c>
       <c r="BM120" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BN120" t="n">
         <v>7</v>
       </c>
       <c r="BO120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT120" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BU120" t="n">
         <v>1</v>
       </c>
       <c r="BV120" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="BW120" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="BX120" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="BY120" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="BZ120" t="n">
-        <v>1.74</v>
+        <v>0.96</v>
       </c>
       <c r="CA120" t="n">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="CB120" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="CC120" t="n">
         <v>0</v>
@@ -57747,10 +57759,10 @@
         <v>0</v>
       </c>
       <c r="CM120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO120" t="n">
         <v>0</v>
@@ -57762,19 +57774,19 @@
         <v>1</v>
       </c>
       <c r="CR120" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="CS120" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="CT120" t="n">
         <v>1</v>
       </c>
       <c r="CU120" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CV120" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CW120" t="n">
         <v>1</v>
@@ -57783,61 +57795,61 @@
         <v>6</v>
       </c>
       <c r="CY120" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CZ120" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="DA120" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="DB120" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="DC120" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="DD120" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DE120" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DF120" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG120" t="n">
         <v>1.5</v>
-      </c>
-      <c r="DE120" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DF120" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DG120" t="n">
-        <v>1.4</v>
       </c>
       <c r="DH120" t="n">
         <v>0.82</v>
       </c>
       <c r="DI120" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="DJ120" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="DK120" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="DL120" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="DM120" t="n">
-        <v>1.6</v>
+        <v>0.97</v>
       </c>
       <c r="DN120" t="n">
-        <v>3.06</v>
+        <v>2.18</v>
       </c>
       <c r="DO120" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
       </c>
       <c r="DQ120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR120" t="b">
         <v>0</v>
@@ -57852,102 +57864,90 @@
         <v>0</v>
       </c>
       <c r="DV120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW120" t="n">
-        <v>17.01</v>
+        <v>17.48</v>
       </c>
       <c r="DX120" t="n">
-        <v>5.56</v>
+        <v>5.64</v>
       </c>
       <c r="DY120" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="DZ120" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="EA120" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="EB120" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC120" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EC120" t="inlineStr"/>
       <c r="ED120" t="inlineStr">
         <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EE120" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EE120" t="inlineStr"/>
       <c r="EF120" t="inlineStr">
         <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="EG120" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EG120" t="inlineStr"/>
       <c r="EH120" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EI120" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EJ120" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EK120" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="EL120" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EM120" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EN120" t="inlineStr">
+        <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="EM120" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EN120" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
       <c r="EO120" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EP120" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.43</t>
         </is>
       </c>
     </row>
@@ -58278,7 +58278,7 @@
         <v>84</v>
       </c>
       <c r="DD121" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DE121" t="n">
         <v>2</v>
@@ -58311,7 +58311,7 @@
         <v>3.7</v>
       </c>
       <c r="DO121" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -59226,7 +59226,7 @@
         <v>74</v>
       </c>
       <c r="DD123" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE123" t="n">
         <v>2</v>
@@ -59259,7 +59259,7 @@
         <v>2.7</v>
       </c>
       <c r="DO123" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -59673,7 +59673,7 @@
         <v>3</v>
       </c>
       <c r="DE124" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF124" t="n">
         <v>3</v>
@@ -59703,7 +59703,7 @@
         <v>3.71</v>
       </c>
       <c r="DO124" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -60163,7 +60163,7 @@
         <v>2.9</v>
       </c>
       <c r="DO125" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -62002,7 +62002,7 @@
         <v>60</v>
       </c>
       <c r="DD129" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE129" t="n">
         <v>1.13</v>
@@ -62035,7 +62035,7 @@
         <v>2.46</v>
       </c>
       <c r="DO129" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -62481,7 +62481,7 @@
         <v>2</v>
       </c>
       <c r="DE130" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF130" t="n">
         <v>2</v>
@@ -62511,7 +62511,7 @@
         <v>3.72</v>
       </c>
       <c r="DO130" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -62987,7 +62987,7 @@
         <v>2.6</v>
       </c>
       <c r="DO131" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -63426,10 +63426,10 @@
         <v>50</v>
       </c>
       <c r="DD132" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE132" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF132" t="n">
         <v>1.33</v>
@@ -63459,7 +63459,7 @@
         <v>2.07</v>
       </c>
       <c r="DO132" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -63894,10 +63894,10 @@
         <v>56</v>
       </c>
       <c r="DD133" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE133" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF133" t="n">
         <v>1.5</v>
@@ -63927,7 +63927,7 @@
         <v>2.14</v>
       </c>
       <c r="DO133" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -64395,7 +64395,7 @@
         <v>3.53</v>
       </c>
       <c r="DO134" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -64833,7 +64833,7 @@
         <v>0.17</v>
       </c>
       <c r="DE135" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF135" t="n">
         <v>0.2</v>
@@ -65298,10 +65298,10 @@
         <v>86</v>
       </c>
       <c r="DD136" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE136" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF136" t="n">
         <v>2.71</v>
@@ -65331,7 +65331,7 @@
         <v>2.87</v>
       </c>
       <c r="DO136" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -66266,7 +66266,7 @@
         <v>83</v>
       </c>
       <c r="DD138" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE138" t="n">
         <v>1.57</v>
@@ -66746,10 +66746,10 @@
         <v>66</v>
       </c>
       <c r="DD139" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DE139" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF139" t="n">
         <v>0.71</v>
@@ -66779,7 +66779,7 @@
         <v>3.03</v>
       </c>
       <c r="DO139" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -67221,7 +67221,7 @@
         <v>1.13</v>
       </c>
       <c r="DE140" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF140" t="n">
         <v>1.14</v>
@@ -67673,7 +67673,7 @@
         <v>1.17</v>
       </c>
       <c r="DE141" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF141" t="n">
         <v>1.2</v>
@@ -68147,7 +68147,7 @@
         <v>3.68</v>
       </c>
       <c r="DO142" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -68577,7 +68577,7 @@
         <v>1.78</v>
       </c>
       <c r="DE143" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF143" t="n">
         <v>1.86</v>
@@ -68607,7 +68607,7 @@
         <v>3.83</v>
       </c>
       <c r="DO143" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -69079,7 +69079,7 @@
         <v>2.27</v>
       </c>
       <c r="DO144" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP144" t="b">
         <v>0</v>
@@ -70006,7 +70006,7 @@
         <v>64</v>
       </c>
       <c r="DD146" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE146" t="n">
         <v>0.75</v>
@@ -70039,7 +70039,7 @@
         <v>2.91</v>
       </c>
       <c r="DO146" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -70983,7 +70983,7 @@
         <v>2.91</v>
       </c>
       <c r="DO148" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -71467,7 +71467,7 @@
         <v>2.7</v>
       </c>
       <c r="DO149" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP149" t="b">
         <v>1</v>
@@ -71927,7 +71927,7 @@
         <v>2.64</v>
       </c>
       <c r="DO150" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -72891,7 +72891,7 @@
         <v>3.58</v>
       </c>
       <c r="DO152" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -73880,82 +73880,3414 @@
       </c>
       <c r="EA154" t="inlineStr">
         <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EB154" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC154" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="ED154" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE154" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EF154" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EG154" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="EH154" t="inlineStr">
+        <is>
+          <t>4.63</t>
+        </is>
+      </c>
+      <c r="EI154" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="EJ154" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EK154" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EL154" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EM154" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EN154" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EO154" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EP154" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>16</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Valencia CF</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>46004.54166666666</v>
+      </c>
+      <c r="G155" t="n">
+        <v>2</v>
+      </c>
+      <c r="H155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I155" t="n">
+        <v>3</v>
+      </c>
+      <c r="J155" t="n">
+        <v>5</v>
+      </c>
+      <c r="K155" t="n">
+        <v>7</v>
+      </c>
+      <c r="L155" t="n">
+        <v>12</v>
+      </c>
+      <c r="M155" t="n">
+        <v>3</v>
+      </c>
+      <c r="N155" t="n">
+        <v>1</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>6</v>
+      </c>
+      <c r="R155" t="n">
+        <v>2</v>
+      </c>
+      <c r="S155" t="n">
+        <v>4</v>
+      </c>
+      <c r="T155" t="n">
+        <v>11</v>
+      </c>
+      <c r="U155" t="n">
+        <v>10</v>
+      </c>
+      <c r="V155" t="n">
+        <v>13</v>
+      </c>
+      <c r="W155" t="n">
+        <v>13</v>
+      </c>
+      <c r="X155" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>Estadio Wanda Metropolitano</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>Rosas, Madrid</t>
+        </is>
+      </c>
+      <c r="AC155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>117</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ155" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK155" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL155" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM155" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN155" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV155" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW155" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX155" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY155" t="n">
+        <v>99</v>
+      </c>
+      <c r="BZ155" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CA155" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CB155" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="CC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR155" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS155" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU155" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV155" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX155" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY155" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ155" t="n">
+        <v>54</v>
+      </c>
+      <c r="DA155" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB155" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC155" t="n">
+        <v>81</v>
+      </c>
+      <c r="DD155" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DE155" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DF155" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DG155" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DH155" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DI155" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ155" t="n">
+        <v>47</v>
+      </c>
+      <c r="DK155" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL155" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DM155" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="DN155" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="DO155" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW155" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="DX155" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="DY155" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="DZ155" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="EA155" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EB155" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EC155" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="ED155" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EE155" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EF155" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="EG155" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EH155" t="inlineStr">
+        <is>
+          <t>9.57</t>
+        </is>
+      </c>
+      <c r="EI155" t="inlineStr">
+        <is>
+          <t>5.55</t>
+        </is>
+      </c>
+      <c r="EJ155" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EK155" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EL155" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EM155" t="inlineStr"/>
+      <c r="EN155" t="inlineStr"/>
+      <c r="EO155" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EP155" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>16</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>RCD Mallorca</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Elche CF</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>46004.63541666666</v>
+      </c>
+      <c r="G156" t="n">
+        <v>3</v>
+      </c>
+      <c r="H156" t="n">
+        <v>1</v>
+      </c>
+      <c r="I156" t="n">
+        <v>4</v>
+      </c>
+      <c r="J156" t="n">
+        <v>1</v>
+      </c>
+      <c r="K156" t="n">
+        <v>1</v>
+      </c>
+      <c r="L156" t="n">
+        <v>2</v>
+      </c>
+      <c r="M156" t="n">
+        <v>3</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>8</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="n">
+        <v>7</v>
+      </c>
+      <c r="T156" t="n">
+        <v>9</v>
+      </c>
+      <c r="U156" t="n">
+        <v>15</v>
+      </c>
+      <c r="V156" t="n">
+        <v>9</v>
+      </c>
+      <c r="W156" t="n">
+        <v>13</v>
+      </c>
+      <c r="X156" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA156" t="inlineStr"/>
+      <c r="AB156" t="inlineStr"/>
+      <c r="AC156" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>298</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>64</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV156" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW156" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX156" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY156" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ156" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CA156" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="CB156" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR156" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS156" t="n">
+        <v>6</v>
+      </c>
+      <c r="CT156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU156" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV156" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX156" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY156" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ156" t="n">
+        <v>36</v>
+      </c>
+      <c r="DA156" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB156" t="n">
+        <v>22</v>
+      </c>
+      <c r="DC156" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD156" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DE156" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DF156" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG156" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DH156" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DI156" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DJ156" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK156" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL156" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DM156" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="DN156" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DO156" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP156" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ156" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR156" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS156" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT156" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU156" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV156" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW156" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="DX156" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="DY156" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="DZ156" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="EA156" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EB156" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EC156" t="inlineStr"/>
+      <c r="ED156" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EE156" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EF156" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EG156" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EH156" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EI156" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EJ156" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EK156" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EL156" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EM156" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EN156" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EO156" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EP156" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>16</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>CA Osasuna</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>46004.72916666666</v>
+      </c>
+      <c r="G157" t="n">
+        <v>2</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>2</v>
+      </c>
+      <c r="J157" t="n">
+        <v>14</v>
+      </c>
+      <c r="K157" t="n">
+        <v>1</v>
+      </c>
+      <c r="L157" t="n">
+        <v>15</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
+        <v>3</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>7</v>
+      </c>
+      <c r="R157" t="n">
+        <v>2</v>
+      </c>
+      <c r="S157" t="n">
+        <v>17</v>
+      </c>
+      <c r="T157" t="n">
+        <v>1</v>
+      </c>
+      <c r="U157" t="n">
+        <v>24</v>
+      </c>
+      <c r="V157" t="n">
+        <v>3</v>
+      </c>
+      <c r="W157" t="n">
+        <v>5</v>
+      </c>
+      <c r="X157" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>Camp Nou</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>Carrer d'Arístides Maillol, Barcelona</t>
+        </is>
+      </c>
+      <c r="AC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>83</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI157" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK157" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN157" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV157" t="n">
+        <v>100</v>
+      </c>
+      <c r="BW157" t="n">
+        <v>16</v>
+      </c>
+      <c r="BX157" t="n">
+        <v>139</v>
+      </c>
+      <c r="BY157" t="n">
+        <v>57</v>
+      </c>
+      <c r="BZ157" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CA157" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="CB157" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="CC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM157" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR157" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS157" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU157" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV157" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX157" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY157" t="n">
+        <v>16</v>
+      </c>
+      <c r="CZ157" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA157" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB157" t="n">
+        <v>51</v>
+      </c>
+      <c r="DC157" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD157" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE157" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DF157" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG157" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DH157" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DI157" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ157" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK157" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL157" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DM157" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="DN157" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="DO157" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP157" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ157" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR157" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS157" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT157" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU157" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV157" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW157" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="DX157" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="DY157" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="DZ157" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA157" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EB157" t="inlineStr"/>
+      <c r="EC157" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="ED157" t="inlineStr"/>
+      <c r="EE157" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EF157" t="inlineStr"/>
+      <c r="EG157" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EH157" t="inlineStr">
+        <is>
+          <t>12.83</t>
+        </is>
+      </c>
+      <c r="EI157" t="inlineStr">
+        <is>
+          <t>8.36</t>
+        </is>
+      </c>
+      <c r="EJ157" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EK157" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EL157" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EM157" t="inlineStr"/>
+      <c r="EN157" t="inlineStr"/>
+      <c r="EO157" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EP157" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>16</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Getafe CF</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>RCD Espanyol</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>46004.83333333334</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>1</v>
+      </c>
+      <c r="I158" t="n">
+        <v>1</v>
+      </c>
+      <c r="J158" t="n">
+        <v>6</v>
+      </c>
+      <c r="K158" t="n">
+        <v>4</v>
+      </c>
+      <c r="L158" t="n">
+        <v>10</v>
+      </c>
+      <c r="M158" t="n">
+        <v>5</v>
+      </c>
+      <c r="N158" t="n">
+        <v>1</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>1</v>
+      </c>
+      <c r="R158" t="n">
+        <v>4</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="n">
+        <v>2</v>
+      </c>
+      <c r="U158" t="n">
+        <v>11</v>
+      </c>
+      <c r="V158" t="n">
+        <v>6</v>
+      </c>
+      <c r="W158" t="n">
+        <v>18</v>
+      </c>
+      <c r="X158" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>Coliseum Alfonso Pérez</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>Avenida de Teresa de Calcuta, Getafe</t>
+        </is>
+      </c>
+      <c r="AC158" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB158" t="n">
+        <v>280</v>
+      </c>
+      <c r="BC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF158" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG158" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI158" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ158" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK158" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM158" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN158" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO158" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ158" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS158" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT158" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV158" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW158" t="n">
+        <v>20</v>
+      </c>
+      <c r="BX158" t="n">
+        <v>120</v>
+      </c>
+      <c r="BY158" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ158" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CA158" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="CB158" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR158" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS158" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU158" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV158" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX158" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY158" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ158" t="n">
+        <v>24</v>
+      </c>
+      <c r="DA158" t="n">
+        <v>62</v>
+      </c>
+      <c r="DB158" t="n">
+        <v>24</v>
+      </c>
+      <c r="DC158" t="n">
+        <v>40</v>
+      </c>
+      <c r="DD158" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DE158" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DF158" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DG158" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH158" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI158" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DJ158" t="n">
+        <v>77</v>
+      </c>
+      <c r="DK158" t="n">
+        <v>38</v>
+      </c>
+      <c r="DL158" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DM158" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DN158" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DO158" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP158" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ158" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR158" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS158" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT158" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU158" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV158" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW158" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="DX158" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="DY158" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="DZ158" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="EA158" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="EB158" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EC158" t="inlineStr"/>
+      <c r="ED158" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EE158" t="inlineStr"/>
+      <c r="EF158" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EG158" t="inlineStr"/>
+      <c r="EH158" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EI158" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="EJ158" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="EK158" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EL158" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EM158" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EN158" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EO158" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EP158" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>16</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Sevilla FC</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>46005.54166666666</v>
+      </c>
+      <c r="G159" t="n">
+        <v>4</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" t="n">
+        <v>4</v>
+      </c>
+      <c r="J159" t="n">
+        <v>5</v>
+      </c>
+      <c r="K159" t="n">
+        <v>3</v>
+      </c>
+      <c r="L159" t="n">
+        <v>8</v>
+      </c>
+      <c r="M159" t="n">
+        <v>1</v>
+      </c>
+      <c r="N159" t="n">
+        <v>1</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>7</v>
+      </c>
+      <c r="R159" t="n">
+        <v>1</v>
+      </c>
+      <c r="S159" t="n">
+        <v>6</v>
+      </c>
+      <c r="T159" t="n">
+        <v>3</v>
+      </c>
+      <c r="U159" t="n">
+        <v>13</v>
+      </c>
+      <c r="V159" t="n">
+        <v>4</v>
+      </c>
+      <c r="W159" t="n">
+        <v>11</v>
+      </c>
+      <c r="X159" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>Estadio Ramón Sánchez Pizjuán</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>Avenida de Eduardo Dato, Sevilla</t>
+        </is>
+      </c>
+      <c r="AC159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>98</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ159" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK159" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM159" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN159" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR159" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT159" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV159" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW159" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX159" t="n">
+        <v>84</v>
+      </c>
+      <c r="BY159" t="n">
+        <v>89</v>
+      </c>
+      <c r="BZ159" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CA159" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CB159" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CC159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR159" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS159" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU159" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV159" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX159" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY159" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ159" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA159" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB159" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC159" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD159" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE159" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF159" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG159" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DH159" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI159" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DJ159" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK159" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL159" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DM159" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="DN159" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DO159" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP159" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ159" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR159" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS159" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT159" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU159" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV159" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW159" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="DX159" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="DY159" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="DZ159" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="EA159" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EB159" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EC159" t="inlineStr"/>
+      <c r="ED159" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EE159" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EF159" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EG159" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EH159" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="EI159" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EJ159" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EK159" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EL159" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EM159" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EN159" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EO159" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EP159" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>16</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Athletic Club Bilbao</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>46005.63541666666</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="n">
+        <v>2</v>
+      </c>
+      <c r="J160" t="n">
+        <v>1</v>
+      </c>
+      <c r="K160" t="n">
+        <v>4</v>
+      </c>
+      <c r="L160" t="n">
+        <v>5</v>
+      </c>
+      <c r="M160" t="n">
+        <v>3</v>
+      </c>
+      <c r="N160" t="n">
+        <v>2</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>2</v>
+      </c>
+      <c r="R160" t="n">
+        <v>2</v>
+      </c>
+      <c r="S160" t="n">
+        <v>3</v>
+      </c>
+      <c r="T160" t="n">
+        <v>12</v>
+      </c>
+      <c r="U160" t="n">
+        <v>5</v>
+      </c>
+      <c r="V160" t="n">
+        <v>14</v>
+      </c>
+      <c r="W160" t="n">
+        <v>11</v>
+      </c>
+      <c r="X160" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA160" t="inlineStr"/>
+      <c r="AB160" t="inlineStr"/>
+      <c r="AC160" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>281</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>52</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG160" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN160" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ160" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR160" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT160" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV160" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW160" t="n">
+        <v>62</v>
+      </c>
+      <c r="BX160" t="n">
+        <v>86</v>
+      </c>
+      <c r="BY160" t="n">
+        <v>122</v>
+      </c>
+      <c r="BZ160" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="CA160" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CB160" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CC160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR160" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS160" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU160" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV160" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX160" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY160" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ160" t="n">
+        <v>28</v>
+      </c>
+      <c r="DA160" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB160" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC160" t="n">
+        <v>53</v>
+      </c>
+      <c r="DD160" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DE160" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DF160" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DG160" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH160" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DI160" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DJ160" t="n">
+        <v>73</v>
+      </c>
+      <c r="DK160" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL160" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM160" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DN160" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="DO160" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP160" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ160" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR160" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS160" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT160" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU160" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV160" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW160" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="DX160" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="DY160" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="DZ160" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="EA160" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EB160" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EC160" t="inlineStr"/>
+      <c r="ED160" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EE160" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EF160" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="EG160" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="EH160" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EI160" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EJ160" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="EK160" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EL160" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EM160" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EN160" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EO160" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EP160" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>16</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>46005.83333333334</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" t="n">
+        <v>2</v>
+      </c>
+      <c r="I161" t="n">
+        <v>3</v>
+      </c>
+      <c r="J161" t="n">
+        <v>5</v>
+      </c>
+      <c r="K161" t="n">
+        <v>7</v>
+      </c>
+      <c r="L161" t="n">
+        <v>12</v>
+      </c>
+      <c r="M161" t="n">
+        <v>3</v>
+      </c>
+      <c r="N161" t="n">
+        <v>1</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>2</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6</v>
+      </c>
+      <c r="S161" t="n">
+        <v>4</v>
+      </c>
+      <c r="T161" t="n">
+        <v>7</v>
+      </c>
+      <c r="U161" t="n">
+        <v>6</v>
+      </c>
+      <c r="V161" t="n">
+        <v>13</v>
+      </c>
+      <c r="W161" t="n">
+        <v>12</v>
+      </c>
+      <c r="X161" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>Estadio de Mendizorroza</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+        </is>
+      </c>
+      <c r="AC161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>84</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ161" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT161" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV161" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW161" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX161" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY161" t="n">
+        <v>95</v>
+      </c>
+      <c r="BZ161" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="CA161" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CB161" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CC161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR161" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS161" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU161" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV161" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX161" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY161" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ161" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA161" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB161" t="n">
+        <v>41</v>
+      </c>
+      <c r="DC161" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD161" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DE161" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DF161" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG161" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH161" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DI161" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DJ161" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK161" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL161" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DM161" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DN161" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DO161" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP161" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ161" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR161" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS161" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT161" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU161" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV161" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW161" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="DX161" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="DY161" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="DZ161" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="EA161" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EB161" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EC161" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="ED161" t="inlineStr"/>
+      <c r="EE161" t="inlineStr"/>
+      <c r="EF161" t="inlineStr"/>
+      <c r="EG161" t="inlineStr"/>
+      <c r="EH161" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EI161" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="EJ161" t="inlineStr">
+        <is>
+          <t>6.07</t>
+        </is>
+      </c>
+      <c r="EK161" t="inlineStr">
+        <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="EB154" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EC154" t="inlineStr">
-        <is>
-          <t>3.41</t>
-        </is>
-      </c>
-      <c r="ED154" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EE154" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EF154" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="EG154" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="EH154" t="inlineStr">
-        <is>
-          <t>5.09</t>
-        </is>
-      </c>
-      <c r="EI154" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
-      </c>
-      <c r="EJ154" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EK154" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EL154" t="inlineStr">
+      <c r="EL161" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EM161" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EN161" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EO161" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EP161" t="inlineStr">
         <is>
           <t>1.91</t>
-        </is>
-      </c>
-      <c r="EM154" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EN154" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="EO154" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EP154" t="inlineStr">
-        <is>
-          <t>1.93</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP161" headerRowCount="1">
-  <autoFilter ref="A1:EP161"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP162" headerRowCount="1">
+  <autoFilter ref="A1:EP162"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP161"/>
+  <dimension ref="A1:EP162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -5613,7 +5613,7 @@
         <v>2</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5643,7 +5643,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -10383,7 +10383,7 @@
         <v>3.14</v>
       </c>
       <c r="DO20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -11305,7 +11305,7 @@
         <v>0.89</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11335,7 +11335,7 @@
         <v>2.67</v>
       </c>
       <c r="DO22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -15135,7 +15135,7 @@
         <v>1.65</v>
       </c>
       <c r="DO30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -16062,7 +16062,7 @@
         <v>50</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DE32" t="n">
         <v>2</v>
@@ -16095,7 +16095,7 @@
         <v>2.84</v>
       </c>
       <c r="DO32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -19417,7 +19417,7 @@
         <v>0.17</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF39" t="n">
         <v>0</v>
@@ -19919,7 +19919,7 @@
         <v>2.95</v>
       </c>
       <c r="DO40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -21331,7 +21331,7 @@
         <v>2.96</v>
       </c>
       <c r="DO43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -24150,7 +24150,7 @@
         <v>100</v>
       </c>
       <c r="DD49" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DE49" t="n">
         <v>2</v>
@@ -24183,7 +24183,7 @@
         <v>2.29</v>
       </c>
       <c r="DO49" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -28127,40 +28127,40 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>45924.8125</v>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L58" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -28169,128 +28169,128 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R58" t="n">
         <v>3</v>
       </c>
       <c r="S58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U58" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="V58" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W58" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="X58" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y58" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Z58" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Estadio Wanda Metropolitano</t>
+          <t>Estadio Municipal de Anoeta</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Rosas, Madrid</t>
+          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
         </is>
       </c>
       <c r="AC58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF58" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AG58" t="n">
-        <v>6.5</v>
+        <v>5.13</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AJ58" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AL58" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AM58" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AN58" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AO58" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AP58" t="n">
         <v>1.99</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AR58" t="n">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="AS58" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AU58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB58" t="n">
-        <v>117</v>
+        <v>290</v>
       </c>
       <c r="BC58" t="n">
         <v>0</v>
       </c>
       <c r="BD58" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="BE58" t="n">
         <v>0</v>
@@ -28305,10 +28305,10 @@
         <v>1</v>
       </c>
       <c r="BI58" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BJ58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BK58" t="n">
         <v>4</v>
@@ -28317,52 +28317,52 @@
         <v>2</v>
       </c>
       <c r="BM58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BN58" t="n">
         <v>6</v>
       </c>
       <c r="BO58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BS58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT58" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BU58" t="n">
         <v>1</v>
       </c>
       <c r="BV58" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="BW58" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="BX58" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="BY58" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="BZ58" t="n">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="CA58" t="n">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="CB58" t="n">
-        <v>3.33</v>
+        <v>2.69</v>
       </c>
       <c r="CC58" t="n">
         <v>0</v>
@@ -28395,7 +28395,7 @@
         <v>0</v>
       </c>
       <c r="CM58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN58" t="n">
         <v>0</v>
@@ -28413,189 +28413,169 @@
         <v>22</v>
       </c>
       <c r="CS58" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CT58" t="n">
         <v>1</v>
       </c>
       <c r="CU58" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CV58" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="CW58" t="n">
         <v>1</v>
       </c>
       <c r="CX58" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="CY58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CZ58" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="DA58" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DB58" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="DC58" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>2.78</v>
+        <v>1.25</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.11</v>
+        <v>0.5</v>
       </c>
       <c r="DF58" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="DG58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH58" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="DI58" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="DJ58" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="DK58" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL58" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="DM58" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="DN58" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="DO58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
       </c>
       <c r="DQ58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU58" t="b">
         <v>0</v>
       </c>
       <c r="DV58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW58" t="n">
-        <v>18.88</v>
+        <v>13.25</v>
       </c>
       <c r="DX58" t="n">
-        <v>6.34</v>
+        <v>3.2</v>
       </c>
       <c r="DY58" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="DZ58" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EA58" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EB58" t="inlineStr">
         <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EC58" t="inlineStr">
-        <is>
-          <t>3.42</t>
-        </is>
-      </c>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EC58" t="inlineStr"/>
       <c r="ED58" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EE58" t="inlineStr">
+        <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="EE58" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
       <c r="EF58" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EG58" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EH58" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="EI58" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="EJ58" t="inlineStr">
         <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EK58" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="EL58" t="inlineStr">
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EK58" t="inlineStr"/>
+      <c r="EL58" t="inlineStr"/>
+      <c r="EM58" t="inlineStr"/>
+      <c r="EN58" t="inlineStr"/>
+      <c r="EO58" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EP58" t="inlineStr">
         <is>
           <t>2.06</t>
-        </is>
-      </c>
-      <c r="EM58" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EN58" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="EO58" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EP58" t="inlineStr">
-        <is>
-          <t>2.18</t>
         </is>
       </c>
     </row>
@@ -28615,40 +28595,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
         <v>45924.8125</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L59" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -28657,128 +28637,128 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R59" t="n">
         <v>3</v>
       </c>
       <c r="S59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U59" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="V59" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W59" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="X59" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y59" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="Z59" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Anoeta</t>
+          <t>Estadio Wanda Metropolitano</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
+          <t>Rosas, Madrid</t>
         </is>
       </c>
       <c r="AC59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF59" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG59" t="n">
-        <v>5.13</v>
+        <v>6.5</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AI59" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AJ59" t="n">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AL59" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AM59" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AN59" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AO59" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AP59" t="n">
         <v>1.99</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AR59" t="n">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="AS59" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AT59" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AU59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB59" t="n">
-        <v>290</v>
+        <v>117</v>
       </c>
       <c r="BC59" t="n">
         <v>0</v>
       </c>
       <c r="BD59" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="BE59" t="n">
         <v>0</v>
@@ -28793,10 +28773,10 @@
         <v>1</v>
       </c>
       <c r="BI59" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BJ59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK59" t="n">
         <v>4</v>
@@ -28805,52 +28785,52 @@
         <v>2</v>
       </c>
       <c r="BM59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BN59" t="n">
         <v>6</v>
       </c>
       <c r="BO59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BS59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT59" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BU59" t="n">
         <v>1</v>
       </c>
       <c r="BV59" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="BW59" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="BX59" t="n">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="BY59" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="BZ59" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="CA59" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="CB59" t="n">
-        <v>2.69</v>
+        <v>3.33</v>
       </c>
       <c r="CC59" t="n">
         <v>0</v>
@@ -28883,7 +28863,7 @@
         <v>0</v>
       </c>
       <c r="CM59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN59" t="n">
         <v>0</v>
@@ -28901,70 +28881,70 @@
         <v>22</v>
       </c>
       <c r="CS59" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CT59" t="n">
         <v>1</v>
       </c>
       <c r="CU59" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CV59" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="CW59" t="n">
         <v>1</v>
       </c>
       <c r="CX59" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CZ59" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="DA59" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="DB59" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="DC59" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.25</v>
+        <v>2.78</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.5</v>
+        <v>1.11</v>
       </c>
       <c r="DF59" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DG59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DH59" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="DI59" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="DJ59" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="DK59" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DL59" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="DM59" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="DN59" t="n">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="DO59" t="n">
         <v>16</v>
@@ -28973,97 +28953,117 @@
         <v>1</v>
       </c>
       <c r="DQ59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU59" t="b">
         <v>0</v>
       </c>
       <c r="DV59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW59" t="n">
-        <v>13.25</v>
+        <v>18.88</v>
       </c>
       <c r="DX59" t="n">
-        <v>3.2</v>
+        <v>6.34</v>
       </c>
       <c r="DY59" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="DZ59" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="EA59" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB59" t="inlineStr">
         <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EC59" t="inlineStr"/>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC59" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
       <c r="ED59" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EE59" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EF59" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EG59" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EH59" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="EI59" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="EJ59" t="inlineStr">
         <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EK59" t="inlineStr"/>
-      <c r="EL59" t="inlineStr"/>
-      <c r="EM59" t="inlineStr"/>
-      <c r="EN59" t="inlineStr"/>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EK59" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EL59" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EM59" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EN59" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
       <c r="EO59" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EP59" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.18</t>
         </is>
       </c>
     </row>
@@ -32682,7 +32682,7 @@
         <v>75</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DE67" t="n">
         <v>1.25</v>
@@ -32715,7 +32715,7 @@
         <v>2.84</v>
       </c>
       <c r="DO67" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -34111,7 +34111,7 @@
         <v>2.27</v>
       </c>
       <c r="DO70" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -38043,146 +38043,146 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45935.6875</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K79" t="n">
         <v>5</v>
       </c>
       <c r="L79" t="n">
+        <v>15</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2</v>
+      </c>
+      <c r="N79" t="n">
+        <v>6</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>5</v>
+      </c>
+      <c r="R79" t="n">
+        <v>3</v>
+      </c>
+      <c r="S79" t="n">
+        <v>9</v>
+      </c>
+      <c r="T79" t="n">
+        <v>9</v>
+      </c>
+      <c r="U79" t="n">
+        <v>14</v>
+      </c>
+      <c r="V79" t="n">
         <v>12</v>
       </c>
-      <c r="M79" t="n">
-        <v>1</v>
-      </c>
-      <c r="N79" t="n">
-        <v>2</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>3</v>
-      </c>
-      <c r="R79" t="n">
-        <v>2</v>
-      </c>
-      <c r="S79" t="n">
-        <v>7</v>
-      </c>
-      <c r="T79" t="n">
-        <v>5</v>
-      </c>
-      <c r="U79" t="n">
-        <v>10</v>
-      </c>
-      <c r="V79" t="n">
-        <v>7</v>
-      </c>
       <c r="W79" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X79" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Y79" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z79" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Anoeta</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="AF79" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AG79" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AI79" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AJ79" t="n">
-        <v>3.85</v>
+        <v>2.96</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AM79" t="n">
         <v>1.44</v>
       </c>
       <c r="AN79" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AO79" t="n">
         <v>2.55</v>
       </c>
       <c r="AP79" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AR79" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AU79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW79" t="n">
         <v>0</v>
@@ -38191,22 +38191,22 @@
         <v>0</v>
       </c>
       <c r="AY79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38221,190 +38221,190 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BJ79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BK79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR79" t="n">
         <v>4</v>
       </c>
-      <c r="BL79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM79" t="n">
+      <c r="BS79" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX79" t="n">
         <v>6</v>
       </c>
-      <c r="BN79" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT79" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV79" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW79" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX79" t="n">
-        <v>101</v>
-      </c>
-      <c r="BY79" t="n">
-        <v>90</v>
-      </c>
-      <c r="BZ79" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="CA79" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB79" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN79" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR79" t="n">
-        <v>14</v>
-      </c>
-      <c r="CS79" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU79" t="n">
-        <v>21</v>
-      </c>
-      <c r="CV79" t="n">
+      <c r="CY79" t="n">
         <v>13</v>
       </c>
-      <c r="CW79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX79" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY79" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ79" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="DA79" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="DB79" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="DC79" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.25</v>
+        <v>2.11</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="DF79" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="DG79" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DH79" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="DI79" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="DJ79" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="DK79" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="DN79" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="DO79" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
       </c>
       <c r="DQ79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS79" t="b">
         <v>0</v>
@@ -38416,94 +38416,102 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW79" t="n">
-        <v>17.19</v>
+        <v>17.75</v>
       </c>
       <c r="DX79" t="n">
-        <v>3.66</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EB79" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EC79" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED79" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EE79" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EG79" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EJ79" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EK79" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EL79" t="inlineStr">
+        <is>
           <t>2.02</t>
         </is>
       </c>
-      <c r="EB79" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC79" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="ED79" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE79" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF79" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG79" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="EH79" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="EI79" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="EJ79" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EK79" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EL79" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EM79" t="inlineStr"/>
-      <c r="EN79" t="inlineStr"/>
+      <c r="EM79" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EN79" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.68</t>
         </is>
       </c>
     </row>
@@ -38523,40 +38531,40 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45935.6875</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K80" t="n">
         <v>5</v>
       </c>
       <c r="L80" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -38565,104 +38573,104 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
+        <v>3</v>
+      </c>
+      <c r="R80" t="n">
+        <v>2</v>
+      </c>
+      <c r="S80" t="n">
+        <v>7</v>
+      </c>
+      <c r="T80" t="n">
         <v>5</v>
       </c>
-      <c r="R80" t="n">
-        <v>3</v>
-      </c>
-      <c r="S80" t="n">
-        <v>9</v>
-      </c>
-      <c r="T80" t="n">
-        <v>9</v>
-      </c>
       <c r="U80" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V80" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W80" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="X80" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Y80" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z80" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>Estadio Municipal de Anoeta</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
         </is>
       </c>
       <c r="AC80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="AF80" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AJ80" t="n">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AL80" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AM80" t="n">
         <v>1.44</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AO80" t="n">
         <v>2.55</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AR80" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AU80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW80" t="n">
         <v>0</v>
@@ -38671,22 +38679,22 @@
         <v>0</v>
       </c>
       <c r="AY80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB80" t="n">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -38701,190 +38709,190 @@
         <v>1</v>
       </c>
       <c r="BI80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BJ80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BK80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM80" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>101</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV80" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX80" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY80" t="n">
         <v>10</v>
       </c>
-      <c r="BN80" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR80" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS80" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT80" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV80" t="n">
-        <v>66</v>
-      </c>
-      <c r="BW80" t="n">
-        <v>34</v>
-      </c>
-      <c r="BX80" t="n">
-        <v>107</v>
-      </c>
-      <c r="BY80" t="n">
-        <v>98</v>
-      </c>
-      <c r="BZ80" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CA80" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CB80" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CC80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR80" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS80" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU80" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV80" t="n">
+      <c r="CZ80" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA80" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>59</v>
+      </c>
+      <c r="DC80" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD80" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE80" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DF80" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DI80" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DJ80" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK80" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL80" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DM80" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DN80" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="DO80" t="n">
         <v>16</v>
       </c>
-      <c r="CW80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX80" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY80" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ80" t="n">
-        <v>54</v>
-      </c>
-      <c r="DA80" t="n">
-        <v>88</v>
-      </c>
-      <c r="DB80" t="n">
-        <v>29</v>
-      </c>
-      <c r="DC80" t="n">
-        <v>88</v>
-      </c>
-      <c r="DD80" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DE80" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DF80" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DG80" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH80" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DI80" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DJ80" t="n">
-        <v>46</v>
-      </c>
-      <c r="DK80" t="n">
-        <v>13</v>
-      </c>
-      <c r="DL80" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="DM80" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="DN80" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="DO80" t="n">
-        <v>15</v>
-      </c>
       <c r="DP80" t="b">
         <v>1</v>
       </c>
       <c r="DQ80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS80" t="b">
         <v>0</v>
@@ -38896,102 +38904,94 @@
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW80" t="n">
-        <v>17.75</v>
+        <v>17.19</v>
       </c>
       <c r="DX80" t="n">
-        <v>9.369999999999999</v>
+        <v>3.66</v>
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EB80" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EC80" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="ED80" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EE80" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EF80" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EG80" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EH80" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EI80" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EJ80" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EK80" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EL80" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EM80" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EN80" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM80" t="inlineStr"/>
+      <c r="EN80" t="inlineStr"/>
       <c r="EO80" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EP80" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.84</t>
         </is>
       </c>
     </row>
@@ -41201,7 +41201,7 @@
         <v>2.75</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF85" t="n">
         <v>3</v>
@@ -47447,7 +47447,7 @@
         <v>3</v>
       </c>
       <c r="DO98" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -48822,7 +48822,7 @@
         <v>42</v>
       </c>
       <c r="DD101" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DE101" t="n">
         <v>0.57</v>
@@ -48855,7 +48855,7 @@
         <v>2.88</v>
       </c>
       <c r="DO101" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -53087,7 +53087,7 @@
         <v>2.91</v>
       </c>
       <c r="DO110" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -56870,7 +56870,7 @@
         <v>53</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DE118" t="n">
         <v>2.1</v>
@@ -56903,7 +56903,7 @@
         <v>3.88</v>
       </c>
       <c r="DO118" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP118" t="b">
         <v>0</v>
@@ -57011,12 +57011,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F119" s="2" t="n">
@@ -57026,25 +57026,25 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K119" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L119" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -57056,125 +57056,117 @@
         <v>4</v>
       </c>
       <c r="R119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S119" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T119" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U119" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="V119" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W119" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X119" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y119" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Z119" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>Estadio de Mestalla</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>Avenida de Suecia, Valencia</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE119" t="n">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="AF119" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="AG119" t="n">
-        <v>2.15</v>
+        <v>2.98</v>
       </c>
       <c r="AH119" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AI119" t="n">
-        <v>1.91</v>
+        <v>3.04</v>
       </c>
       <c r="AJ119" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="AK119" t="n">
-        <v>1.72</v>
+        <v>2.43</v>
       </c>
       <c r="AL119" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AM119" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="AN119" t="n">
-        <v>1.84</v>
+        <v>2.87</v>
       </c>
       <c r="AO119" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="AR119" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="AS119" t="n">
-        <v>2.89</v>
+        <v>2.05</v>
       </c>
       <c r="AT119" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AU119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW119" t="n">
         <v>0</v>
       </c>
       <c r="AX119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB119" t="n">
-        <v>-1</v>
+        <v>298</v>
       </c>
       <c r="BC119" t="n">
         <v>0</v>
       </c>
       <c r="BD119" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="BE119" t="n">
         <v>0</v>
@@ -57189,64 +57181,64 @@
         <v>1</v>
       </c>
       <c r="BI119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ119" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BK119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL119" t="n">
         <v>6</v>
       </c>
-      <c r="BL119" t="n">
-        <v>1</v>
-      </c>
       <c r="BM119" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BN119" t="n">
         <v>7</v>
       </c>
       <c r="BO119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT119" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BU119" t="n">
         <v>1</v>
       </c>
       <c r="BV119" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="BW119" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="BX119" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="BY119" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="BZ119" t="n">
-        <v>1.74</v>
+        <v>0.96</v>
       </c>
       <c r="CA119" t="n">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="CB119" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="CC119" t="n">
         <v>0</v>
@@ -57279,10 +57271,10 @@
         <v>0</v>
       </c>
       <c r="CM119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO119" t="n">
         <v>0</v>
@@ -57294,19 +57286,19 @@
         <v>1</v>
       </c>
       <c r="CR119" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="CS119" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="CT119" t="n">
         <v>1</v>
       </c>
       <c r="CU119" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CV119" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CW119" t="n">
         <v>1</v>
@@ -57315,61 +57307,61 @@
         <v>6</v>
       </c>
       <c r="CY119" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CZ119" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="DA119" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="DB119" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="DC119" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="DD119" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DE119" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DF119" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG119" t="n">
         <v>1.5</v>
-      </c>
-      <c r="DE119" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DF119" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DG119" t="n">
-        <v>1.4</v>
       </c>
       <c r="DH119" t="n">
         <v>0.82</v>
       </c>
       <c r="DI119" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="DJ119" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="DK119" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="DL119" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="DM119" t="n">
-        <v>1.6</v>
+        <v>0.97</v>
       </c>
       <c r="DN119" t="n">
-        <v>3.06</v>
+        <v>2.18</v>
       </c>
       <c r="DO119" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
       </c>
       <c r="DQ119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR119" t="b">
         <v>0</v>
@@ -57384,102 +57376,90 @@
         <v>0</v>
       </c>
       <c r="DV119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW119" t="n">
-        <v>17.01</v>
+        <v>17.48</v>
       </c>
       <c r="DX119" t="n">
-        <v>5.56</v>
+        <v>5.64</v>
       </c>
       <c r="DY119" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="DZ119" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="EA119" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="EB119" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC119" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr"/>
       <c r="ED119" t="inlineStr">
         <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EE119" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EE119" t="inlineStr"/>
       <c r="EF119" t="inlineStr">
         <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="EG119" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EG119" t="inlineStr"/>
       <c r="EH119" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EI119" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EJ119" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EK119" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="EL119" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EM119" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EN119" t="inlineStr">
+        <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="EM119" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EN119" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
       <c r="EO119" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EP119" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.43</t>
         </is>
       </c>
     </row>
@@ -57499,12 +57479,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F120" s="2" t="n">
@@ -57514,25 +57494,25 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K120" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L120" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -57544,117 +57524,125 @@
         <v>4</v>
       </c>
       <c r="R120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S120" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T120" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U120" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="V120" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W120" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="X120" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y120" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Z120" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA120" t="inlineStr"/>
-      <c r="AB120" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>Avenida de Suecia, Valencia</t>
+        </is>
+      </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE120" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="AF120" t="n">
-        <v>2.58</v>
+        <v>3.45</v>
       </c>
       <c r="AG120" t="n">
-        <v>2.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH120" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AI120" t="n">
-        <v>3.04</v>
+        <v>1.91</v>
       </c>
       <c r="AJ120" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="AK120" t="n">
-        <v>2.43</v>
+        <v>1.72</v>
       </c>
       <c r="AL120" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AM120" t="n">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="AN120" t="n">
-        <v>2.87</v>
+        <v>1.84</v>
       </c>
       <c r="AO120" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.77</v>
+        <v>1.37</v>
       </c>
       <c r="AR120" t="n">
-        <v>4.45</v>
+        <v>2.85</v>
       </c>
       <c r="AS120" t="n">
-        <v>2.05</v>
+        <v>2.89</v>
       </c>
       <c r="AT120" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AU120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW120" t="n">
         <v>0</v>
       </c>
       <c r="AX120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB120" t="n">
-        <v>298</v>
+        <v>-1</v>
       </c>
       <c r="BC120" t="n">
         <v>0</v>
       </c>
       <c r="BD120" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="BE120" t="n">
         <v>0</v>
@@ -57669,64 +57657,64 @@
         <v>1</v>
       </c>
       <c r="BI120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ120" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BK120" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BL120" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BM120" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BN120" t="n">
         <v>7</v>
       </c>
       <c r="BO120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT120" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BU120" t="n">
         <v>1</v>
       </c>
       <c r="BV120" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="BW120" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="BX120" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="BY120" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="BZ120" t="n">
-        <v>0.96</v>
+        <v>1.74</v>
       </c>
       <c r="CA120" t="n">
-        <v>1.63</v>
+        <v>1.09</v>
       </c>
       <c r="CB120" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="CC120" t="n">
         <v>0</v>
@@ -57759,10 +57747,10 @@
         <v>0</v>
       </c>
       <c r="CM120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO120" t="n">
         <v>0</v>
@@ -57774,19 +57762,19 @@
         <v>1</v>
       </c>
       <c r="CR120" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="CS120" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="CT120" t="n">
         <v>1</v>
       </c>
       <c r="CU120" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CV120" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CW120" t="n">
         <v>1</v>
@@ -57795,52 +57783,52 @@
         <v>6</v>
       </c>
       <c r="CY120" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CZ120" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="DA120" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="DB120" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="DC120" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="DF120" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG120" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DH120" t="n">
         <v>0.82</v>
       </c>
       <c r="DI120" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="DJ120" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="DK120" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="DL120" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="DM120" t="n">
-        <v>0.97</v>
+        <v>1.6</v>
       </c>
       <c r="DN120" t="n">
-        <v>2.18</v>
+        <v>3.06</v>
       </c>
       <c r="DO120" t="n">
         <v>16</v>
@@ -57849,7 +57837,7 @@
         <v>1</v>
       </c>
       <c r="DQ120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR120" t="b">
         <v>0</v>
@@ -57864,90 +57852,102 @@
         <v>0</v>
       </c>
       <c r="DV120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW120" t="n">
-        <v>17.48</v>
+        <v>17.01</v>
       </c>
       <c r="DX120" t="n">
-        <v>5.64</v>
+        <v>5.56</v>
       </c>
       <c r="DY120" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="DZ120" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="EA120" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB120" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EC120" t="inlineStr"/>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC120" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
       <c r="ED120" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EE120" t="inlineStr"/>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE120" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
       <c r="EF120" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="EG120" t="inlineStr"/>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EG120" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EH120" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EI120" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EJ120" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EK120" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EL120" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EM120" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EN120" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EO120" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EP120" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -61099,7 +61099,7 @@
         <v>2.27</v>
       </c>
       <c r="DO127" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP127" t="b">
         <v>0</v>
@@ -61575,7 +61575,7 @@
         <v>2.72</v>
       </c>
       <c r="DO128" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -66269,7 +66269,7 @@
         <v>1.25</v>
       </c>
       <c r="DE138" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF138" t="n">
         <v>1.17</v>
@@ -66299,7 +66299,7 @@
         <v>2.89</v>
       </c>
       <c r="DO138" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -67670,7 +67670,7 @@
         <v>52</v>
       </c>
       <c r="DD141" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DE141" t="n">
         <v>0.38</v>
@@ -67703,7 +67703,7 @@
         <v>2.43</v>
       </c>
       <c r="DO141" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -70507,7 +70507,7 @@
         <v>4.01</v>
       </c>
       <c r="DO147" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -72415,7 +72415,7 @@
         <v>2.81</v>
       </c>
       <c r="DO151" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -77228,17 +77228,17 @@
       </c>
       <c r="EA161" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EB161" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="EC161" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="ED161" t="inlineStr"/>
@@ -77247,47 +77247,511 @@
       <c r="EG161" t="inlineStr"/>
       <c r="EH161" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EI161" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="EJ161" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="EK161" t="inlineStr">
         <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EL161" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EM161" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EN161" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EO161" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EP161" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>16</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>46006.83333333334</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>8</v>
+      </c>
+      <c r="K162" t="n">
+        <v>3</v>
+      </c>
+      <c r="L162" t="n">
+        <v>11</v>
+      </c>
+      <c r="M162" t="n">
+        <v>4</v>
+      </c>
+      <c r="N162" t="n">
+        <v>1</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>7</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6</v>
+      </c>
+      <c r="S162" t="n">
+        <v>16</v>
+      </c>
+      <c r="T162" t="n">
+        <v>7</v>
+      </c>
+      <c r="U162" t="n">
+        <v>23</v>
+      </c>
+      <c r="V162" t="n">
+        <v>13</v>
+      </c>
+      <c r="W162" t="n">
+        <v>10</v>
+      </c>
+      <c r="X162" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA162" t="inlineStr"/>
+      <c r="AB162" t="inlineStr"/>
+      <c r="AC162" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>68</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI162" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK162" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM162" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN162" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS162" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV162" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW162" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX162" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY162" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ162" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CA162" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CB162" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="CC162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR162" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS162" t="n">
+        <v>33</v>
+      </c>
+      <c r="CT162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU162" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV162" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX162" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY162" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ162" t="n">
+        <v>22</v>
+      </c>
+      <c r="DA162" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB162" t="n">
+        <v>7</v>
+      </c>
+      <c r="DC162" t="n">
+        <v>52</v>
+      </c>
+      <c r="DD162" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DE162" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF162" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DG162" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DH162" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI162" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DJ162" t="n">
+        <v>79</v>
+      </c>
+      <c r="DK162" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL162" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DM162" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DN162" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="DO162" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP162" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ162" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR162" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS162" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT162" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU162" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV162" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW162" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="DX162" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DY162" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="DZ162" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA162" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EB162" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC162" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="ED162" t="inlineStr"/>
+      <c r="EE162" t="inlineStr"/>
+      <c r="EF162" t="inlineStr"/>
+      <c r="EG162" t="inlineStr"/>
+      <c r="EH162" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EI162" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EJ162" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EK162" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL162" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EM162" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EN162" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EO162" t="inlineStr">
+        <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="EL161" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="EM161" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EN161" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="EO161" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EP161" t="inlineStr">
-        <is>
-          <t>1.91</t>
+      <c r="EP162" t="inlineStr">
+        <is>
+          <t>1.86</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP162" headerRowCount="1">
-  <autoFilter ref="A1:EP162"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP169" headerRowCount="1">
+  <autoFilter ref="A1:EP169"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP162"/>
+  <dimension ref="A1:EP169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DE2" t="n">
         <v>1.11</v>
@@ -2286,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="DE3" t="n">
         <v>0.5</v>
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2769,7 +2769,7 @@
         <v>1.63</v>
       </c>
       <c r="DE4" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3234,10 +3234,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3735,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4641,7 +4641,7 @@
         <v>1.78</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5125,7 +5125,7 @@
         <v>2.11</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -6094,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE11" t="n">
         <v>0.22</v>
@@ -6127,7 +6127,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6557,7 +6557,7 @@
         <v>1.63</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -7033,7 +7033,7 @@
         <v>1.63</v>
       </c>
       <c r="DE13" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -7063,7 +7063,7 @@
         <v>0.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -8002,10 +8002,10 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="DE15" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -8035,7 +8035,7 @@
         <v>2.67</v>
       </c>
       <c r="DO15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8470,7 +8470,7 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE16" t="n">
         <v>0.38</v>
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8938,7 +8938,7 @@
         <v>50</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="DE17" t="n">
         <v>0.75</v>
@@ -8971,7 +8971,7 @@
         <v>2.89</v>
       </c>
       <c r="DO17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9878,7 +9878,7 @@
         <v>0</v>
       </c>
       <c r="DD19" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DE19" t="n">
         <v>2.1</v>
@@ -9911,7 +9911,7 @@
         <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -11807,7 +11807,7 @@
         <v>1.81</v>
       </c>
       <c r="DO23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12262,7 +12262,7 @@
         <v>25</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE24" t="n">
         <v>1.13</v>
@@ -12741,7 +12741,7 @@
         <v>1.56</v>
       </c>
       <c r="DE25" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF25" t="n">
         <v>3</v>
@@ -12771,7 +12771,7 @@
         <v>3.34</v>
       </c>
       <c r="DO25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13222,10 +13222,10 @@
         <v>50</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF26" t="n">
         <v>0</v>
@@ -13255,7 +13255,7 @@
         <v>2.11</v>
       </c>
       <c r="DO26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13690,10 +13690,10 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF27" t="n">
         <v>0</v>
@@ -13723,7 +13723,7 @@
         <v>2.25</v>
       </c>
       <c r="DO27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14178,10 +14178,10 @@
         <v>0</v>
       </c>
       <c r="DD28" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE28" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -14211,7 +14211,7 @@
         <v>2.14</v>
       </c>
       <c r="DO28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14671,7 +14671,7 @@
         <v>1.49</v>
       </c>
       <c r="DO29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -16065,7 +16065,7 @@
         <v>1.14</v>
       </c>
       <c r="DE32" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DF32" t="n">
         <v>0</v>
@@ -17515,7 +17515,7 @@
         <v>4.77</v>
       </c>
       <c r="DO35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17965,7 +17965,7 @@
         <v>1.78</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF36" t="n">
         <v>3</v>
@@ -17995,7 +17995,7 @@
         <v>2.75</v>
       </c>
       <c r="DO36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18479,7 +18479,7 @@
         <v>2.71</v>
       </c>
       <c r="DO37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18959,7 +18959,7 @@
         <v>2.12</v>
       </c>
       <c r="DO38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19414,7 +19414,7 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="DE39" t="n">
         <v>1.5</v>
@@ -19447,7 +19447,7 @@
         <v>2.04</v>
       </c>
       <c r="DO39" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19886,7 +19886,7 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE40" t="n">
         <v>1.11</v>
@@ -20395,7 +20395,7 @@
         <v>0.57</v>
       </c>
       <c r="DO41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20833,7 +20833,7 @@
         <v>2.11</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF42" t="n">
         <v>3</v>
@@ -21301,7 +21301,7 @@
         <v>1.63</v>
       </c>
       <c r="DE43" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF43" t="n">
         <v>1.5</v>
@@ -21762,7 +21762,7 @@
         <v>75</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DE44" t="n">
         <v>0.89</v>
@@ -21795,7 +21795,7 @@
         <v>2.35</v>
       </c>
       <c r="DO44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22250,7 +22250,7 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE45" t="n">
         <v>1.57</v>
@@ -22391,170 +22391,170 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
         <v>45920.6875</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
         <v>3</v>
       </c>
       <c r="J46" t="n">
+        <v>4</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4</v>
+      </c>
+      <c r="L46" t="n">
+        <v>8</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
         <v>7</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>5</v>
+      </c>
+      <c r="R46" t="n">
+        <v>3</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
+        <v>8</v>
+      </c>
+      <c r="V46" t="n">
+        <v>9</v>
+      </c>
+      <c r="W46" t="n">
+        <v>20</v>
+      </c>
+      <c r="X46" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Estadio de Mendizorroza</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+        </is>
+      </c>
+      <c r="AC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="n">
         <v>7</v>
       </c>
-      <c r="M46" t="n">
-        <v>2</v>
-      </c>
-      <c r="N46" t="n">
-        <v>2</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>8</v>
-      </c>
-      <c r="R46" t="n">
-        <v>3</v>
-      </c>
-      <c r="S46" t="n">
-        <v>18</v>
-      </c>
-      <c r="T46" t="n">
-        <v>3</v>
-      </c>
-      <c r="U46" t="n">
-        <v>26</v>
-      </c>
-      <c r="V46" t="n">
-        <v>6</v>
-      </c>
-      <c r="W46" t="n">
-        <v>10</v>
-      </c>
-      <c r="X46" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>66</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>Estadio de la Cerámica</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>Plaza Labrador, Villarreal</t>
-        </is>
-      </c>
-      <c r="AC46" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>3</v>
-      </c>
       <c r="AE46" t="n">
-        <v>1.55</v>
+        <v>2.33</v>
       </c>
       <c r="AF46" t="n">
-        <v>3.8</v>
+        <v>3.01</v>
       </c>
       <c r="AG46" t="n">
-        <v>5.25</v>
+        <v>3.28</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.01</v>
+        <v>2.43</v>
       </c>
       <c r="AJ46" t="n">
-        <v>3.05</v>
+        <v>4.85</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AN46" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AO46" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AP46" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AU46" t="n">
         <v>3</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW46" t="n">
         <v>1</v>
       </c>
       <c r="AX46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB46" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="BC46" t="n">
         <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BE46" t="n">
         <v>0</v>
@@ -22572,178 +22572,178 @@
         <v>1</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK46" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT46" t="n">
         <v>6</v>
       </c>
-      <c r="BL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN46" t="n">
+      <c r="BU46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV46" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CB46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR46" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS46" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU46" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV46" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX46" t="n">
         <v>6</v>
       </c>
-      <c r="BO46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP46" t="n">
-        <v>3</v>
-      </c>
-      <c r="BQ46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS46" t="n">
+      <c r="CY46" t="n">
         <v>4</v>
       </c>
-      <c r="BT46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV46" t="n">
-        <v>90</v>
-      </c>
-      <c r="BW46" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX46" t="n">
-        <v>112</v>
-      </c>
-      <c r="BY46" t="n">
-        <v>57</v>
-      </c>
-      <c r="BZ46" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CA46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB46" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="CC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS46" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU46" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV46" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX46" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY46" t="n">
-        <v>20</v>
-      </c>
       <c r="CZ46" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DA46" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB46" t="n">
         <v>50</v>
       </c>
       <c r="DC46" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>2.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE46" t="n">
-        <v>0.22</v>
+        <v>1.11</v>
       </c>
       <c r="DF46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DG46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DH46" t="n">
         <v>1.75</v>
       </c>
       <c r="DI46" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DJ46" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK46" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL46" t="n">
-        <v>2.48</v>
+        <v>1.19</v>
       </c>
       <c r="DM46" t="n">
-        <v>0.71</v>
+        <v>1.32</v>
       </c>
       <c r="DN46" t="n">
-        <v>3.19</v>
+        <v>2.51</v>
       </c>
       <c r="DO46" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22767,99 +22767,87 @@
         <v>1</v>
       </c>
       <c r="DW46" t="n">
-        <v>27.48</v>
+        <v>27.45</v>
       </c>
       <c r="DX46" t="n">
-        <v>4.71</v>
+        <v>4.36</v>
       </c>
       <c r="DY46" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="DZ46" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="EA46" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EB46" t="inlineStr">
         <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC46" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
-      </c>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EC46" t="inlineStr"/>
       <c r="ED46" t="inlineStr">
         <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE46" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EE46" t="inlineStr"/>
       <c r="EF46" t="inlineStr">
         <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="EG46" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EG46" t="inlineStr"/>
       <c r="EH46" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="EI46" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EJ46" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="EK46" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EL46" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EM46" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EN46" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="EO46" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EP46" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.16</t>
         </is>
       </c>
     </row>
@@ -22879,170 +22867,170 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
         <v>45920.6875</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
+        <v>7</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
         <v>8</v>
       </c>
-      <c r="M47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" t="n">
-        <v>7</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>5</v>
-      </c>
       <c r="R47" t="n">
         <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>26</v>
+      </c>
+      <c r="V47" t="n">
         <v>6</v>
       </c>
-      <c r="U47" t="n">
-        <v>8</v>
-      </c>
-      <c r="V47" t="n">
-        <v>9</v>
-      </c>
       <c r="W47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="X47" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Y47" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="Z47" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Estadio de Mendizorroza</t>
+          <t>Estadio de la Cerámica</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+          <t>Plaza Labrador, Villarreal</t>
         </is>
       </c>
       <c r="AC47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD47" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.33</v>
+        <v>1.55</v>
       </c>
       <c r="AF47" t="n">
-        <v>3.01</v>
+        <v>3.8</v>
       </c>
       <c r="AG47" t="n">
-        <v>3.28</v>
+        <v>5.25</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.43</v>
+        <v>2.01</v>
       </c>
       <c r="AJ47" t="n">
-        <v>4.85</v>
+        <v>3.05</v>
       </c>
       <c r="AK47" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AO47" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AP47" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AR47" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AU47" t="n">
         <v>3</v>
       </c>
       <c r="AV47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
         <v>1</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB47" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="BC47" t="n">
         <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
         <v>0</v>
@@ -23060,73 +23048,73 @@
         <v>1</v>
       </c>
       <c r="BJ47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BL47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BN47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ47" t="n">
         <v>1</v>
       </c>
       <c r="BR47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BS47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BT47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BU47" t="n">
         <v>1</v>
       </c>
       <c r="BV47" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="BW47" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="BX47" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="BY47" t="n">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="BZ47" t="n">
-        <v>1.22</v>
+        <v>2.84</v>
       </c>
       <c r="CA47" t="n">
-        <v>1.08</v>
+        <v>0.75</v>
       </c>
       <c r="CB47" t="n">
-        <v>2.3</v>
+        <v>3.58</v>
       </c>
       <c r="CC47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG47" t="n">
         <v>0</v>
@@ -23144,13 +23132,13 @@
         <v>0</v>
       </c>
       <c r="CL47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM47" t="n">
         <v>0</v>
       </c>
       <c r="CN47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO47" t="n">
         <v>0</v>
@@ -23162,73 +23150,73 @@
         <v>1</v>
       </c>
       <c r="CR47" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="CS47" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="CT47" t="n">
         <v>1</v>
       </c>
       <c r="CU47" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="CV47" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX47" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY47" t="n">
         <v>20</v>
       </c>
-      <c r="CW47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX47" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY47" t="n">
-        <v>4</v>
-      </c>
       <c r="CZ47" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA47" t="n">
         <v>50</v>
-      </c>
-      <c r="DA47" t="n">
-        <v>100</v>
       </c>
       <c r="DB47" t="n">
         <v>50</v>
       </c>
       <c r="DC47" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DH47" t="n">
         <v>1.75</v>
       </c>
       <c r="DI47" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DJ47" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK47" t="n">
         <v>50</v>
       </c>
-      <c r="DK47" t="n">
-        <v>0</v>
-      </c>
       <c r="DL47" t="n">
-        <v>1.19</v>
+        <v>2.48</v>
       </c>
       <c r="DM47" t="n">
-        <v>1.32</v>
+        <v>0.71</v>
       </c>
       <c r="DN47" t="n">
-        <v>2.51</v>
+        <v>3.19</v>
       </c>
       <c r="DO47" t="n">
         <v>16</v>
@@ -23255,87 +23243,99 @@
         <v>1</v>
       </c>
       <c r="DW47" t="n">
-        <v>27.45</v>
+        <v>27.48</v>
       </c>
       <c r="DX47" t="n">
-        <v>4.36</v>
+        <v>4.71</v>
       </c>
       <c r="DY47" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ47" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="EA47" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EB47" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EC47" t="inlineStr"/>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EC47" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
       <c r="ED47" t="inlineStr">
         <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EE47" t="inlineStr"/>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EE47" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
       <c r="EF47" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="EG47" t="inlineStr"/>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EG47" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
       <c r="EH47" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="EI47" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="EJ47" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EK47" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EL47" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EM47" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EN47" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EO47" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EP47" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23674,7 @@
         <v>25</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE48" t="n">
         <v>0.88</v>
@@ -23707,7 +23707,7 @@
         <v>2.96</v>
       </c>
       <c r="DO48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24153,7 +24153,7 @@
         <v>1.14</v>
       </c>
       <c r="DE49" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DF49" t="n">
         <v>1</v>
@@ -24633,7 +24633,7 @@
         <v>1.63</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF50" t="n">
         <v>0.5</v>
@@ -24663,7 +24663,7 @@
         <v>2.63</v>
       </c>
       <c r="DO50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -26075,7 +26075,7 @@
         <v>2.61</v>
       </c>
       <c r="DO53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -27047,7 +27047,7 @@
         <v>2.17</v>
       </c>
       <c r="DO55" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27502,7 +27502,7 @@
         <v>100</v>
       </c>
       <c r="DD56" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="DE56" t="n">
         <v>2.1</v>
@@ -27535,7 +27535,7 @@
         <v>3.18</v>
       </c>
       <c r="DO56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27981,7 +27981,7 @@
         <v>1.38</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF57" t="n">
         <v>3</v>
@@ -28449,7 +28449,7 @@
         <v>1.25</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF58" t="n">
         <v>0.5</v>
@@ -28479,7 +28479,7 @@
         <v>3.85</v>
       </c>
       <c r="DO58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29402,7 +29402,7 @@
         <v>100</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE60" t="n">
         <v>0.38</v>
@@ -29870,10 +29870,10 @@
         <v>100</v>
       </c>
       <c r="DD61" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DE61" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DF61" t="n">
         <v>1.5</v>
@@ -29903,7 +29903,7 @@
         <v>3.12</v>
       </c>
       <c r="DO61" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30338,7 +30338,7 @@
         <v>100</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DE62" t="n">
         <v>1.57</v>
@@ -30859,7 +30859,7 @@
         <v>2.16</v>
       </c>
       <c r="DO63" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31319,7 +31319,7 @@
         <v>4.16</v>
       </c>
       <c r="DO64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31765,7 +31765,7 @@
         <v>1.63</v>
       </c>
       <c r="DE65" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF65" t="n">
         <v>0.67</v>
@@ -31795,7 +31795,7 @@
         <v>2</v>
       </c>
       <c r="DO65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32230,7 +32230,7 @@
         <v>50</v>
       </c>
       <c r="DD66" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="DE66" t="n">
         <v>0.88</v>
@@ -32263,7 +32263,7 @@
         <v>4.16</v>
       </c>
       <c r="DO66" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32685,7 +32685,7 @@
         <v>1.14</v>
       </c>
       <c r="DE67" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF67" t="n">
         <v>1</v>
@@ -33157,7 +33157,7 @@
         <v>2</v>
       </c>
       <c r="DE68" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DF68" t="n">
         <v>2.33</v>
@@ -33621,7 +33621,7 @@
         <v>3</v>
       </c>
       <c r="DE69" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF69" t="n">
         <v>3</v>
@@ -33651,7 +33651,7 @@
         <v>3.83</v>
       </c>
       <c r="DO69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34566,7 +34566,7 @@
         <v>67</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE71" t="n">
         <v>0.5</v>
@@ -34599,7 +34599,7 @@
         <v>2.23</v>
       </c>
       <c r="DO71" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35046,7 +35046,7 @@
         <v>88</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE72" t="n">
         <v>1.13</v>
@@ -35522,7 +35522,7 @@
         <v>88</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DE73" t="n">
         <v>0.89</v>
@@ -35555,7 +35555,7 @@
         <v>2.02</v>
       </c>
       <c r="DO73" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -36010,7 +36010,7 @@
         <v>88</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DE74" t="n">
         <v>0.38</v>
@@ -36043,7 +36043,7 @@
         <v>1.79</v>
       </c>
       <c r="DO74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36501,7 +36501,7 @@
         <v>1.78</v>
       </c>
       <c r="DE75" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF75" t="n">
         <v>1.75</v>
@@ -36531,7 +36531,7 @@
         <v>3.06</v>
       </c>
       <c r="DO75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36966,7 +36966,7 @@
         <v>67</v>
       </c>
       <c r="DD76" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE76" t="n">
         <v>1.86</v>
@@ -36999,7 +36999,7 @@
         <v>3.16</v>
       </c>
       <c r="DO76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -37897,7 +37897,7 @@
         <v>1.25</v>
       </c>
       <c r="DE78" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DF78" t="n">
         <v>0.33</v>
@@ -37927,7 +37927,7 @@
         <v>3.75</v>
       </c>
       <c r="DO78" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38043,40 +38043,40 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45935.6875</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K79" t="n">
         <v>5</v>
       </c>
       <c r="L79" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N79" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -38085,104 +38085,104 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
+        <v>3</v>
+      </c>
+      <c r="R79" t="n">
+        <v>2</v>
+      </c>
+      <c r="S79" t="n">
+        <v>7</v>
+      </c>
+      <c r="T79" t="n">
         <v>5</v>
       </c>
-      <c r="R79" t="n">
-        <v>3</v>
-      </c>
-      <c r="S79" t="n">
-        <v>9</v>
-      </c>
-      <c r="T79" t="n">
-        <v>9</v>
-      </c>
       <c r="U79" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V79" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W79" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="X79" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Y79" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z79" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>Estadio Municipal de Anoeta</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
         </is>
       </c>
       <c r="AC79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD79" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="AF79" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AG79" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AJ79" t="n">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AL79" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AM79" t="n">
         <v>1.44</v>
       </c>
       <c r="AN79" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AO79" t="n">
         <v>2.55</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AR79" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AU79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW79" t="n">
         <v>0</v>
@@ -38191,22 +38191,22 @@
         <v>0</v>
       </c>
       <c r="AY79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB79" t="n">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38221,178 +38221,178 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BJ79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BK79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>101</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX79" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY79" t="n">
         <v>10</v>
       </c>
-      <c r="BN79" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR79" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS79" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT79" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV79" t="n">
-        <v>66</v>
-      </c>
-      <c r="BW79" t="n">
-        <v>34</v>
-      </c>
-      <c r="BX79" t="n">
-        <v>107</v>
-      </c>
-      <c r="BY79" t="n">
-        <v>98</v>
-      </c>
-      <c r="BZ79" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CA79" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CB79" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR79" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS79" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU79" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV79" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX79" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY79" t="n">
-        <v>13</v>
-      </c>
       <c r="CZ79" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="DA79" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="DB79" t="n">
+        <v>59</v>
+      </c>
+      <c r="DC79" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE79" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DF79" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DI79" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DJ79" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK79" t="n">
         <v>29</v>
       </c>
-      <c r="DC79" t="n">
-        <v>88</v>
-      </c>
-      <c r="DD79" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DE79" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DF79" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DG79" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH79" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DI79" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DJ79" t="n">
-        <v>46</v>
-      </c>
-      <c r="DK79" t="n">
-        <v>13</v>
-      </c>
       <c r="DL79" t="n">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="DN79" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="DO79" t="n">
         <v>16</v>
@@ -38401,10 +38401,10 @@
         <v>1</v>
       </c>
       <c r="DQ79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS79" t="b">
         <v>0</v>
@@ -38416,102 +38416,94 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW79" t="n">
-        <v>17.75</v>
+        <v>17.19</v>
       </c>
       <c r="DX79" t="n">
-        <v>9.369999999999999</v>
+        <v>3.66</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="ED79" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EE79" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EF79" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EG79" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EH79" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EI79" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EJ79" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EK79" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EL79" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EM79" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EN79" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM79" t="inlineStr"/>
+      <c r="EN79" t="inlineStr"/>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.84</t>
         </is>
       </c>
     </row>
@@ -38531,146 +38523,146 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45935.6875</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K80" t="n">
         <v>5</v>
       </c>
       <c r="L80" t="n">
+        <v>15</v>
+      </c>
+      <c r="M80" t="n">
+        <v>2</v>
+      </c>
+      <c r="N80" t="n">
+        <v>6</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>5</v>
+      </c>
+      <c r="R80" t="n">
+        <v>3</v>
+      </c>
+      <c r="S80" t="n">
+        <v>9</v>
+      </c>
+      <c r="T80" t="n">
+        <v>9</v>
+      </c>
+      <c r="U80" t="n">
+        <v>14</v>
+      </c>
+      <c r="V80" t="n">
         <v>12</v>
       </c>
-      <c r="M80" t="n">
-        <v>1</v>
-      </c>
-      <c r="N80" t="n">
-        <v>2</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>3</v>
-      </c>
-      <c r="R80" t="n">
-        <v>2</v>
-      </c>
-      <c r="S80" t="n">
-        <v>7</v>
-      </c>
-      <c r="T80" t="n">
-        <v>5</v>
-      </c>
-      <c r="U80" t="n">
-        <v>10</v>
-      </c>
-      <c r="V80" t="n">
-        <v>7</v>
-      </c>
       <c r="W80" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X80" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Y80" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z80" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Anoeta</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD80" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="AF80" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AG80" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AI80" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AJ80" t="n">
-        <v>3.85</v>
+        <v>2.96</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AL80" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AM80" t="n">
         <v>1.44</v>
       </c>
       <c r="AN80" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AO80" t="n">
         <v>2.55</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AR80" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AU80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW80" t="n">
         <v>0</v>
@@ -38679,22 +38671,22 @@
         <v>0</v>
       </c>
       <c r="AY80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB80" t="n">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -38709,178 +38701,178 @@
         <v>1</v>
       </c>
       <c r="BI80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BJ80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BK80" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR80" t="n">
         <v>4</v>
       </c>
-      <c r="BL80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM80" t="n">
+      <c r="BS80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV80" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX80" t="n">
         <v>6</v>
       </c>
-      <c r="BN80" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT80" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV80" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW80" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX80" t="n">
-        <v>101</v>
-      </c>
-      <c r="BY80" t="n">
-        <v>90</v>
-      </c>
-      <c r="BZ80" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="CA80" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB80" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CC80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN80" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR80" t="n">
-        <v>14</v>
-      </c>
-      <c r="CS80" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU80" t="n">
-        <v>21</v>
-      </c>
-      <c r="CV80" t="n">
+      <c r="CY80" t="n">
         <v>13</v>
       </c>
-      <c r="CW80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX80" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY80" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ80" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="DA80" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="DB80" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="DC80" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.25</v>
+        <v>2.11</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="DF80" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="DG80" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DH80" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="DI80" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="DJ80" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="DK80" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="DL80" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="DM80" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="DN80" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="DO80" t="n">
         <v>16</v>
@@ -38889,10 +38881,10 @@
         <v>1</v>
       </c>
       <c r="DQ80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS80" t="b">
         <v>0</v>
@@ -38904,94 +38896,102 @@
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW80" t="n">
-        <v>17.19</v>
+        <v>17.75</v>
       </c>
       <c r="DX80" t="n">
-        <v>3.66</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EB80" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EC80" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED80" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EE80" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EF80" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EG80" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EH80" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EI80" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EJ80" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EK80" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EL80" t="inlineStr">
+        <is>
           <t>2.02</t>
         </is>
       </c>
-      <c r="EB80" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC80" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="ED80" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE80" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF80" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG80" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="EH80" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="EI80" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="EJ80" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EK80" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EL80" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EM80" t="inlineStr"/>
-      <c r="EN80" t="inlineStr"/>
+      <c r="EM80" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EN80" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
       <c r="EO80" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EP80" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.68</t>
         </is>
       </c>
     </row>
@@ -39325,7 +39325,7 @@
         <v>0.89</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF81" t="n">
         <v>0.75</v>
@@ -39355,7 +39355,7 @@
         <v>3.36</v>
       </c>
       <c r="DO81" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -39794,7 +39794,7 @@
         <v>84</v>
       </c>
       <c r="DD82" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DE82" t="n">
         <v>1.57</v>
@@ -40281,7 +40281,7 @@
         <v>1.25</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF83" t="n">
         <v>1</v>
@@ -40311,7 +40311,7 @@
         <v>2.72</v>
       </c>
       <c r="DO83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -40771,7 +40771,7 @@
         <v>3.49</v>
       </c>
       <c r="DO84" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41198,7 +41198,7 @@
         <v>88</v>
       </c>
       <c r="DD85" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="DE85" t="n">
         <v>1.5</v>
@@ -41231,7 +41231,7 @@
         <v>3.94</v>
       </c>
       <c r="DO85" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41703,7 +41703,7 @@
         <v>2.53</v>
       </c>
       <c r="DO86" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42621,7 +42621,7 @@
         <v>0.89</v>
       </c>
       <c r="DE88" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF88" t="n">
         <v>0.8</v>
@@ -42651,7 +42651,7 @@
         <v>3.09</v>
       </c>
       <c r="DO88" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43106,7 +43106,7 @@
         <v>80</v>
       </c>
       <c r="DD89" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="DE89" t="n">
         <v>1.11</v>
@@ -43139,7 +43139,7 @@
         <v>2.17</v>
       </c>
       <c r="DO89" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -44099,7 +44099,7 @@
         <v>2.36</v>
       </c>
       <c r="DO91" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP91" t="b">
         <v>0</v>
@@ -44529,7 +44529,7 @@
         <v>1.25</v>
       </c>
       <c r="DE92" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF92" t="n">
         <v>1</v>
@@ -44559,7 +44559,7 @@
         <v>2.81</v>
       </c>
       <c r="DO92" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45006,7 +45006,7 @@
         <v>90</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DE93" t="n">
         <v>0.5</v>
@@ -45039,7 +45039,7 @@
         <v>2.1</v>
       </c>
       <c r="DO93" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -46454,7 +46454,7 @@
         <v>50</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE96" t="n">
         <v>1.86</v>
@@ -46487,7 +46487,7 @@
         <v>2.51</v>
       </c>
       <c r="DO96" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -46967,7 +46967,7 @@
         <v>2.31</v>
       </c>
       <c r="DO97" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -47417,7 +47417,7 @@
         <v>1.63</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF98" t="n">
         <v>2.25</v>
@@ -47886,10 +47886,10 @@
         <v>75</v>
       </c>
       <c r="DD99" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE99" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DF99" t="n">
         <v>3</v>
@@ -47919,7 +47919,7 @@
         <v>4.52</v>
       </c>
       <c r="DO99" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -48346,10 +48346,10 @@
         <v>84</v>
       </c>
       <c r="DD100" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE100" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DF100" t="n">
         <v>2.5</v>
@@ -48379,7 +48379,7 @@
         <v>2.21</v>
       </c>
       <c r="DO100" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -48825,7 +48825,7 @@
         <v>1.14</v>
       </c>
       <c r="DE101" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF101" t="n">
         <v>0.67</v>
@@ -49758,7 +49758,7 @@
         <v>74</v>
       </c>
       <c r="DD103" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="DE103" t="n">
         <v>1.11</v>
@@ -49791,7 +49791,7 @@
         <v>3.29</v>
       </c>
       <c r="DO103" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50237,7 +50237,7 @@
         <v>2.78</v>
       </c>
       <c r="DE104" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF104" t="n">
         <v>2.6</v>
@@ -50267,7 +50267,7 @@
         <v>2.79</v>
       </c>
       <c r="DO104" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -50735,7 +50735,7 @@
         <v>2.92</v>
       </c>
       <c r="DO105" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -51178,7 +51178,7 @@
         <v>70</v>
       </c>
       <c r="DD106" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE106" t="n">
         <v>0.38</v>
@@ -51211,7 +51211,7 @@
         <v>3.13</v>
       </c>
       <c r="DO106" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -51646,10 +51646,10 @@
         <v>88</v>
       </c>
       <c r="DD107" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="DE107" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DF107" t="n">
         <v>0.25</v>
@@ -51679,7 +51679,7 @@
         <v>2.18</v>
       </c>
       <c r="DO107" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -53057,7 +53057,7 @@
         <v>1.63</v>
       </c>
       <c r="DE110" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF110" t="n">
         <v>1.8</v>
@@ -53542,7 +53542,7 @@
         <v>60</v>
       </c>
       <c r="DD111" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DE111" t="n">
         <v>0.22</v>
@@ -53575,7 +53575,7 @@
         <v>1.9</v>
       </c>
       <c r="DO111" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP111" t="b">
         <v>0</v>
@@ -54021,7 +54021,7 @@
         <v>2</v>
       </c>
       <c r="DE112" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF112" t="n">
         <v>2.2</v>
@@ -54502,10 +54502,10 @@
         <v>62</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DE113" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF113" t="n">
         <v>0.83</v>
@@ -54535,7 +54535,7 @@
         <v>2.36</v>
       </c>
       <c r="DO113" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -55019,7 +55019,7 @@
         <v>2.35</v>
       </c>
       <c r="DO114" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -55487,7 +55487,7 @@
         <v>3.1</v>
       </c>
       <c r="DO115" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -55947,7 +55947,7 @@
         <v>2.69</v>
       </c>
       <c r="DO116" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -56435,7 +56435,7 @@
         <v>2.5</v>
       </c>
       <c r="DO117" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -57011,12 +57011,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F119" s="2" t="n">
@@ -57026,25 +57026,25 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K119" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L119" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -57056,117 +57056,125 @@
         <v>4</v>
       </c>
       <c r="R119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S119" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T119" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U119" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="V119" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W119" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="X119" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y119" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Z119" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA119" t="inlineStr"/>
-      <c r="AB119" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>Avenida de Suecia, Valencia</t>
+        </is>
+      </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE119" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="AF119" t="n">
-        <v>2.58</v>
+        <v>3.45</v>
       </c>
       <c r="AG119" t="n">
-        <v>2.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH119" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AI119" t="n">
-        <v>3.04</v>
+        <v>1.91</v>
       </c>
       <c r="AJ119" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="AK119" t="n">
-        <v>2.43</v>
+        <v>1.72</v>
       </c>
       <c r="AL119" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AM119" t="n">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="AN119" t="n">
-        <v>2.87</v>
+        <v>1.84</v>
       </c>
       <c r="AO119" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.77</v>
+        <v>1.37</v>
       </c>
       <c r="AR119" t="n">
-        <v>4.45</v>
+        <v>2.85</v>
       </c>
       <c r="AS119" t="n">
-        <v>2.05</v>
+        <v>2.89</v>
       </c>
       <c r="AT119" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AU119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW119" t="n">
         <v>0</v>
       </c>
       <c r="AX119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB119" t="n">
-        <v>298</v>
+        <v>-1</v>
       </c>
       <c r="BC119" t="n">
         <v>0</v>
       </c>
       <c r="BD119" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="BE119" t="n">
         <v>0</v>
@@ -57181,64 +57189,64 @@
         <v>1</v>
       </c>
       <c r="BI119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ119" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BK119" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BL119" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BM119" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BN119" t="n">
         <v>7</v>
       </c>
       <c r="BO119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT119" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BU119" t="n">
         <v>1</v>
       </c>
       <c r="BV119" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="BW119" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="BX119" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="BY119" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="BZ119" t="n">
-        <v>0.96</v>
+        <v>1.74</v>
       </c>
       <c r="CA119" t="n">
-        <v>1.63</v>
+        <v>1.09</v>
       </c>
       <c r="CB119" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="CC119" t="n">
         <v>0</v>
@@ -57271,10 +57279,10 @@
         <v>0</v>
       </c>
       <c r="CM119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO119" t="n">
         <v>0</v>
@@ -57286,19 +57294,19 @@
         <v>1</v>
       </c>
       <c r="CR119" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="CS119" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="CT119" t="n">
         <v>1</v>
       </c>
       <c r="CU119" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CV119" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CW119" t="n">
         <v>1</v>
@@ -57307,52 +57315,52 @@
         <v>6</v>
       </c>
       <c r="CY119" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CZ119" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="DA119" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="DB119" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="DC119" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE119" t="n">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="DF119" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG119" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DH119" t="n">
         <v>0.82</v>
       </c>
       <c r="DI119" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="DJ119" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="DK119" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="DL119" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="DM119" t="n">
-        <v>0.97</v>
+        <v>1.6</v>
       </c>
       <c r="DN119" t="n">
-        <v>2.18</v>
+        <v>3.06</v>
       </c>
       <c r="DO119" t="n">
         <v>16</v>
@@ -57361,7 +57369,7 @@
         <v>1</v>
       </c>
       <c r="DQ119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR119" t="b">
         <v>0</v>
@@ -57376,90 +57384,102 @@
         <v>0</v>
       </c>
       <c r="DV119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW119" t="n">
-        <v>17.48</v>
+        <v>17.01</v>
       </c>
       <c r="DX119" t="n">
-        <v>5.64</v>
+        <v>5.56</v>
       </c>
       <c r="DY119" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="DZ119" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="EA119" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB119" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EC119" t="inlineStr"/>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
       <c r="ED119" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EE119" t="inlineStr"/>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE119" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
       <c r="EF119" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="EG119" t="inlineStr"/>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EG119" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EH119" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EI119" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EJ119" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EK119" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EL119" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EM119" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EN119" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EO119" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EP119" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -57479,12 +57499,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F120" s="2" t="n">
@@ -57494,25 +57514,25 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K120" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L120" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -57524,125 +57544,117 @@
         <v>4</v>
       </c>
       <c r="R120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S120" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T120" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U120" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="V120" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W120" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X120" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y120" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Z120" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>Estadio de Mestalla</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>Avenida de Suecia, Valencia</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AA120" t="inlineStr"/>
+      <c r="AB120" t="inlineStr"/>
       <c r="AC120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE120" t="n">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="AF120" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="AG120" t="n">
-        <v>2.15</v>
+        <v>2.98</v>
       </c>
       <c r="AH120" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AI120" t="n">
-        <v>1.91</v>
+        <v>3.04</v>
       </c>
       <c r="AJ120" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="AK120" t="n">
-        <v>1.72</v>
+        <v>2.43</v>
       </c>
       <c r="AL120" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AM120" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="AN120" t="n">
-        <v>1.84</v>
+        <v>2.87</v>
       </c>
       <c r="AO120" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="AR120" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="AS120" t="n">
-        <v>2.89</v>
+        <v>2.05</v>
       </c>
       <c r="AT120" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AU120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW120" t="n">
         <v>0</v>
       </c>
       <c r="AX120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB120" t="n">
-        <v>-1</v>
+        <v>298</v>
       </c>
       <c r="BC120" t="n">
         <v>0</v>
       </c>
       <c r="BD120" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="BE120" t="n">
         <v>0</v>
@@ -57657,64 +57669,64 @@
         <v>1</v>
       </c>
       <c r="BI120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ120" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BK120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL120" t="n">
         <v>6</v>
       </c>
-      <c r="BL120" t="n">
-        <v>1</v>
-      </c>
       <c r="BM120" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BN120" t="n">
         <v>7</v>
       </c>
       <c r="BO120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT120" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BU120" t="n">
         <v>1</v>
       </c>
       <c r="BV120" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="BW120" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="BX120" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="BY120" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="BZ120" t="n">
-        <v>1.74</v>
+        <v>0.96</v>
       </c>
       <c r="CA120" t="n">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="CB120" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="CC120" t="n">
         <v>0</v>
@@ -57747,10 +57759,10 @@
         <v>0</v>
       </c>
       <c r="CM120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO120" t="n">
         <v>0</v>
@@ -57762,19 +57774,19 @@
         <v>1</v>
       </c>
       <c r="CR120" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="CS120" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="CT120" t="n">
         <v>1</v>
       </c>
       <c r="CU120" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CV120" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CW120" t="n">
         <v>1</v>
@@ -57783,52 +57795,52 @@
         <v>6</v>
       </c>
       <c r="CY120" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CZ120" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="DA120" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="DB120" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="DC120" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="DD120" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DE120" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DF120" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG120" t="n">
         <v>1.5</v>
-      </c>
-      <c r="DE120" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DF120" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DG120" t="n">
-        <v>1.4</v>
       </c>
       <c r="DH120" t="n">
         <v>0.82</v>
       </c>
       <c r="DI120" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="DJ120" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="DK120" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="DL120" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="DM120" t="n">
-        <v>1.6</v>
+        <v>0.97</v>
       </c>
       <c r="DN120" t="n">
-        <v>3.06</v>
+        <v>2.18</v>
       </c>
       <c r="DO120" t="n">
         <v>16</v>
@@ -57837,7 +57849,7 @@
         <v>1</v>
       </c>
       <c r="DQ120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR120" t="b">
         <v>0</v>
@@ -57852,102 +57864,90 @@
         <v>0</v>
       </c>
       <c r="DV120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW120" t="n">
-        <v>17.01</v>
+        <v>17.48</v>
       </c>
       <c r="DX120" t="n">
-        <v>5.56</v>
+        <v>5.64</v>
       </c>
       <c r="DY120" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="DZ120" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="EA120" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="EB120" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC120" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EC120" t="inlineStr"/>
       <c r="ED120" t="inlineStr">
         <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EE120" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EE120" t="inlineStr"/>
       <c r="EF120" t="inlineStr">
         <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="EG120" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EG120" t="inlineStr"/>
       <c r="EH120" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EI120" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EJ120" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EK120" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="EL120" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EM120" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EN120" t="inlineStr">
+        <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="EM120" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EN120" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
       <c r="EO120" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EP120" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.43</t>
         </is>
       </c>
     </row>
@@ -58281,7 +58281,7 @@
         <v>0.89</v>
       </c>
       <c r="DE121" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DF121" t="n">
         <v>0.83</v>
@@ -58311,7 +58311,7 @@
         <v>3.7</v>
       </c>
       <c r="DO121" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -58754,7 +58754,7 @@
         <v>68</v>
       </c>
       <c r="DD122" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE122" t="n">
         <v>0.89</v>
@@ -58787,7 +58787,7 @@
         <v>2.75</v>
       </c>
       <c r="DO122" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -59229,7 +59229,7 @@
         <v>1.56</v>
       </c>
       <c r="DE123" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DF123" t="n">
         <v>1.83</v>
@@ -59259,7 +59259,7 @@
         <v>2.7</v>
       </c>
       <c r="DO123" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -60130,10 +60130,10 @@
         <v>84</v>
       </c>
       <c r="DD125" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE125" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF125" t="n">
         <v>2</v>
@@ -60163,7 +60163,7 @@
         <v>2.9</v>
       </c>
       <c r="DO125" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -60598,10 +60598,10 @@
         <v>83</v>
       </c>
       <c r="DD126" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="DE126" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF126" t="n">
         <v>2.67</v>
@@ -60631,7 +60631,7 @@
         <v>3.29</v>
       </c>
       <c r="DO126" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -61066,7 +61066,7 @@
         <v>69</v>
       </c>
       <c r="DD127" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DE127" t="n">
         <v>1.11</v>
@@ -62005,7 +62005,7 @@
         <v>1.38</v>
       </c>
       <c r="DE129" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF129" t="n">
         <v>1.6</v>
@@ -62957,7 +62957,7 @@
         <v>2.11</v>
       </c>
       <c r="DE131" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF131" t="n">
         <v>1.86</v>
@@ -63927,7 +63927,7 @@
         <v>2.14</v>
       </c>
       <c r="DO133" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -64365,7 +64365,7 @@
         <v>3</v>
       </c>
       <c r="DE134" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF134" t="n">
         <v>3</v>
@@ -64395,7 +64395,7 @@
         <v>3.53</v>
       </c>
       <c r="DO134" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -64830,7 +64830,7 @@
         <v>67</v>
       </c>
       <c r="DD135" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="DE135" t="n">
         <v>0.88</v>
@@ -64863,7 +64863,7 @@
         <v>2.45</v>
       </c>
       <c r="DO135" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -65331,7 +65331,7 @@
         <v>2.87</v>
       </c>
       <c r="DO136" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -65811,7 +65811,7 @@
         <v>2.59</v>
       </c>
       <c r="DO137" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP137" t="b">
         <v>1</v>
@@ -67218,7 +67218,7 @@
         <v>72</v>
       </c>
       <c r="DD140" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DE140" t="n">
         <v>2.1</v>
@@ -67251,7 +67251,7 @@
         <v>3.35</v>
       </c>
       <c r="DO140" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -68117,7 +68117,7 @@
         <v>3</v>
       </c>
       <c r="DE142" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF142" t="n">
         <v>3</v>
@@ -68147,7 +68147,7 @@
         <v>3.68</v>
       </c>
       <c r="DO142" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -69046,10 +69046,10 @@
         <v>72</v>
       </c>
       <c r="DD144" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DE144" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF144" t="n">
         <v>0.71</v>
@@ -69079,7 +69079,7 @@
         <v>2.27</v>
       </c>
       <c r="DO144" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP144" t="b">
         <v>0</v>
@@ -69522,7 +69522,7 @@
         <v>79</v>
       </c>
       <c r="DD145" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="DE145" t="n">
         <v>1.13</v>
@@ -69555,7 +69555,7 @@
         <v>3.06</v>
       </c>
       <c r="DO145" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -70009,7 +70009,7 @@
         <v>1.56</v>
       </c>
       <c r="DE146" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF146" t="n">
         <v>1.57</v>
@@ -70039,7 +70039,7 @@
         <v>2.91</v>
       </c>
       <c r="DO146" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -70477,7 +70477,7 @@
         <v>1.63</v>
       </c>
       <c r="DE147" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DF147" t="n">
         <v>1.86</v>
@@ -70953,7 +70953,7 @@
         <v>1.78</v>
       </c>
       <c r="DE148" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF148" t="n">
         <v>1.63</v>
@@ -71894,10 +71894,10 @@
         <v>50</v>
       </c>
       <c r="DD150" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE150" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF150" t="n">
         <v>1.57</v>
@@ -71927,7 +71927,7 @@
         <v>2.64</v>
       </c>
       <c r="DO150" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -72858,10 +72858,10 @@
         <v>67</v>
       </c>
       <c r="DD152" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE152" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DF152" t="n">
         <v>3</v>
@@ -72891,7 +72891,7 @@
         <v>3.58</v>
       </c>
       <c r="DO152" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -73318,7 +73318,7 @@
         <v>88</v>
       </c>
       <c r="DD153" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE153" t="n">
         <v>0.89</v>
@@ -73351,7 +73351,7 @@
         <v>2.58</v>
       </c>
       <c r="DO153" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP153" t="b">
         <v>1</v>
@@ -73839,7 +73839,7 @@
         <v>2.67</v>
       </c>
       <c r="DO154" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP154" t="b">
         <v>1</v>
@@ -74327,7 +74327,7 @@
         <v>2.77</v>
       </c>
       <c r="DO155" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP155" t="b">
         <v>1</v>
@@ -75283,7 +75283,7 @@
         <v>3.26</v>
       </c>
       <c r="DO157" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP157" t="b">
         <v>1</v>
@@ -76227,7 +76227,7 @@
         <v>2.3</v>
       </c>
       <c r="DO159" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP159" t="b">
         <v>1</v>
@@ -76703,7 +76703,7 @@
         <v>2.74</v>
       </c>
       <c r="DO160" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP160" t="b">
         <v>1</v>
@@ -77187,7 +77187,7 @@
         <v>3.5</v>
       </c>
       <c r="DO161" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP161" t="b">
         <v>1</v>
@@ -77752,6 +77752,3334 @@
       <c r="EP162" t="inlineStr">
         <is>
           <t>1.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>17</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Valencia CF</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>RCD Mallorca</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>46010.83333333334</v>
+      </c>
+      <c r="G163" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" t="n">
+        <v>1</v>
+      </c>
+      <c r="I163" t="n">
+        <v>2</v>
+      </c>
+      <c r="J163" t="n">
+        <v>12</v>
+      </c>
+      <c r="K163" t="n">
+        <v>3</v>
+      </c>
+      <c r="L163" t="n">
+        <v>15</v>
+      </c>
+      <c r="M163" t="n">
+        <v>2</v>
+      </c>
+      <c r="N163" t="n">
+        <v>3</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>2</v>
+      </c>
+      <c r="R163" t="n">
+        <v>2</v>
+      </c>
+      <c r="S163" t="n">
+        <v>15</v>
+      </c>
+      <c r="T163" t="n">
+        <v>2</v>
+      </c>
+      <c r="U163" t="n">
+        <v>17</v>
+      </c>
+      <c r="V163" t="n">
+        <v>4</v>
+      </c>
+      <c r="W163" t="n">
+        <v>10</v>
+      </c>
+      <c r="X163" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>Avenida de Suecia, Valencia</t>
+        </is>
+      </c>
+      <c r="AC163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI163" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ163" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK163" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM163" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN163" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ163" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR163" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT163" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV163" t="n">
+        <v>80</v>
+      </c>
+      <c r="BW163" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX163" t="n">
+        <v>124</v>
+      </c>
+      <c r="BY163" t="n">
+        <v>57</v>
+      </c>
+      <c r="BZ163" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CA163" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="CB163" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="CC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR163" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS163" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU163" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV163" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX163" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY163" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ163" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA163" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB163" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC163" t="n">
+        <v>57</v>
+      </c>
+      <c r="DD163" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DE163" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DF163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG163" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH163" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DI163" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DJ163" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK163" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL163" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM163" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DN163" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DO163" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP163" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ163" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR163" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS163" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT163" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU163" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV163" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW163" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="DX163" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="DY163" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="DZ163" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="EA163" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EB163" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EC163" t="inlineStr"/>
+      <c r="ED163" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EE163" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EF163" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EG163" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="EH163" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="EI163" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EJ163" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EK163" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EL163" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EM163" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EN163" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EO163" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EP163" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>17</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>46011.54166666666</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>4</v>
+      </c>
+      <c r="K164" t="n">
+        <v>3</v>
+      </c>
+      <c r="L164" t="n">
+        <v>7</v>
+      </c>
+      <c r="M164" t="n">
+        <v>2</v>
+      </c>
+      <c r="N164" t="n">
+        <v>1</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>3</v>
+      </c>
+      <c r="R164" t="n">
+        <v>2</v>
+      </c>
+      <c r="S164" t="n">
+        <v>7</v>
+      </c>
+      <c r="T164" t="n">
+        <v>4</v>
+      </c>
+      <c r="U164" t="n">
+        <v>10</v>
+      </c>
+      <c r="V164" t="n">
+        <v>6</v>
+      </c>
+      <c r="W164" t="n">
+        <v>14</v>
+      </c>
+      <c r="X164" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Carlos Tartiere</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>Calle de Ricardo Vázquez Prada, Barrio de la Ería, Oviedo</t>
+        </is>
+      </c>
+      <c r="AC164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN164" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO164" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS164" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV164" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW164" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX164" t="n">
+        <v>109</v>
+      </c>
+      <c r="BY164" t="n">
+        <v>81</v>
+      </c>
+      <c r="BZ164" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CA164" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="CB164" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR164" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS164" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU164" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV164" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX164" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY164" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ164" t="n">
+        <v>34</v>
+      </c>
+      <c r="DA164" t="n">
+        <v>68</v>
+      </c>
+      <c r="DB164" t="n">
+        <v>15</v>
+      </c>
+      <c r="DC164" t="n">
+        <v>54</v>
+      </c>
+      <c r="DD164" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DE164" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DF164" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DG164" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH164" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DI164" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DJ164" t="n">
+        <v>66</v>
+      </c>
+      <c r="DK164" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL164" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DM164" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DN164" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DO164" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW164" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="DX164" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="DY164" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="DZ164" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="EA164" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EB164" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EC164" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="ED164" t="inlineStr"/>
+      <c r="EE164" t="inlineStr"/>
+      <c r="EF164" t="inlineStr"/>
+      <c r="EG164" t="inlineStr"/>
+      <c r="EH164" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EI164" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EJ164" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="EK164" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EL164" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EM164" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EN164" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EO164" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EP164" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>17</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>46011.63541666666</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" t="n">
+        <v>1</v>
+      </c>
+      <c r="I165" t="n">
+        <v>2</v>
+      </c>
+      <c r="J165" t="n">
+        <v>7</v>
+      </c>
+      <c r="K165" t="n">
+        <v>10</v>
+      </c>
+      <c r="L165" t="n">
+        <v>17</v>
+      </c>
+      <c r="M165" t="n">
+        <v>6</v>
+      </c>
+      <c r="N165" t="n">
+        <v>2</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>3</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6</v>
+      </c>
+      <c r="S165" t="n">
+        <v>10</v>
+      </c>
+      <c r="T165" t="n">
+        <v>12</v>
+      </c>
+      <c r="U165" t="n">
+        <v>13</v>
+      </c>
+      <c r="V165" t="n">
+        <v>18</v>
+      </c>
+      <c r="W165" t="n">
+        <v>16</v>
+      </c>
+      <c r="X165" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>Estadio Ciudad de Valencia</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>Calle San Vicente de Paúl 44, Valencia</t>
+        </is>
+      </c>
+      <c r="AC165" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>71</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG165" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI165" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ165" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK165" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL165" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM165" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN165" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ165" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS165" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT165" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV165" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW165" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX165" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY165" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ165" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CA165" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CB165" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="CC165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR165" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS165" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU165" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV165" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX165" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY165" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ165" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA165" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB165" t="n">
+        <v>54</v>
+      </c>
+      <c r="DC165" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD165" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DE165" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DF165" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DG165" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH165" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DI165" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ165" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK165" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL165" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DM165" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DN165" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="DO165" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP165" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ165" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR165" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS165" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT165" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU165" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV165" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW165" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="DX165" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="DY165" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="DZ165" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA165" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EB165" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EC165" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="ED165" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EE165" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EF165" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EG165" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EH165" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EI165" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EJ165" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EK165" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EL165" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EM165" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EN165" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EO165" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EP165" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>17</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>CA Osasuna</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>46011.72916666666</v>
+      </c>
+      <c r="G166" t="n">
+        <v>3</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>3</v>
+      </c>
+      <c r="J166" t="n">
+        <v>9</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>9</v>
+      </c>
+      <c r="M166" t="n">
+        <v>2</v>
+      </c>
+      <c r="N166" t="n">
+        <v>2</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>7</v>
+      </c>
+      <c r="R166" t="n">
+        <v>3</v>
+      </c>
+      <c r="S166" t="n">
+        <v>9</v>
+      </c>
+      <c r="T166" t="n">
+        <v>4</v>
+      </c>
+      <c r="U166" t="n">
+        <v>16</v>
+      </c>
+      <c r="V166" t="n">
+        <v>7</v>
+      </c>
+      <c r="W166" t="n">
+        <v>16</v>
+      </c>
+      <c r="X166" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>Carretera El Sadar, Iruñea</t>
+        </is>
+      </c>
+      <c r="AC166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>287</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN166" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ166" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR166" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT166" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU166" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV166" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW166" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX166" t="n">
+        <v>84</v>
+      </c>
+      <c r="BY166" t="n">
+        <v>82</v>
+      </c>
+      <c r="BZ166" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CA166" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CB166" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CC166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM166" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR166" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS166" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU166" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV166" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX166" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY166" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ166" t="n">
+        <v>29</v>
+      </c>
+      <c r="DA166" t="n">
+        <v>58</v>
+      </c>
+      <c r="DB166" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC166" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD166" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE166" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF166" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DG166" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DH166" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DI166" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ166" t="n">
+        <v>72</v>
+      </c>
+      <c r="DK166" t="n">
+        <v>43</v>
+      </c>
+      <c r="DL166" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DM166" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DN166" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="DO166" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP166" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ166" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR166" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS166" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT166" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU166" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV166" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW166" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="DX166" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="DY166" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="DZ166" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA166" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="EB166" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EC166" t="inlineStr"/>
+      <c r="ED166" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EE166" t="inlineStr"/>
+      <c r="EF166" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EG166" t="inlineStr"/>
+      <c r="EH166" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="EI166" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="EJ166" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EK166" t="inlineStr"/>
+      <c r="EL166" t="inlineStr"/>
+      <c r="EM166" t="inlineStr"/>
+      <c r="EN166" t="inlineStr"/>
+      <c r="EO166" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EP166" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>17</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Sevilla FC</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>46011.83333333334</v>
+      </c>
+      <c r="G167" t="n">
+        <v>2</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" t="n">
+        <v>2</v>
+      </c>
+      <c r="J167" t="n">
+        <v>6</v>
+      </c>
+      <c r="K167" t="n">
+        <v>5</v>
+      </c>
+      <c r="L167" t="n">
+        <v>11</v>
+      </c>
+      <c r="M167" t="n">
+        <v>2</v>
+      </c>
+      <c r="N167" t="n">
+        <v>4</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>8</v>
+      </c>
+      <c r="R167" t="n">
+        <v>5</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="n">
+        <v>9</v>
+      </c>
+      <c r="U167" t="n">
+        <v>18</v>
+      </c>
+      <c r="V167" t="n">
+        <v>14</v>
+      </c>
+      <c r="W167" t="n">
+        <v>13</v>
+      </c>
+      <c r="X167" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>Estadio Santiago Bernabéu</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>Avenida de Concha Espina 1, Chamartín, Madrid</t>
+        </is>
+      </c>
+      <c r="AC167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>84</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>53</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG167" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI167" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK167" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL167" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM167" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN167" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP167" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR167" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS167" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT167" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV167" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW167" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX167" t="n">
+        <v>108</v>
+      </c>
+      <c r="BY167" t="n">
+        <v>64</v>
+      </c>
+      <c r="BZ167" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CA167" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB167" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="CC167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR167" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS167" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU167" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV167" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX167" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY167" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ167" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA167" t="n">
+        <v>87</v>
+      </c>
+      <c r="DB167" t="n">
+        <v>41</v>
+      </c>
+      <c r="DC167" t="n">
+        <v>54</v>
+      </c>
+      <c r="DD167" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DE167" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DF167" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DG167" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH167" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DI167" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DJ167" t="n">
+        <v>41</v>
+      </c>
+      <c r="DK167" t="n">
+        <v>14</v>
+      </c>
+      <c r="DL167" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="DM167" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DN167" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="DO167" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP167" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ167" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR167" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS167" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT167" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU167" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV167" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW167" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="DX167" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="DY167" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="DZ167" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA167" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EB167" t="inlineStr"/>
+      <c r="EC167" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="ED167" t="inlineStr"/>
+      <c r="EE167" t="inlineStr"/>
+      <c r="EF167" t="inlineStr"/>
+      <c r="EG167" t="inlineStr"/>
+      <c r="EH167" t="inlineStr">
+        <is>
+          <t>13.71</t>
+        </is>
+      </c>
+      <c r="EI167" t="inlineStr">
+        <is>
+          <t>7.06</t>
+        </is>
+      </c>
+      <c r="EJ167" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EK167" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EL167" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EM167" t="inlineStr"/>
+      <c r="EN167" t="inlineStr"/>
+      <c r="EO167" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EP167" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>17</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Girona FC</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>46012.54166666666</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>3</v>
+      </c>
+      <c r="I168" t="n">
+        <v>3</v>
+      </c>
+      <c r="J168" t="n">
+        <v>3</v>
+      </c>
+      <c r="K168" t="n">
+        <v>4</v>
+      </c>
+      <c r="L168" t="n">
+        <v>7</v>
+      </c>
+      <c r="M168" t="n">
+        <v>2</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>2</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6</v>
+      </c>
+      <c r="S168" t="n">
+        <v>7</v>
+      </c>
+      <c r="T168" t="n">
+        <v>8</v>
+      </c>
+      <c r="U168" t="n">
+        <v>9</v>
+      </c>
+      <c r="V168" t="n">
+        <v>14</v>
+      </c>
+      <c r="W168" t="n">
+        <v>7</v>
+      </c>
+      <c r="X168" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>Estadi Municipal de Montilivi</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>Avenida Montlivi 141, Girona</t>
+        </is>
+      </c>
+      <c r="AC168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>117</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN168" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV168" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW168" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX168" t="n">
+        <v>103</v>
+      </c>
+      <c r="BY168" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ168" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="CA168" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CB168" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CC168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR168" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS168" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU168" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV168" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX168" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY168" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ168" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA168" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB168" t="n">
+        <v>26</v>
+      </c>
+      <c r="DC168" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD168" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE168" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF168" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DG168" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DH168" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DI168" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ168" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK168" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL168" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DM168" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DN168" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="DO168" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP168" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ168" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR168" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW168" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="DX168" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DY168" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="DZ168" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="EA168" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EB168" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EC168" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="ED168" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EE168" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EF168" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EG168" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EH168" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EI168" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="EJ168" t="inlineStr">
+        <is>
+          <t>4.99</t>
+        </is>
+      </c>
+      <c r="EK168" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EL168" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EM168" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EN168" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EO168" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EP168" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>17</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>46012.63541666666</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>2</v>
+      </c>
+      <c r="I169" t="n">
+        <v>2</v>
+      </c>
+      <c r="J169" t="n">
+        <v>5</v>
+      </c>
+      <c r="K169" t="n">
+        <v>10</v>
+      </c>
+      <c r="L169" t="n">
+        <v>15</v>
+      </c>
+      <c r="M169" t="n">
+        <v>1</v>
+      </c>
+      <c r="N169" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" t="n">
+        <v>1</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>5</v>
+      </c>
+      <c r="R169" t="n">
+        <v>5</v>
+      </c>
+      <c r="S169" t="n">
+        <v>9</v>
+      </c>
+      <c r="T169" t="n">
+        <v>14</v>
+      </c>
+      <c r="U169" t="n">
+        <v>14</v>
+      </c>
+      <c r="V169" t="n">
+        <v>19</v>
+      </c>
+      <c r="W169" t="n">
+        <v>10</v>
+      </c>
+      <c r="X169" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>79</v>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>Estadio de la Cerámica</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>Plaza Labrador, Villarreal</t>
+        </is>
+      </c>
+      <c r="AC169" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>83</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI169" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM169" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN169" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV169" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW169" t="n">
+        <v>93</v>
+      </c>
+      <c r="BX169" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY169" t="n">
+        <v>155</v>
+      </c>
+      <c r="BZ169" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CA169" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CB169" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="CC169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN169" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR169" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS169" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU169" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV169" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX169" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY169" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ169" t="n">
+        <v>76</v>
+      </c>
+      <c r="DA169" t="n">
+        <v>94</v>
+      </c>
+      <c r="DB169" t="n">
+        <v>57</v>
+      </c>
+      <c r="DC169" t="n">
+        <v>94</v>
+      </c>
+      <c r="DD169" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DE169" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DF169" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DG169" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH169" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DI169" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="DJ169" t="n">
+        <v>26</v>
+      </c>
+      <c r="DK169" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL169" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DM169" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="DN169" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="DO169" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP169" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ169" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW169" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="DX169" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="DY169" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="DZ169" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="EA169" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EB169" t="inlineStr"/>
+      <c r="EC169" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="ED169" t="inlineStr"/>
+      <c r="EE169" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EF169" t="inlineStr"/>
+      <c r="EG169" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH169" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EI169" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="EJ169" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="EK169" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EL169" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EM169" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN169" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EO169" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EP169" t="inlineStr">
+        <is>
+          <t>1.41</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP169" headerRowCount="1">
-  <autoFilter ref="A1:EP169"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP172" headerRowCount="1">
+  <autoFilter ref="A1:EP172"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP169"/>
+  <dimension ref="A1:EP172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1805,7 +1805,7 @@
         <v>1</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -4173,7 +4173,7 @@
         <v>0.89</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4203,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4638,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DE8" t="n">
         <v>1.11</v>
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE10" t="n">
         <v>1.5</v>
@@ -5643,7 +5643,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6554,7 +6554,7 @@
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE12" t="n">
         <v>0.5</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7547,7 +7547,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -9393,7 +9393,7 @@
         <v>1.25</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9423,7 +9423,7 @@
         <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -10350,10 +10350,10 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -10383,7 +10383,7 @@
         <v>3.14</v>
       </c>
       <c r="DO20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10837,7 +10837,7 @@
         <v>1.25</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>1.06</v>
       </c>
       <c r="DO21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11335,7 +11335,7 @@
         <v>2.67</v>
       </c>
       <c r="DO22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11774,7 +11774,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE23" t="n">
         <v>0.89</v>
@@ -12265,7 +12265,7 @@
         <v>1.44</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF24" t="n">
         <v>1</v>
@@ -12295,7 +12295,7 @@
         <v>2.77</v>
       </c>
       <c r="DO24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -15102,7 +15102,7 @@
         <v>50</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE30" t="n">
         <v>0.88</v>
@@ -15135,7 +15135,7 @@
         <v>1.65</v>
       </c>
       <c r="DO30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15619,7 +15619,7 @@
         <v>1.56</v>
       </c>
       <c r="DO31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16095,7 +16095,7 @@
         <v>2.84</v>
       </c>
       <c r="DO32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16555,7 +16555,7 @@
         <v>2.15</v>
       </c>
       <c r="DO33" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17039,7 +17039,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="DO34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17962,7 +17962,7 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DE36" t="n">
         <v>0.5</v>
@@ -19889,7 +19889,7 @@
         <v>2</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF40" t="n">
         <v>3</v>
@@ -19919,7 +19919,7 @@
         <v>2.95</v>
       </c>
       <c r="DO40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20863,7 +20863,7 @@
         <v>2.33</v>
       </c>
       <c r="DO42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21298,7 +21298,7 @@
         <v>50</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE43" t="n">
         <v>0.78</v>
@@ -21331,7 +21331,7 @@
         <v>2.96</v>
       </c>
       <c r="DO43" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -22253,7 +22253,7 @@
         <v>2.63</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF45" t="n">
         <v>3</v>
@@ -22283,7 +22283,7 @@
         <v>3.56</v>
       </c>
       <c r="DO45" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -24183,7 +24183,7 @@
         <v>2.29</v>
       </c>
       <c r="DO49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -25114,7 +25114,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE51" t="n">
         <v>0.5</v>
@@ -25147,7 +25147,7 @@
         <v>1.99</v>
       </c>
       <c r="DO51" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25585,7 +25585,7 @@
         <v>3</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF52" t="n">
         <v>3</v>
@@ -25615,7 +25615,7 @@
         <v>3.7</v>
       </c>
       <c r="DO52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25723,143 +25723,143 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
         <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L53" t="n">
+        <v>11</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>10</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2</v>
+      </c>
+      <c r="S53" t="n">
+        <v>11</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>21</v>
+      </c>
+      <c r="V53" t="n">
+        <v>5</v>
+      </c>
+      <c r="W53" t="n">
         <v>9</v>
       </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>2</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>5</v>
-      </c>
-      <c r="R53" t="n">
-        <v>3</v>
-      </c>
-      <c r="S53" t="n">
-        <v>12</v>
-      </c>
-      <c r="T53" t="n">
-        <v>3</v>
-      </c>
-      <c r="U53" t="n">
-        <v>17</v>
-      </c>
-      <c r="V53" t="n">
-        <v>6</v>
-      </c>
-      <c r="W53" t="n">
-        <v>19</v>
-      </c>
       <c r="X53" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y53" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="Z53" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>San Mamés Barria</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE53" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ53" t="n">
         <v>1.47</v>
       </c>
-      <c r="AF53" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AR53" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AS53" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AU53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV53" t="n">
         <v>0</v>
@@ -25868,13 +25868,13 @@
         <v>1</v>
       </c>
       <c r="AX53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA53" t="n">
         <v>1</v>
@@ -25886,7 +25886,7 @@
         <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BE53" t="n">
         <v>0</v>
@@ -25901,28 +25901,28 @@
         <v>1</v>
       </c>
       <c r="BI53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BJ53" t="n">
         <v>1</v>
       </c>
       <c r="BK53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BL53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BN53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ53" t="n">
         <v>0</v>
@@ -25931,7 +25931,7 @@
         <v>2</v>
       </c>
       <c r="BS53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT53" t="n">
         <v>2</v>
@@ -25940,139 +25940,139 @@
         <v>1</v>
       </c>
       <c r="BV53" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="BW53" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BX53" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="BY53" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CB53" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR53" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS53" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU53" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV53" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX53" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY53" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ53" t="n">
         <v>59</v>
       </c>
-      <c r="BZ53" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CA53" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB53" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="CC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS53" t="n">
+      <c r="DA53" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB53" t="n">
         <v>17</v>
       </c>
-      <c r="CT53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU53" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV53" t="n">
-        <v>19</v>
-      </c>
-      <c r="CW53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX53" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY53" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ53" t="n">
+      <c r="DC53" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD53" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DE53" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DF53" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH53" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ53" t="n">
         <v>42</v>
       </c>
-      <c r="DA53" t="n">
-        <v>67</v>
-      </c>
-      <c r="DB53" t="n">
+      <c r="DK53" t="n">
         <v>42</v>
       </c>
-      <c r="DC53" t="n">
-        <v>67</v>
-      </c>
-      <c r="DD53" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="DE53" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DF53" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DH53" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DI53" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DJ53" t="n">
-        <v>59</v>
-      </c>
-      <c r="DK53" t="n">
-        <v>34</v>
-      </c>
       <c r="DL53" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="DM53" t="n">
-        <v>1.18</v>
+        <v>0.47</v>
       </c>
       <c r="DN53" t="n">
-        <v>2.61</v>
+        <v>1.62</v>
       </c>
       <c r="DO53" t="n">
         <v>17</v>
@@ -26084,10 +26084,10 @@
         <v>1</v>
       </c>
       <c r="DR53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT53" t="b">
         <v>0</v>
@@ -26099,79 +26099,75 @@
         <v>1</v>
       </c>
       <c r="DW53" t="n">
-        <v>17.43</v>
+        <v>20.5</v>
       </c>
       <c r="DX53" t="n">
-        <v>4.72</v>
+        <v>6.93</v>
       </c>
       <c r="DY53" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="DZ53" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA53" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EB53" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC53" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC53" t="inlineStr"/>
       <c r="ED53" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EE53" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF53" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EG53" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EH53" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EI53" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EJ53" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EK53" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EL53" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EM53" t="inlineStr">
@@ -26186,12 +26182,12 @@
       </c>
       <c r="EO53" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP53" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -26211,40 +26207,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>8</v>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -26253,101 +26249,101 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T54" t="n">
         <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W54" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="X54" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y54" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="Z54" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>San Mamés Barria</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="AF54" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="AG54" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AI54" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AJ54" t="n">
-        <v>4.05</v>
+        <v>3.08</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AN54" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AO54" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AR54" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AU54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV54" t="n">
         <v>0</v>
@@ -26356,13 +26352,13 @@
         <v>1</v>
       </c>
       <c r="AX54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA54" t="n">
         <v>1</v>
@@ -26374,7 +26370,7 @@
         <v>0</v>
       </c>
       <c r="BD54" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BE54" t="n">
         <v>0</v>
@@ -26389,28 +26385,28 @@
         <v>1</v>
       </c>
       <c r="BI54" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BJ54" t="n">
         <v>1</v>
       </c>
       <c r="BK54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BN54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ54" t="n">
         <v>0</v>
@@ -26419,7 +26415,7 @@
         <v>2</v>
       </c>
       <c r="BS54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT54" t="n">
         <v>2</v>
@@ -26428,25 +26424,25 @@
         <v>1</v>
       </c>
       <c r="BV54" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="BW54" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BX54" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="BY54" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="BZ54" t="n">
-        <v>2.59</v>
+        <v>1.96</v>
       </c>
       <c r="CA54" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="CB54" t="n">
-        <v>3.26</v>
+        <v>2.71</v>
       </c>
       <c r="CC54" t="n">
         <v>0</v>
@@ -26476,10 +26472,10 @@
         <v>0</v>
       </c>
       <c r="CL54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN54" t="n">
         <v>0</v>
@@ -26494,19 +26490,19 @@
         <v>1</v>
       </c>
       <c r="CR54" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="CS54" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CT54" t="n">
         <v>1</v>
       </c>
       <c r="CU54" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="CV54" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="CW54" t="n">
         <v>1</v>
@@ -26515,56 +26511,56 @@
         <v>3</v>
       </c>
       <c r="CY54" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CZ54" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA54" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB54" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC54" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD54" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE54" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF54" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DI54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DJ54" t="n">
         <v>59</v>
       </c>
-      <c r="DA54" t="n">
-        <v>59</v>
-      </c>
-      <c r="DB54" t="n">
+      <c r="DK54" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL54" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM54" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DN54" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="DO54" t="n">
         <v>17</v>
       </c>
-      <c r="DC54" t="n">
-        <v>84</v>
-      </c>
-      <c r="DD54" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DE54" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="DF54" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH54" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI54" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DJ54" t="n">
-        <v>42</v>
-      </c>
-      <c r="DK54" t="n">
-        <v>42</v>
-      </c>
-      <c r="DL54" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="DM54" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="DN54" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="DO54" t="n">
-        <v>16</v>
-      </c>
       <c r="DP54" t="b">
         <v>1</v>
       </c>
@@ -26572,10 +26568,10 @@
         <v>1</v>
       </c>
       <c r="DR54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT54" t="b">
         <v>0</v>
@@ -26587,75 +26583,79 @@
         <v>1</v>
       </c>
       <c r="DW54" t="n">
-        <v>20.5</v>
+        <v>17.43</v>
       </c>
       <c r="DX54" t="n">
-        <v>6.93</v>
+        <v>4.72</v>
       </c>
       <c r="DY54" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="DZ54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="EA54" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EB54" t="inlineStr">
         <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC54" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED54" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE54" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="EC54" t="inlineStr"/>
-      <c r="ED54" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EE54" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="EF54" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EG54" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="EH54" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="EI54" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="EJ54" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EK54" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EL54" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EM54" t="inlineStr">
@@ -26670,12 +26670,12 @@
       </c>
       <c r="EO54" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EP54" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -26695,12 +26695,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
@@ -26710,25 +26710,25 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -26740,119 +26740,119 @@
         <v>2</v>
       </c>
       <c r="R55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S55" t="n">
+        <v>9</v>
+      </c>
+      <c r="T55" t="n">
         <v>14</v>
       </c>
-      <c r="T55" t="n">
-        <v>7</v>
-      </c>
       <c r="U55" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V55" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="W55" t="n">
         <v>17</v>
       </c>
       <c r="X55" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Y55" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="Z55" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Estadio Ramón Sánchez Pizjuán</t>
+          <t>Estadio Ciudad de Valencia</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Avenida de Eduardo Dato, Sevilla</t>
+          <t>Calle San Vicente de Paúl 44, Valencia</t>
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE55" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="AF55" t="n">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI55" t="n">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="AJ55" t="n">
-        <v>3.4</v>
+        <v>2.07</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL55" t="n">
         <v>2</v>
       </c>
       <c r="AM55" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN55" t="n">
         <v>1.5</v>
       </c>
-      <c r="AN55" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AO55" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP55" t="n">
         <v>2.38</v>
       </c>
-      <c r="AP55" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AQ55" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.72</v>
+        <v>4.05</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AU55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV55" t="n">
         <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX55" t="n">
         <v>1</v>
       </c>
       <c r="AY55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB55" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="BC55" t="n">
         <v>0</v>
@@ -26873,76 +26873,76 @@
         <v>1</v>
       </c>
       <c r="BI55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL55" t="n">
         <v>2</v>
       </c>
       <c r="BM55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BN55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO55" t="n">
         <v>0</v>
       </c>
       <c r="BP55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU55" t="n">
         <v>1</v>
       </c>
       <c r="BV55" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="BW55" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="BX55" t="n">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="BY55" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="BZ55" t="n">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
       <c r="CA55" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="CB55" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="CC55" t="n">
         <v>0</v>
       </c>
       <c r="CD55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE55" t="n">
         <v>0</v>
       </c>
       <c r="CF55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG55" t="n">
         <v>0</v>
@@ -26966,7 +26966,7 @@
         <v>0</v>
       </c>
       <c r="CN55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO55" t="n">
         <v>0</v>
@@ -26978,73 +26978,73 @@
         <v>1</v>
       </c>
       <c r="CR55" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="CS55" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="CT55" t="n">
         <v>1</v>
       </c>
       <c r="CU55" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="CV55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CW55" t="n">
         <v>1</v>
       </c>
       <c r="CX55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY55" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CZ55" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA55" t="n">
         <v>100</v>
       </c>
       <c r="DB55" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="DC55" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.25</v>
+        <v>0.29</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="DF55" t="n">
         <v>0.5</v>
       </c>
       <c r="DG55" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DH55" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="DI55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ55" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK55" t="n">
         <v>0</v>
       </c>
       <c r="DL55" t="n">
-        <v>1.24</v>
+        <v>0.84</v>
       </c>
       <c r="DM55" t="n">
-        <v>0.93</v>
+        <v>2.34</v>
       </c>
       <c r="DN55" t="n">
-        <v>2.17</v>
+        <v>3.18</v>
       </c>
       <c r="DO55" t="n">
         <v>16</v>
@@ -27059,10 +27059,10 @@
         <v>1</v>
       </c>
       <c r="DS55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU55" t="b">
         <v>0</v>
@@ -27071,99 +27071,87 @@
         <v>1</v>
       </c>
       <c r="DW55" t="n">
-        <v>27.52</v>
+        <v>22.21</v>
       </c>
       <c r="DX55" t="n">
-        <v>3.08</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DY55" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ55" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="EA55" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EB55" t="inlineStr"/>
+      <c r="EC55" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="ED55" t="inlineStr"/>
+      <c r="EE55" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF55" t="inlineStr"/>
+      <c r="EG55" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH55" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI55" t="inlineStr">
+        <is>
+          <t>5.86</t>
+        </is>
+      </c>
+      <c r="EJ55" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="EK55" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL55" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EB55" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EC55" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="ED55" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EE55" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF55" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG55" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EH55" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EI55" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EJ55" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="EK55" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EL55" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
       <c r="EM55" t="inlineStr">
         <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN55" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EO55" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EP55" t="inlineStr">
+        <is>
           <t>1.68</t>
-        </is>
-      </c>
-      <c r="EN55" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EO55" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EP55" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -27183,12 +27171,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -27198,149 +27186,149 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I56" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3</v>
+      </c>
+      <c r="L56" t="n">
+        <v>6</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2</v>
+      </c>
+      <c r="R56" t="n">
         <v>5</v>
       </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
+      <c r="S56" t="n">
+        <v>14</v>
+      </c>
+      <c r="T56" t="n">
         <v>7</v>
       </c>
-      <c r="L56" t="n">
-        <v>8</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>2</v>
-      </c>
-      <c r="R56" t="n">
-        <v>10</v>
-      </c>
-      <c r="S56" t="n">
-        <v>9</v>
-      </c>
-      <c r="T56" t="n">
-        <v>14</v>
-      </c>
       <c r="U56" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V56" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="W56" t="n">
         <v>17</v>
       </c>
       <c r="X56" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y56" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="Z56" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Estadio Ciudad de Valencia</t>
+          <t>Estadio Ramón Sánchez Pizjuán</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Calle San Vicente de Paúl 44, Valencia</t>
+          <t>Avenida de Eduardo Dato, Sevilla</t>
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE56" t="n">
-        <v>8</v>
+        <v>3.15</v>
       </c>
       <c r="AF56" t="n">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI56" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT56" t="n">
         <v>1.4</v>
       </c>
-      <c r="AJ56" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AU56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV56" t="n">
         <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX56" t="n">
         <v>1</v>
       </c>
       <c r="AY56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB56" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="BC56" t="n">
         <v>0</v>
@@ -27361,76 +27349,76 @@
         <v>1</v>
       </c>
       <c r="BI56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT56" t="n">
         <v>5</v>
       </c>
-      <c r="BK56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL56" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM56" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN56" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ56" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR56" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT56" t="n">
-        <v>2</v>
-      </c>
       <c r="BU56" t="n">
         <v>1</v>
       </c>
       <c r="BV56" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="BW56" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="BX56" t="n">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="BY56" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="BZ56" t="n">
-        <v>1.02</v>
+        <v>1.67</v>
       </c>
       <c r="CA56" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="CB56" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="CC56" t="n">
         <v>0</v>
       </c>
       <c r="CD56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE56" t="n">
         <v>0</v>
       </c>
       <c r="CF56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG56" t="n">
         <v>0</v>
@@ -27454,7 +27442,7 @@
         <v>0</v>
       </c>
       <c r="CN56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO56" t="n">
         <v>0</v>
@@ -27466,73 +27454,73 @@
         <v>1</v>
       </c>
       <c r="CR56" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="CS56" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="CT56" t="n">
         <v>1</v>
       </c>
       <c r="CU56" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV56" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW56" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX56" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY56" t="n">
         <v>9</v>
       </c>
-      <c r="CV56" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW56" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX56" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY56" t="n">
-        <v>3</v>
-      </c>
       <c r="CZ56" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA56" t="n">
         <v>100</v>
       </c>
       <c r="DB56" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC56" t="n">
         <v>75</v>
       </c>
-      <c r="DC56" t="n">
-        <v>100</v>
-      </c>
       <c r="DD56" t="n">
-        <v>0.29</v>
+        <v>1.25</v>
       </c>
       <c r="DE56" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="DF56" t="n">
         <v>0.5</v>
       </c>
       <c r="DG56" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DH56" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ56" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK56" t="n">
         <v>0</v>
       </c>
       <c r="DL56" t="n">
-        <v>0.84</v>
+        <v>1.24</v>
       </c>
       <c r="DM56" t="n">
-        <v>2.34</v>
+        <v>0.93</v>
       </c>
       <c r="DN56" t="n">
-        <v>3.18</v>
+        <v>2.17</v>
       </c>
       <c r="DO56" t="n">
         <v>16</v>
@@ -27547,10 +27535,10 @@
         <v>1</v>
       </c>
       <c r="DS56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU56" t="b">
         <v>0</v>
@@ -27559,87 +27547,99 @@
         <v>1</v>
       </c>
       <c r="DW56" t="n">
-        <v>22.21</v>
+        <v>27.52</v>
       </c>
       <c r="DX56" t="n">
-        <v>8.289999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="DY56" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="DZ56" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA56" t="inlineStr">
         <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EB56" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EB56" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
       <c r="EC56" t="inlineStr">
         <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="ED56" t="inlineStr"/>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="ED56" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="EE56" t="inlineStr">
         <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EF56" t="inlineStr"/>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EF56" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
       <c r="EG56" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EH56" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EI56" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EJ56" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EK56" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EL56" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EM56" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EN56" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EO56" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EP56" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
         <v>2.1</v>
       </c>
       <c r="DO57" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28917,7 +28917,7 @@
         <v>2.78</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF59" t="n">
         <v>2</v>
@@ -28947,7 +28947,7 @@
         <v>2.98</v>
       </c>
       <c r="DO59" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29435,7 +29435,7 @@
         <v>2.17</v>
       </c>
       <c r="DO60" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30341,7 +30341,7 @@
         <v>1</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF62" t="n">
         <v>0</v>
@@ -30371,7 +30371,7 @@
         <v>2.32</v>
       </c>
       <c r="DO62" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP62" t="b">
         <v>0</v>
@@ -32715,7 +32715,7 @@
         <v>2.84</v>
       </c>
       <c r="DO67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33154,7 +33154,7 @@
         <v>59</v>
       </c>
       <c r="DD68" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE68" t="n">
         <v>1.88</v>
@@ -33187,7 +33187,7 @@
         <v>2.52</v>
       </c>
       <c r="DO68" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -34078,7 +34078,7 @@
         <v>50</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE70" t="n">
         <v>0.22</v>
@@ -34111,7 +34111,7 @@
         <v>2.27</v>
       </c>
       <c r="DO70" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -35049,7 +35049,7 @@
         <v>2</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF72" t="n">
         <v>2.33</v>
@@ -35079,7 +35079,7 @@
         <v>2.29</v>
       </c>
       <c r="DO72" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -36498,7 +36498,7 @@
         <v>59</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DE75" t="n">
         <v>0.5600000000000001</v>
@@ -37467,7 +37467,7 @@
         <v>2.1</v>
       </c>
       <c r="DO77" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38043,146 +38043,146 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45935.6875</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K79" t="n">
         <v>5</v>
       </c>
       <c r="L79" t="n">
+        <v>15</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2</v>
+      </c>
+      <c r="N79" t="n">
+        <v>6</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>5</v>
+      </c>
+      <c r="R79" t="n">
+        <v>3</v>
+      </c>
+      <c r="S79" t="n">
+        <v>9</v>
+      </c>
+      <c r="T79" t="n">
+        <v>9</v>
+      </c>
+      <c r="U79" t="n">
+        <v>14</v>
+      </c>
+      <c r="V79" t="n">
         <v>12</v>
       </c>
-      <c r="M79" t="n">
-        <v>1</v>
-      </c>
-      <c r="N79" t="n">
-        <v>2</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>3</v>
-      </c>
-      <c r="R79" t="n">
-        <v>2</v>
-      </c>
-      <c r="S79" t="n">
-        <v>7</v>
-      </c>
-      <c r="T79" t="n">
-        <v>5</v>
-      </c>
-      <c r="U79" t="n">
-        <v>10</v>
-      </c>
-      <c r="V79" t="n">
-        <v>7</v>
-      </c>
       <c r="W79" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X79" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Y79" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z79" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Anoeta</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="AF79" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AG79" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AI79" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AJ79" t="n">
-        <v>3.85</v>
+        <v>2.96</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AM79" t="n">
         <v>1.44</v>
       </c>
       <c r="AN79" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AO79" t="n">
         <v>2.55</v>
       </c>
       <c r="AP79" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AR79" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AU79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW79" t="n">
         <v>0</v>
@@ -38191,22 +38191,22 @@
         <v>0</v>
       </c>
       <c r="AY79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38221,190 +38221,190 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BJ79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BK79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR79" t="n">
         <v>4</v>
       </c>
-      <c r="BL79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM79" t="n">
+      <c r="BS79" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX79" t="n">
         <v>6</v>
       </c>
-      <c r="BN79" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT79" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV79" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW79" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX79" t="n">
-        <v>101</v>
-      </c>
-      <c r="BY79" t="n">
-        <v>90</v>
-      </c>
-      <c r="BZ79" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="CA79" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB79" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN79" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR79" t="n">
-        <v>14</v>
-      </c>
-      <c r="CS79" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU79" t="n">
-        <v>21</v>
-      </c>
-      <c r="CV79" t="n">
+      <c r="CY79" t="n">
         <v>13</v>
       </c>
-      <c r="CW79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX79" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY79" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ79" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="DA79" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="DB79" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="DC79" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.25</v>
+        <v>2.11</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="DF79" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="DG79" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DH79" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="DI79" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="DJ79" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="DK79" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="DN79" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="DO79" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
       </c>
       <c r="DQ79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS79" t="b">
         <v>0</v>
@@ -38416,94 +38416,102 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW79" t="n">
-        <v>17.19</v>
+        <v>17.75</v>
       </c>
       <c r="DX79" t="n">
-        <v>3.66</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EB79" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EC79" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED79" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EE79" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EG79" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EJ79" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EK79" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EL79" t="inlineStr">
+        <is>
           <t>2.02</t>
         </is>
       </c>
-      <c r="EB79" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC79" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="ED79" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE79" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF79" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG79" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="EH79" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="EI79" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="EJ79" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EK79" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EL79" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EM79" t="inlineStr"/>
-      <c r="EN79" t="inlineStr"/>
+      <c r="EM79" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EN79" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.68</t>
         </is>
       </c>
     </row>
@@ -38523,40 +38531,40 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45935.6875</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K80" t="n">
         <v>5</v>
       </c>
       <c r="L80" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -38565,104 +38573,104 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
+        <v>3</v>
+      </c>
+      <c r="R80" t="n">
+        <v>2</v>
+      </c>
+      <c r="S80" t="n">
+        <v>7</v>
+      </c>
+      <c r="T80" t="n">
         <v>5</v>
       </c>
-      <c r="R80" t="n">
-        <v>3</v>
-      </c>
-      <c r="S80" t="n">
-        <v>9</v>
-      </c>
-      <c r="T80" t="n">
-        <v>9</v>
-      </c>
       <c r="U80" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V80" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W80" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="X80" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Y80" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z80" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>Estadio Municipal de Anoeta</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
         </is>
       </c>
       <c r="AC80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="AF80" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AJ80" t="n">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AL80" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AM80" t="n">
         <v>1.44</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AO80" t="n">
         <v>2.55</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AR80" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AU80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW80" t="n">
         <v>0</v>
@@ -38671,22 +38679,22 @@
         <v>0</v>
       </c>
       <c r="AY80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB80" t="n">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -38701,190 +38709,190 @@
         <v>1</v>
       </c>
       <c r="BI80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BJ80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BK80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM80" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>101</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV80" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX80" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY80" t="n">
         <v>10</v>
       </c>
-      <c r="BN80" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR80" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS80" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT80" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV80" t="n">
-        <v>66</v>
-      </c>
-      <c r="BW80" t="n">
-        <v>34</v>
-      </c>
-      <c r="BX80" t="n">
-        <v>107</v>
-      </c>
-      <c r="BY80" t="n">
-        <v>98</v>
-      </c>
-      <c r="BZ80" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CA80" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CB80" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CC80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR80" t="n">
+      <c r="CZ80" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA80" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>59</v>
+      </c>
+      <c r="DC80" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD80" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE80" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF80" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DI80" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DJ80" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK80" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL80" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DM80" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DN80" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="DO80" t="n">
         <v>17</v>
       </c>
-      <c r="CS80" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU80" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV80" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX80" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY80" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ80" t="n">
-        <v>54</v>
-      </c>
-      <c r="DA80" t="n">
-        <v>88</v>
-      </c>
-      <c r="DB80" t="n">
-        <v>29</v>
-      </c>
-      <c r="DC80" t="n">
-        <v>88</v>
-      </c>
-      <c r="DD80" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DE80" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DF80" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DG80" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH80" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DI80" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DJ80" t="n">
-        <v>46</v>
-      </c>
-      <c r="DK80" t="n">
-        <v>13</v>
-      </c>
-      <c r="DL80" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="DM80" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="DN80" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="DO80" t="n">
-        <v>16</v>
-      </c>
       <c r="DP80" t="b">
         <v>1</v>
       </c>
       <c r="DQ80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS80" t="b">
         <v>0</v>
@@ -38896,102 +38904,94 @@
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW80" t="n">
-        <v>17.75</v>
+        <v>17.19</v>
       </c>
       <c r="DX80" t="n">
-        <v>9.369999999999999</v>
+        <v>3.66</v>
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EB80" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EC80" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="ED80" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EE80" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EF80" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EG80" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EH80" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EI80" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EJ80" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EK80" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EL80" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EM80" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EN80" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM80" t="inlineStr"/>
+      <c r="EN80" t="inlineStr"/>
       <c r="EO80" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EP80" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.84</t>
         </is>
       </c>
     </row>
@@ -39797,7 +39797,7 @@
         <v>0.78</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF82" t="n">
         <v>0.75</v>
@@ -39827,7 +39827,7 @@
         <v>2.32</v>
       </c>
       <c r="DO82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -42158,7 +42158,7 @@
         <v>38</v>
       </c>
       <c r="DD87" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE87" t="n">
         <v>0.88</v>
@@ -42191,7 +42191,7 @@
         <v>3.24</v>
       </c>
       <c r="DO87" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -43109,7 +43109,7 @@
         <v>0.29</v>
       </c>
       <c r="DE89" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF89" t="n">
         <v>0.33</v>
@@ -43611,7 +43611,7 @@
         <v>3.13</v>
       </c>
       <c r="DO90" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -45527,7 +45527,7 @@
         <v>2.42</v>
       </c>
       <c r="DO94" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -45978,10 +45978,10 @@
         <v>70</v>
       </c>
       <c r="DD95" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DE95" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF95" t="n">
         <v>2</v>
@@ -46011,7 +46011,7 @@
         <v>2.58</v>
       </c>
       <c r="DO95" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -47414,7 +47414,7 @@
         <v>75</v>
       </c>
       <c r="DD98" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE98" t="n">
         <v>1.33</v>
@@ -47447,7 +47447,7 @@
         <v>3</v>
       </c>
       <c r="DO98" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -48855,7 +48855,7 @@
         <v>2.88</v>
       </c>
       <c r="DO101" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -49323,7 +49323,7 @@
         <v>2.07</v>
       </c>
       <c r="DO102" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -49761,7 +49761,7 @@
         <v>2.44</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF103" t="n">
         <v>2.6</v>
@@ -52137,7 +52137,7 @@
         <v>1.56</v>
       </c>
       <c r="DE108" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF108" t="n">
         <v>1.6</v>
@@ -52167,7 +52167,7 @@
         <v>3.06</v>
       </c>
       <c r="DO108" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -52635,7 +52635,7 @@
         <v>3.52</v>
       </c>
       <c r="DO109" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -53054,7 +53054,7 @@
         <v>80</v>
       </c>
       <c r="DD110" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE110" t="n">
         <v>0.5600000000000001</v>
@@ -53087,7 +53087,7 @@
         <v>2.91</v>
       </c>
       <c r="DO110" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -54018,7 +54018,7 @@
         <v>70</v>
       </c>
       <c r="DD112" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE112" t="n">
         <v>0.78</v>
@@ -54051,7 +54051,7 @@
         <v>3.11</v>
       </c>
       <c r="DO112" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -56402,7 +56402,7 @@
         <v>75</v>
       </c>
       <c r="DD117" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DE117" t="n">
         <v>0.5</v>
@@ -56903,7 +56903,7 @@
         <v>3.88</v>
       </c>
       <c r="DO118" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP118" t="b">
         <v>0</v>
@@ -57011,12 +57011,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F119" s="2" t="n">
@@ -57026,25 +57026,25 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K119" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L119" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -57056,125 +57056,117 @@
         <v>4</v>
       </c>
       <c r="R119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S119" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T119" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U119" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="V119" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W119" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X119" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y119" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Z119" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>Estadio de Mestalla</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>Avenida de Suecia, Valencia</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE119" t="n">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="AF119" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="AG119" t="n">
-        <v>2.15</v>
+        <v>2.98</v>
       </c>
       <c r="AH119" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AI119" t="n">
-        <v>1.91</v>
+        <v>3.04</v>
       </c>
       <c r="AJ119" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="AK119" t="n">
-        <v>1.72</v>
+        <v>2.43</v>
       </c>
       <c r="AL119" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AM119" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="AN119" t="n">
-        <v>1.84</v>
+        <v>2.87</v>
       </c>
       <c r="AO119" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="AR119" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="AS119" t="n">
-        <v>2.89</v>
+        <v>2.05</v>
       </c>
       <c r="AT119" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AU119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW119" t="n">
         <v>0</v>
       </c>
       <c r="AX119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB119" t="n">
-        <v>-1</v>
+        <v>298</v>
       </c>
       <c r="BC119" t="n">
         <v>0</v>
       </c>
       <c r="BD119" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="BE119" t="n">
         <v>0</v>
@@ -57189,64 +57181,64 @@
         <v>1</v>
       </c>
       <c r="BI119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ119" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BK119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL119" t="n">
         <v>6</v>
       </c>
-      <c r="BL119" t="n">
-        <v>1</v>
-      </c>
       <c r="BM119" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BN119" t="n">
         <v>7</v>
       </c>
       <c r="BO119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT119" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BU119" t="n">
         <v>1</v>
       </c>
       <c r="BV119" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="BW119" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="BX119" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="BY119" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="BZ119" t="n">
-        <v>1.74</v>
+        <v>0.96</v>
       </c>
       <c r="CA119" t="n">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="CB119" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="CC119" t="n">
         <v>0</v>
@@ -57279,10 +57271,10 @@
         <v>0</v>
       </c>
       <c r="CM119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO119" t="n">
         <v>0</v>
@@ -57294,19 +57286,19 @@
         <v>1</v>
       </c>
       <c r="CR119" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="CS119" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="CT119" t="n">
         <v>1</v>
       </c>
       <c r="CU119" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CV119" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CW119" t="n">
         <v>1</v>
@@ -57315,61 +57307,61 @@
         <v>6</v>
       </c>
       <c r="CY119" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CZ119" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="DA119" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="DB119" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="DC119" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="DE119" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF119" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG119" t="n">
         <v>1.5</v>
-      </c>
-      <c r="DF119" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DG119" t="n">
-        <v>1.4</v>
       </c>
       <c r="DH119" t="n">
         <v>0.82</v>
       </c>
       <c r="DI119" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="DJ119" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="DK119" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="DL119" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="DM119" t="n">
-        <v>1.6</v>
+        <v>0.97</v>
       </c>
       <c r="DN119" t="n">
-        <v>3.06</v>
+        <v>2.18</v>
       </c>
       <c r="DO119" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
       </c>
       <c r="DQ119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR119" t="b">
         <v>0</v>
@@ -57384,102 +57376,90 @@
         <v>0</v>
       </c>
       <c r="DV119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW119" t="n">
-        <v>17.01</v>
+        <v>17.48</v>
       </c>
       <c r="DX119" t="n">
-        <v>5.56</v>
+        <v>5.64</v>
       </c>
       <c r="DY119" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="DZ119" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="EA119" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="EB119" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC119" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr"/>
       <c r="ED119" t="inlineStr">
         <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EE119" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EE119" t="inlineStr"/>
       <c r="EF119" t="inlineStr">
         <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="EG119" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EG119" t="inlineStr"/>
       <c r="EH119" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EI119" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EJ119" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EK119" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="EL119" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EM119" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EN119" t="inlineStr">
+        <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="EM119" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EN119" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
       <c r="EO119" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EP119" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.43</t>
         </is>
       </c>
     </row>
@@ -57499,12 +57479,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F120" s="2" t="n">
@@ -57514,25 +57494,25 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K120" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L120" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -57544,117 +57524,125 @@
         <v>4</v>
       </c>
       <c r="R120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S120" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T120" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U120" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="V120" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W120" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="X120" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y120" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Z120" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA120" t="inlineStr"/>
-      <c r="AB120" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>Avenida de Suecia, Valencia</t>
+        </is>
+      </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE120" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="AF120" t="n">
-        <v>2.58</v>
+        <v>3.45</v>
       </c>
       <c r="AG120" t="n">
-        <v>2.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH120" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AI120" t="n">
-        <v>3.04</v>
+        <v>1.91</v>
       </c>
       <c r="AJ120" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="AK120" t="n">
-        <v>2.43</v>
+        <v>1.72</v>
       </c>
       <c r="AL120" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AM120" t="n">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="AN120" t="n">
-        <v>2.87</v>
+        <v>1.84</v>
       </c>
       <c r="AO120" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.77</v>
+        <v>1.37</v>
       </c>
       <c r="AR120" t="n">
-        <v>4.45</v>
+        <v>2.85</v>
       </c>
       <c r="AS120" t="n">
-        <v>2.05</v>
+        <v>2.89</v>
       </c>
       <c r="AT120" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AU120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW120" t="n">
         <v>0</v>
       </c>
       <c r="AX120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB120" t="n">
-        <v>298</v>
+        <v>-1</v>
       </c>
       <c r="BC120" t="n">
         <v>0</v>
       </c>
       <c r="BD120" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="BE120" t="n">
         <v>0</v>
@@ -57669,64 +57657,64 @@
         <v>1</v>
       </c>
       <c r="BI120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ120" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BK120" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BL120" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BM120" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BN120" t="n">
         <v>7</v>
       </c>
       <c r="BO120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT120" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BU120" t="n">
         <v>1</v>
       </c>
       <c r="BV120" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="BW120" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="BX120" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="BY120" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="BZ120" t="n">
-        <v>0.96</v>
+        <v>1.74</v>
       </c>
       <c r="CA120" t="n">
-        <v>1.63</v>
+        <v>1.09</v>
       </c>
       <c r="CB120" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="CC120" t="n">
         <v>0</v>
@@ -57759,10 +57747,10 @@
         <v>0</v>
       </c>
       <c r="CM120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO120" t="n">
         <v>0</v>
@@ -57774,19 +57762,19 @@
         <v>1</v>
       </c>
       <c r="CR120" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="CS120" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="CT120" t="n">
         <v>1</v>
       </c>
       <c r="CU120" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CV120" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CW120" t="n">
         <v>1</v>
@@ -57795,61 +57783,61 @@
         <v>6</v>
       </c>
       <c r="CY120" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CZ120" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="DA120" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="DB120" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="DC120" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="DF120" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG120" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DH120" t="n">
         <v>0.82</v>
       </c>
       <c r="DI120" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="DJ120" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="DK120" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="DL120" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="DM120" t="n">
-        <v>0.97</v>
+        <v>1.6</v>
       </c>
       <c r="DN120" t="n">
-        <v>2.18</v>
+        <v>3.06</v>
       </c>
       <c r="DO120" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
       </c>
       <c r="DQ120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR120" t="b">
         <v>0</v>
@@ -57864,90 +57852,102 @@
         <v>0</v>
       </c>
       <c r="DV120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW120" t="n">
-        <v>17.48</v>
+        <v>17.01</v>
       </c>
       <c r="DX120" t="n">
-        <v>5.64</v>
+        <v>5.56</v>
       </c>
       <c r="DY120" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="DZ120" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="EA120" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB120" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EC120" t="inlineStr"/>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC120" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
       <c r="ED120" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EE120" t="inlineStr"/>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE120" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
       <c r="EF120" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="EG120" t="inlineStr"/>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EG120" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EH120" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EI120" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EJ120" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EK120" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EL120" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EM120" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EN120" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EO120" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EP120" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -59703,7 +59703,7 @@
         <v>3.71</v>
       </c>
       <c r="DO124" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -61069,7 +61069,7 @@
         <v>0.78</v>
       </c>
       <c r="DE127" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF127" t="n">
         <v>0.67</v>
@@ -61099,7 +61099,7 @@
         <v>2.27</v>
       </c>
       <c r="DO127" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP127" t="b">
         <v>0</v>
@@ -61542,7 +61542,7 @@
         <v>82</v>
       </c>
       <c r="DD128" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE128" t="n">
         <v>0.75</v>
@@ -61575,7 +61575,7 @@
         <v>2.72</v>
       </c>
       <c r="DO128" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -62035,7 +62035,7 @@
         <v>2.46</v>
       </c>
       <c r="DO129" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -62478,7 +62478,7 @@
         <v>59</v>
       </c>
       <c r="DD130" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE130" t="n">
         <v>2.1</v>
@@ -62511,7 +62511,7 @@
         <v>3.72</v>
       </c>
       <c r="DO130" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -62987,7 +62987,7 @@
         <v>2.6</v>
       </c>
       <c r="DO131" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -63459,7 +63459,7 @@
         <v>2.07</v>
       </c>
       <c r="DO132" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -66299,7 +66299,7 @@
         <v>2.89</v>
       </c>
       <c r="DO138" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -66749,7 +66749,7 @@
         <v>0.89</v>
       </c>
       <c r="DE139" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF139" t="n">
         <v>0.71</v>
@@ -66779,7 +66779,7 @@
         <v>3.03</v>
       </c>
       <c r="DO139" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -67703,7 +67703,7 @@
         <v>2.43</v>
       </c>
       <c r="DO141" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -68574,7 +68574,7 @@
         <v>60</v>
       </c>
       <c r="DD143" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DE143" t="n">
         <v>2.1</v>
@@ -68607,7 +68607,7 @@
         <v>3.83</v>
       </c>
       <c r="DO143" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -69525,7 +69525,7 @@
         <v>2.44</v>
       </c>
       <c r="DE145" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF145" t="n">
         <v>2.71</v>
@@ -70474,7 +70474,7 @@
         <v>93</v>
       </c>
       <c r="DD147" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE147" t="n">
         <v>2.11</v>
@@ -70507,7 +70507,7 @@
         <v>4.01</v>
       </c>
       <c r="DO147" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -70950,7 +70950,7 @@
         <v>67</v>
       </c>
       <c r="DD148" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DE148" t="n">
         <v>1.33</v>
@@ -70983,7 +70983,7 @@
         <v>2.91</v>
       </c>
       <c r="DO148" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -71434,7 +71434,7 @@
         <v>63</v>
       </c>
       <c r="DD149" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE149" t="n">
         <v>0.75</v>
@@ -71467,7 +71467,7 @@
         <v>2.7</v>
       </c>
       <c r="DO149" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP149" t="b">
         <v>1</v>
@@ -72385,7 +72385,7 @@
         <v>2.11</v>
       </c>
       <c r="DE151" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF151" t="n">
         <v>2</v>
@@ -72415,7 +72415,7 @@
         <v>2.81</v>
       </c>
       <c r="DO151" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -74799,7 +74799,7 @@
         <v>2.17</v>
       </c>
       <c r="DO156" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP156" t="b">
         <v>1</v>
@@ -75721,7 +75721,7 @@
         <v>1.38</v>
       </c>
       <c r="DE158" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DF158" t="n">
         <v>1.57</v>
@@ -75751,7 +75751,7 @@
         <v>2.67</v>
       </c>
       <c r="DO158" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP158" t="b">
         <v>1</v>
@@ -77651,7 +77651,7 @@
         <v>3.18</v>
       </c>
       <c r="DO162" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP162" t="b">
         <v>0</v>
@@ -81080,6 +81080,1418 @@
       <c r="EP169" t="inlineStr">
         <is>
           <t>1.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>17</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Elche CF</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>46012.72916666666</v>
+      </c>
+      <c r="G170" t="n">
+        <v>4</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" t="n">
+        <v>4</v>
+      </c>
+      <c r="J170" t="n">
+        <v>4</v>
+      </c>
+      <c r="K170" t="n">
+        <v>5</v>
+      </c>
+      <c r="L170" t="n">
+        <v>9</v>
+      </c>
+      <c r="M170" t="n">
+        <v>2</v>
+      </c>
+      <c r="N170" t="n">
+        <v>3</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>6</v>
+      </c>
+      <c r="R170" t="n">
+        <v>8</v>
+      </c>
+      <c r="S170" t="n">
+        <v>12</v>
+      </c>
+      <c r="T170" t="n">
+        <v>10</v>
+      </c>
+      <c r="U170" t="n">
+        <v>18</v>
+      </c>
+      <c r="V170" t="n">
+        <v>18</v>
+      </c>
+      <c r="W170" t="n">
+        <v>15</v>
+      </c>
+      <c r="X170" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Martínez Valero</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>Avenida Manuel Martínez Valero 3, Elche</t>
+        </is>
+      </c>
+      <c r="AC170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>295</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI170" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ170" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM170" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN170" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT170" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV170" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW170" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX170" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY170" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ170" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CA170" t="n">
+        <v>2</v>
+      </c>
+      <c r="CB170" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="CC170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR170" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS170" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU170" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV170" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX170" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY170" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ170" t="n">
+        <v>41</v>
+      </c>
+      <c r="DA170" t="n">
+        <v>66</v>
+      </c>
+      <c r="DB170" t="n">
+        <v>23</v>
+      </c>
+      <c r="DC170" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD170" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DE170" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF170" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG170" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DH170" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DI170" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ170" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK170" t="n">
+        <v>35</v>
+      </c>
+      <c r="DL170" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DM170" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DN170" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DO170" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP170" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ170" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR170" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS170" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT170" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU170" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV170" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW170" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="DX170" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="DY170" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="DZ170" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="EA170" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EB170" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EC170" t="inlineStr"/>
+      <c r="ED170" t="inlineStr"/>
+      <c r="EE170" t="inlineStr"/>
+      <c r="EF170" t="inlineStr"/>
+      <c r="EG170" t="inlineStr"/>
+      <c r="EH170" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EI170" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="EJ170" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EK170" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EL170" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EM170" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EN170" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EO170" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EP170" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>17</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Getafe CF</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>46012.83333333334</v>
+      </c>
+      <c r="G171" t="n">
+        <v>4</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" t="n">
+        <v>4</v>
+      </c>
+      <c r="J171" t="n">
+        <v>7</v>
+      </c>
+      <c r="K171" t="n">
+        <v>5</v>
+      </c>
+      <c r="L171" t="n">
+        <v>12</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" t="n">
+        <v>1</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>8</v>
+      </c>
+      <c r="R171" t="n">
+        <v>3</v>
+      </c>
+      <c r="S171" t="n">
+        <v>11</v>
+      </c>
+      <c r="T171" t="n">
+        <v>12</v>
+      </c>
+      <c r="U171" t="n">
+        <v>19</v>
+      </c>
+      <c r="V171" t="n">
+        <v>15</v>
+      </c>
+      <c r="W171" t="n">
+        <v>13</v>
+      </c>
+      <c r="X171" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA171" t="inlineStr"/>
+      <c r="AB171" t="inlineStr"/>
+      <c r="AC171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>284</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF171" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI171" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL171" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM171" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN171" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV171" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW171" t="n">
+        <v>54</v>
+      </c>
+      <c r="BX171" t="n">
+        <v>77</v>
+      </c>
+      <c r="BY171" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ171" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CA171" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CB171" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="CC171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR171" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS171" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU171" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV171" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX171" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY171" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ171" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA171" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB171" t="n">
+        <v>51</v>
+      </c>
+      <c r="DC171" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD171" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DE171" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF171" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DG171" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DH171" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DI171" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DJ171" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK171" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL171" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DM171" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="DN171" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="DO171" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP171" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ171" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR171" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS171" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT171" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU171" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV171" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW171" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="DX171" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="DY171" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="DZ171" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA171" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="EB171" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EC171" t="inlineStr"/>
+      <c r="ED171" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EE171" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EF171" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EG171" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="EH171" t="inlineStr">
+        <is>
+          <t>5.72</t>
+        </is>
+      </c>
+      <c r="EI171" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EJ171" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EK171" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EL171" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EM171" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EN171" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EO171" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EP171" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>17</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Athletic Club Bilbao</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>RCD Espanyol</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>46013.83333333334</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="n">
+        <v>2</v>
+      </c>
+      <c r="I172" t="n">
+        <v>3</v>
+      </c>
+      <c r="J172" t="n">
+        <v>8</v>
+      </c>
+      <c r="K172" t="n">
+        <v>4</v>
+      </c>
+      <c r="L172" t="n">
+        <v>12</v>
+      </c>
+      <c r="M172" t="n">
+        <v>5</v>
+      </c>
+      <c r="N172" t="n">
+        <v>2</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>7</v>
+      </c>
+      <c r="R172" t="n">
+        <v>5</v>
+      </c>
+      <c r="S172" t="n">
+        <v>10</v>
+      </c>
+      <c r="T172" t="n">
+        <v>5</v>
+      </c>
+      <c r="U172" t="n">
+        <v>17</v>
+      </c>
+      <c r="V172" t="n">
+        <v>10</v>
+      </c>
+      <c r="W172" t="n">
+        <v>10</v>
+      </c>
+      <c r="X172" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>San Mamés Barria</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
+        </is>
+      </c>
+      <c r="AC172" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>280</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>31</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK172" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM172" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN172" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT172" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV172" t="n">
+        <v>63</v>
+      </c>
+      <c r="BW172" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX172" t="n">
+        <v>136</v>
+      </c>
+      <c r="BY172" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ172" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CA172" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CB172" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="CC172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR172" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS172" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU172" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV172" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX172" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY172" t="n">
+        <v>15</v>
+      </c>
+      <c r="CZ172" t="n">
+        <v>31</v>
+      </c>
+      <c r="DA172" t="n">
+        <v>51</v>
+      </c>
+      <c r="DB172" t="n">
+        <v>26</v>
+      </c>
+      <c r="DC172" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD172" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE172" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DF172" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DG172" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DH172" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DI172" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DJ172" t="n">
+        <v>69</v>
+      </c>
+      <c r="DK172" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL172" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DM172" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DN172" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="DO172" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP172" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ172" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR172" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS172" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT172" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU172" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV172" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW172" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="DX172" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="DY172" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="DZ172" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA172" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EB172" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC172" t="inlineStr"/>
+      <c r="ED172" t="inlineStr"/>
+      <c r="EE172" t="inlineStr"/>
+      <c r="EF172" t="inlineStr"/>
+      <c r="EG172" t="inlineStr"/>
+      <c r="EH172" t="inlineStr">
+        <is>
+          <t>4.82</t>
+        </is>
+      </c>
+      <c r="EI172" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EJ172" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EK172" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EL172" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EM172" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EN172" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EO172" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EP172" t="inlineStr">
+        <is>
+          <t>2.09</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP172" headerRowCount="1">
-  <autoFilter ref="A1:EP172"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP177" headerRowCount="1">
+  <autoFilter ref="A1:EP177"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP172"/>
+  <dimension ref="A1:EP177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2769,7 +2769,7 @@
         <v>1.63</v>
       </c>
       <c r="DE4" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE7" t="n">
         <v>1</v>
@@ -4203,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -5122,7 +5122,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE9" t="n">
         <v>1.33</v>
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE10" t="n">
         <v>1.5</v>
@@ -6127,7 +6127,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -7547,7 +7547,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8005,7 +8005,7 @@
         <v>0.29</v>
       </c>
       <c r="DE15" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -8470,10 +8470,10 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8971,7 +8971,7 @@
         <v>2.89</v>
       </c>
       <c r="DO17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -10383,7 +10383,7 @@
         <v>3.14</v>
       </c>
       <c r="DO20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -11302,7 +11302,7 @@
         <v>50</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE22" t="n">
         <v>1.5</v>
@@ -11774,7 +11774,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE23" t="n">
         <v>0.89</v>
@@ -12295,7 +12295,7 @@
         <v>2.77</v>
       </c>
       <c r="DO24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -14638,10 +14638,10 @@
         <v>25</v>
       </c>
       <c r="DD29" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF29" t="n">
         <v>0.5</v>
@@ -14671,7 +14671,7 @@
         <v>1.49</v>
       </c>
       <c r="DO29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15105,7 +15105,7 @@
         <v>1.78</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DF30" t="n">
         <v>3</v>
@@ -15586,7 +15586,7 @@
         <v>50</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE31" t="n">
         <v>0.22</v>
@@ -15619,7 +15619,7 @@
         <v>1.56</v>
       </c>
       <c r="DO31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16062,10 +16062,10 @@
         <v>50</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE32" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DF32" t="n">
         <v>0</v>
@@ -16095,7 +16095,7 @@
         <v>2.84</v>
       </c>
       <c r="DO32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -18449,7 +18449,7 @@
         <v>2.78</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF37" t="n">
         <v>1</v>
@@ -18479,7 +18479,7 @@
         <v>2.71</v>
       </c>
       <c r="DO37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18926,7 +18926,7 @@
         <v>67</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE38" t="n">
         <v>0.75</v>
@@ -19886,7 +19886,7 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DE40" t="n">
         <v>1</v>
@@ -19919,7 +19919,7 @@
         <v>2.95</v>
       </c>
       <c r="DO40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20365,7 +20365,7 @@
         <v>3</v>
       </c>
       <c r="DE41" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DF41" t="n">
         <v>0</v>
@@ -20395,7 +20395,7 @@
         <v>0.57</v>
       </c>
       <c r="DO41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20830,7 +20830,7 @@
         <v>75</v>
       </c>
       <c r="DD42" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE42" t="n">
         <v>0.5600000000000001</v>
@@ -22283,7 +22283,7 @@
         <v>3.56</v>
       </c>
       <c r="DO45" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -23219,7 +23219,7 @@
         <v>3.19</v>
       </c>
       <c r="DO47" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23677,7 +23677,7 @@
         <v>1.44</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DF48" t="n">
         <v>2</v>
@@ -23707,7 +23707,7 @@
         <v>2.96</v>
       </c>
       <c r="DO48" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24150,7 +24150,7 @@
         <v>100</v>
       </c>
       <c r="DD49" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE49" t="n">
         <v>1.88</v>
@@ -24183,7 +24183,7 @@
         <v>2.29</v>
       </c>
       <c r="DO49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -25114,7 +25114,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE51" t="n">
         <v>0.5</v>
@@ -25615,7 +25615,7 @@
         <v>3.7</v>
       </c>
       <c r="DO52" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25723,40 +25723,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -25765,101 +25765,101 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T53" t="n">
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W53" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="X53" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y53" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="Z53" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>San Mamés Barria</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="AF53" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="AG53" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AJ53" t="n">
-        <v>4.05</v>
+        <v>3.08</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AO53" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AR53" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AU53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV53" t="n">
         <v>0</v>
@@ -25868,13 +25868,13 @@
         <v>1</v>
       </c>
       <c r="AX53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA53" t="n">
         <v>1</v>
@@ -25886,7 +25886,7 @@
         <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BE53" t="n">
         <v>0</v>
@@ -25901,28 +25901,28 @@
         <v>1</v>
       </c>
       <c r="BI53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BJ53" t="n">
         <v>1</v>
       </c>
       <c r="BK53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BN53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ53" t="n">
         <v>0</v>
@@ -25931,7 +25931,7 @@
         <v>2</v>
       </c>
       <c r="BS53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT53" t="n">
         <v>2</v>
@@ -25940,25 +25940,25 @@
         <v>1</v>
       </c>
       <c r="BV53" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="BW53" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BX53" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="BY53" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="BZ53" t="n">
-        <v>2.59</v>
+        <v>1.96</v>
       </c>
       <c r="CA53" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="CB53" t="n">
-        <v>3.26</v>
+        <v>2.71</v>
       </c>
       <c r="CC53" t="n">
         <v>0</v>
@@ -25988,10 +25988,10 @@
         <v>0</v>
       </c>
       <c r="CL53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN53" t="n">
         <v>0</v>
@@ -26006,19 +26006,19 @@
         <v>1</v>
       </c>
       <c r="CR53" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="CS53" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CT53" t="n">
         <v>1</v>
       </c>
       <c r="CU53" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="CV53" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="CW53" t="n">
         <v>1</v>
@@ -26027,52 +26027,52 @@
         <v>3</v>
       </c>
       <c r="CY53" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CZ53" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA53" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB53" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC53" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD53" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE53" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF53" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DI53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DJ53" t="n">
         <v>59</v>
       </c>
-      <c r="DA53" t="n">
-        <v>59</v>
-      </c>
-      <c r="DB53" t="n">
-        <v>17</v>
-      </c>
-      <c r="DC53" t="n">
-        <v>84</v>
-      </c>
-      <c r="DD53" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DE53" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="DF53" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH53" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI53" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DJ53" t="n">
-        <v>42</v>
-      </c>
       <c r="DK53" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="DL53" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="DM53" t="n">
-        <v>0.47</v>
+        <v>1.18</v>
       </c>
       <c r="DN53" t="n">
-        <v>1.62</v>
+        <v>2.61</v>
       </c>
       <c r="DO53" t="n">
         <v>17</v>
@@ -26084,10 +26084,10 @@
         <v>1</v>
       </c>
       <c r="DR53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT53" t="b">
         <v>0</v>
@@ -26099,75 +26099,79 @@
         <v>1</v>
       </c>
       <c r="DW53" t="n">
-        <v>20.5</v>
+        <v>17.43</v>
       </c>
       <c r="DX53" t="n">
-        <v>6.93</v>
+        <v>4.72</v>
       </c>
       <c r="DY53" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="DZ53" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="EA53" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EB53" t="inlineStr">
         <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC53" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED53" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE53" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="EC53" t="inlineStr"/>
-      <c r="ED53" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EE53" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="EF53" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EG53" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="EH53" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="EI53" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="EJ53" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EK53" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EL53" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EM53" t="inlineStr">
@@ -26182,12 +26186,12 @@
       </c>
       <c r="EO53" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EP53" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -26207,143 +26211,143 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
         <v>8</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L54" t="n">
+        <v>11</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>4</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>10</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2</v>
+      </c>
+      <c r="S54" t="n">
+        <v>11</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>21</v>
+      </c>
+      <c r="V54" t="n">
+        <v>5</v>
+      </c>
+      <c r="W54" t="n">
         <v>9</v>
       </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>2</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>5</v>
-      </c>
-      <c r="R54" t="n">
-        <v>3</v>
-      </c>
-      <c r="S54" t="n">
-        <v>12</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3</v>
-      </c>
-      <c r="U54" t="n">
-        <v>17</v>
-      </c>
-      <c r="V54" t="n">
-        <v>6</v>
-      </c>
-      <c r="W54" t="n">
-        <v>19</v>
-      </c>
       <c r="X54" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y54" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="Z54" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>San Mamés Barria</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE54" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ54" t="n">
         <v>1.47</v>
       </c>
-      <c r="AF54" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AR54" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AS54" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AU54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV54" t="n">
         <v>0</v>
@@ -26352,13 +26356,13 @@
         <v>1</v>
       </c>
       <c r="AX54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA54" t="n">
         <v>1</v>
@@ -26370,7 +26374,7 @@
         <v>0</v>
       </c>
       <c r="BD54" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BE54" t="n">
         <v>0</v>
@@ -26385,28 +26389,28 @@
         <v>1</v>
       </c>
       <c r="BI54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BJ54" t="n">
         <v>1</v>
       </c>
       <c r="BK54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BL54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BN54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ54" t="n">
         <v>0</v>
@@ -26415,7 +26419,7 @@
         <v>2</v>
       </c>
       <c r="BS54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT54" t="n">
         <v>2</v>
@@ -26424,142 +26428,142 @@
         <v>1</v>
       </c>
       <c r="BV54" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="BW54" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BX54" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="BY54" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ54" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CA54" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CB54" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR54" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS54" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU54" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV54" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX54" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY54" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ54" t="n">
         <v>59</v>
       </c>
-      <c r="BZ54" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CA54" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB54" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="CC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR54" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS54" t="n">
+      <c r="DA54" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB54" t="n">
         <v>17</v>
       </c>
-      <c r="CT54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU54" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV54" t="n">
-        <v>19</v>
-      </c>
-      <c r="CW54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX54" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY54" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ54" t="n">
+      <c r="DC54" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD54" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DE54" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DF54" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH54" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ54" t="n">
         <v>42</v>
       </c>
-      <c r="DA54" t="n">
-        <v>67</v>
-      </c>
-      <c r="DB54" t="n">
+      <c r="DK54" t="n">
         <v>42</v>
       </c>
-      <c r="DC54" t="n">
-        <v>67</v>
-      </c>
-      <c r="DD54" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DE54" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DF54" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG54" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DH54" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DI54" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DJ54" t="n">
-        <v>59</v>
-      </c>
-      <c r="DK54" t="n">
-        <v>34</v>
-      </c>
       <c r="DL54" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="DM54" t="n">
-        <v>1.18</v>
+        <v>0.47</v>
       </c>
       <c r="DN54" t="n">
-        <v>2.61</v>
+        <v>1.62</v>
       </c>
       <c r="DO54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26568,10 +26572,10 @@
         <v>1</v>
       </c>
       <c r="DR54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT54" t="b">
         <v>0</v>
@@ -26583,79 +26587,75 @@
         <v>1</v>
       </c>
       <c r="DW54" t="n">
-        <v>17.43</v>
+        <v>20.5</v>
       </c>
       <c r="DX54" t="n">
-        <v>4.72</v>
+        <v>6.93</v>
       </c>
       <c r="DY54" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="DZ54" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA54" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EB54" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC54" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC54" t="inlineStr"/>
       <c r="ED54" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EE54" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF54" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EG54" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EH54" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EI54" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EJ54" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EK54" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EL54" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EM54" t="inlineStr">
@@ -26670,12 +26670,12 @@
       </c>
       <c r="EO54" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP54" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -26695,12 +26695,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
@@ -26710,149 +26710,149 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="n">
+        <v>6</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2</v>
+      </c>
+      <c r="R55" t="n">
         <v>5</v>
       </c>
-      <c r="J55" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" t="n">
+      <c r="S55" t="n">
+        <v>14</v>
+      </c>
+      <c r="T55" t="n">
         <v>7</v>
       </c>
-      <c r="L55" t="n">
-        <v>8</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>2</v>
-      </c>
-      <c r="R55" t="n">
-        <v>10</v>
-      </c>
-      <c r="S55" t="n">
-        <v>9</v>
-      </c>
-      <c r="T55" t="n">
-        <v>14</v>
-      </c>
       <c r="U55" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V55" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="W55" t="n">
         <v>17</v>
       </c>
       <c r="X55" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y55" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="Z55" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Estadio Ciudad de Valencia</t>
+          <t>Estadio Ramón Sánchez Pizjuán</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Calle San Vicente de Paúl 44, Valencia</t>
+          <t>Avenida de Eduardo Dato, Sevilla</t>
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE55" t="n">
-        <v>8</v>
+        <v>3.15</v>
       </c>
       <c r="AF55" t="n">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI55" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT55" t="n">
         <v>1.4</v>
       </c>
-      <c r="AJ55" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AU55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV55" t="n">
         <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX55" t="n">
         <v>1</v>
       </c>
       <c r="AY55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB55" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="BC55" t="n">
         <v>0</v>
@@ -26873,76 +26873,76 @@
         <v>1</v>
       </c>
       <c r="BI55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT55" t="n">
         <v>5</v>
       </c>
-      <c r="BK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL55" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM55" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN55" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ55" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR55" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT55" t="n">
-        <v>2</v>
-      </c>
       <c r="BU55" t="n">
         <v>1</v>
       </c>
       <c r="BV55" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="BW55" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="BX55" t="n">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="BY55" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="BZ55" t="n">
-        <v>1.02</v>
+        <v>1.67</v>
       </c>
       <c r="CA55" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="CB55" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="CC55" t="n">
         <v>0</v>
       </c>
       <c r="CD55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE55" t="n">
         <v>0</v>
       </c>
       <c r="CF55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG55" t="n">
         <v>0</v>
@@ -26966,7 +26966,7 @@
         <v>0</v>
       </c>
       <c r="CN55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO55" t="n">
         <v>0</v>
@@ -26978,76 +26978,76 @@
         <v>1</v>
       </c>
       <c r="CR55" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="CS55" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="CT55" t="n">
         <v>1</v>
       </c>
       <c r="CU55" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV55" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX55" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY55" t="n">
         <v>9</v>
       </c>
-      <c r="CV55" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW55" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX55" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY55" t="n">
-        <v>3</v>
-      </c>
       <c r="CZ55" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA55" t="n">
         <v>100</v>
       </c>
       <c r="DB55" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC55" t="n">
         <v>75</v>
       </c>
-      <c r="DC55" t="n">
-        <v>100</v>
-      </c>
       <c r="DD55" t="n">
-        <v>0.29</v>
+        <v>1.25</v>
       </c>
       <c r="DE55" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DF55" t="n">
         <v>0.5</v>
       </c>
       <c r="DG55" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DH55" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ55" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK55" t="n">
         <v>0</v>
       </c>
       <c r="DL55" t="n">
-        <v>0.84</v>
+        <v>1.24</v>
       </c>
       <c r="DM55" t="n">
-        <v>2.34</v>
+        <v>0.93</v>
       </c>
       <c r="DN55" t="n">
-        <v>3.18</v>
+        <v>2.17</v>
       </c>
       <c r="DO55" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27059,10 +27059,10 @@
         <v>1</v>
       </c>
       <c r="DS55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU55" t="b">
         <v>0</v>
@@ -27071,87 +27071,99 @@
         <v>1</v>
       </c>
       <c r="DW55" t="n">
-        <v>22.21</v>
+        <v>27.52</v>
       </c>
       <c r="DX55" t="n">
-        <v>8.289999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="DY55" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="DZ55" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA55" t="inlineStr">
         <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EB55" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EB55" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
       <c r="EC55" t="inlineStr">
         <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="ED55" t="inlineStr"/>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="ED55" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="EE55" t="inlineStr">
         <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EF55" t="inlineStr"/>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EF55" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
       <c r="EG55" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EH55" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EI55" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EJ55" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EK55" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EL55" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EM55" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EN55" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EO55" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EP55" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -27171,12 +27183,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -27186,25 +27198,25 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -27216,119 +27228,119 @@
         <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S56" t="n">
+        <v>9</v>
+      </c>
+      <c r="T56" t="n">
         <v>14</v>
       </c>
-      <c r="T56" t="n">
-        <v>7</v>
-      </c>
       <c r="U56" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V56" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="W56" t="n">
         <v>17</v>
       </c>
       <c r="X56" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Y56" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="Z56" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Estadio Ramón Sánchez Pizjuán</t>
+          <t>Estadio Ciudad de Valencia</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Avenida de Eduardo Dato, Sevilla</t>
+          <t>Calle San Vicente de Paúl 44, Valencia</t>
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE56" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="AF56" t="n">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="AG56" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI56" t="n">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="AJ56" t="n">
-        <v>3.4</v>
+        <v>2.07</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL56" t="n">
         <v>2</v>
       </c>
       <c r="AM56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN56" t="n">
         <v>1.5</v>
       </c>
-      <c r="AN56" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AO56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP56" t="n">
         <v>2.38</v>
       </c>
-      <c r="AP56" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AQ56" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AR56" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.72</v>
+        <v>4.05</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AU56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV56" t="n">
         <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX56" t="n">
         <v>1</v>
       </c>
       <c r="AY56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB56" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="BC56" t="n">
         <v>0</v>
@@ -27349,76 +27361,76 @@
         <v>1</v>
       </c>
       <c r="BI56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL56" t="n">
         <v>2</v>
       </c>
       <c r="BM56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BN56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO56" t="n">
         <v>0</v>
       </c>
       <c r="BP56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU56" t="n">
         <v>1</v>
       </c>
       <c r="BV56" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="BW56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="BX56" t="n">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="BY56" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="BZ56" t="n">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
       <c r="CA56" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="CB56" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="CC56" t="n">
         <v>0</v>
       </c>
       <c r="CD56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE56" t="n">
         <v>0</v>
       </c>
       <c r="CF56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG56" t="n">
         <v>0</v>
@@ -27442,7 +27454,7 @@
         <v>0</v>
       </c>
       <c r="CN56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO56" t="n">
         <v>0</v>
@@ -27454,73 +27466,73 @@
         <v>1</v>
       </c>
       <c r="CR56" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="CS56" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="CT56" t="n">
         <v>1</v>
       </c>
       <c r="CU56" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="CV56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CW56" t="n">
         <v>1</v>
       </c>
       <c r="CX56" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY56" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CZ56" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA56" t="n">
         <v>100</v>
       </c>
       <c r="DB56" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="DC56" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.25</v>
+        <v>0.29</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="DF56" t="n">
         <v>0.5</v>
       </c>
       <c r="DG56" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DH56" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="DI56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ56" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK56" t="n">
         <v>0</v>
       </c>
       <c r="DL56" t="n">
-        <v>1.24</v>
+        <v>0.84</v>
       </c>
       <c r="DM56" t="n">
-        <v>0.93</v>
+        <v>2.34</v>
       </c>
       <c r="DN56" t="n">
-        <v>2.17</v>
+        <v>3.18</v>
       </c>
       <c r="DO56" t="n">
         <v>16</v>
@@ -27535,10 +27547,10 @@
         <v>1</v>
       </c>
       <c r="DS56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU56" t="b">
         <v>0</v>
@@ -27547,99 +27559,87 @@
         <v>1</v>
       </c>
       <c r="DW56" t="n">
-        <v>27.52</v>
+        <v>22.21</v>
       </c>
       <c r="DX56" t="n">
-        <v>3.08</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DY56" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ56" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="EA56" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EB56" t="inlineStr"/>
+      <c r="EC56" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="ED56" t="inlineStr"/>
+      <c r="EE56" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF56" t="inlineStr"/>
+      <c r="EG56" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH56" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI56" t="inlineStr">
+        <is>
+          <t>5.86</t>
+        </is>
+      </c>
+      <c r="EJ56" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="EK56" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL56" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EB56" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EC56" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="ED56" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EE56" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF56" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG56" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EH56" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EI56" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EJ56" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="EK56" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EL56" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
       <c r="EM56" t="inlineStr">
         <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN56" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EO56" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EP56" t="inlineStr">
+        <is>
           <t>1.68</t>
-        </is>
-      </c>
-      <c r="EN56" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EO56" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EP56" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -28947,7 +28947,7 @@
         <v>2.98</v>
       </c>
       <c r="DO59" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29402,7 +29402,7 @@
         <v>100</v>
       </c>
       <c r="DD60" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DE60" t="n">
         <v>0.38</v>
@@ -29435,7 +29435,7 @@
         <v>2.17</v>
       </c>
       <c r="DO60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29873,7 +29873,7 @@
         <v>0.78</v>
       </c>
       <c r="DE61" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DF61" t="n">
         <v>1.5</v>
@@ -32233,7 +32233,7 @@
         <v>2.44</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DF66" t="n">
         <v>3</v>
@@ -32263,7 +32263,7 @@
         <v>4.16</v>
       </c>
       <c r="DO66" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32682,7 +32682,7 @@
         <v>75</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE67" t="n">
         <v>1.11</v>
@@ -33154,7 +33154,7 @@
         <v>59</v>
       </c>
       <c r="DD68" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE68" t="n">
         <v>1.88</v>
@@ -33187,7 +33187,7 @@
         <v>2.52</v>
       </c>
       <c r="DO68" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -35046,7 +35046,7 @@
         <v>88</v>
       </c>
       <c r="DD72" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DE72" t="n">
         <v>1</v>
@@ -35079,7 +35079,7 @@
         <v>2.29</v>
       </c>
       <c r="DO72" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -36013,7 +36013,7 @@
         <v>1</v>
       </c>
       <c r="DE74" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DF74" t="n">
         <v>0.25</v>
@@ -36969,7 +36969,7 @@
         <v>2.63</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF76" t="n">
         <v>3</v>
@@ -36999,7 +36999,7 @@
         <v>3.16</v>
       </c>
       <c r="DO76" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -37897,7 +37897,7 @@
         <v>1.25</v>
       </c>
       <c r="DE78" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DF78" t="n">
         <v>0.33</v>
@@ -38362,7 +38362,7 @@
         <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE79" t="n">
         <v>1.5</v>
@@ -39322,7 +39322,7 @@
         <v>59</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE81" t="n">
         <v>1.33</v>
@@ -39355,7 +39355,7 @@
         <v>3.36</v>
       </c>
       <c r="DO81" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -41231,7 +41231,7 @@
         <v>3.94</v>
       </c>
       <c r="DO85" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41703,7 +41703,7 @@
         <v>2.53</v>
       </c>
       <c r="DO86" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42158,10 +42158,10 @@
         <v>38</v>
       </c>
       <c r="DD87" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DF87" t="n">
         <v>2.5</v>
@@ -42191,7 +42191,7 @@
         <v>3.24</v>
       </c>
       <c r="DO87" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -42618,7 +42618,7 @@
         <v>68</v>
       </c>
       <c r="DD88" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE88" t="n">
         <v>0.78</v>
@@ -43611,7 +43611,7 @@
         <v>3.13</v>
       </c>
       <c r="DO90" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44069,7 +44069,7 @@
         <v>1.56</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DF91" t="n">
         <v>1.75</v>
@@ -45494,7 +45494,7 @@
         <v>78</v>
       </c>
       <c r="DD94" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE94" t="n">
         <v>0.38</v>
@@ -45527,7 +45527,7 @@
         <v>2.42</v>
       </c>
       <c r="DO94" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46011,7 +46011,7 @@
         <v>2.58</v>
       </c>
       <c r="DO95" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46457,7 +46457,7 @@
         <v>1.44</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF96" t="n">
         <v>1.75</v>
@@ -46487,7 +46487,7 @@
         <v>2.51</v>
       </c>
       <c r="DO96" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -47889,7 +47889,7 @@
         <v>2.63</v>
       </c>
       <c r="DE99" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DF99" t="n">
         <v>3</v>
@@ -48346,7 +48346,7 @@
         <v>84</v>
       </c>
       <c r="DD100" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DE100" t="n">
         <v>1.88</v>
@@ -48379,7 +48379,7 @@
         <v>2.21</v>
       </c>
       <c r="DO100" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -48822,7 +48822,7 @@
         <v>42</v>
       </c>
       <c r="DD101" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE101" t="n">
         <v>0.5</v>
@@ -49791,7 +49791,7 @@
         <v>3.29</v>
       </c>
       <c r="DO103" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50705,7 +50705,7 @@
         <v>1.25</v>
       </c>
       <c r="DE105" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DF105" t="n">
         <v>1.4</v>
@@ -51181,7 +51181,7 @@
         <v>2.63</v>
       </c>
       <c r="DE106" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DF106" t="n">
         <v>3</v>
@@ -51211,7 +51211,7 @@
         <v>3.13</v>
       </c>
       <c r="DO106" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -52635,7 +52635,7 @@
         <v>3.52</v>
       </c>
       <c r="DO109" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -54018,7 +54018,7 @@
         <v>70</v>
       </c>
       <c r="DD112" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE112" t="n">
         <v>0.78</v>
@@ -55914,10 +55914,10 @@
         <v>64</v>
       </c>
       <c r="DD116" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE116" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF116" t="n">
         <v>2.17</v>
@@ -55947,7 +55947,7 @@
         <v>2.69</v>
       </c>
       <c r="DO116" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -56870,7 +56870,7 @@
         <v>53</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE118" t="n">
         <v>2.1</v>
@@ -56903,7 +56903,7 @@
         <v>3.88</v>
       </c>
       <c r="DO118" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP118" t="b">
         <v>0</v>
@@ -58278,10 +58278,10 @@
         <v>84</v>
       </c>
       <c r="DD121" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE121" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DF121" t="n">
         <v>0.83</v>
@@ -58311,7 +58311,7 @@
         <v>3.7</v>
       </c>
       <c r="DO121" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -59673,7 +59673,7 @@
         <v>3</v>
       </c>
       <c r="DE124" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DF124" t="n">
         <v>3</v>
@@ -59703,7 +59703,7 @@
         <v>3.71</v>
       </c>
       <c r="DO124" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -60130,7 +60130,7 @@
         <v>84</v>
       </c>
       <c r="DD125" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DE125" t="n">
         <v>0.78</v>
@@ -60631,7 +60631,7 @@
         <v>3.29</v>
       </c>
       <c r="DO126" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -62035,7 +62035,7 @@
         <v>2.46</v>
       </c>
       <c r="DO129" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -62478,7 +62478,7 @@
         <v>59</v>
       </c>
       <c r="DD130" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE130" t="n">
         <v>2.1</v>
@@ -62511,7 +62511,7 @@
         <v>3.72</v>
       </c>
       <c r="DO130" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -62954,7 +62954,7 @@
         <v>69</v>
       </c>
       <c r="DD131" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE131" t="n">
         <v>1.11</v>
@@ -63459,7 +63459,7 @@
         <v>2.07</v>
       </c>
       <c r="DO132" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -64833,7 +64833,7 @@
         <v>0.29</v>
       </c>
       <c r="DE135" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DF135" t="n">
         <v>0.2</v>
@@ -65781,7 +65781,7 @@
         <v>1.25</v>
       </c>
       <c r="DE137" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF137" t="n">
         <v>1.67</v>
@@ -65811,7 +65811,7 @@
         <v>2.59</v>
       </c>
       <c r="DO137" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP137" t="b">
         <v>1</v>
@@ -66746,7 +66746,7 @@
         <v>66</v>
       </c>
       <c r="DD139" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE139" t="n">
         <v>1.75</v>
@@ -66779,7 +66779,7 @@
         <v>3.03</v>
       </c>
       <c r="DO139" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -67670,10 +67670,10 @@
         <v>52</v>
       </c>
       <c r="DD141" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE141" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DF141" t="n">
         <v>1.2</v>
@@ -67703,7 +67703,7 @@
         <v>2.43</v>
       </c>
       <c r="DO141" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -69555,7 +69555,7 @@
         <v>3.06</v>
       </c>
       <c r="DO145" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -70477,7 +70477,7 @@
         <v>1.78</v>
       </c>
       <c r="DE147" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DF147" t="n">
         <v>1.86</v>
@@ -71434,7 +71434,7 @@
         <v>63</v>
       </c>
       <c r="DD149" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE149" t="n">
         <v>0.75</v>
@@ -72382,7 +72382,7 @@
         <v>63</v>
       </c>
       <c r="DD151" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE151" t="n">
         <v>1</v>
@@ -72415,7 +72415,7 @@
         <v>2.81</v>
       </c>
       <c r="DO151" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -72891,7 +72891,7 @@
         <v>3.58</v>
       </c>
       <c r="DO152" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -73318,7 +73318,7 @@
         <v>88</v>
       </c>
       <c r="DD153" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DE153" t="n">
         <v>0.89</v>
@@ -74297,7 +74297,7 @@
         <v>2.78</v>
       </c>
       <c r="DE155" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DF155" t="n">
         <v>2.75</v>
@@ -74327,7 +74327,7 @@
         <v>2.77</v>
       </c>
       <c r="DO155" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP155" t="b">
         <v>1</v>
@@ -75283,7 +75283,7 @@
         <v>3.26</v>
       </c>
       <c r="DO157" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP157" t="b">
         <v>1</v>
@@ -75751,7 +75751,7 @@
         <v>2.67</v>
       </c>
       <c r="DO158" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP158" t="b">
         <v>1</v>
@@ -76670,10 +76670,10 @@
         <v>53</v>
       </c>
       <c r="DD160" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DE160" t="n">
         <v>0.89</v>
-      </c>
-      <c r="DE160" t="n">
-        <v>0.88</v>
       </c>
       <c r="DF160" t="n">
         <v>0.63</v>
@@ -76703,7 +76703,7 @@
         <v>2.74</v>
       </c>
       <c r="DO160" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP160" t="b">
         <v>1</v>
@@ -77618,7 +77618,7 @@
         <v>52</v>
       </c>
       <c r="DD162" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE162" t="n">
         <v>1.5</v>
@@ -79534,7 +79534,7 @@
         <v>79</v>
       </c>
       <c r="DD166" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DE166" t="n">
         <v>0.5</v>
@@ -80945,7 +80945,7 @@
         <v>2.44</v>
       </c>
       <c r="DE169" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DF169" t="n">
         <v>2.75</v>
@@ -80975,7 +80975,7 @@
         <v>4.09</v>
       </c>
       <c r="DO169" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP169" t="b">
         <v>1</v>
@@ -81418,7 +81418,7 @@
         <v>59</v>
       </c>
       <c r="DD170" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DE170" t="n">
         <v>1</v>
@@ -81451,7 +81451,7 @@
         <v>2.82</v>
       </c>
       <c r="DO170" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP170" t="b">
         <v>1</v>
@@ -82395,7 +82395,7 @@
         <v>2.99</v>
       </c>
       <c r="DO172" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP172" t="b">
         <v>1</v>
@@ -82492,6 +82492,2354 @@
       <c r="EP172" t="inlineStr">
         <is>
           <t>2.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>18</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Getafe CF</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>46024.83333333334</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" t="n">
+        <v>1</v>
+      </c>
+      <c r="I173" t="n">
+        <v>2</v>
+      </c>
+      <c r="J173" t="n">
+        <v>3</v>
+      </c>
+      <c r="K173" t="n">
+        <v>2</v>
+      </c>
+      <c r="L173" t="n">
+        <v>5</v>
+      </c>
+      <c r="M173" t="n">
+        <v>3</v>
+      </c>
+      <c r="N173" t="n">
+        <v>4</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>4</v>
+      </c>
+      <c r="R173" t="n">
+        <v>4</v>
+      </c>
+      <c r="S173" t="n">
+        <v>9</v>
+      </c>
+      <c r="T173" t="n">
+        <v>8</v>
+      </c>
+      <c r="U173" t="n">
+        <v>13</v>
+      </c>
+      <c r="V173" t="n">
+        <v>12</v>
+      </c>
+      <c r="W173" t="n">
+        <v>13</v>
+      </c>
+      <c r="X173" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA173" t="inlineStr"/>
+      <c r="AB173" t="inlineStr"/>
+      <c r="AC173" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB173" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>33</v>
+      </c>
+      <c r="BE173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF173" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG173" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI173" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ173" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM173" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ173" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR173" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT173" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV173" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW173" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX173" t="n">
+        <v>114</v>
+      </c>
+      <c r="BY173" t="n">
+        <v>114</v>
+      </c>
+      <c r="BZ173" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CA173" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CB173" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="CC173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI173" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ173" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM173" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP173" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ173" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR173" t="n">
+        <v>32</v>
+      </c>
+      <c r="CS173" t="n">
+        <v>32</v>
+      </c>
+      <c r="CT173" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU173" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV173" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW173" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX173" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY173" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ173" t="n">
+        <v>28</v>
+      </c>
+      <c r="DA173" t="n">
+        <v>61</v>
+      </c>
+      <c r="DB173" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC173" t="n">
+        <v>54</v>
+      </c>
+      <c r="DD173" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DE173" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF173" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DG173" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH173" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DI173" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DJ173" t="n">
+        <v>72</v>
+      </c>
+      <c r="DK173" t="n">
+        <v>40</v>
+      </c>
+      <c r="DL173" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="DM173" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DN173" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="DO173" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP173" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ173" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR173" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS173" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT173" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU173" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV173" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW173" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="DX173" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="DY173" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="DZ173" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA173" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EB173" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EC173" t="inlineStr"/>
+      <c r="ED173" t="inlineStr"/>
+      <c r="EE173" t="inlineStr"/>
+      <c r="EF173" t="inlineStr"/>
+      <c r="EG173" t="inlineStr"/>
+      <c r="EH173" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="EI173" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EJ173" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EK173" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EL173" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EM173" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EN173" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EO173" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EP173" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>18</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Valencia CF</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>46025.54166666666</v>
+      </c>
+      <c r="G174" t="n">
+        <v>4</v>
+      </c>
+      <c r="H174" t="n">
+        <v>1</v>
+      </c>
+      <c r="I174" t="n">
+        <v>5</v>
+      </c>
+      <c r="J174" t="n">
+        <v>2</v>
+      </c>
+      <c r="K174" t="n">
+        <v>4</v>
+      </c>
+      <c r="L174" t="n">
+        <v>6</v>
+      </c>
+      <c r="M174" t="n">
+        <v>1</v>
+      </c>
+      <c r="N174" t="n">
+        <v>3</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>6</v>
+      </c>
+      <c r="R174" t="n">
+        <v>5</v>
+      </c>
+      <c r="S174" t="n">
+        <v>6</v>
+      </c>
+      <c r="T174" t="n">
+        <v>11</v>
+      </c>
+      <c r="U174" t="n">
+        <v>12</v>
+      </c>
+      <c r="V174" t="n">
+        <v>16</v>
+      </c>
+      <c r="W174" t="n">
+        <v>10</v>
+      </c>
+      <c r="X174" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA174" t="inlineStr"/>
+      <c r="AB174" t="inlineStr"/>
+      <c r="AC174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>281</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF174" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG174" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH174" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI174" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ174" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM174" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ174" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR174" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT174" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU174" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV174" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW174" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX174" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY174" t="n">
+        <v>95</v>
+      </c>
+      <c r="BZ174" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CA174" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CB174" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="CC174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN174" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP174" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR174" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS174" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU174" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV174" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW174" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX174" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY174" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ174" t="n">
+        <v>37</v>
+      </c>
+      <c r="DA174" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB174" t="n">
+        <v>12</v>
+      </c>
+      <c r="DC174" t="n">
+        <v>72</v>
+      </c>
+      <c r="DD174" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DE174" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DF174" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DG174" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DH174" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DI174" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DJ174" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK174" t="n">
+        <v>18</v>
+      </c>
+      <c r="DL174" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DM174" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DN174" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DO174" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP174" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ174" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR174" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS174" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT174" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU174" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV174" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW174" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="DX174" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="DY174" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="DZ174" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA174" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EB174" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EC174" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="ED174" t="inlineStr"/>
+      <c r="EE174" t="inlineStr"/>
+      <c r="EF174" t="inlineStr"/>
+      <c r="EG174" t="inlineStr"/>
+      <c r="EH174" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="EI174" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EJ174" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EK174" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EL174" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EM174" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EN174" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EO174" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EP174" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>18</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>CA Osasuna</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Athletic Club Bilbao</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>46025.63541666666</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="n">
+        <v>1</v>
+      </c>
+      <c r="I175" t="n">
+        <v>2</v>
+      </c>
+      <c r="J175" t="n">
+        <v>1</v>
+      </c>
+      <c r="K175" t="n">
+        <v>9</v>
+      </c>
+      <c r="L175" t="n">
+        <v>10</v>
+      </c>
+      <c r="M175" t="n">
+        <v>3</v>
+      </c>
+      <c r="N175" t="n">
+        <v>3</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>4</v>
+      </c>
+      <c r="R175" t="n">
+        <v>6</v>
+      </c>
+      <c r="S175" t="n">
+        <v>7</v>
+      </c>
+      <c r="T175" t="n">
+        <v>10</v>
+      </c>
+      <c r="U175" t="n">
+        <v>11</v>
+      </c>
+      <c r="V175" t="n">
+        <v>16</v>
+      </c>
+      <c r="W175" t="n">
+        <v>12</v>
+      </c>
+      <c r="X175" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>Carretera El Sadar, Iruñea</t>
+        </is>
+      </c>
+      <c r="AC175" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AU175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF175" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG175" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ175" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL175" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM175" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN175" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ175" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR175" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT175" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV175" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW175" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX175" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY175" t="n">
+        <v>134</v>
+      </c>
+      <c r="BZ175" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CA175" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CB175" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CC175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI175" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ175" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP175" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ175" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR175" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS175" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT175" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU175" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV175" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW175" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX175" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY175" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ175" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA175" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB175" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC175" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD175" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DE175" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DF175" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG175" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DH175" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DI175" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DJ175" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK175" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL175" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DM175" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DN175" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="DO175" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP175" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ175" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR175" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS175" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT175" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU175" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV175" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW175" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="DX175" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="DY175" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="DZ175" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA175" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EB175" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EC175" t="inlineStr"/>
+      <c r="ED175" t="inlineStr"/>
+      <c r="EE175" t="inlineStr"/>
+      <c r="EF175" t="inlineStr"/>
+      <c r="EG175" t="inlineStr"/>
+      <c r="EH175" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EI175" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EJ175" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EK175" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EL175" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EM175" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EN175" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EO175" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EP175" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>18</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Elche CF</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>46025.72916666666</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="n">
+        <v>3</v>
+      </c>
+      <c r="I176" t="n">
+        <v>4</v>
+      </c>
+      <c r="J176" t="n">
+        <v>6</v>
+      </c>
+      <c r="K176" t="n">
+        <v>2</v>
+      </c>
+      <c r="L176" t="n">
+        <v>8</v>
+      </c>
+      <c r="M176" t="n">
+        <v>3</v>
+      </c>
+      <c r="N176" t="n">
+        <v>3</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>2</v>
+      </c>
+      <c r="R176" t="n">
+        <v>4</v>
+      </c>
+      <c r="S176" t="n">
+        <v>13</v>
+      </c>
+      <c r="T176" t="n">
+        <v>8</v>
+      </c>
+      <c r="U176" t="n">
+        <v>15</v>
+      </c>
+      <c r="V176" t="n">
+        <v>12</v>
+      </c>
+      <c r="W176" t="n">
+        <v>8</v>
+      </c>
+      <c r="X176" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>78</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Martínez Valero</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>Avenida Manuel Martínez Valero 3, Elche</t>
+        </is>
+      </c>
+      <c r="AC176" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ176" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>76</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>51</v>
+      </c>
+      <c r="BE176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF176" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG176" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH176" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI176" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ176" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK176" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM176" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN176" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP176" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ176" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR176" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS176" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT176" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU176" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV176" t="n">
+        <v>97</v>
+      </c>
+      <c r="BW176" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX176" t="n">
+        <v>163</v>
+      </c>
+      <c r="BY176" t="n">
+        <v>51</v>
+      </c>
+      <c r="BZ176" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA176" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CB176" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CC176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI176" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ176" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL176" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ176" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR176" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS176" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT176" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU176" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV176" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW176" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX176" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY176" t="n">
+        <v>15</v>
+      </c>
+      <c r="CZ176" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA176" t="n">
+        <v>89</v>
+      </c>
+      <c r="DB176" t="n">
+        <v>6</v>
+      </c>
+      <c r="DC176" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD176" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DE176" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF176" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DG176" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DH176" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DI176" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="DJ176" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK176" t="n">
+        <v>11</v>
+      </c>
+      <c r="DL176" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DM176" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DN176" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="DO176" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP176" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ176" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR176" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS176" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT176" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU176" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV176" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW176" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="DX176" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="DY176" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="DZ176" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="EA176" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EB176" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EC176" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="ED176" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EE176" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EF176" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="EG176" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EH176" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EI176" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="EJ176" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EK176" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EL176" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EM176" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EN176" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EO176" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EP176" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>18</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>RCD Espanyol</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>46025.83333333334</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>2</v>
+      </c>
+      <c r="I177" t="n">
+        <v>2</v>
+      </c>
+      <c r="J177" t="n">
+        <v>5</v>
+      </c>
+      <c r="K177" t="n">
+        <v>7</v>
+      </c>
+      <c r="L177" t="n">
+        <v>12</v>
+      </c>
+      <c r="M177" t="n">
+        <v>1</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>7</v>
+      </c>
+      <c r="R177" t="n">
+        <v>6</v>
+      </c>
+      <c r="S177" t="n">
+        <v>7</v>
+      </c>
+      <c r="T177" t="n">
+        <v>9</v>
+      </c>
+      <c r="U177" t="n">
+        <v>14</v>
+      </c>
+      <c r="V177" t="n">
+        <v>15</v>
+      </c>
+      <c r="W177" t="n">
+        <v>10</v>
+      </c>
+      <c r="X177" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>69</v>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>RCDE Stadium</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+        </is>
+      </c>
+      <c r="AC177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ177" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AU177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ177" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB177" t="n">
+        <v>83</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF177" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG177" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH177" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI177" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ177" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK177" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL177" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM177" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN177" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ177" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT177" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU177" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV177" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW177" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX177" t="n">
+        <v>66</v>
+      </c>
+      <c r="BY177" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ177" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CA177" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CB177" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CC177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI177" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ177" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM177" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ177" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR177" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS177" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT177" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU177" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV177" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW177" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX177" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY177" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ177" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA177" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB177" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC177" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD177" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DE177" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DF177" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DG177" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DH177" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DI177" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DJ177" t="n">
+        <v>33</v>
+      </c>
+      <c r="DK177" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL177" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DM177" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="DN177" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="DO177" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP177" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ177" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR177" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS177" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT177" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU177" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV177" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW177" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="DX177" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="DY177" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="DZ177" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA177" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EB177" t="inlineStr"/>
+      <c r="EC177" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="ED177" t="inlineStr"/>
+      <c r="EE177" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EF177" t="inlineStr"/>
+      <c r="EG177" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EH177" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EI177" t="inlineStr">
+        <is>
+          <t>4.91</t>
+        </is>
+      </c>
+      <c r="EJ177" t="inlineStr">
+        <is>
+          <t>5.85</t>
+        </is>
+      </c>
+      <c r="EK177" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EL177" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EM177" t="inlineStr"/>
+      <c r="EN177" t="inlineStr"/>
+      <c r="EO177" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EP177" t="inlineStr">
+        <is>
+          <t>1.63</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP182" headerRowCount="1">
-  <autoFilter ref="A1:EP182"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP186" headerRowCount="1">
+  <autoFilter ref="A1:EP186"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP182"/>
+  <dimension ref="A1:EP186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DE2" t="n">
         <v>1</v>
@@ -2286,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE3" t="n">
         <v>0.5600000000000001</v>
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -3237,7 +3237,7 @@
         <v>1.44</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -5613,7 +5613,7 @@
         <v>1.9</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
         <v>2.67</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6127,7 +6127,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6557,7 +6557,7 @@
         <v>1.78</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -8938,7 +8938,7 @@
         <v>50</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE17" t="n">
         <v>1</v>
@@ -8971,7 +8971,7 @@
         <v>2.89</v>
       </c>
       <c r="DO17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9878,7 +9878,7 @@
         <v>0</v>
       </c>
       <c r="DD19" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE19" t="n">
         <v>2.1</v>
@@ -9911,7 +9911,7 @@
         <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -11305,7 +11305,7 @@
         <v>1.1</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -12771,7 +12771,7 @@
         <v>3.34</v>
       </c>
       <c r="DO25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13222,10 +13222,10 @@
         <v>50</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF26" t="n">
         <v>0</v>
@@ -13255,7 +13255,7 @@
         <v>2.11</v>
       </c>
       <c r="DO26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13690,7 +13690,7 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DE27" t="n">
         <v>1.11</v>
@@ -14671,7 +14671,7 @@
         <v>1.49</v>
       </c>
       <c r="DO29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15135,7 +15135,7 @@
         <v>1.65</v>
       </c>
       <c r="DO30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15589,7 +15589,7 @@
         <v>1.9</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -17006,7 +17006,7 @@
         <v>50</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE34" t="n">
         <v>0.5600000000000001</v>
@@ -17039,7 +17039,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="DO34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17515,7 +17515,7 @@
         <v>4.77</v>
       </c>
       <c r="DO35" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17965,7 +17965,7 @@
         <v>1.6</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF36" t="n">
         <v>3</v>
@@ -17995,7 +17995,7 @@
         <v>2.75</v>
       </c>
       <c r="DO36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18479,7 +18479,7 @@
         <v>2.71</v>
       </c>
       <c r="DO37" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -19417,7 +19417,7 @@
         <v>0.29</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF39" t="n">
         <v>0</v>
@@ -21301,7 +21301,7 @@
         <v>1.78</v>
       </c>
       <c r="DE43" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF43" t="n">
         <v>1.5</v>
@@ -21331,7 +21331,7 @@
         <v>2.96</v>
       </c>
       <c r="DO43" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21762,7 +21762,7 @@
         <v>75</v>
       </c>
       <c r="DD44" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DE44" t="n">
         <v>1.1</v>
@@ -22391,170 +22391,170 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
         <v>45920.6875</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
         <v>3</v>
       </c>
       <c r="J46" t="n">
+        <v>4</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4</v>
+      </c>
+      <c r="L46" t="n">
+        <v>8</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
         <v>7</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>5</v>
+      </c>
+      <c r="R46" t="n">
+        <v>3</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
+        <v>8</v>
+      </c>
+      <c r="V46" t="n">
+        <v>9</v>
+      </c>
+      <c r="W46" t="n">
+        <v>20</v>
+      </c>
+      <c r="X46" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Estadio de Mendizorroza</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+        </is>
+      </c>
+      <c r="AC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="n">
         <v>7</v>
       </c>
-      <c r="M46" t="n">
-        <v>2</v>
-      </c>
-      <c r="N46" t="n">
-        <v>2</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>8</v>
-      </c>
-      <c r="R46" t="n">
-        <v>3</v>
-      </c>
-      <c r="S46" t="n">
-        <v>18</v>
-      </c>
-      <c r="T46" t="n">
-        <v>3</v>
-      </c>
-      <c r="U46" t="n">
-        <v>26</v>
-      </c>
-      <c r="V46" t="n">
-        <v>6</v>
-      </c>
-      <c r="W46" t="n">
-        <v>10</v>
-      </c>
-      <c r="X46" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>66</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>Estadio de la Cerámica</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>Plaza Labrador, Villarreal</t>
-        </is>
-      </c>
-      <c r="AC46" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>3</v>
-      </c>
       <c r="AE46" t="n">
-        <v>1.55</v>
+        <v>2.33</v>
       </c>
       <c r="AF46" t="n">
-        <v>3.8</v>
+        <v>3.01</v>
       </c>
       <c r="AG46" t="n">
-        <v>5.25</v>
+        <v>3.28</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.01</v>
+        <v>2.43</v>
       </c>
       <c r="AJ46" t="n">
-        <v>3.05</v>
+        <v>4.85</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AN46" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AO46" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AP46" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AU46" t="n">
         <v>3</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW46" t="n">
         <v>1</v>
       </c>
       <c r="AX46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB46" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="BC46" t="n">
         <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BE46" t="n">
         <v>0</v>
@@ -22572,178 +22572,178 @@
         <v>1</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK46" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT46" t="n">
         <v>6</v>
       </c>
-      <c r="BL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN46" t="n">
+      <c r="BU46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV46" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CB46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR46" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS46" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU46" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV46" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX46" t="n">
         <v>6</v>
       </c>
-      <c r="BO46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP46" t="n">
-        <v>3</v>
-      </c>
-      <c r="BQ46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS46" t="n">
+      <c r="CY46" t="n">
         <v>4</v>
       </c>
-      <c r="BT46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV46" t="n">
-        <v>90</v>
-      </c>
-      <c r="BW46" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX46" t="n">
-        <v>112</v>
-      </c>
-      <c r="BY46" t="n">
-        <v>57</v>
-      </c>
-      <c r="BZ46" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CA46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB46" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="CC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS46" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU46" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV46" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX46" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY46" t="n">
-        <v>20</v>
-      </c>
       <c r="CZ46" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DA46" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB46" t="n">
         <v>50</v>
       </c>
       <c r="DC46" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>2.44</v>
+        <v>1.5</v>
       </c>
       <c r="DE46" t="n">
-        <v>0.22</v>
+        <v>1.11</v>
       </c>
       <c r="DF46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DG46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DH46" t="n">
         <v>1.75</v>
       </c>
       <c r="DI46" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DJ46" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK46" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL46" t="n">
-        <v>2.48</v>
+        <v>1.19</v>
       </c>
       <c r="DM46" t="n">
-        <v>0.71</v>
+        <v>1.32</v>
       </c>
       <c r="DN46" t="n">
-        <v>3.19</v>
+        <v>2.51</v>
       </c>
       <c r="DO46" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22767,99 +22767,87 @@
         <v>1</v>
       </c>
       <c r="DW46" t="n">
-        <v>27.48</v>
+        <v>27.45</v>
       </c>
       <c r="DX46" t="n">
-        <v>4.71</v>
+        <v>4.36</v>
       </c>
       <c r="DY46" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="DZ46" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="EA46" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EB46" t="inlineStr">
         <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC46" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
-      </c>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EC46" t="inlineStr"/>
       <c r="ED46" t="inlineStr">
         <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE46" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EE46" t="inlineStr"/>
       <c r="EF46" t="inlineStr">
         <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="EG46" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EG46" t="inlineStr"/>
       <c r="EH46" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="EI46" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EJ46" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="EK46" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EL46" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EM46" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EN46" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="EO46" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EP46" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.16</t>
         </is>
       </c>
     </row>
@@ -22879,170 +22867,170 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
         <v>45920.6875</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
+        <v>7</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
         <v>8</v>
       </c>
-      <c r="M47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" t="n">
-        <v>7</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>5</v>
-      </c>
       <c r="R47" t="n">
         <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>26</v>
+      </c>
+      <c r="V47" t="n">
         <v>6</v>
       </c>
-      <c r="U47" t="n">
-        <v>8</v>
-      </c>
-      <c r="V47" t="n">
-        <v>9</v>
-      </c>
       <c r="W47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="X47" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Y47" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="Z47" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Estadio de Mendizorroza</t>
+          <t>Estadio de la Cerámica</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+          <t>Plaza Labrador, Villarreal</t>
         </is>
       </c>
       <c r="AC47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD47" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.33</v>
+        <v>1.55</v>
       </c>
       <c r="AF47" t="n">
-        <v>3.01</v>
+        <v>3.8</v>
       </c>
       <c r="AG47" t="n">
-        <v>3.28</v>
+        <v>5.25</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.43</v>
+        <v>2.01</v>
       </c>
       <c r="AJ47" t="n">
-        <v>4.85</v>
+        <v>3.05</v>
       </c>
       <c r="AK47" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AO47" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AP47" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AR47" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AU47" t="n">
         <v>3</v>
       </c>
       <c r="AV47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
         <v>1</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB47" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="BC47" t="n">
         <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
         <v>0</v>
@@ -23060,73 +23048,73 @@
         <v>1</v>
       </c>
       <c r="BJ47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BL47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BN47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ47" t="n">
         <v>1</v>
       </c>
       <c r="BR47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BS47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BT47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BU47" t="n">
         <v>1</v>
       </c>
       <c r="BV47" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="BW47" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="BX47" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="BY47" t="n">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="BZ47" t="n">
-        <v>1.22</v>
+        <v>2.84</v>
       </c>
       <c r="CA47" t="n">
-        <v>1.08</v>
+        <v>0.75</v>
       </c>
       <c r="CB47" t="n">
-        <v>2.3</v>
+        <v>3.58</v>
       </c>
       <c r="CC47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG47" t="n">
         <v>0</v>
@@ -23144,13 +23132,13 @@
         <v>0</v>
       </c>
       <c r="CL47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM47" t="n">
         <v>0</v>
       </c>
       <c r="CN47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO47" t="n">
         <v>0</v>
@@ -23162,73 +23150,73 @@
         <v>1</v>
       </c>
       <c r="CR47" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="CS47" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="CT47" t="n">
         <v>1</v>
       </c>
       <c r="CU47" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="CV47" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX47" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY47" t="n">
         <v>20</v>
       </c>
-      <c r="CW47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX47" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY47" t="n">
-        <v>4</v>
-      </c>
       <c r="CZ47" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA47" t="n">
         <v>50</v>
-      </c>
-      <c r="DA47" t="n">
-        <v>100</v>
       </c>
       <c r="DB47" t="n">
         <v>50</v>
       </c>
       <c r="DC47" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.11</v>
+        <v>0.2</v>
       </c>
       <c r="DF47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DH47" t="n">
         <v>1.75</v>
       </c>
       <c r="DI47" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DJ47" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK47" t="n">
         <v>50</v>
       </c>
-      <c r="DK47" t="n">
-        <v>0</v>
-      </c>
       <c r="DL47" t="n">
-        <v>1.19</v>
+        <v>2.48</v>
       </c>
       <c r="DM47" t="n">
-        <v>1.32</v>
+        <v>0.71</v>
       </c>
       <c r="DN47" t="n">
-        <v>2.51</v>
+        <v>3.19</v>
       </c>
       <c r="DO47" t="n">
         <v>18</v>
@@ -23255,87 +23243,99 @@
         <v>1</v>
       </c>
       <c r="DW47" t="n">
-        <v>27.45</v>
+        <v>27.48</v>
       </c>
       <c r="DX47" t="n">
-        <v>4.36</v>
+        <v>4.71</v>
       </c>
       <c r="DY47" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ47" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="EA47" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EB47" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EC47" t="inlineStr"/>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EC47" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
       <c r="ED47" t="inlineStr">
         <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EE47" t="inlineStr"/>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EE47" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
       <c r="EF47" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="EG47" t="inlineStr"/>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EG47" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
       <c r="EH47" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="EI47" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="EJ47" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EK47" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EL47" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EM47" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EN47" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EO47" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EP47" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -25615,7 +25615,7 @@
         <v>3.7</v>
       </c>
       <c r="DO52" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25723,143 +25723,143 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
         <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L53" t="n">
+        <v>11</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>10</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2</v>
+      </c>
+      <c r="S53" t="n">
+        <v>11</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>21</v>
+      </c>
+      <c r="V53" t="n">
+        <v>5</v>
+      </c>
+      <c r="W53" t="n">
         <v>9</v>
       </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>2</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>5</v>
-      </c>
-      <c r="R53" t="n">
-        <v>3</v>
-      </c>
-      <c r="S53" t="n">
-        <v>12</v>
-      </c>
-      <c r="T53" t="n">
-        <v>3</v>
-      </c>
-      <c r="U53" t="n">
-        <v>17</v>
-      </c>
-      <c r="V53" t="n">
-        <v>6</v>
-      </c>
-      <c r="W53" t="n">
-        <v>19</v>
-      </c>
       <c r="X53" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y53" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="Z53" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>San Mamés Barria</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE53" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ53" t="n">
         <v>1.47</v>
       </c>
-      <c r="AF53" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AR53" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AS53" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AU53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV53" t="n">
         <v>0</v>
@@ -25868,13 +25868,13 @@
         <v>1</v>
       </c>
       <c r="AX53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA53" t="n">
         <v>1</v>
@@ -25886,7 +25886,7 @@
         <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BE53" t="n">
         <v>0</v>
@@ -25901,28 +25901,28 @@
         <v>1</v>
       </c>
       <c r="BI53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BJ53" t="n">
         <v>1</v>
       </c>
       <c r="BK53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BL53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BN53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ53" t="n">
         <v>0</v>
@@ -25931,7 +25931,7 @@
         <v>2</v>
       </c>
       <c r="BS53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT53" t="n">
         <v>2</v>
@@ -25940,139 +25940,139 @@
         <v>1</v>
       </c>
       <c r="BV53" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="BW53" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BX53" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="BY53" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CB53" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR53" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS53" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU53" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV53" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX53" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY53" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ53" t="n">
         <v>59</v>
       </c>
-      <c r="BZ53" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CA53" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB53" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="CC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS53" t="n">
+      <c r="DA53" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB53" t="n">
         <v>17</v>
       </c>
-      <c r="CT53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU53" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV53" t="n">
-        <v>19</v>
-      </c>
-      <c r="CW53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX53" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY53" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ53" t="n">
+      <c r="DC53" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD53" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DE53" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DF53" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH53" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ53" t="n">
         <v>42</v>
       </c>
-      <c r="DA53" t="n">
-        <v>67</v>
-      </c>
-      <c r="DB53" t="n">
+      <c r="DK53" t="n">
         <v>42</v>
       </c>
-      <c r="DC53" t="n">
-        <v>67</v>
-      </c>
-      <c r="DD53" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DE53" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF53" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DH53" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DI53" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DJ53" t="n">
-        <v>59</v>
-      </c>
-      <c r="DK53" t="n">
-        <v>34</v>
-      </c>
       <c r="DL53" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="DM53" t="n">
-        <v>1.18</v>
+        <v>0.47</v>
       </c>
       <c r="DN53" t="n">
-        <v>2.61</v>
+        <v>1.62</v>
       </c>
       <c r="DO53" t="n">
         <v>18</v>
@@ -26084,10 +26084,10 @@
         <v>1</v>
       </c>
       <c r="DR53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT53" t="b">
         <v>0</v>
@@ -26099,79 +26099,75 @@
         <v>1</v>
       </c>
       <c r="DW53" t="n">
-        <v>17.43</v>
+        <v>20.5</v>
       </c>
       <c r="DX53" t="n">
-        <v>4.72</v>
+        <v>6.93</v>
       </c>
       <c r="DY53" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="DZ53" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA53" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EB53" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC53" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC53" t="inlineStr"/>
       <c r="ED53" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EE53" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF53" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EG53" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EH53" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EI53" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EJ53" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EK53" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EL53" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EM53" t="inlineStr">
@@ -26186,12 +26182,12 @@
       </c>
       <c r="EO53" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP53" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -26211,40 +26207,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>8</v>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -26253,101 +26249,101 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T54" t="n">
         <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W54" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="X54" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y54" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="Z54" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>San Mamés Barria</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="AF54" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="AG54" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AI54" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AJ54" t="n">
-        <v>4.05</v>
+        <v>3.08</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AN54" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AO54" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AR54" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AU54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV54" t="n">
         <v>0</v>
@@ -26356,13 +26352,13 @@
         <v>1</v>
       </c>
       <c r="AX54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA54" t="n">
         <v>1</v>
@@ -26374,7 +26370,7 @@
         <v>0</v>
       </c>
       <c r="BD54" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BE54" t="n">
         <v>0</v>
@@ -26389,28 +26385,28 @@
         <v>1</v>
       </c>
       <c r="BI54" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BJ54" t="n">
         <v>1</v>
       </c>
       <c r="BK54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BN54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ54" t="n">
         <v>0</v>
@@ -26419,7 +26415,7 @@
         <v>2</v>
       </c>
       <c r="BS54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT54" t="n">
         <v>2</v>
@@ -26428,25 +26424,25 @@
         <v>1</v>
       </c>
       <c r="BV54" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="BW54" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BX54" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="BY54" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="BZ54" t="n">
-        <v>2.59</v>
+        <v>1.96</v>
       </c>
       <c r="CA54" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="CB54" t="n">
-        <v>3.26</v>
+        <v>2.71</v>
       </c>
       <c r="CC54" t="n">
         <v>0</v>
@@ -26476,10 +26472,10 @@
         <v>0</v>
       </c>
       <c r="CL54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN54" t="n">
         <v>0</v>
@@ -26494,19 +26490,19 @@
         <v>1</v>
       </c>
       <c r="CR54" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="CS54" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CT54" t="n">
         <v>1</v>
       </c>
       <c r="CU54" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="CV54" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="CW54" t="n">
         <v>1</v>
@@ -26515,55 +26511,55 @@
         <v>3</v>
       </c>
       <c r="CY54" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CZ54" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA54" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB54" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC54" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD54" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE54" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF54" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DI54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DJ54" t="n">
         <v>59</v>
       </c>
-      <c r="DA54" t="n">
-        <v>59</v>
-      </c>
-      <c r="DB54" t="n">
-        <v>17</v>
-      </c>
-      <c r="DC54" t="n">
-        <v>84</v>
-      </c>
-      <c r="DD54" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="DE54" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DF54" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH54" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI54" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DJ54" t="n">
-        <v>42</v>
-      </c>
       <c r="DK54" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="DL54" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="DM54" t="n">
-        <v>0.47</v>
+        <v>1.18</v>
       </c>
       <c r="DN54" t="n">
-        <v>1.62</v>
+        <v>2.61</v>
       </c>
       <c r="DO54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26572,10 +26568,10 @@
         <v>1</v>
       </c>
       <c r="DR54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT54" t="b">
         <v>0</v>
@@ -26587,75 +26583,79 @@
         <v>1</v>
       </c>
       <c r="DW54" t="n">
-        <v>20.5</v>
+        <v>17.43</v>
       </c>
       <c r="DX54" t="n">
-        <v>6.93</v>
+        <v>4.72</v>
       </c>
       <c r="DY54" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="DZ54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="EA54" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EB54" t="inlineStr">
         <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC54" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="ED54" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE54" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="EC54" t="inlineStr"/>
-      <c r="ED54" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EE54" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="EF54" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EG54" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="EH54" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="EI54" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="EJ54" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EK54" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EL54" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EM54" t="inlineStr">
@@ -26670,12 +26670,12 @@
       </c>
       <c r="EO54" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EP54" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -26695,12 +26695,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
@@ -26710,149 +26710,149 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="n">
+        <v>6</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2</v>
+      </c>
+      <c r="R55" t="n">
         <v>5</v>
       </c>
-      <c r="J55" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" t="n">
+      <c r="S55" t="n">
+        <v>14</v>
+      </c>
+      <c r="T55" t="n">
         <v>7</v>
       </c>
-      <c r="L55" t="n">
-        <v>8</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>2</v>
-      </c>
-      <c r="R55" t="n">
-        <v>10</v>
-      </c>
-      <c r="S55" t="n">
-        <v>9</v>
-      </c>
-      <c r="T55" t="n">
-        <v>14</v>
-      </c>
       <c r="U55" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V55" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="W55" t="n">
         <v>17</v>
       </c>
       <c r="X55" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y55" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="Z55" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Estadio Ciudad de Valencia</t>
+          <t>Estadio Ramón Sánchez Pizjuán</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Calle San Vicente de Paúl 44, Valencia</t>
+          <t>Avenida de Eduardo Dato, Sevilla</t>
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE55" t="n">
-        <v>8</v>
+        <v>3.15</v>
       </c>
       <c r="AF55" t="n">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI55" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT55" t="n">
         <v>1.4</v>
       </c>
-      <c r="AJ55" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AU55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV55" t="n">
         <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX55" t="n">
         <v>1</v>
       </c>
       <c r="AY55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB55" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="BC55" t="n">
         <v>0</v>
@@ -26873,76 +26873,76 @@
         <v>1</v>
       </c>
       <c r="BI55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT55" t="n">
         <v>5</v>
       </c>
-      <c r="BK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL55" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM55" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN55" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ55" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR55" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT55" t="n">
-        <v>2</v>
-      </c>
       <c r="BU55" t="n">
         <v>1</v>
       </c>
       <c r="BV55" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="BW55" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="BX55" t="n">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="BY55" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="BZ55" t="n">
-        <v>1.02</v>
+        <v>1.67</v>
       </c>
       <c r="CA55" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="CB55" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="CC55" t="n">
         <v>0</v>
       </c>
       <c r="CD55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE55" t="n">
         <v>0</v>
       </c>
       <c r="CF55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG55" t="n">
         <v>0</v>
@@ -26966,7 +26966,7 @@
         <v>0</v>
       </c>
       <c r="CN55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO55" t="n">
         <v>0</v>
@@ -26978,76 +26978,76 @@
         <v>1</v>
       </c>
       <c r="CR55" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="CS55" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="CT55" t="n">
         <v>1</v>
       </c>
       <c r="CU55" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV55" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX55" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY55" t="n">
         <v>9</v>
       </c>
-      <c r="CV55" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW55" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX55" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY55" t="n">
-        <v>3</v>
-      </c>
       <c r="CZ55" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA55" t="n">
         <v>100</v>
       </c>
       <c r="DB55" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC55" t="n">
         <v>75</v>
       </c>
-      <c r="DC55" t="n">
-        <v>100</v>
-      </c>
       <c r="DD55" t="n">
-        <v>0.29</v>
+        <v>1.11</v>
       </c>
       <c r="DE55" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DF55" t="n">
         <v>0.5</v>
       </c>
       <c r="DG55" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DH55" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ55" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK55" t="n">
         <v>0</v>
       </c>
       <c r="DL55" t="n">
-        <v>0.84</v>
+        <v>1.24</v>
       </c>
       <c r="DM55" t="n">
-        <v>2.34</v>
+        <v>0.93</v>
       </c>
       <c r="DN55" t="n">
-        <v>3.18</v>
+        <v>2.17</v>
       </c>
       <c r="DO55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27059,10 +27059,10 @@
         <v>1</v>
       </c>
       <c r="DS55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU55" t="b">
         <v>0</v>
@@ -27071,87 +27071,99 @@
         <v>1</v>
       </c>
       <c r="DW55" t="n">
-        <v>22.21</v>
+        <v>27.52</v>
       </c>
       <c r="DX55" t="n">
-        <v>8.289999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="DY55" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="DZ55" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA55" t="inlineStr">
         <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EB55" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EB55" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
       <c r="EC55" t="inlineStr">
         <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="ED55" t="inlineStr"/>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="ED55" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="EE55" t="inlineStr">
         <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EF55" t="inlineStr"/>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EF55" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
       <c r="EG55" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EH55" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EI55" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EJ55" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EK55" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EL55" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EM55" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EN55" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EO55" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EP55" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -27171,12 +27183,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -27186,25 +27198,25 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -27216,119 +27228,119 @@
         <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S56" t="n">
+        <v>9</v>
+      </c>
+      <c r="T56" t="n">
         <v>14</v>
       </c>
-      <c r="T56" t="n">
-        <v>7</v>
-      </c>
       <c r="U56" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V56" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="W56" t="n">
         <v>17</v>
       </c>
       <c r="X56" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Y56" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="Z56" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Estadio Ramón Sánchez Pizjuán</t>
+          <t>Estadio Ciudad de Valencia</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Avenida de Eduardo Dato, Sevilla</t>
+          <t>Calle San Vicente de Paúl 44, Valencia</t>
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE56" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="AF56" t="n">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="AG56" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI56" t="n">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="AJ56" t="n">
-        <v>3.4</v>
+        <v>2.07</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL56" t="n">
         <v>2</v>
       </c>
       <c r="AM56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN56" t="n">
         <v>1.5</v>
       </c>
-      <c r="AN56" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AO56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP56" t="n">
         <v>2.38</v>
       </c>
-      <c r="AP56" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AQ56" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AR56" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.72</v>
+        <v>4.05</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AU56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV56" t="n">
         <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX56" t="n">
         <v>1</v>
       </c>
       <c r="AY56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB56" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="BC56" t="n">
         <v>0</v>
@@ -27349,76 +27361,76 @@
         <v>1</v>
       </c>
       <c r="BI56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL56" t="n">
         <v>2</v>
       </c>
       <c r="BM56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BN56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO56" t="n">
         <v>0</v>
       </c>
       <c r="BP56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU56" t="n">
         <v>1</v>
       </c>
       <c r="BV56" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="BW56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="BX56" t="n">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="BY56" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="BZ56" t="n">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
       <c r="CA56" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="CB56" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="CC56" t="n">
         <v>0</v>
       </c>
       <c r="CD56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE56" t="n">
         <v>0</v>
       </c>
       <c r="CF56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG56" t="n">
         <v>0</v>
@@ -27442,7 +27454,7 @@
         <v>0</v>
       </c>
       <c r="CN56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO56" t="n">
         <v>0</v>
@@ -27454,73 +27466,73 @@
         <v>1</v>
       </c>
       <c r="CR56" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="CS56" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="CT56" t="n">
         <v>1</v>
       </c>
       <c r="CU56" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="CV56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CW56" t="n">
         <v>1</v>
       </c>
       <c r="CX56" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY56" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CZ56" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA56" t="n">
         <v>100</v>
       </c>
       <c r="DB56" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="DC56" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.11</v>
+        <v>0.29</v>
       </c>
       <c r="DE56" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF56" t="n">
         <v>0.5</v>
       </c>
       <c r="DG56" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DH56" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="DI56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ56" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK56" t="n">
         <v>0</v>
       </c>
       <c r="DL56" t="n">
-        <v>1.24</v>
+        <v>0.84</v>
       </c>
       <c r="DM56" t="n">
-        <v>0.93</v>
+        <v>2.34</v>
       </c>
       <c r="DN56" t="n">
-        <v>2.17</v>
+        <v>3.18</v>
       </c>
       <c r="DO56" t="n">
         <v>17</v>
@@ -27535,10 +27547,10 @@
         <v>1</v>
       </c>
       <c r="DS56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU56" t="b">
         <v>0</v>
@@ -27547,99 +27559,87 @@
         <v>1</v>
       </c>
       <c r="DW56" t="n">
-        <v>27.52</v>
+        <v>22.21</v>
       </c>
       <c r="DX56" t="n">
-        <v>3.08</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DY56" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ56" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="EA56" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EB56" t="inlineStr"/>
+      <c r="EC56" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="ED56" t="inlineStr"/>
+      <c r="EE56" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF56" t="inlineStr"/>
+      <c r="EG56" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH56" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI56" t="inlineStr">
+        <is>
+          <t>5.86</t>
+        </is>
+      </c>
+      <c r="EJ56" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="EK56" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL56" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EB56" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EC56" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="ED56" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EE56" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EF56" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EG56" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EH56" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EI56" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EJ56" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="EK56" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EL56" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
       <c r="EM56" t="inlineStr">
         <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN56" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EO56" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EP56" t="inlineStr">
+        <is>
           <t>1.68</t>
-        </is>
-      </c>
-      <c r="EN56" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EO56" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EP56" t="inlineStr">
-        <is>
-          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -27978,10 +27978,10 @@
         <v>75</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF57" t="n">
         <v>3</v>
@@ -28011,7 +28011,7 @@
         <v>2.1</v>
       </c>
       <c r="DO57" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28127,40 +28127,40 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>45924.8125</v>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L58" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -28169,128 +28169,128 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R58" t="n">
         <v>3</v>
       </c>
       <c r="S58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U58" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="V58" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W58" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="X58" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y58" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Z58" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Estadio Wanda Metropolitano</t>
+          <t>Estadio Municipal de Anoeta</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Rosas, Madrid</t>
+          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
         </is>
       </c>
       <c r="AC58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF58" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AG58" t="n">
-        <v>6.5</v>
+        <v>5.13</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AJ58" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AL58" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AM58" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AN58" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AO58" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AP58" t="n">
         <v>1.99</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AR58" t="n">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="AS58" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AU58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB58" t="n">
-        <v>117</v>
+        <v>290</v>
       </c>
       <c r="BC58" t="n">
         <v>0</v>
       </c>
       <c r="BD58" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="BE58" t="n">
         <v>0</v>
@@ -28305,10 +28305,10 @@
         <v>1</v>
       </c>
       <c r="BI58" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BJ58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BK58" t="n">
         <v>4</v>
@@ -28317,52 +28317,52 @@
         <v>2</v>
       </c>
       <c r="BM58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BN58" t="n">
         <v>6</v>
       </c>
       <c r="BO58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BS58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT58" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BU58" t="n">
         <v>1</v>
       </c>
       <c r="BV58" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="BW58" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="BX58" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="BY58" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="BZ58" t="n">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="CA58" t="n">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="CB58" t="n">
-        <v>3.33</v>
+        <v>2.69</v>
       </c>
       <c r="CC58" t="n">
         <v>0</v>
@@ -28395,7 +28395,7 @@
         <v>0</v>
       </c>
       <c r="CM58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN58" t="n">
         <v>0</v>
@@ -28413,70 +28413,70 @@
         <v>22</v>
       </c>
       <c r="CS58" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CT58" t="n">
         <v>1</v>
       </c>
       <c r="CU58" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CV58" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="CW58" t="n">
         <v>1</v>
       </c>
       <c r="CX58" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="CY58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CZ58" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="DA58" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DB58" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="DC58" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>2.78</v>
+        <v>1.22</v>
       </c>
       <c r="DE58" t="n">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF58" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="DG58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH58" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="DI58" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="DJ58" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="DK58" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL58" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="DM58" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="DN58" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="DO58" t="n">
         <v>18</v>
@@ -28485,117 +28485,97 @@
         <v>1</v>
       </c>
       <c r="DQ58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU58" t="b">
         <v>0</v>
       </c>
       <c r="DV58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW58" t="n">
-        <v>18.88</v>
+        <v>13.25</v>
       </c>
       <c r="DX58" t="n">
-        <v>6.34</v>
+        <v>3.2</v>
       </c>
       <c r="DY58" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="DZ58" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EA58" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EB58" t="inlineStr">
         <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EC58" t="inlineStr">
-        <is>
-          <t>3.42</t>
-        </is>
-      </c>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EC58" t="inlineStr"/>
       <c r="ED58" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EE58" t="inlineStr">
+        <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="EE58" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
       <c r="EF58" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EG58" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EH58" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="EI58" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="EJ58" t="inlineStr">
         <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EK58" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="EL58" t="inlineStr">
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EK58" t="inlineStr"/>
+      <c r="EL58" t="inlineStr"/>
+      <c r="EM58" t="inlineStr"/>
+      <c r="EN58" t="inlineStr"/>
+      <c r="EO58" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EP58" t="inlineStr">
         <is>
           <t>2.06</t>
-        </is>
-      </c>
-      <c r="EM58" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EN58" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="EO58" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EP58" t="inlineStr">
-        <is>
-          <t>2.18</t>
         </is>
       </c>
     </row>
@@ -28615,40 +28595,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
         <v>45924.8125</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L59" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -28657,128 +28637,128 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R59" t="n">
         <v>3</v>
       </c>
       <c r="S59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U59" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="V59" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W59" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="X59" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y59" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="Z59" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Anoeta</t>
+          <t>Estadio Wanda Metropolitano</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
+          <t>Rosas, Madrid</t>
         </is>
       </c>
       <c r="AC59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF59" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG59" t="n">
-        <v>5.13</v>
+        <v>6.5</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AI59" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AJ59" t="n">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AL59" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AM59" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AN59" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AO59" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AP59" t="n">
         <v>1.99</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AR59" t="n">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="AS59" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AT59" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AU59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB59" t="n">
-        <v>290</v>
+        <v>117</v>
       </c>
       <c r="BC59" t="n">
         <v>0</v>
       </c>
       <c r="BD59" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="BE59" t="n">
         <v>0</v>
@@ -28793,10 +28773,10 @@
         <v>1</v>
       </c>
       <c r="BI59" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BJ59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK59" t="n">
         <v>4</v>
@@ -28805,52 +28785,52 @@
         <v>2</v>
       </c>
       <c r="BM59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BN59" t="n">
         <v>6</v>
       </c>
       <c r="BO59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BS59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT59" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BU59" t="n">
         <v>1</v>
       </c>
       <c r="BV59" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="BW59" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="BX59" t="n">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="BY59" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="BZ59" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="CA59" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="CB59" t="n">
-        <v>2.69</v>
+        <v>3.33</v>
       </c>
       <c r="CC59" t="n">
         <v>0</v>
@@ -28883,7 +28863,7 @@
         <v>0</v>
       </c>
       <c r="CM59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN59" t="n">
         <v>0</v>
@@ -28901,70 +28881,70 @@
         <v>22</v>
       </c>
       <c r="CS59" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CT59" t="n">
         <v>1</v>
       </c>
       <c r="CU59" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CV59" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="CW59" t="n">
         <v>1</v>
       </c>
       <c r="CX59" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CZ59" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="DA59" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="DB59" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="DC59" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.22</v>
+        <v>2.78</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="DF59" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DG59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DH59" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="DI59" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="DJ59" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="DK59" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DL59" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="DM59" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="DN59" t="n">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="DO59" t="n">
         <v>18</v>
@@ -28973,97 +28953,117 @@
         <v>1</v>
       </c>
       <c r="DQ59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU59" t="b">
         <v>0</v>
       </c>
       <c r="DV59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW59" t="n">
-        <v>13.25</v>
+        <v>18.88</v>
       </c>
       <c r="DX59" t="n">
-        <v>3.2</v>
+        <v>6.34</v>
       </c>
       <c r="DY59" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="DZ59" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="EA59" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB59" t="inlineStr">
         <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EC59" t="inlineStr"/>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC59" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
       <c r="ED59" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EE59" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EF59" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EG59" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EH59" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="EI59" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="EJ59" t="inlineStr">
         <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EK59" t="inlineStr"/>
-      <c r="EL59" t="inlineStr"/>
-      <c r="EM59" t="inlineStr"/>
-      <c r="EN59" t="inlineStr"/>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EK59" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EL59" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EM59" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EN59" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
       <c r="EO59" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EP59" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.18</t>
         </is>
       </c>
     </row>
@@ -29870,7 +29870,7 @@
         <v>100</v>
       </c>
       <c r="DD61" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE61" t="n">
         <v>2.2</v>
@@ -29903,7 +29903,7 @@
         <v>3.12</v>
       </c>
       <c r="DO61" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30338,7 +30338,7 @@
         <v>100</v>
       </c>
       <c r="DD62" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DE62" t="n">
         <v>1.75</v>
@@ -30826,7 +30826,7 @@
         <v>59</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE63" t="n">
         <v>1.1</v>
@@ -31765,7 +31765,7 @@
         <v>1.44</v>
       </c>
       <c r="DE65" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF65" t="n">
         <v>0.67</v>
@@ -32230,7 +32230,7 @@
         <v>50</v>
       </c>
       <c r="DD66" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE66" t="n">
         <v>0.89</v>
@@ -32263,7 +32263,7 @@
         <v>4.16</v>
       </c>
       <c r="DO66" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -33621,7 +33621,7 @@
         <v>3</v>
       </c>
       <c r="DE69" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF69" t="n">
         <v>3</v>
@@ -33651,7 +33651,7 @@
         <v>3.83</v>
       </c>
       <c r="DO69" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34081,7 +34081,7 @@
         <v>1.78</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF70" t="n">
         <v>2</v>
@@ -34111,7 +34111,7 @@
         <v>2.27</v>
       </c>
       <c r="DO70" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -35079,7 +35079,7 @@
         <v>2.29</v>
       </c>
       <c r="DO72" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35522,7 +35522,7 @@
         <v>88</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE73" t="n">
         <v>1.1</v>
@@ -36010,7 +36010,7 @@
         <v>88</v>
       </c>
       <c r="DD74" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DE74" t="n">
         <v>0.33</v>
@@ -36999,7 +36999,7 @@
         <v>3.16</v>
       </c>
       <c r="DO76" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -38365,7 +38365,7 @@
         <v>1.9</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF79" t="n">
         <v>2.5</v>
@@ -39794,7 +39794,7 @@
         <v>84</v>
       </c>
       <c r="DD82" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE82" t="n">
         <v>1.75</v>
@@ -40771,7 +40771,7 @@
         <v>3.49</v>
       </c>
       <c r="DO84" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41198,10 +41198,10 @@
         <v>88</v>
       </c>
       <c r="DD85" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF85" t="n">
         <v>3</v>
@@ -41231,7 +41231,7 @@
         <v>3.94</v>
       </c>
       <c r="DO85" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41673,7 +41673,7 @@
         <v>2.78</v>
       </c>
       <c r="DE86" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF86" t="n">
         <v>2.5</v>
@@ -41703,7 +41703,7 @@
         <v>2.53</v>
       </c>
       <c r="DO86" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42621,7 +42621,7 @@
         <v>1.1</v>
       </c>
       <c r="DE88" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF88" t="n">
         <v>0.8</v>
@@ -43578,7 +43578,7 @@
         <v>84</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE90" t="n">
         <v>2.1</v>
@@ -43611,7 +43611,7 @@
         <v>3.13</v>
       </c>
       <c r="DO90" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -45006,7 +45006,7 @@
         <v>90</v>
       </c>
       <c r="DD93" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DE93" t="n">
         <v>0.5600000000000001</v>
@@ -45039,7 +45039,7 @@
         <v>2.1</v>
       </c>
       <c r="DO93" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -46011,7 +46011,7 @@
         <v>2.58</v>
       </c>
       <c r="DO95" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46487,7 +46487,7 @@
         <v>2.51</v>
       </c>
       <c r="DO96" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -48361,7 +48361,7 @@
         <v>1.13</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF100" t="n">
         <v>0.67</v>
@@ -48851,7 +48851,7 @@
         <v>3</v>
       </c>
       <c r="DO101" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -49290,7 +49290,7 @@
         <v>75</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE102" t="n">
         <v>1</v>
@@ -49323,7 +49323,7 @@
         <v>2.07</v>
       </c>
       <c r="DO102" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -49758,7 +49758,7 @@
         <v>74</v>
       </c>
       <c r="DD103" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE103" t="n">
         <v>1</v>
@@ -49791,7 +49791,7 @@
         <v>3.29</v>
       </c>
       <c r="DO103" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50735,7 +50735,7 @@
         <v>2.92</v>
       </c>
       <c r="DO105" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -53542,10 +53542,10 @@
         <v>60</v>
       </c>
       <c r="DD111" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE111" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF111" t="n">
         <v>0.6</v>
@@ -53575,7 +53575,7 @@
         <v>1.9</v>
       </c>
       <c r="DO111" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP111" t="b">
         <v>0</v>
@@ -54021,7 +54021,7 @@
         <v>1.9</v>
       </c>
       <c r="DE112" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF112" t="n">
         <v>2.2</v>
@@ -54502,10 +54502,10 @@
         <v>62</v>
       </c>
       <c r="DD113" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DE113" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF113" t="n">
         <v>0.83</v>
@@ -54535,7 +54535,7 @@
         <v>2.36</v>
       </c>
       <c r="DO113" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -54989,7 +54989,7 @@
         <v>1.11</v>
       </c>
       <c r="DE114" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF114" t="n">
         <v>0.8</v>
@@ -55947,7 +55947,7 @@
         <v>2.69</v>
       </c>
       <c r="DO116" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -56435,7 +56435,7 @@
         <v>2.5</v>
       </c>
       <c r="DO117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -57011,12 +57011,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F119" s="2" t="n">
@@ -57026,25 +57026,25 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K119" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L119" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M119" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -57056,131 +57056,123 @@
         <v>4</v>
       </c>
       <c r="R119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S119" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T119" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U119" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="V119" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W119" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X119" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y119" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Z119" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>Estadio de Mestalla</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>Avenida de Suecia, Valencia</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE119" t="n">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="AF119" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="AG119" t="n">
-        <v>2.15</v>
+        <v>2.98</v>
       </c>
       <c r="AH119" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AI119" t="n">
-        <v>1.91</v>
+        <v>3.04</v>
       </c>
       <c r="AJ119" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="AK119" t="n">
-        <v>1.72</v>
+        <v>2.43</v>
       </c>
       <c r="AL119" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AM119" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="AN119" t="n">
-        <v>1.84</v>
+        <v>2.87</v>
       </c>
       <c r="AO119" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="AR119" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="AS119" t="n">
-        <v>2.89</v>
+        <v>2.05</v>
       </c>
       <c r="AT119" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AU119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW119" t="n">
         <v>0</v>
       </c>
       <c r="AX119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB119" t="n">
-        <v>-1</v>
+        <v>298</v>
       </c>
       <c r="BC119" t="n">
         <v>0</v>
       </c>
       <c r="BD119" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="BE119" t="n">
         <v>0</v>
       </c>
       <c r="BF119" t="n">
-        <v>45820</v>
+        <v>17507</v>
       </c>
       <c r="BG119" t="n">
         <v>2</v>
@@ -57189,64 +57181,64 @@
         <v>1</v>
       </c>
       <c r="BI119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ119" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BK119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL119" t="n">
         <v>6</v>
       </c>
-      <c r="BL119" t="n">
-        <v>1</v>
-      </c>
       <c r="BM119" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BN119" t="n">
         <v>7</v>
       </c>
       <c r="BO119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR119" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BS119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT119" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BU119" t="n">
         <v>1</v>
       </c>
       <c r="BV119" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="BW119" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="BX119" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="BY119" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="BZ119" t="n">
-        <v>1.74</v>
+        <v>0.96</v>
       </c>
       <c r="CA119" t="n">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="CB119" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="CC119" t="n">
         <v>0</v>
@@ -57279,10 +57271,10 @@
         <v>0</v>
       </c>
       <c r="CM119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO119" t="n">
         <v>0</v>
@@ -57294,19 +57286,19 @@
         <v>1</v>
       </c>
       <c r="CR119" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="CS119" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="CT119" t="n">
         <v>1</v>
       </c>
       <c r="CU119" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CV119" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CW119" t="n">
         <v>1</v>
@@ -57315,52 +57307,52 @@
         <v>6</v>
       </c>
       <c r="CY119" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CZ119" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="DA119" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="DB119" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="DC119" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="DD119" t="n">
         <v>1.44</v>
       </c>
       <c r="DE119" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DF119" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG119" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="DH119" t="n">
         <v>0.82</v>
       </c>
       <c r="DI119" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="DJ119" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="DK119" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="DL119" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="DM119" t="n">
-        <v>1.6</v>
+        <v>0.97</v>
       </c>
       <c r="DN119" t="n">
-        <v>3.06</v>
+        <v>2.18</v>
       </c>
       <c r="DO119" t="n">
         <v>18</v>
@@ -57369,7 +57361,7 @@
         <v>1</v>
       </c>
       <c r="DQ119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR119" t="b">
         <v>0</v>
@@ -57384,102 +57376,90 @@
         <v>0</v>
       </c>
       <c r="DV119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW119" t="n">
-        <v>17.01</v>
+        <v>17.48</v>
       </c>
       <c r="DX119" t="n">
-        <v>5.56</v>
+        <v>5.64</v>
       </c>
       <c r="DY119" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="DZ119" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="EA119" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="EB119" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC119" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr"/>
       <c r="ED119" t="inlineStr">
         <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EE119" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EE119" t="inlineStr"/>
       <c r="EF119" t="inlineStr">
         <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="EG119" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EG119" t="inlineStr"/>
       <c r="EH119" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EI119" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EJ119" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EK119" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="EL119" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EM119" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EN119" t="inlineStr">
+        <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="EM119" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EN119" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
       <c r="EO119" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EP119" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.43</t>
         </is>
       </c>
     </row>
@@ -57499,12 +57479,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F120" s="2" t="n">
@@ -57514,25 +57494,25 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K120" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L120" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -57544,189 +57524,197 @@
         <v>4</v>
       </c>
       <c r="R120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S120" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T120" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U120" t="n">
+        <v>17</v>
+      </c>
+      <c r="V120" t="n">
+        <v>9</v>
+      </c>
+      <c r="W120" t="n">
+        <v>13</v>
+      </c>
+      <c r="X120" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>Avenida de Suecia, Valencia</t>
+        </is>
+      </c>
+      <c r="AC120" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>45820</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK120" t="n">
         <v>6</v>
       </c>
-      <c r="V120" t="n">
-        <v>14</v>
-      </c>
-      <c r="W120" t="n">
-        <v>15</v>
-      </c>
-      <c r="X120" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y120" t="n">
-        <v>39</v>
-      </c>
-      <c r="Z120" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA120" t="inlineStr"/>
-      <c r="AB120" t="inlineStr"/>
-      <c r="AC120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD120" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE120" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AF120" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AG120" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AH120" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AI120" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AJ120" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AK120" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AL120" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM120" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AN120" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AO120" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AP120" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AQ120" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AR120" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AS120" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT120" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AU120" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV120" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ120" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA120" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB120" t="n">
-        <v>298</v>
-      </c>
-      <c r="BC120" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD120" t="n">
-        <v>47</v>
-      </c>
-      <c r="BE120" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF120" t="n">
-        <v>17507</v>
-      </c>
-      <c r="BG120" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH120" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI120" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ120" t="n">
-        <v>8</v>
-      </c>
-      <c r="BK120" t="n">
-        <v>1</v>
-      </c>
       <c r="BL120" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BM120" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BN120" t="n">
         <v>7</v>
       </c>
       <c r="BO120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BR120" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BS120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT120" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BU120" t="n">
         <v>1</v>
       </c>
       <c r="BV120" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="BW120" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="BX120" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="BY120" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="BZ120" t="n">
-        <v>0.96</v>
+        <v>1.74</v>
       </c>
       <c r="CA120" t="n">
-        <v>1.63</v>
+        <v>1.09</v>
       </c>
       <c r="CB120" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="CC120" t="n">
         <v>0</v>
@@ -57759,10 +57747,10 @@
         <v>0</v>
       </c>
       <c r="CM120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO120" t="n">
         <v>0</v>
@@ -57774,19 +57762,19 @@
         <v>1</v>
       </c>
       <c r="CR120" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="CS120" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="CT120" t="n">
         <v>1</v>
       </c>
       <c r="CU120" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CV120" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CW120" t="n">
         <v>1</v>
@@ -57795,52 +57783,52 @@
         <v>6</v>
       </c>
       <c r="CY120" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CZ120" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="DA120" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="DB120" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="DC120" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="DD120" t="n">
         <v>1.44</v>
       </c>
       <c r="DE120" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="DF120" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG120" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DH120" t="n">
         <v>0.82</v>
       </c>
       <c r="DI120" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="DJ120" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="DK120" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="DL120" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="DM120" t="n">
-        <v>0.97</v>
+        <v>1.6</v>
       </c>
       <c r="DN120" t="n">
-        <v>2.18</v>
+        <v>3.06</v>
       </c>
       <c r="DO120" t="n">
         <v>18</v>
@@ -57849,7 +57837,7 @@
         <v>1</v>
       </c>
       <c r="DQ120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR120" t="b">
         <v>0</v>
@@ -57864,90 +57852,102 @@
         <v>0</v>
       </c>
       <c r="DV120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW120" t="n">
-        <v>17.48</v>
+        <v>17.01</v>
       </c>
       <c r="DX120" t="n">
-        <v>5.64</v>
+        <v>5.56</v>
       </c>
       <c r="DY120" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="DZ120" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="EA120" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB120" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EC120" t="inlineStr"/>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC120" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
       <c r="ED120" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EE120" t="inlineStr"/>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE120" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
       <c r="EF120" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="EG120" t="inlineStr"/>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EG120" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EH120" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EI120" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EJ120" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EK120" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EL120" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EM120" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EN120" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EO120" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EP120" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.76</t>
         </is>
       </c>
     </row>
@@ -60141,7 +60141,7 @@
         <v>1.89</v>
       </c>
       <c r="DE125" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF125" t="n">
         <v>2</v>
@@ -60171,7 +60171,7 @@
         <v>2.9</v>
       </c>
       <c r="DO125" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -60606,7 +60606,7 @@
         <v>83</v>
       </c>
       <c r="DD126" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE126" t="n">
         <v>0.5600000000000001</v>
@@ -60639,7 +60639,7 @@
         <v>3.29</v>
       </c>
       <c r="DO126" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -61074,7 +61074,7 @@
         <v>69</v>
       </c>
       <c r="DD127" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE127" t="n">
         <v>1</v>
@@ -61583,7 +61583,7 @@
         <v>2.72</v>
       </c>
       <c r="DO128" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -62010,7 +62010,7 @@
         <v>60</v>
       </c>
       <c r="DD129" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE129" t="n">
         <v>1.3</v>
@@ -62043,7 +62043,7 @@
         <v>2.46</v>
       </c>
       <c r="DO129" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -63434,7 +63434,7 @@
         <v>50</v>
       </c>
       <c r="DD132" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE132" t="n">
         <v>0.38</v>
@@ -63905,7 +63905,7 @@
         <v>1.44</v>
       </c>
       <c r="DE133" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF133" t="n">
         <v>1.5</v>
@@ -64381,7 +64381,7 @@
         <v>3</v>
       </c>
       <c r="DE134" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF134" t="n">
         <v>3</v>
@@ -64411,7 +64411,7 @@
         <v>3.53</v>
       </c>
       <c r="DO134" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -65347,7 +65347,7 @@
         <v>2.87</v>
       </c>
       <c r="DO136" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -65827,7 +65827,7 @@
         <v>2.59</v>
       </c>
       <c r="DO137" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP137" t="b">
         <v>1</v>
@@ -66285,7 +66285,7 @@
         <v>1.11</v>
       </c>
       <c r="DE138" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF138" t="n">
         <v>1.17</v>
@@ -67234,7 +67234,7 @@
         <v>72</v>
       </c>
       <c r="DD140" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DE140" t="n">
         <v>2.1</v>
@@ -67267,7 +67267,7 @@
         <v>3.35</v>
       </c>
       <c r="DO140" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -69062,7 +69062,7 @@
         <v>72</v>
       </c>
       <c r="DD144" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE144" t="n">
         <v>0.5600000000000001</v>
@@ -69538,7 +69538,7 @@
         <v>79</v>
       </c>
       <c r="DD145" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE145" t="n">
         <v>1</v>
@@ -69571,7 +69571,7 @@
         <v>3.06</v>
       </c>
       <c r="DO145" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -70025,7 +70025,7 @@
         <v>1.5</v>
       </c>
       <c r="DE146" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF146" t="n">
         <v>1.57</v>
@@ -70055,7 +70055,7 @@
         <v>2.91</v>
       </c>
       <c r="DO146" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -70523,7 +70523,7 @@
         <v>4.01</v>
       </c>
       <c r="DO147" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -73855,7 +73855,7 @@
         <v>2.67</v>
       </c>
       <c r="DO154" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP154" t="b">
         <v>1</v>
@@ -75269,7 +75269,7 @@
         <v>3</v>
       </c>
       <c r="DE157" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF157" t="n">
         <v>3</v>
@@ -75299,7 +75299,7 @@
         <v>3.26</v>
       </c>
       <c r="DO157" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP157" t="b">
         <v>1</v>
@@ -75734,7 +75734,7 @@
         <v>40</v>
       </c>
       <c r="DD158" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE158" t="n">
         <v>1.75</v>
@@ -77203,7 +77203,7 @@
         <v>3.5</v>
       </c>
       <c r="DO161" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP161" t="b">
         <v>1</v>
@@ -77637,7 +77637,7 @@
         <v>1.13</v>
       </c>
       <c r="DE162" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF162" t="n">
         <v>1.17</v>
@@ -78590,7 +78590,7 @@
         <v>54</v>
       </c>
       <c r="DD164" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE164" t="n">
         <v>1.88</v>
@@ -79065,7 +79065,7 @@
         <v>0.29</v>
       </c>
       <c r="DE165" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DF165" t="n">
         <v>0.17</v>
@@ -79553,7 +79553,7 @@
         <v>1.89</v>
       </c>
       <c r="DE166" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF166" t="n">
         <v>1.86</v>
@@ -79583,7 +79583,7 @@
         <v>2.61</v>
       </c>
       <c r="DO166" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP166" t="b">
         <v>1</v>
@@ -80470,7 +80470,7 @@
         <v>76</v>
       </c>
       <c r="DD168" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DE168" t="n">
         <v>1.3</v>
@@ -80503,7 +80503,7 @@
         <v>2.48</v>
       </c>
       <c r="DO168" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP168" t="b">
         <v>1</v>
@@ -80958,7 +80958,7 @@
         <v>94</v>
       </c>
       <c r="DD169" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE169" t="n">
         <v>2.2</v>
@@ -80991,7 +80991,7 @@
         <v>4.09</v>
       </c>
       <c r="DO169" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP169" t="b">
         <v>1</v>
@@ -81927,7 +81927,7 @@
         <v>2.79</v>
       </c>
       <c r="DO171" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP171" t="b">
         <v>1</v>
@@ -83819,7 +83819,7 @@
         <v>2.87</v>
       </c>
       <c r="DO175" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP175" t="b">
         <v>1</v>
@@ -83991,13 +83991,13 @@
         <v>4</v>
       </c>
       <c r="S176" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T176" t="n">
         <v>8</v>
       </c>
       <c r="U176" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V176" t="n">
         <v>12</v>
@@ -84172,13 +84172,13 @@
         <v>51</v>
       </c>
       <c r="BZ176" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="CA176" t="n">
         <v>1.21</v>
       </c>
       <c r="CB176" t="n">
-        <v>3.01</v>
+        <v>3.07</v>
       </c>
       <c r="CC176" t="n">
         <v>0</v>
@@ -84295,7 +84295,7 @@
         <v>2.73</v>
       </c>
       <c r="DO176" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP176" t="b">
         <v>1</v>
@@ -85280,17 +85280,17 @@
       </c>
       <c r="EA178" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EB178" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="EC178" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="ED178" t="inlineStr"/>
@@ -85299,12 +85299,12 @@
       <c r="EG178" t="inlineStr"/>
       <c r="EH178" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="EI178" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="EJ178" t="inlineStr">
@@ -85314,24 +85314,24 @@
       </c>
       <c r="EK178" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EL178" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EM178" t="inlineStr"/>
       <c r="EN178" t="inlineStr"/>
       <c r="EO178" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EP178" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -85673,7 +85673,7 @@
         <v>2.67</v>
       </c>
       <c r="DE179" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF179" t="n">
         <v>2.63</v>
@@ -85703,7 +85703,7 @@
         <v>3.81</v>
       </c>
       <c r="DO179" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP179" t="b">
         <v>1</v>
@@ -85744,62 +85744,54 @@
       </c>
       <c r="EA179" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EB179" t="inlineStr"/>
       <c r="EC179" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="ED179" t="inlineStr"/>
-      <c r="EE179" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
+      <c r="EE179" t="inlineStr"/>
       <c r="EF179" t="inlineStr"/>
-      <c r="EG179" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
+      <c r="EG179" t="inlineStr"/>
       <c r="EH179" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="EI179" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="EJ179" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EK179" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EL179" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EM179" t="inlineStr"/>
       <c r="EN179" t="inlineStr"/>
       <c r="EO179" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="EP179" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
     </row>
@@ -86204,62 +86196,78 @@
       </c>
       <c r="EA180" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EB180" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EC180" t="inlineStr"/>
-      <c r="ED180" t="inlineStr"/>
-      <c r="EE180" t="inlineStr"/>
-      <c r="EF180" t="inlineStr"/>
-      <c r="EG180" t="inlineStr"/>
+      <c r="ED180" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EE180" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EF180" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EG180" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
       <c r="EH180" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EI180" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="EJ180" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EK180" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EL180" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EM180" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EN180" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EO180" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EP180" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.97</t>
         </is>
       </c>
     </row>
@@ -86327,13 +86335,13 @@
         <v>6</v>
       </c>
       <c r="S181" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T181" t="n">
         <v>12</v>
       </c>
       <c r="U181" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V181" t="n">
         <v>18</v>
@@ -86508,13 +86516,13 @@
         <v>106</v>
       </c>
       <c r="BZ181" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="CA181" t="n">
         <v>1.92</v>
       </c>
       <c r="CB181" t="n">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="CC181" t="n">
         <v>0</v>
@@ -86631,7 +86639,7 @@
         <v>2.22</v>
       </c>
       <c r="DO181" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP181" t="b">
         <v>1</v>
@@ -86672,12 +86680,12 @@
       </c>
       <c r="EA181" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="EB181" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EC181" t="inlineStr"/>
@@ -86687,47 +86695,47 @@
       <c r="EG181" t="inlineStr"/>
       <c r="EH181" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="EI181" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="EJ181" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EK181" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EL181" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EM181" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EN181" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EO181" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EP181" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.87</t>
         </is>
       </c>
     </row>
@@ -87099,7 +87107,7 @@
         <v>2.9</v>
       </c>
       <c r="DO182" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP182" t="b">
         <v>1</v>
@@ -87140,82 +87148,1990 @@
       </c>
       <c r="EA182" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EB182" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EC182" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="ED182" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EE182" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EF182" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EG182" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EH182" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EI182" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="EJ182" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="EK182" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EL182" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EM182" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EN182" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EO182" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EP182" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>19</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Getafe CF</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>46031.83333333334</v>
+      </c>
+      <c r="G183" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" t="n">
+        <v>2</v>
+      </c>
+      <c r="I183" t="n">
+        <v>3</v>
+      </c>
+      <c r="J183" t="n">
+        <v>2</v>
+      </c>
+      <c r="K183" t="n">
+        <v>4</v>
+      </c>
+      <c r="L183" t="n">
+        <v>6</v>
+      </c>
+      <c r="M183" t="n">
+        <v>2</v>
+      </c>
+      <c r="N183" t="n">
+        <v>1</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>3</v>
+      </c>
+      <c r="R183" t="n">
+        <v>5</v>
+      </c>
+      <c r="S183" t="n">
+        <v>3</v>
+      </c>
+      <c r="T183" t="n">
+        <v>7</v>
+      </c>
+      <c r="U183" t="n">
+        <v>6</v>
+      </c>
+      <c r="V183" t="n">
+        <v>12</v>
+      </c>
+      <c r="W183" t="n">
+        <v>17</v>
+      </c>
+      <c r="X183" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>Coliseum Alfonso Pérez</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>Avenida de Teresa de Calcuta, Getafe</t>
+        </is>
+      </c>
+      <c r="AC183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI183" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AK183" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AL183" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM183" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AN183" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP183" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ183" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR183" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS183" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT183" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AU183" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ183" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB183" t="n">
+        <v>290</v>
+      </c>
+      <c r="BC183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD183" t="n">
+        <v>58</v>
+      </c>
+      <c r="BE183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF183" t="n">
+        <v>7497</v>
+      </c>
+      <c r="BG183" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ183" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL183" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM183" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN183" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT183" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV183" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW183" t="n">
+        <v>65</v>
+      </c>
+      <c r="BX183" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY183" t="n">
+        <v>119</v>
+      </c>
+      <c r="BZ183" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="CA183" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CB183" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CC183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR183" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS183" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU183" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV183" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX183" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY183" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ183" t="n">
+        <v>23</v>
+      </c>
+      <c r="DA183" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB183" t="n">
+        <v>18</v>
+      </c>
+      <c r="DC183" t="n">
+        <v>52</v>
+      </c>
+      <c r="DD183" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DE183" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF183" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG183" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DH183" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DI183" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ183" t="n">
+        <v>78</v>
+      </c>
+      <c r="DK183" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL183" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DM183" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DN183" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="DO183" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP183" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ183" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR183" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS183" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT183" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU183" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV183" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW183" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="DX183" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="DY183" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="DZ183" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="EA183" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EB183" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EC183" t="inlineStr"/>
+      <c r="ED183" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EE183" t="inlineStr"/>
+      <c r="EF183" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EG183" t="inlineStr"/>
+      <c r="EH183" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EI183" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="EJ183" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="EK183" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EL183" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EM183" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EN183" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EO183" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EP183" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>19</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>46032.54166666666</v>
+      </c>
+      <c r="G184" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" t="n">
+        <v>1</v>
+      </c>
+      <c r="I184" t="n">
+        <v>2</v>
+      </c>
+      <c r="J184" t="n">
+        <v>5</v>
+      </c>
+      <c r="K184" t="n">
+        <v>2</v>
+      </c>
+      <c r="L184" t="n">
+        <v>7</v>
+      </c>
+      <c r="M184" t="n">
+        <v>3</v>
+      </c>
+      <c r="N184" t="n">
+        <v>1</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>3</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="n">
+        <v>9</v>
+      </c>
+      <c r="U184" t="n">
+        <v>13</v>
+      </c>
+      <c r="V184" t="n">
+        <v>15</v>
+      </c>
+      <c r="W184" t="n">
+        <v>15</v>
+      </c>
+      <c r="X184" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Carlos Tartiere</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>Calle de Ricardo Vázquez Prada, Barrio de la Ería, Oviedo</t>
+        </is>
+      </c>
+      <c r="AC184" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AF184" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG184" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH184" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI184" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ184" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AK184" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL184" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM184" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN184" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO184" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AP184" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ184" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR184" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AS184" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT184" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB184" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>45</v>
+      </c>
+      <c r="BE184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF184" t="n">
+        <v>25549</v>
+      </c>
+      <c r="BG184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI184" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM184" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN184" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ184" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT184" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV184" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW184" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX184" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY184" t="n">
+        <v>89</v>
+      </c>
+      <c r="BZ184" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CA184" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CB184" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CC184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR184" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS184" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU184" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV184" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX184" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY184" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ184" t="n">
+        <v>33</v>
+      </c>
+      <c r="DA184" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB184" t="n">
+        <v>6</v>
+      </c>
+      <c r="DC184" t="n">
+        <v>56</v>
+      </c>
+      <c r="DD184" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DE184" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DF184" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DG184" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH184" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DI184" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DJ184" t="n">
+        <v>67</v>
+      </c>
+      <c r="DK184" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL184" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DM184" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DN184" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DO184" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP184" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ184" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR184" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS184" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT184" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU184" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV184" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW184" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="DX184" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DY184" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="DZ184" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA184" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EB184" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EC184" t="inlineStr">
+        <is>
+          <t>3.78</t>
+        </is>
+      </c>
+      <c r="ED184" t="inlineStr"/>
+      <c r="EE184" t="inlineStr"/>
+      <c r="EF184" t="inlineStr"/>
+      <c r="EG184" t="inlineStr"/>
+      <c r="EH184" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EI184" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="EJ184" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="EK184" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EL184" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EM184" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN184" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EO184" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EP184" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>19</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>46032.63541666666</v>
+      </c>
+      <c r="G185" t="n">
+        <v>3</v>
+      </c>
+      <c r="H185" t="n">
+        <v>1</v>
+      </c>
+      <c r="I185" t="n">
+        <v>4</v>
+      </c>
+      <c r="J185" t="n">
+        <v>1</v>
+      </c>
+      <c r="K185" t="n">
+        <v>6</v>
+      </c>
+      <c r="L185" t="n">
+        <v>7</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" t="n">
+        <v>2</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>4</v>
+      </c>
+      <c r="R185" t="n">
+        <v>5</v>
+      </c>
+      <c r="S185" t="n">
+        <v>7</v>
+      </c>
+      <c r="T185" t="n">
+        <v>11</v>
+      </c>
+      <c r="U185" t="n">
+        <v>11</v>
+      </c>
+      <c r="V185" t="n">
+        <v>16</v>
+      </c>
+      <c r="W185" t="n">
+        <v>10</v>
+      </c>
+      <c r="X185" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z185" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>Estadio de la Cerámica</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>Plaza Labrador, Villarreal</t>
+        </is>
+      </c>
+      <c r="AC185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG185" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AK185" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL185" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM185" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN185" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO185" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP185" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ185" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR185" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS185" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AT185" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU185" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX185" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ185" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB185" t="n">
+        <v>76</v>
+      </c>
+      <c r="BC185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD185" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF185" t="n">
+        <v>17011</v>
+      </c>
+      <c r="BG185" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ185" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL185" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM185" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN185" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP185" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS185" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV185" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW185" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX185" t="n">
+        <v>86</v>
+      </c>
+      <c r="BY185" t="n">
+        <v>134</v>
+      </c>
+      <c r="BZ185" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CA185" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CB185" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="CC185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR185" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS185" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU185" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV185" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX185" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY185" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ185" t="n">
+        <v>41</v>
+      </c>
+      <c r="DA185" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB185" t="n">
+        <v>23</v>
+      </c>
+      <c r="DC185" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD185" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DE185" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DF185" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DG185" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH185" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DI185" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DJ185" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK185" t="n">
+        <v>37</v>
+      </c>
+      <c r="DL185" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DM185" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DN185" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="DO185" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP185" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ185" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR185" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS185" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT185" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU185" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV185" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW185" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="DX185" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="DY185" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="DZ185" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="EA185" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EB185" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EC185" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="ED185" t="inlineStr"/>
+      <c r="EE185" t="inlineStr"/>
+      <c r="EF185" t="inlineStr"/>
+      <c r="EG185" t="inlineStr"/>
+      <c r="EH185" t="inlineStr">
+        <is>
+          <t>7.76</t>
+        </is>
+      </c>
+      <c r="EI185" t="inlineStr">
+        <is>
+          <t>4.29</t>
+        </is>
+      </c>
+      <c r="EJ185" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EK185" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EL185" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EM185" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EN185" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EO185" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EP185" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>19</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Girona FC</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>CA Osasuna</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>46032.72916666666</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" t="n">
+        <v>1</v>
+      </c>
+      <c r="J186" t="n">
+        <v>2</v>
+      </c>
+      <c r="K186" t="n">
+        <v>1</v>
+      </c>
+      <c r="L186" t="n">
+        <v>3</v>
+      </c>
+      <c r="M186" t="n">
+        <v>2</v>
+      </c>
+      <c r="N186" t="n">
+        <v>6</v>
+      </c>
+      <c r="O186" t="n">
+        <v>1</v>
+      </c>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>4</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" t="n">
+        <v>4</v>
+      </c>
+      <c r="T186" t="n">
+        <v>12</v>
+      </c>
+      <c r="U186" t="n">
+        <v>8</v>
+      </c>
+      <c r="V186" t="n">
+        <v>12</v>
+      </c>
+      <c r="W186" t="n">
+        <v>14</v>
+      </c>
+      <c r="X186" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z186" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>Estadi Municipal de Montilivi</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>Avenida Montlivi 141, Girona</t>
+        </is>
+      </c>
+      <c r="AC186" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD186" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF186" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG186" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH186" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI186" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ186" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK186" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL186" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM186" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN186" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AO186" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP186" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ186" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR186" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AS186" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT186" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ186" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA186" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB186" t="n">
+        <v>312</v>
+      </c>
+      <c r="BC186" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD186" t="n">
+        <v>33</v>
+      </c>
+      <c r="BE186" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF186" t="n">
+        <v>12059</v>
+      </c>
+      <c r="BG186" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH186" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI186" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ186" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK186" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL186" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM186" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN186" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO186" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP186" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ186" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR186" t="n">
+        <v>6</v>
+      </c>
+      <c r="BS186" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT186" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU186" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV186" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW186" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX186" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY186" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ186" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CA186" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CB186" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CC186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI186" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ186" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM186" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ186" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR186" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS186" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT186" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU186" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV186" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW186" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX186" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY186" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ186" t="n">
+        <v>39</v>
+      </c>
+      <c r="DA186" t="n">
+        <v>61</v>
+      </c>
+      <c r="DB186" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC186" t="n">
+        <v>56</v>
+      </c>
+      <c r="DD186" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DE186" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF186" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG186" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DH186" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI186" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DJ186" t="n">
+        <v>61</v>
+      </c>
+      <c r="DK186" t="n">
+        <v>39</v>
+      </c>
+      <c r="DL186" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DM186" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="DN186" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DO186" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP186" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ186" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR186" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS186" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT186" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU186" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV186" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW186" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="DX186" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DY186" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="DZ186" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="EA186" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EB186" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC186" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="ED186" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EE186" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EF186" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="EG186" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EH186" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="EI186" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EJ186" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EK186" t="inlineStr">
+        <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="EB182" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC182" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="ED182" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE182" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EF182" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="EG182" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="EH182" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="EI182" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="EJ182" t="inlineStr">
-        <is>
-          <t>3.88</t>
-        </is>
-      </c>
-      <c r="EK182" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EL182" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="EM182" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EN182" t="inlineStr">
-        <is>
-          <t>2.54</t>
-        </is>
-      </c>
-      <c r="EO182" t="inlineStr">
+      <c r="EL186" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EM186" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EN186" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EO186" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EP186" t="inlineStr">
         <is>
           <t>1.97</t>
-        </is>
-      </c>
-      <c r="EP182" t="inlineStr">
-        <is>
-          <t>1.88</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -90952,7 +90952,7 @@
       </c>
       <c r="EA190" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EB190" t="inlineStr">
@@ -90962,22 +90962,22 @@
       </c>
       <c r="EC190" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="ED190" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EE190" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="EF190" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="EG190" t="inlineStr">
@@ -91007,27 +91007,27 @@
       </c>
       <c r="EL190" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EM190" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EN190" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EO190" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EP190" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.24</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP190" headerRowCount="1">
-  <autoFilter ref="A1:EP190"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP191" headerRowCount="1">
+  <autoFilter ref="A1:EP191"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP190"/>
+  <dimension ref="A1:EP191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5122,7 +5122,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DE9" t="n">
         <v>1.3</v>
@@ -8941,7 +8941,7 @@
         <v>2.5</v>
       </c>
       <c r="DE17" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF17" t="n">
         <v>3</v>
@@ -15586,7 +15586,7 @@
         <v>50</v>
       </c>
       <c r="DD31" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DE31" t="n">
         <v>0.2</v>
@@ -18929,7 +18929,7 @@
         <v>1.1</v>
       </c>
       <c r="DE38" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF38" t="n">
         <v>0.67</v>
@@ -20830,7 +20830,7 @@
         <v>75</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DE42" t="n">
         <v>0.5</v>
@@ -26045,7 +26045,7 @@
         <v>1.6</v>
       </c>
       <c r="DE53" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -26530,7 +26530,7 @@
         <v>84</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DE54" t="n">
         <v>0.33</v>
@@ -30371,7 +30371,7 @@
         <v>2.32</v>
       </c>
       <c r="DO62" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP62" t="b">
         <v>0</v>
@@ -38842,7 +38842,7 @@
         <v>88</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DE80" t="n">
         <v>1.3</v>
@@ -40741,7 +40741,7 @@
         <v>3</v>
       </c>
       <c r="DE84" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF84" t="n">
         <v>3</v>
@@ -45494,7 +45494,7 @@
         <v>78</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DE94" t="n">
         <v>0.44</v>
@@ -49293,7 +49293,7 @@
         <v>1.22</v>
       </c>
       <c r="DE102" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF102" t="n">
         <v>1.25</v>
@@ -55914,7 +55914,7 @@
         <v>64</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DE116" t="n">
         <v>2</v>
@@ -61553,7 +61553,7 @@
         <v>1.78</v>
       </c>
       <c r="DE128" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF128" t="n">
         <v>2</v>
@@ -62962,7 +62962,7 @@
         <v>69</v>
       </c>
       <c r="DD131" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DE131" t="n">
         <v>1.11</v>
@@ -71453,7 +71453,7 @@
         <v>1.9</v>
       </c>
       <c r="DE149" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF149" t="n">
         <v>1.86</v>
@@ -72398,7 +72398,7 @@
         <v>63</v>
       </c>
       <c r="DD151" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DE151" t="n">
         <v>1</v>
@@ -73825,7 +73825,7 @@
         <v>1.22</v>
       </c>
       <c r="DE154" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF154" t="n">
         <v>1.43</v>
@@ -84738,7 +84738,7 @@
         <v>84</v>
       </c>
       <c r="DD177" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DE177" t="n">
         <v>2.2</v>
@@ -86125,7 +86125,7 @@
         <v>1.44</v>
       </c>
       <c r="DE180" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF180" t="n">
         <v>1.63</v>
@@ -91030,6 +91030,478 @@
           <t>3.24</t>
         </is>
       </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Spain_La_Liga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>20</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>RCD Espanyol</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Girona FC</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>46038.83333333334</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>2</v>
+      </c>
+      <c r="I191" t="n">
+        <v>2</v>
+      </c>
+      <c r="J191" t="n">
+        <v>5</v>
+      </c>
+      <c r="K191" t="n">
+        <v>4</v>
+      </c>
+      <c r="L191" t="n">
+        <v>9</v>
+      </c>
+      <c r="M191" t="n">
+        <v>5</v>
+      </c>
+      <c r="N191" t="n">
+        <v>5</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>2</v>
+      </c>
+      <c r="R191" t="n">
+        <v>4</v>
+      </c>
+      <c r="S191" t="n">
+        <v>12</v>
+      </c>
+      <c r="T191" t="n">
+        <v>3</v>
+      </c>
+      <c r="U191" t="n">
+        <v>14</v>
+      </c>
+      <c r="V191" t="n">
+        <v>7</v>
+      </c>
+      <c r="W191" t="n">
+        <v>17</v>
+      </c>
+      <c r="X191" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>RCDE Stadium</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+        </is>
+      </c>
+      <c r="AC191" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH191" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI191" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ191" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AK191" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL191" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM191" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN191" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO191" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AP191" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ191" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR191" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS191" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT191" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ191" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA191" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB191" t="n">
+        <v>312</v>
+      </c>
+      <c r="BC191" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD191" t="n">
+        <v>64</v>
+      </c>
+      <c r="BE191" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF191" t="n">
+        <v>28451</v>
+      </c>
+      <c r="BG191" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH191" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI191" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ191" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK191" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL191" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM191" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN191" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO191" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP191" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ191" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR191" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS191" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT191" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU191" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV191" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW191" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX191" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY191" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ191" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CA191" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CB191" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CC191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD191" t="n">
+        <v>2</v>
+      </c>
+      <c r="CE191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF191" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI191" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ191" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ191" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR191" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS191" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT191" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU191" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV191" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW191" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX191" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY191" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ191" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA191" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB191" t="n">
+        <v>16</v>
+      </c>
+      <c r="DC191" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD191" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DE191" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DF191" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DG191" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH191" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DI191" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DJ191" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK191" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL191" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DM191" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DN191" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="DO191" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP191" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ191" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR191" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS191" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT191" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU191" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV191" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW191" t="n">
+        <v>13</v>
+      </c>
+      <c r="DX191" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="DY191" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="DZ191" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="EA191" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EB191" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="EC191" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="ED191" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EE191" t="inlineStr">
+        <is>
+          <t>4.56</t>
+        </is>
+      </c>
+      <c r="EF191" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EG191" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EH191" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EI191" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EJ191" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EK191" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EL191" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EM191" t="inlineStr"/>
+      <c r="EN191" t="inlineStr"/>
+      <c r="EO191" t="inlineStr"/>
+      <c r="EP191" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_La_Liga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP199" headerRowCount="1">
-  <autoFilter ref="A1:EP199"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP200" headerRowCount="1">
+  <autoFilter ref="A1:EP200"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP199"/>
+  <dimension ref="A1:EP200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4641,7 +4641,7 @@
         <v>1.6</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DE10" t="n">
         <v>1.3</v>
@@ -5643,7 +5643,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -7547,7 +7547,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -10867,7 +10867,7 @@
         <v>1.06</v>
       </c>
       <c r="DO21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11774,7 +11774,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DE23" t="n">
         <v>1</v>
@@ -13693,7 +13693,7 @@
         <v>1.2</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF27" t="n">
         <v>0</v>
@@ -13723,7 +13723,7 @@
         <v>2.25</v>
       </c>
       <c r="DO27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -16555,7 +16555,7 @@
         <v>2.15</v>
       </c>
       <c r="DO33" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -22391,170 +22391,170 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
         <v>45920.6875</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
         <v>3</v>
       </c>
       <c r="J46" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
+        <v>7</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
         <v>8</v>
       </c>
-      <c r="M46" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" t="n">
-        <v>7</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>5</v>
-      </c>
       <c r="R46" t="n">
         <v>3</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>26</v>
+      </c>
+      <c r="V46" t="n">
         <v>6</v>
       </c>
-      <c r="U46" t="n">
-        <v>8</v>
-      </c>
-      <c r="V46" t="n">
-        <v>9</v>
-      </c>
       <c r="W46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="X46" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Y46" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="Z46" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Estadio de Mendizorroza</t>
+          <t>Estadio de la Cerámica</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+          <t>Plaza Labrador, Villarreal</t>
         </is>
       </c>
       <c r="AC46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD46" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.33</v>
+        <v>1.55</v>
       </c>
       <c r="AF46" t="n">
-        <v>3.01</v>
+        <v>3.8</v>
       </c>
       <c r="AG46" t="n">
-        <v>3.28</v>
+        <v>5.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.43</v>
+        <v>2.01</v>
       </c>
       <c r="AJ46" t="n">
-        <v>4.85</v>
+        <v>3.05</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AO46" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AP46" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AR46" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AU46" t="n">
         <v>3</v>
       </c>
       <c r="AV46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
         <v>1</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB46" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="BC46" t="n">
         <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
         <v>0</v>
@@ -22572,73 +22572,73 @@
         <v>1</v>
       </c>
       <c r="BJ46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BL46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BN46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ46" t="n">
         <v>1</v>
       </c>
       <c r="BR46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BS46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BT46" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BU46" t="n">
         <v>1</v>
       </c>
       <c r="BV46" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="BW46" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="BX46" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="BY46" t="n">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="BZ46" t="n">
-        <v>1.22</v>
+        <v>2.84</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.08</v>
+        <v>0.75</v>
       </c>
       <c r="CB46" t="n">
-        <v>2.3</v>
+        <v>3.58</v>
       </c>
       <c r="CC46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG46" t="n">
         <v>0</v>
@@ -22656,13 +22656,13 @@
         <v>0</v>
       </c>
       <c r="CL46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM46" t="n">
         <v>0</v>
       </c>
       <c r="CN46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO46" t="n">
         <v>0</v>
@@ -22674,73 +22674,73 @@
         <v>1</v>
       </c>
       <c r="CR46" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="CS46" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="CT46" t="n">
         <v>1</v>
       </c>
       <c r="CU46" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="CV46" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX46" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY46" t="n">
         <v>20</v>
       </c>
-      <c r="CW46" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX46" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY46" t="n">
-        <v>4</v>
-      </c>
       <c r="CZ46" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA46" t="n">
         <v>50</v>
-      </c>
-      <c r="DA46" t="n">
-        <v>100</v>
       </c>
       <c r="DB46" t="n">
         <v>50</v>
       </c>
       <c r="DC46" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.11</v>
+        <v>0.2</v>
       </c>
       <c r="DF46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DH46" t="n">
         <v>1.75</v>
       </c>
       <c r="DI46" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DJ46" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK46" t="n">
         <v>50</v>
       </c>
-      <c r="DK46" t="n">
-        <v>0</v>
-      </c>
       <c r="DL46" t="n">
-        <v>1.19</v>
+        <v>2.48</v>
       </c>
       <c r="DM46" t="n">
-        <v>1.32</v>
+        <v>0.71</v>
       </c>
       <c r="DN46" t="n">
-        <v>2.51</v>
+        <v>3.19</v>
       </c>
       <c r="DO46" t="n">
         <v>19</v>
@@ -22767,89 +22767,101 @@
         <v>1</v>
       </c>
       <c r="DW46" t="n">
-        <v>27.45</v>
+        <v>27.48</v>
       </c>
       <c r="DX46" t="n">
-        <v>4.36</v>
+        <v>4.71</v>
       </c>
       <c r="DY46" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ46" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="EA46" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EB46" t="inlineStr"/>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EB46" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
       <c r="EC46" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="ED46" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EE46" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="EF46" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="EG46" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EH46" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EI46" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EJ46" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EK46" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EL46" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EM46" t="inlineStr">
         <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EN46" t="inlineStr"/>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EN46" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
       <c r="EO46" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="EP46" t="inlineStr"/>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EP46" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -22867,170 +22879,170 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
         <v>45920.6875</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" t="n">
         <v>3</v>
       </c>
       <c r="J47" t="n">
+        <v>4</v>
+      </c>
+      <c r="K47" t="n">
+        <v>4</v>
+      </c>
+      <c r="L47" t="n">
+        <v>8</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
         <v>7</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>3</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>6</v>
+      </c>
+      <c r="U47" t="n">
+        <v>8</v>
+      </c>
+      <c r="V47" t="n">
+        <v>9</v>
+      </c>
+      <c r="W47" t="n">
+        <v>20</v>
+      </c>
+      <c r="X47" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Estadio de Mendizorroza</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Paseo de Cervantes, Vitoria-Gasteiz</t>
+        </is>
+      </c>
+      <c r="AC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD47" t="n">
         <v>7</v>
       </c>
-      <c r="M47" t="n">
-        <v>2</v>
-      </c>
-      <c r="N47" t="n">
-        <v>2</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>8</v>
-      </c>
-      <c r="R47" t="n">
-        <v>3</v>
-      </c>
-      <c r="S47" t="n">
-        <v>18</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3</v>
-      </c>
-      <c r="U47" t="n">
-        <v>26</v>
-      </c>
-      <c r="V47" t="n">
-        <v>6</v>
-      </c>
-      <c r="W47" t="n">
-        <v>10</v>
-      </c>
-      <c r="X47" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>66</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Estadio de la Cerámica</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>Plaza Labrador, Villarreal</t>
-        </is>
-      </c>
-      <c r="AC47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>3</v>
-      </c>
       <c r="AE47" t="n">
-        <v>1.55</v>
+        <v>2.33</v>
       </c>
       <c r="AF47" t="n">
-        <v>3.8</v>
+        <v>3.01</v>
       </c>
       <c r="AG47" t="n">
-        <v>5.25</v>
+        <v>3.28</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.01</v>
+        <v>2.43</v>
       </c>
       <c r="AJ47" t="n">
-        <v>3.05</v>
+        <v>4.85</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AN47" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AO47" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AP47" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AU47" t="n">
         <v>3</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW47" t="n">
         <v>1</v>
       </c>
       <c r="AX47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB47" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="BC47" t="n">
         <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BE47" t="n">
         <v>0</v>
@@ -23048,178 +23060,178 @@
         <v>1</v>
       </c>
       <c r="BJ47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT47" t="n">
         <v>6</v>
       </c>
-      <c r="BL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN47" t="n">
+      <c r="BU47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV47" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW47" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY47" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CA47" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CB47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR47" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS47" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU47" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV47" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX47" t="n">
         <v>6</v>
       </c>
-      <c r="BO47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP47" t="n">
-        <v>3</v>
-      </c>
-      <c r="BQ47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS47" t="n">
+      <c r="CY47" t="n">
         <v>4</v>
       </c>
-      <c r="BT47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV47" t="n">
-        <v>90</v>
-      </c>
-      <c r="BW47" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX47" t="n">
-        <v>112</v>
-      </c>
-      <c r="BY47" t="n">
-        <v>57</v>
-      </c>
-      <c r="BZ47" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CA47" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB47" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="CC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR47" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS47" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU47" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV47" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX47" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY47" t="n">
-        <v>20</v>
-      </c>
       <c r="CZ47" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DA47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB47" t="n">
         <v>50</v>
       </c>
       <c r="DC47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD47" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="DF47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DG47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DH47" t="n">
         <v>1.75</v>
       </c>
       <c r="DI47" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DJ47" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK47" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL47" t="n">
-        <v>2.48</v>
+        <v>1.19</v>
       </c>
       <c r="DM47" t="n">
-        <v>0.71</v>
+        <v>1.32</v>
       </c>
       <c r="DN47" t="n">
-        <v>3.19</v>
+        <v>2.51</v>
       </c>
       <c r="DO47" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23243,101 +23255,89 @@
         <v>1</v>
       </c>
       <c r="DW47" t="n">
-        <v>27.48</v>
+        <v>27.45</v>
       </c>
       <c r="DX47" t="n">
-        <v>4.71</v>
+        <v>4.36</v>
       </c>
       <c r="DY47" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="DZ47" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="EA47" t="inlineStr">
         <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EB47" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
-      </c>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EB47" t="inlineStr"/>
       <c r="EC47" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="ED47" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="EE47" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="EF47" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EG47" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EH47" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="EI47" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EJ47" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EK47" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EL47" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EM47" t="inlineStr">
         <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EN47" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EN47" t="inlineStr"/>
       <c r="EO47" t="inlineStr">
         <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="EP47" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EP47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -25114,7 +25114,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DE51" t="n">
         <v>0.5</v>
@@ -25147,7 +25147,7 @@
         <v>1.99</v>
       </c>
       <c r="DO51" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25723,143 +25723,143 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
         <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L53" t="n">
+        <v>11</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>10</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2</v>
+      </c>
+      <c r="S53" t="n">
+        <v>11</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>21</v>
+      </c>
+      <c r="V53" t="n">
+        <v>5</v>
+      </c>
+      <c r="W53" t="n">
         <v>9</v>
       </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>2</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>5</v>
-      </c>
-      <c r="R53" t="n">
-        <v>3</v>
-      </c>
-      <c r="S53" t="n">
-        <v>12</v>
-      </c>
-      <c r="T53" t="n">
-        <v>3</v>
-      </c>
-      <c r="U53" t="n">
-        <v>17</v>
-      </c>
-      <c r="V53" t="n">
-        <v>6</v>
-      </c>
-      <c r="W53" t="n">
-        <v>19</v>
-      </c>
       <c r="X53" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y53" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="Z53" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>San Mamés Barria</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE53" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ53" t="n">
         <v>1.47</v>
       </c>
-      <c r="AF53" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AR53" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AS53" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AU53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV53" t="n">
         <v>0</v>
@@ -25868,13 +25868,13 @@
         <v>1</v>
       </c>
       <c r="AX53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA53" t="n">
         <v>1</v>
@@ -25886,7 +25886,7 @@
         <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BE53" t="n">
         <v>0</v>
@@ -25901,28 +25901,28 @@
         <v>1</v>
       </c>
       <c r="BI53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BJ53" t="n">
         <v>1</v>
       </c>
       <c r="BK53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BL53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BN53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ53" t="n">
         <v>0</v>
@@ -25931,7 +25931,7 @@
         <v>2</v>
       </c>
       <c r="BS53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT53" t="n">
         <v>2</v>
@@ -25940,139 +25940,139 @@
         <v>1</v>
       </c>
       <c r="BV53" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="BW53" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BX53" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="BY53" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CB53" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR53" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS53" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU53" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV53" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX53" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY53" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ53" t="n">
         <v>59</v>
       </c>
-      <c r="BZ53" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CA53" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB53" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="CC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS53" t="n">
+      <c r="DA53" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB53" t="n">
         <v>17</v>
       </c>
-      <c r="CT53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU53" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV53" t="n">
-        <v>19</v>
-      </c>
-      <c r="CW53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX53" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY53" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ53" t="n">
+      <c r="DC53" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD53" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DE53" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DF53" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH53" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ53" t="n">
         <v>42</v>
       </c>
-      <c r="DA53" t="n">
-        <v>67</v>
-      </c>
-      <c r="DB53" t="n">
+      <c r="DK53" t="n">
         <v>42</v>
       </c>
-      <c r="DC53" t="n">
-        <v>67</v>
-      </c>
-      <c r="DD53" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DE53" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DF53" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DH53" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DI53" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DJ53" t="n">
-        <v>59</v>
-      </c>
-      <c r="DK53" t="n">
-        <v>34</v>
-      </c>
       <c r="DL53" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="DM53" t="n">
-        <v>1.18</v>
+        <v>0.47</v>
       </c>
       <c r="DN53" t="n">
-        <v>2.61</v>
+        <v>1.62</v>
       </c>
       <c r="DO53" t="n">
         <v>20</v>
@@ -26084,10 +26084,10 @@
         <v>1</v>
       </c>
       <c r="DR53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT53" t="b">
         <v>0</v>
@@ -26099,49 +26099,45 @@
         <v>1</v>
       </c>
       <c r="DW53" t="n">
-        <v>17.43</v>
+        <v>20.5</v>
       </c>
       <c r="DX53" t="n">
-        <v>4.72</v>
+        <v>6.93</v>
       </c>
       <c r="DY53" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="DZ53" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA53" t="inlineStr">
         <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EB53" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EB53" t="inlineStr"/>
       <c r="EC53" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="ED53" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EE53" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EF53" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EG53" t="inlineStr">
@@ -26156,42 +26152,42 @@
       </c>
       <c r="EI53" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EJ53" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EK53" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EL53" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EM53" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EN53" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EO53" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EP53" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.37</t>
         </is>
       </c>
     </row>
@@ -26211,40 +26207,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>45923.70833333334</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>8</v>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -26253,101 +26249,101 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T54" t="n">
         <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W54" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="X54" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y54" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="Z54" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>San Mamés Barria</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Rafael Moreno Pitxitxi Kalea, Bilbao</t>
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="AF54" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="AG54" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AI54" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AJ54" t="n">
-        <v>4.05</v>
+        <v>3.08</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AN54" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AO54" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AR54" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AU54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV54" t="n">
         <v>0</v>
@@ -26356,13 +26352,13 @@
         <v>1</v>
       </c>
       <c r="AX54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA54" t="n">
         <v>1</v>
@@ -26374,7 +26370,7 @@
         <v>0</v>
       </c>
       <c r="BD54" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BE54" t="n">
         <v>0</v>
@@ -26389,28 +26385,28 @@
         <v>1</v>
       </c>
       <c r="BI54" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BJ54" t="n">
         <v>1</v>
       </c>
       <c r="BK54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BN54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ54" t="n">
         <v>0</v>
@@ -26419,7 +26415,7 @@
         <v>2</v>
       </c>
       <c r="BS54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT54" t="n">
         <v>2</v>
@@ -26428,25 +26424,25 @@
         <v>1</v>
       </c>
       <c r="BV54" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="BW54" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BX54" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="BY54" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="BZ54" t="n">
-        <v>2.59</v>
+        <v>1.96</v>
       </c>
       <c r="CA54" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="CB54" t="n">
-        <v>3.26</v>
+        <v>2.71</v>
       </c>
       <c r="CC54" t="n">
         <v>0</v>
@@ -26476,10 +26472,10 @@
         <v>0</v>
       </c>
       <c r="CL54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN54" t="n">
         <v>0</v>
@@ -26494,19 +26490,19 @@
         <v>1</v>
       </c>
       <c r="CR54" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="CS54" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CT54" t="n">
         <v>1</v>
       </c>
       <c r="CU54" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="CV54" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="CW54" t="n">
         <v>1</v>
@@ -26515,52 +26511,52 @@
         <v>3</v>
       </c>
       <c r="CY54" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CZ54" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA54" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB54" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC54" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD54" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE54" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DF54" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DI54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DJ54" t="n">
         <v>59</v>
       </c>
-      <c r="DA54" t="n">
-        <v>59</v>
-      </c>
-      <c r="DB54" t="n">
-        <v>17</v>
-      </c>
-      <c r="DC54" t="n">
-        <v>84</v>
-      </c>
-      <c r="DD54" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="DE54" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="DF54" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH54" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI54" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DJ54" t="n">
-        <v>42</v>
-      </c>
       <c r="DK54" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="DL54" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="DM54" t="n">
-        <v>0.47</v>
+        <v>1.18</v>
       </c>
       <c r="DN54" t="n">
-        <v>1.62</v>
+        <v>2.61</v>
       </c>
       <c r="DO54" t="n">
         <v>20</v>
@@ -26572,10 +26568,10 @@
         <v>1</v>
       </c>
       <c r="DR54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT54" t="b">
         <v>0</v>
@@ -26587,95 +26583,99 @@
         <v>1</v>
       </c>
       <c r="DW54" t="n">
-        <v>20.5</v>
+        <v>17.43</v>
       </c>
       <c r="DX54" t="n">
-        <v>6.93</v>
+        <v>4.72</v>
       </c>
       <c r="DY54" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="DZ54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="EA54" t="inlineStr">
         <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EB54" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EC54" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="ED54" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EE54" t="inlineStr">
+        <is>
+          <t>7.25</t>
+        </is>
+      </c>
+      <c r="EF54" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="EG54" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EH54" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EI54" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EJ54" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EK54" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EL54" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EM54" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EN54" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="EB54" t="inlineStr"/>
-      <c r="EC54" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="ED54" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="EE54" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="EF54" t="inlineStr">
-        <is>
-          <t>3.21</t>
-        </is>
-      </c>
-      <c r="EG54" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EH54" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="EI54" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EJ54" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EK54" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EL54" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EM54" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EN54" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="EO54" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EP54" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
     </row>
@@ -29435,7 +29435,7 @@
         <v>2.17</v>
       </c>
       <c r="DO60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -32685,7 +32685,7 @@
         <v>1.33</v>
       </c>
       <c r="DE67" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF67" t="n">
         <v>1</v>
@@ -32715,7 +32715,7 @@
         <v>2.84</v>
       </c>
       <c r="DO67" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33154,7 +33154,7 @@
         <v>59</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DE68" t="n">
         <v>2</v>
@@ -33187,7 +33187,7 @@
         <v>2.52</v>
       </c>
       <c r="DO68" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -37467,7 +37467,7 @@
         <v>2.1</v>
       </c>
       <c r="DO77" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -37927,7 +37927,7 @@
         <v>3.75</v>
       </c>
       <c r="DO78" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38043,146 +38043,146 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45935.6875</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K79" t="n">
         <v>5</v>
       </c>
       <c r="L79" t="n">
+        <v>15</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2</v>
+      </c>
+      <c r="N79" t="n">
+        <v>6</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>5</v>
+      </c>
+      <c r="R79" t="n">
+        <v>3</v>
+      </c>
+      <c r="S79" t="n">
+        <v>9</v>
+      </c>
+      <c r="T79" t="n">
+        <v>9</v>
+      </c>
+      <c r="U79" t="n">
+        <v>14</v>
+      </c>
+      <c r="V79" t="n">
         <v>12</v>
       </c>
-      <c r="M79" t="n">
-        <v>1</v>
-      </c>
-      <c r="N79" t="n">
-        <v>2</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>3</v>
-      </c>
-      <c r="R79" t="n">
-        <v>2</v>
-      </c>
-      <c r="S79" t="n">
-        <v>7</v>
-      </c>
-      <c r="T79" t="n">
-        <v>5</v>
-      </c>
-      <c r="U79" t="n">
-        <v>10</v>
-      </c>
-      <c r="V79" t="n">
-        <v>7</v>
-      </c>
       <c r="W79" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X79" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Y79" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z79" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Anoeta</t>
+          <t>RCDE Stadium</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
+          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
         </is>
       </c>
       <c r="AC79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="AF79" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AG79" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AI79" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AJ79" t="n">
-        <v>3.85</v>
+        <v>2.96</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AM79" t="n">
         <v>1.44</v>
       </c>
       <c r="AN79" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AO79" t="n">
         <v>2.55</v>
       </c>
       <c r="AP79" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AR79" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AU79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW79" t="n">
         <v>0</v>
@@ -38191,28 +38191,28 @@
         <v>0</v>
       </c>
       <c r="AY79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
       </c>
       <c r="BF79" t="n">
-        <v>31189</v>
+        <v>32778</v>
       </c>
       <c r="BG79" t="n">
         <v>2</v>
@@ -38221,178 +38221,178 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BJ79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BK79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR79" t="n">
         <v>4</v>
       </c>
-      <c r="BL79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM79" t="n">
+      <c r="BS79" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX79" t="n">
         <v>6</v>
       </c>
-      <c r="BN79" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT79" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV79" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW79" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX79" t="n">
-        <v>101</v>
-      </c>
-      <c r="BY79" t="n">
-        <v>90</v>
-      </c>
-      <c r="BZ79" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="CA79" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB79" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN79" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR79" t="n">
-        <v>14</v>
-      </c>
-      <c r="CS79" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU79" t="n">
-        <v>21</v>
-      </c>
-      <c r="CV79" t="n">
+      <c r="CY79" t="n">
         <v>13</v>
       </c>
-      <c r="CW79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX79" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY79" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ79" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="DA79" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="DB79" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="DC79" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.91</v>
+        <v>1.3</v>
       </c>
       <c r="DF79" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="DG79" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DH79" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="DI79" t="n">
-        <v>0.71</v>
+        <v>1.71</v>
       </c>
       <c r="DJ79" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="DK79" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="DN79" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="DO79" t="n">
         <v>20</v>
@@ -38401,10 +38401,10 @@
         <v>1</v>
       </c>
       <c r="DQ79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS79" t="b">
         <v>0</v>
@@ -38416,94 +38416,102 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW79" t="n">
-        <v>17.19</v>
+        <v>17.75</v>
       </c>
       <c r="DX79" t="n">
-        <v>3.66</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="ED79" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EE79" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EG79" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EJ79" t="inlineStr">
+        <is>
           <t>2.02</t>
         </is>
       </c>
-      <c r="ED79" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EE79" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="EF79" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="EG79" t="inlineStr"/>
-      <c r="EH79" t="inlineStr"/>
-      <c r="EI79" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EJ79" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
       <c r="EK79" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EL79" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EM79" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EN79" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.85</t>
         </is>
       </c>
     </row>
@@ -38523,40 +38531,40 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45935.6875</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K80" t="n">
         <v>5</v>
       </c>
       <c r="L80" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -38565,314 +38573,314 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
+        <v>3</v>
+      </c>
+      <c r="R80" t="n">
+        <v>2</v>
+      </c>
+      <c r="S80" t="n">
+        <v>7</v>
+      </c>
+      <c r="T80" t="n">
         <v>5</v>
       </c>
-      <c r="R80" t="n">
-        <v>3</v>
-      </c>
-      <c r="S80" t="n">
-        <v>9</v>
-      </c>
-      <c r="T80" t="n">
-        <v>9</v>
-      </c>
       <c r="U80" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V80" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W80" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="X80" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Y80" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z80" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>RCDE Stadium</t>
+          <t>Estadio Municipal de Anoeta</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>Avenida Baix Llobregat 100, Cornella de Llobregat</t>
+          <t>Paseo de Anoeta 1, Donostia-San Sebastián</t>
         </is>
       </c>
       <c r="AC80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="AF80" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AJ80" t="n">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AL80" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AM80" t="n">
         <v>1.44</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AO80" t="n">
         <v>2.55</v>
       </c>
       <c r="AP80" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>291</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>31189</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>101</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV80" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX80" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY80" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ80" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA80" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>59</v>
+      </c>
+      <c r="DC80" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD80" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DE80" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DF80" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DI80" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DJ80" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK80" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL80" t="n">
         <v>1.96</v>
       </c>
-      <c r="AQ80" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR80" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AS80" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AT80" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AU80" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV80" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY80" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB80" t="n">
-        <v>284</v>
-      </c>
-      <c r="BC80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD80" t="n">
-        <v>88</v>
-      </c>
-      <c r="BE80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF80" t="n">
-        <v>32778</v>
-      </c>
-      <c r="BG80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI80" t="n">
-        <v>5</v>
-      </c>
-      <c r="BJ80" t="n">
-        <v>5</v>
-      </c>
-      <c r="BK80" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM80" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN80" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR80" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS80" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT80" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV80" t="n">
-        <v>66</v>
-      </c>
-      <c r="BW80" t="n">
-        <v>34</v>
-      </c>
-      <c r="BX80" t="n">
-        <v>107</v>
-      </c>
-      <c r="BY80" t="n">
-        <v>98</v>
-      </c>
-      <c r="BZ80" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CA80" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CB80" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CC80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR80" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS80" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU80" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV80" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX80" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY80" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ80" t="n">
-        <v>54</v>
-      </c>
-      <c r="DA80" t="n">
-        <v>88</v>
-      </c>
-      <c r="DB80" t="n">
-        <v>29</v>
-      </c>
-      <c r="DC80" t="n">
-        <v>88</v>
-      </c>
-      <c r="DD80" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="DE80" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="DF80" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DG80" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH80" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DI80" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DJ80" t="n">
-        <v>46</v>
-      </c>
-      <c r="DK80" t="n">
-        <v>13</v>
-      </c>
-      <c r="DL80" t="n">
-        <v>1.51</v>
-      </c>
       <c r="DM80" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="DN80" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="DO80" t="n">
         <v>20</v>
@@ -38881,10 +38889,10 @@
         <v>1</v>
       </c>
       <c r="DQ80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS80" t="b">
         <v>0</v>
@@ -38896,102 +38904,94 @@
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW80" t="n">
-        <v>17.75</v>
+        <v>17.19</v>
       </c>
       <c r="DX80" t="n">
-        <v>9.369999999999999</v>
+        <v>3.66</v>
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EB80" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EC80" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="ED80" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EE80" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EF80" t="inlineStr">
         <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="EG80" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EH80" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="EG80" t="inlineStr"/>
+      <c r="EH80" t="inlineStr"/>
       <c r="EI80" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EJ80" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EK80" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EL80" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EM80" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EN80" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EO80" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EP80" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.03</t>
         </is>
       </c>
     </row>
@@ -40311,7 +40311,7 @@
         <v>2.72</v>
       </c>
       <c r="DO83" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -42158,7 +42158,7 @@
         <v>38</v>
       </c>
       <c r="DD87" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DE87" t="n">
         <v>0.8</v>
@@ -42191,7 +42191,7 @@
         <v>3.24</v>
       </c>
       <c r="DO87" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -44529,7 +44529,7 @@
         <v>1.4</v>
       </c>
       <c r="DE92" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF92" t="n">
         <v>1</v>
@@ -44559,7 +44559,7 @@
         <v>2.81</v>
       </c>
       <c r="DO92" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45527,7 +45527,7 @@
         <v>2.42</v>
       </c>
       <c r="DO94" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -50237,7 +50237,7 @@
         <v>2.8</v>
       </c>
       <c r="DE104" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF104" t="n">
         <v>2.6</v>
@@ -50267,7 +50267,7 @@
         <v>2.79</v>
       </c>
       <c r="DO104" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -52635,7 +52635,7 @@
         <v>3.52</v>
       </c>
       <c r="DO109" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -54018,7 +54018,7 @@
         <v>70</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DE112" t="n">
         <v>1</v>
@@ -54051,7 +54051,7 @@
         <v>3.11</v>
       </c>
       <c r="DO112" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -55019,7 +55019,7 @@
         <v>2.35</v>
       </c>
       <c r="DO114" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -62486,7 +62486,7 @@
         <v>59</v>
       </c>
       <c r="DD130" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DE130" t="n">
         <v>2.1</v>
@@ -62519,7 +62519,7 @@
         <v>3.72</v>
       </c>
       <c r="DO130" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -62965,7 +62965,7 @@
         <v>1.73</v>
       </c>
       <c r="DE131" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF131" t="n">
         <v>1.86</v>
@@ -62995,7 +62995,7 @@
         <v>2.6</v>
       </c>
       <c r="DO131" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -63467,7 +63467,7 @@
         <v>2.07</v>
       </c>
       <c r="DO132" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -66315,7 +66315,7 @@
         <v>2.89</v>
       </c>
       <c r="DO138" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -71450,7 +71450,7 @@
         <v>63</v>
       </c>
       <c r="DD149" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DE149" t="n">
         <v>1.2</v>
@@ -71483,7 +71483,7 @@
         <v>2.7</v>
       </c>
       <c r="DO149" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP149" t="b">
         <v>1</v>
@@ -71913,7 +71913,7 @@
         <v>1.4</v>
       </c>
       <c r="DE150" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF150" t="n">
         <v>1.57</v>
@@ -71943,7 +71943,7 @@
         <v>2.64</v>
       </c>
       <c r="DO150" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -74815,7 +74815,7 @@
         <v>2.17</v>
       </c>
       <c r="DO156" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP156" t="b">
         <v>1</v>
@@ -76243,7 +76243,7 @@
         <v>2.3</v>
       </c>
       <c r="DO159" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP159" t="b">
         <v>1</v>
@@ -80013,7 +80013,7 @@
         <v>2.7</v>
       </c>
       <c r="DE167" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF167" t="n">
         <v>2.57</v>
@@ -80043,7 +80043,7 @@
         <v>3.51</v>
       </c>
       <c r="DO167" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP167" t="b">
         <v>1</v>
@@ -81434,7 +81434,7 @@
         <v>59</v>
       </c>
       <c r="DD170" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DE170" t="n">
         <v>0.91</v>
@@ -81467,7 +81467,7 @@
         <v>2.82</v>
       </c>
       <c r="DO170" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP170" t="b">
         <v>1</v>
@@ -84262,7 +84262,7 @@
         <v>64</v>
       </c>
       <c r="DD176" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DE176" t="n">
         <v>1.78</v>
@@ -85811,12 +85811,12 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F180" s="2" t="n">
@@ -85826,134 +85826,126 @@
         <v>1</v>
       </c>
       <c r="H180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J180" t="n">
+        <v>3</v>
+      </c>
+      <c r="K180" t="n">
         <v>6</v>
       </c>
-      <c r="K180" t="n">
+      <c r="L180" t="n">
+        <v>9</v>
+      </c>
+      <c r="M180" t="n">
+        <v>2</v>
+      </c>
+      <c r="N180" t="n">
+        <v>1</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>2</v>
+      </c>
+      <c r="R180" t="n">
+        <v>4</v>
+      </c>
+      <c r="S180" t="n">
         <v>7</v>
       </c>
-      <c r="L180" t="n">
-        <v>13</v>
-      </c>
-      <c r="M180" t="n">
-        <v>2</v>
-      </c>
-      <c r="N180" t="n">
-        <v>2</v>
-      </c>
-      <c r="O180" t="n">
-        <v>1</v>
-      </c>
-      <c r="P180" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>7</v>
-      </c>
-      <c r="R